--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rb5c1c21d62fd4ad6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rc62d32ec75f1441c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R3e6f8e6bbb474272"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rdc9bc0be82454ab8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rab692c7eb13d4a3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R7287cd73fd854f71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R9d9af4342b0a4e28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Re9347249b4f84e82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -72,6 +72,10 @@
       <x:color rgb="FF854D0E"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
   <x:fills count="9">
     <x:fill>
@@ -116,7 +120,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="13">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -184,11 +188,29 @@
         <x:color rgb="FFD8DEE4"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD5DEE5"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD5DEE5"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD5DEE5"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD5DEE5"/>
+      </x:left>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="208">
+  <x:cellXfs count="215">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -693,6 +715,19 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -704,7 +739,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -715,7 +750,7 @@
         <x:color rgb="FF075985"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EEF5"/>
         </x:patternFill>
       </x:fill>
@@ -726,7 +761,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4CC"/>
         </x:patternFill>
       </x:fill>
@@ -737,7 +772,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -747,7 +782,7 @@
         <x:color rgb="FF4B5563"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEEF1F4"/>
         </x:patternFill>
       </x:fill>
@@ -758,7 +793,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -769,7 +804,7 @@
         <x:color rgb="FF075985"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EEF5"/>
         </x:patternFill>
       </x:fill>
@@ -780,7 +815,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4CC"/>
         </x:patternFill>
       </x:fill>
@@ -791,7 +826,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -801,7 +836,7 @@
         <x:color rgb="FF4B5563"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEEF1F4"/>
         </x:patternFill>
       </x:fill>
@@ -956,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re28ac82d4fde41bf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1ed1c80d132a4a72"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1240,7 +1275,7 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1252,19 +1287,19 @@
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
       <x:c r="G6" s="96" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"进行中")</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="97"/>
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.2619047619047619</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1273,7 +1308,7 @@
       </x:c>
       <x:c r="O6" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N6)</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1339,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：阶段二——确定六张核心表字段与整合规则
-总体状态：进行中
-已完成：两个Git仓库、阶段二v1模板、公共字段与编号规则</x:v>
+        <x:v>当前阶段：阶段二——六张核心表字段已暂定，转换规则v1已建立
+总体状态：等待同事确认前三张表并组织联合评审
+已完成：两个Git仓库、阶段二模板、后三张字段、坊间空间关系表、转换规则表v1</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1377,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 你审核城门表、尺度关系表、功能分区规则的字段。
-2. 同事审核坊功能表、道路分级表、水渠表的字段。
-3. 全员一起确认六张专题表如何自动转换成实体表和关系表。</x:v>
+        <x:v>1. 同事审核坊功能表、道路分级表、水渠表字段。
+2. 全员召开六张核心表字段联合评审。
+3. 评审通过后冻结字段规范v1，并用少量文献试填。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1423,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>不要同时手工填写专题表和通用实体/关系表；专题表作为录入入口，之后由转换脚本生成通用表。远程上传平台仓库前，先处理超过100MB的青瓷模拟数据。</x:v>
+        <x:v>六张核心主题表保持不变；“坊间空间关系”和“转换规则”是辅助表。坊间空间关系最终自动进入统一关系表，反向关系查询时推导，不重复录入。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1467,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b38c5674833482b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c6bc370b11343b5"/>
 </x:worksheet>
 </file>
 
@@ -1593,7 +1628,7 @@
       <x:c r="K4" s="16" t="str">
         <x:v>Git基线6977c62</x:v>
       </x:c>
-      <x:c r="L4" s="16" t="str"/>
+      <x:c r="L4" s="16"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="16" t="str">
@@ -1629,7 +1664,7 @@
       <x:c r="K5" s="16" t="str">
         <x:v>.gitignore</x:v>
       </x:c>
-      <x:c r="L5" s="16" t="str"/>
+      <x:c r="L5" s="16"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="16" t="str">
@@ -1665,7 +1700,7 @@
       <x:c r="K6" s="16" t="str">
         <x:v>tang-changan-knowledge-graph</x:v>
       </x:c>
-      <x:c r="L6" s="16" t="str"/>
+      <x:c r="L6" s="16"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="16" t="str">
@@ -1739,7 +1774,7 @@
       <x:c r="K8" s="16" t="str">
         <x:v>公共证据、审核、时期字段</x:v>
       </x:c>
-      <x:c r="L8" s="16" t="str"/>
+      <x:c r="L8" s="16"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="16" t="str">
@@ -1775,7 +1810,7 @@
       <x:c r="K9" s="16" t="str">
         <x:v>TC-FANG/ROAD/CANAL/GATE/SCALE/RULE</x:v>
       </x:c>
-      <x:c r="L9" s="16" t="str"/>
+      <x:c r="L9" s="16"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="16" t="str">
@@ -1811,7 +1846,7 @@
       <x:c r="K10" s="16" t="str">
         <x:v>12张工作表模板，Git 656647b</x:v>
       </x:c>
-      <x:c r="L10" s="16" t="str"/>
+      <x:c r="L10" s="16"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="16" t="str">
@@ -1832,11 +1867,11 @@
       <x:c r="F11" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G11" s="17" t="str"/>
+      <x:c r="G11" s="17"/>
       <x:c r="H11" s="17" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="I11" s="17" t="str"/>
+      <x:c r="I11" s="17"/>
       <x:c r="J11" s="16" t="str">
         <x:v>组织字段评审</x:v>
       </x:c>
@@ -1866,18 +1901,18 @@
       <x:c r="F12" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G12" s="17" t="str"/>
+      <x:c r="G12" s="17"/>
       <x:c r="H12" s="17" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="I12" s="17" t="str"/>
+      <x:c r="I12" s="17"/>
       <x:c r="J12" s="16" t="str">
         <x:v>组织字段评审</x:v>
       </x:c>
       <x:c r="K12" s="16" t="str">
         <x:v>道路分级表最终字段</x:v>
       </x:c>
-      <x:c r="L12" s="16" t="str"/>
+      <x:c r="L12" s="16"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="16" t="str">
@@ -1898,18 +1933,18 @@
       <x:c r="F13" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G13" s="17" t="str"/>
+      <x:c r="G13" s="17"/>
       <x:c r="H13" s="17" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="I13" s="17" t="str"/>
+      <x:c r="I13" s="17"/>
       <x:c r="J13" s="16" t="str">
         <x:v>组织字段评审</x:v>
       </x:c>
       <x:c r="K13" s="16" t="str">
         <x:v>水渠表最终字段</x:v>
       </x:c>
-      <x:c r="L13" s="16" t="str"/>
+      <x:c r="L13" s="16"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="16" t="str">
@@ -1925,7 +1960,7 @@
         <x:v>我</x:v>
       </x:c>
       <x:c r="E14" s="16" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F14" s="16" t="str">
         <x:v>P0</x:v>
@@ -1936,14 +1971,16 @@
       <x:c r="H14" s="17" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="I14" s="17" t="str"/>
+      <x:c r="I14" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="J14" s="16" t="str">
-        <x:v>审核字段是否满足考古和文献需求</x:v>
+        <x:v>参加六张表联合评审</x:v>
       </x:c>
       <x:c r="K14" s="16" t="str">
         <x:v>城门表最终字段</x:v>
       </x:c>
-      <x:c r="L14" s="16" t="str"/>
+      <x:c r="L14" s="16"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="16" t="str">
@@ -1959,7 +1996,7 @@
         <x:v>我</x:v>
       </x:c>
       <x:c r="E15" s="16" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F15" s="16" t="str">
         <x:v>P0</x:v>
@@ -1970,14 +2007,16 @@
       <x:c r="H15" s="17" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="I15" s="17" t="str"/>
+      <x:c r="I15" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="J15" s="16" t="str">
-        <x:v>确认单位换算和误差规则</x:v>
+        <x:v>参加六张表联合评审</x:v>
       </x:c>
       <x:c r="K15" s="16" t="str">
         <x:v>尺度关系表最终字段</x:v>
       </x:c>
-      <x:c r="L15" s="16" t="str"/>
+      <x:c r="L15" s="16"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="16" t="str">
@@ -1993,7 +2032,7 @@
         <x:v>我</x:v>
       </x:c>
       <x:c r="E16" s="16" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F16" s="16" t="str">
         <x:v>P0</x:v>
@@ -2004,14 +2043,16 @@
       <x:c r="H16" s="17" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="I16" s="17" t="str"/>
+      <x:c r="I16" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="J16" s="16" t="str">
-        <x:v>确认正例、反例和推导格式</x:v>
+        <x:v>参加六张表联合评审</x:v>
       </x:c>
       <x:c r="K16" s="16" t="str">
         <x:v>功能分区规则最终字段</x:v>
       </x:c>
-      <x:c r="L16" s="16" t="str"/>
+      <x:c r="L16" s="16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="16" t="str">
@@ -2027,7 +2068,7 @@
         <x:v>共同</x:v>
       </x:c>
       <x:c r="E17" s="16" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F17" s="16" t="str">
         <x:v>P0</x:v>
@@ -2038,15 +2079,17 @@
       <x:c r="H17" s="17" t="str">
         <x:v>2026-08-14</x:v>
       </x:c>
-      <x:c r="I17" s="17" t="str"/>
+      <x:c r="I17" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="J17" s="16" t="str">
-        <x:v>形成自动转换映射</x:v>
+        <x:v>后续编写并测试转换脚本</x:v>
       </x:c>
       <x:c r="K17" s="16" t="str">
-        <x:v>字段映射说明v1</x:v>
+        <x:v>转换规则表v1、坊间空间关系表</x:v>
       </x:c>
       <x:c r="L17" s="16" t="str">
-        <x:v>不要重复手工录入通用表</x:v>
+        <x:v>专题表作为录入入口，自动生成通用实体/关系</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2068,18 +2111,18 @@
       <x:c r="F18" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G18" s="17" t="str"/>
+      <x:c r="G18" s="17"/>
       <x:c r="H18" s="17" t="str">
         <x:v>2026-08-14</x:v>
       </x:c>
-      <x:c r="I18" s="17" t="str"/>
+      <x:c r="I18" s="17"/>
       <x:c r="J18" s="16" t="str">
         <x:v>约定评审时间</x:v>
       </x:c>
       <x:c r="K18" s="16" t="str">
         <x:v>评审记录</x:v>
       </x:c>
-      <x:c r="L18" s="16" t="str"/>
+      <x:c r="L18" s="16"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="16" t="str">
@@ -2100,18 +2143,18 @@
       <x:c r="F19" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G19" s="17" t="str"/>
+      <x:c r="G19" s="17"/>
       <x:c r="H19" s="17" t="str">
         <x:v>2026-08-15</x:v>
       </x:c>
-      <x:c r="I19" s="17" t="str"/>
+      <x:c r="I19" s="17"/>
       <x:c r="J19" s="16" t="str">
         <x:v>评审通过后Git存档</x:v>
       </x:c>
       <x:c r="K19" s="16" t="str">
         <x:v>字段规范v1</x:v>
       </x:c>
-      <x:c r="L19" s="16" t="str"/>
+      <x:c r="L19" s="16"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="16" t="str">
@@ -2132,16 +2175,16 @@
       <x:c r="F20" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G20" s="17" t="str"/>
-      <x:c r="H20" s="17" t="str"/>
-      <x:c r="I20" s="17" t="str"/>
+      <x:c r="G20" s="17"/>
+      <x:c r="H20" s="17"/>
+      <x:c r="I20" s="17"/>
       <x:c r="J20" s="16" t="str">
         <x:v>完成字段规范后开始</x:v>
       </x:c>
       <x:c r="K20" s="16" t="str">
         <x:v>文献登记表</x:v>
       </x:c>
-      <x:c r="L20" s="16" t="str"/>
+      <x:c r="L20" s="16"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="16" t="str">
@@ -2162,16 +2205,16 @@
       <x:c r="F21" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G21" s="17" t="str"/>
-      <x:c r="H21" s="17" t="str"/>
-      <x:c r="I21" s="17" t="str"/>
+      <x:c r="G21" s="17"/>
+      <x:c r="H21" s="17"/>
+      <x:c r="I21" s="17"/>
       <x:c r="J21" s="16" t="str">
         <x:v>按六张表分别列缺口</x:v>
       </x:c>
       <x:c r="K21" s="16" t="str">
         <x:v>文献需求清单</x:v>
       </x:c>
-      <x:c r="L21" s="16" t="str"/>
+      <x:c r="L21" s="16"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="16" t="str">
@@ -2192,16 +2235,16 @@
       <x:c r="F22" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G22" s="17" t="str"/>
-      <x:c r="H22" s="17" t="str"/>
-      <x:c r="I22" s="17" t="str"/>
+      <x:c r="G22" s="17"/>
+      <x:c r="H22" s="17"/>
+      <x:c r="I22" s="17"/>
       <x:c r="J22" s="16" t="str">
         <x:v>优先权威考古报告</x:v>
       </x:c>
       <x:c r="K22" s="16" t="str">
         <x:v>新增文献</x:v>
       </x:c>
-      <x:c r="L22" s="16" t="str"/>
+      <x:c r="L22" s="16"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="16" t="str">
@@ -2222,16 +2265,16 @@
       <x:c r="F23" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G23" s="17" t="str"/>
-      <x:c r="H23" s="17" t="str"/>
-      <x:c r="I23" s="17" t="str"/>
+      <x:c r="G23" s="17"/>
+      <x:c r="H23" s="17"/>
+      <x:c r="I23" s="17"/>
       <x:c r="J23" s="16" t="str">
         <x:v>用于尺度和坐标</x:v>
       </x:c>
       <x:c r="K23" s="16" t="str">
         <x:v>新增文献</x:v>
       </x:c>
-      <x:c r="L23" s="16" t="str"/>
+      <x:c r="L23" s="16"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="16" t="str">
@@ -2252,16 +2295,16 @@
       <x:c r="F24" s="16" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="G24" s="17" t="str"/>
-      <x:c r="H24" s="17" t="str"/>
-      <x:c r="I24" s="17" t="str"/>
+      <x:c r="G24" s="17"/>
+      <x:c r="H24" s="17"/>
+      <x:c r="I24" s="17"/>
       <x:c r="J24" s="16" t="str">
         <x:v>明确可用于坐标和尺度的来源</x:v>
       </x:c>
       <x:c r="K24" s="16" t="str">
         <x:v>质量分级规则</x:v>
       </x:c>
-      <x:c r="L24" s="16" t="str"/>
+      <x:c r="L24" s="16"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="16" t="str">
@@ -2282,16 +2325,16 @@
       <x:c r="F25" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G25" s="17" t="str"/>
-      <x:c r="H25" s="17" t="str"/>
-      <x:c r="I25" s="17" t="str"/>
+      <x:c r="G25" s="17"/>
+      <x:c r="H25" s="17"/>
+      <x:c r="I25" s="17"/>
       <x:c r="J25" s="16" t="str">
         <x:v>字段冻结后选择</x:v>
       </x:c>
       <x:c r="K25" s="16" t="str">
         <x:v>试验对象清单</x:v>
       </x:c>
-      <x:c r="L25" s="16" t="str"/>
+      <x:c r="L25" s="16"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="16" t="str">
@@ -2312,16 +2355,16 @@
       <x:c r="F26" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G26" s="17" t="str"/>
-      <x:c r="H26" s="17" t="str"/>
-      <x:c r="I26" s="17" t="str"/>
+      <x:c r="G26" s="17"/>
+      <x:c r="H26" s="17"/>
+      <x:c r="I26" s="17"/>
       <x:c r="J26" s="16" t="str">
         <x:v>使用可追溯证据</x:v>
       </x:c>
       <x:c r="K26" s="16" t="str">
         <x:v>样例记录</x:v>
       </x:c>
-      <x:c r="L26" s="16" t="str"/>
+      <x:c r="L26" s="16"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="16" t="str">
@@ -2342,16 +2385,16 @@
       <x:c r="F27" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G27" s="17" t="str"/>
-      <x:c r="H27" s="17" t="str"/>
-      <x:c r="I27" s="17" t="str"/>
+      <x:c r="G27" s="17"/>
+      <x:c r="H27" s="17"/>
+      <x:c r="I27" s="17"/>
       <x:c r="J27" s="16" t="str">
         <x:v>分工录入</x:v>
       </x:c>
       <x:c r="K27" s="16" t="str">
         <x:v>小型样例数据集</x:v>
       </x:c>
-      <x:c r="L27" s="16" t="str"/>
+      <x:c r="L27" s="16"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="16" t="str">
@@ -2372,16 +2415,16 @@
       <x:c r="F28" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G28" s="17" t="str"/>
-      <x:c r="H28" s="17" t="str"/>
-      <x:c r="I28" s="17" t="str"/>
+      <x:c r="G28" s="17"/>
+      <x:c r="H28" s="17"/>
+      <x:c r="I28" s="17"/>
       <x:c r="J28" s="16" t="str">
         <x:v>逐条审核</x:v>
       </x:c>
       <x:c r="K28" s="16" t="str">
         <x:v>样例审核记录</x:v>
       </x:c>
-      <x:c r="L28" s="16" t="str"/>
+      <x:c r="L28" s="16"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="16" t="str">
@@ -2402,16 +2445,16 @@
       <x:c r="F29" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G29" s="17" t="str"/>
-      <x:c r="H29" s="17" t="str"/>
-      <x:c r="I29" s="17" t="str"/>
+      <x:c r="G29" s="17"/>
+      <x:c r="H29" s="17"/>
+      <x:c r="I29" s="17"/>
       <x:c r="J29" s="16" t="str">
         <x:v>样例通过后升级</x:v>
       </x:c>
       <x:c r="K29" s="16" t="str">
         <x:v>knowledge-graph-extraction v2</x:v>
       </x:c>
-      <x:c r="L29" s="16" t="str"/>
+      <x:c r="L29" s="16"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="16" t="str">
@@ -2432,16 +2475,16 @@
       <x:c r="F30" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G30" s="17" t="str"/>
-      <x:c r="H30" s="17" t="str"/>
-      <x:c r="I30" s="17" t="str"/>
+      <x:c r="G30" s="17"/>
+      <x:c r="H30" s="17"/>
+      <x:c r="I30" s="17"/>
       <x:c r="J30" s="16" t="str">
         <x:v>与字段规范一致</x:v>
       </x:c>
       <x:c r="K30" s="16" t="str">
         <x:v>提取规范v2</x:v>
       </x:c>
-      <x:c r="L30" s="16" t="str"/>
+      <x:c r="L30" s="16"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="16" t="str">
@@ -2462,16 +2505,16 @@
       <x:c r="F31" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G31" s="17" t="str"/>
-      <x:c r="H31" s="17" t="str"/>
-      <x:c r="I31" s="17" t="str"/>
+      <x:c r="G31" s="17"/>
+      <x:c r="H31" s="17"/>
+      <x:c r="I31" s="17"/>
       <x:c r="J31" s="16" t="str">
         <x:v>比较人工审核结果</x:v>
       </x:c>
       <x:c r="K31" s="16" t="str">
         <x:v>测试报告</x:v>
       </x:c>
-      <x:c r="L31" s="16" t="str"/>
+      <x:c r="L31" s="16"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="16" t="str">
@@ -2492,16 +2535,16 @@
       <x:c r="F32" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G32" s="17" t="str"/>
-      <x:c r="H32" s="17" t="str"/>
-      <x:c r="I32" s="17" t="str"/>
+      <x:c r="G32" s="17"/>
+      <x:c r="H32" s="17"/>
+      <x:c r="I32" s="17"/>
       <x:c r="J32" s="16" t="str">
         <x:v>保留通用技术架构</x:v>
       </x:c>
       <x:c r="K32" s="16" t="str">
         <x:v>唐长安城平台基线</x:v>
       </x:c>
-      <x:c r="L32" s="16" t="str"/>
+      <x:c r="L32" s="16"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="16" t="str">
@@ -2522,16 +2565,16 @@
       <x:c r="F33" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G33" s="17" t="str"/>
-      <x:c r="H33" s="17" t="str"/>
-      <x:c r="I33" s="17" t="str"/>
+      <x:c r="G33" s="17"/>
+      <x:c r="H33" s="17"/>
+      <x:c r="I33" s="17"/>
       <x:c r="J33" s="16" t="str">
         <x:v>依据字段规范</x:v>
       </x:c>
       <x:c r="K33" s="16" t="str">
         <x:v>JSON Schema</x:v>
       </x:c>
-      <x:c r="L33" s="16" t="str"/>
+      <x:c r="L33" s="16"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="16" t="str">
@@ -2552,16 +2595,16 @@
       <x:c r="F34" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G34" s="17" t="str"/>
-      <x:c r="H34" s="17" t="str"/>
-      <x:c r="I34" s="17" t="str"/>
+      <x:c r="G34" s="17"/>
+      <x:c r="H34" s="17"/>
+      <x:c r="I34" s="17"/>
       <x:c r="J34" s="16" t="str">
         <x:v>先支持小型样例</x:v>
       </x:c>
       <x:c r="K34" s="16" t="str">
         <x:v>转换脚本</x:v>
       </x:c>
-      <x:c r="L34" s="16" t="str"/>
+      <x:c r="L34" s="16"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="16" t="str">
@@ -2582,16 +2625,16 @@
       <x:c r="F35" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G35" s="17" t="str"/>
-      <x:c r="H35" s="17" t="str"/>
-      <x:c r="I35" s="17" t="str"/>
+      <x:c r="G35" s="17"/>
+      <x:c r="H35" s="17"/>
+      <x:c r="I35" s="17"/>
       <x:c r="J35" s="16" t="str">
         <x:v>逐项验收</x:v>
       </x:c>
       <x:c r="K35" s="16" t="str">
         <x:v>平台样例验收报告</x:v>
       </x:c>
-      <x:c r="L35" s="16" t="str"/>
+      <x:c r="L35" s="16"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="16" t="str">
@@ -2612,16 +2655,16 @@
       <x:c r="F36" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G36" s="17" t="str"/>
-      <x:c r="H36" s="17" t="str"/>
-      <x:c r="I36" s="17" t="str"/>
+      <x:c r="G36" s="17"/>
+      <x:c r="H36" s="17"/>
+      <x:c r="I36" s="17"/>
       <x:c r="J36" s="16" t="str">
         <x:v>小样例通过后分批提取</x:v>
       </x:c>
       <x:c r="K36" s="16" t="str">
         <x:v>坊功能全量表</x:v>
       </x:c>
-      <x:c r="L36" s="16" t="str"/>
+      <x:c r="L36" s="16"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="16" t="str">
@@ -2642,16 +2685,16 @@
       <x:c r="F37" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G37" s="17" t="str"/>
-      <x:c r="H37" s="17" t="str"/>
-      <x:c r="I37" s="17" t="str"/>
+      <x:c r="G37" s="17"/>
+      <x:c r="H37" s="17"/>
+      <x:c r="I37" s="17"/>
       <x:c r="J37" s="16" t="str">
         <x:v>分批提取与审核</x:v>
       </x:c>
       <x:c r="K37" s="16" t="str">
         <x:v>道路全量表</x:v>
       </x:c>
-      <x:c r="L37" s="16" t="str"/>
+      <x:c r="L37" s="16"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="16" t="str">
@@ -2672,16 +2715,16 @@
       <x:c r="F38" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G38" s="17" t="str"/>
-      <x:c r="H38" s="17" t="str"/>
-      <x:c r="I38" s="17" t="str"/>
+      <x:c r="G38" s="17"/>
+      <x:c r="H38" s="17"/>
+      <x:c r="I38" s="17"/>
       <x:c r="J38" s="16" t="str">
         <x:v>分批提取与审核</x:v>
       </x:c>
       <x:c r="K38" s="16" t="str">
         <x:v>水渠全量表</x:v>
       </x:c>
-      <x:c r="L38" s="16" t="str"/>
+      <x:c r="L38" s="16"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="16" t="str">
@@ -2702,16 +2745,16 @@
       <x:c r="F39" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G39" s="17" t="str"/>
-      <x:c r="H39" s="17" t="str"/>
-      <x:c r="I39" s="17" t="str"/>
+      <x:c r="G39" s="17"/>
+      <x:c r="H39" s="17"/>
+      <x:c r="I39" s="17"/>
       <x:c r="J39" s="16" t="str">
         <x:v>严格区分城门与内门</x:v>
       </x:c>
       <x:c r="K39" s="16" t="str">
         <x:v>城门全量表</x:v>
       </x:c>
-      <x:c r="L39" s="16" t="str"/>
+      <x:c r="L39" s="16"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="16" t="str">
@@ -2732,16 +2775,16 @@
       <x:c r="F40" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G40" s="17" t="str"/>
-      <x:c r="H40" s="17" t="str"/>
-      <x:c r="I40" s="17" t="str"/>
+      <x:c r="G40" s="17"/>
+      <x:c r="H40" s="17"/>
+      <x:c r="I40" s="17"/>
       <x:c r="J40" s="16" t="str">
         <x:v>全部公式人工复核</x:v>
       </x:c>
       <x:c r="K40" s="16" t="str">
         <x:v>尺度关系全量表</x:v>
       </x:c>
-      <x:c r="L40" s="16" t="str"/>
+      <x:c r="L40" s="16"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="16" t="str">
@@ -2762,16 +2805,16 @@
       <x:c r="F41" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G41" s="17" t="str"/>
-      <x:c r="H41" s="17" t="str"/>
-      <x:c r="I41" s="17" t="str"/>
+      <x:c r="G41" s="17"/>
+      <x:c r="H41" s="17"/>
+      <x:c r="I41" s="17"/>
       <x:c r="J41" s="16" t="str">
         <x:v>必须检索反例</x:v>
       </x:c>
       <x:c r="K41" s="16" t="str">
         <x:v>规则全量表</x:v>
       </x:c>
-      <x:c r="L41" s="16" t="str"/>
+      <x:c r="L41" s="16"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="16" t="str">
@@ -2792,16 +2835,16 @@
       <x:c r="F42" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G42" s="17" t="str"/>
-      <x:c r="H42" s="17" t="str"/>
-      <x:c r="I42" s="17" t="str"/>
+      <x:c r="G42" s="17"/>
+      <x:c r="H42" s="17"/>
+      <x:c r="I42" s="17"/>
       <x:c r="J42" s="16" t="str">
         <x:v>全量导入前完成</x:v>
       </x:c>
       <x:c r="K42" s="16" t="str">
         <x:v>质量报告</x:v>
       </x:c>
-      <x:c r="L42" s="16" t="str"/>
+      <x:c r="L42" s="16"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="16" t="str">
@@ -2822,16 +2865,16 @@
       <x:c r="F43" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G43" s="17" t="str"/>
-      <x:c r="H43" s="17" t="str"/>
-      <x:c r="I43" s="17" t="str"/>
+      <x:c r="G43" s="17"/>
+      <x:c r="H43" s="17"/>
+      <x:c r="I43" s="17"/>
       <x:c r="J43" s="16" t="str">
         <x:v>发布前完成</x:v>
       </x:c>
       <x:c r="K43" s="16" t="str">
         <x:v>系统测试报告</x:v>
       </x:c>
-      <x:c r="L43" s="16" t="str"/>
+      <x:c r="L43" s="16"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="16" t="str">
@@ -2852,16 +2895,16 @@
       <x:c r="F44" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G44" s="17" t="str"/>
-      <x:c r="H44" s="17" t="str"/>
-      <x:c r="I44" s="17" t="str"/>
+      <x:c r="G44" s="17"/>
+      <x:c r="H44" s="17"/>
+      <x:c r="I44" s="17"/>
       <x:c r="J44" s="16" t="str">
         <x:v>完成最终审核</x:v>
       </x:c>
       <x:c r="K44" s="16" t="str">
         <x:v>tang_changan_v1</x:v>
       </x:c>
-      <x:c r="L44" s="16" t="str"/>
+      <x:c r="L44" s="16"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="16" t="str">
@@ -2882,16 +2925,16 @@
       <x:c r="F45" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G45" s="17" t="str"/>
-      <x:c r="H45" s="17" t="str"/>
-      <x:c r="I45" s="17" t="str"/>
+      <x:c r="G45" s="17"/>
+      <x:c r="H45" s="17"/>
+      <x:c r="I45" s="17"/>
       <x:c r="J45" s="16" t="str">
         <x:v>检查权限与版权</x:v>
       </x:c>
       <x:c r="K45" s="16" t="str">
         <x:v>正式发布</x:v>
       </x:c>
-      <x:c r="L45" s="16" t="str"/>
+      <x:c r="L45" s="16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3270,6 +3313,26 @@
         <x:v>以后每次工作后更新本表</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="212" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+      <x:c r="B8" s="213" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C8" s="213" t="str">
+        <x:v>新增坊间空间关系表与专题表转换规则v1；确认后三张字段</x:v>
+      </x:c>
+      <x:c r="D8" s="213" t="str">
+        <x:v>阶段二v1模板</x:v>
+      </x:c>
+      <x:c r="E8" s="213" t="str">
+        <x:v>同事确认前三张表并召开联合评审</x:v>
+      </x:c>
+      <x:c r="F8" s="214" t="str">
+        <x:v>六张核心表不变，新增两张辅助表</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rab692c7eb13d4a3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R7287cd73fd854f71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R9d9af4342b0a4e28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Re9347249b4f84e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R5b9ddf5a9ff34225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R258c9ac137a84eb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R1b2964248bc54c31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R65dd0d5893834f59"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1ed1c80d132a4a72"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc30ee2fc16894c5c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1293,7 +1293,7 @@
       <x:c r="F6" s="70"/>
       <x:c r="G6" s="96" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"进行中")</x:f>
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H6" s="97"/>
       <x:c r="I6" s="98"/>
@@ -1308,7 +1308,7 @@
       </x:c>
       <x:c r="O6" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N6)</x:f>
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1359,7 +1359,7 @@
       </x:c>
       <x:c r="O9" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N9)</x:f>
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1374,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：阶段二——六张核心表字段已暂定，转换规则v1已建立
-总体状态：等待同事确认前三张表并组织联合评审
-已完成：两个Git仓库、阶段二模板、后三张字段、坊间空间关系表、转换规则表v1</x:v>
+        <x:v>当前阶段：阶段四小型样例已启动
+总体状态：第一批史料片段与基础对象已录入，全部保持待审核
+已完成：9条史料片段、13个实体、6条关系、2条道路、2条水渠、5座城门、1组尺度、1条候选规则</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 同事审核坊功能表、道路分级表、水渠表字段。
-2. 全员召开六张核心表字段联合评审。
-3. 评审通过后冻结字段规范v1，并用少量文献试填。</x:v>
+        <x:v>1. 对第一批原文逐条与扫描版核对。
+2. 继续提取平康坊、崇仁坊、兴庆坊、胜业坊、永嘉坊。
+3. 补充坊间空间关系，并检查专题表转通用表结果。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>六张核心主题表保持不变；“坊间空间关系”和“转换规则”是辅助表。坊间空间关系最终自动进入统一关系表，反向关系查询时推导，不重复录入。</x:v>
+        <x:v>本批次没有填写坐标或米制换算；所有记录均为“待审核”。候选功能规则必须继续寻找反例。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c6bc370b11343b5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3901c6738564ad9"/>
 </x:worksheet>
 </file>
 
@@ -2170,21 +2170,25 @@
         <x:v>我</x:v>
       </x:c>
       <x:c r="E20" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F20" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G20" s="17"/>
+      <x:c r="G20" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="H20" s="17"/>
       <x:c r="I20" s="17"/>
       <x:c r="J20" s="16" t="str">
-        <x:v>完成字段规范后开始</x:v>
+        <x:v>核对3份现有文献并补齐来源编号</x:v>
       </x:c>
       <x:c r="K20" s="16" t="str">
-        <x:v>文献登记表</x:v>
-      </x:c>
-      <x:c r="L20" s="16"/>
+        <x:v>小型样例文献选择方案v1</x:v>
+      </x:c>
+      <x:c r="L20" s="16" t="str">
+        <x:v>已完成初选，待正式登记来源表</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="16" t="str">
@@ -2200,21 +2204,25 @@
         <x:v>共同</x:v>
       </x:c>
       <x:c r="E21" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F21" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G21" s="17"/>
+      <x:c r="G21" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="H21" s="17"/>
       <x:c r="I21" s="17"/>
       <x:c r="J21" s="16" t="str">
-        <x:v>按六张表分别列缺口</x:v>
+        <x:v>确认考古、尺度、水系资料的取得顺序</x:v>
       </x:c>
       <x:c r="K21" s="16" t="str">
-        <x:v>文献需求清单</x:v>
-      </x:c>
-      <x:c r="L21" s="16"/>
+        <x:v>初步文献缺口与优先级</x:v>
+      </x:c>
+      <x:c r="L21" s="16" t="str">
+        <x:v>优先取得《隋唐长安城遗址·考古资料编》</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="16" t="str">
@@ -2320,19 +2328,21 @@
         <x:v>共同</x:v>
       </x:c>
       <x:c r="E25" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F25" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G25" s="17"/>
+      <x:c r="G25" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="H25" s="17"/>
       <x:c r="I25" s="17"/>
       <x:c r="J25" s="16" t="str">
-        <x:v>字段冻结后选择</x:v>
+        <x:v>继续补齐5坊样例</x:v>
       </x:c>
       <x:c r="K25" s="16" t="str">
-        <x:v>试验对象清单</x:v>
+        <x:v>第一批基础对象已录入</x:v>
       </x:c>
       <x:c r="L25" s="16"/>
     </x:row>
@@ -2350,19 +2360,21 @@
         <x:v>我</x:v>
       </x:c>
       <x:c r="E26" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F26" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G26" s="17"/>
+      <x:c r="G26" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="H26" s="17"/>
       <x:c r="I26" s="17"/>
       <x:c r="J26" s="16" t="str">
-        <x:v>使用可追溯证据</x:v>
+        <x:v>补充2组尺度和2条规则</x:v>
       </x:c>
       <x:c r="K26" s="16" t="str">
-        <x:v>样例记录</x:v>
+        <x:v>1组尺度、1条候选规则</x:v>
       </x:c>
       <x:c r="L26" s="16"/>
     </x:row>
@@ -2380,19 +2392,21 @@
         <x:v>共同</x:v>
       </x:c>
       <x:c r="E27" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F27" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G27" s="17"/>
+      <x:c r="G27" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="H27" s="17"/>
       <x:c r="I27" s="17"/>
       <x:c r="J27" s="16" t="str">
-        <x:v>分工录入</x:v>
+        <x:v>继续填写坊功能与坊间空间关系</x:v>
       </x:c>
       <x:c r="K27" s="16" t="str">
-        <x:v>小型样例数据集</x:v>
+        <x:v>第1批小样例工作簿</x:v>
       </x:c>
       <x:c r="L27" s="16"/>
     </x:row>
@@ -3333,6 +3347,46 @@
         <x:v>六张核心表不变，新增两张辅助表</x:v>
       </x:c>
     </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="212" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+      <x:c r="B9" s="213" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C9" s="213" t="str">
+        <x:v>完成小型样例文献初选，确定3份现有主文献、5份建议补充资料及样例对象群</x:v>
+      </x:c>
+      <x:c r="D9" s="213" t="str">
+        <x:v>小型样例文献选择方案_v1.md</x:v>
+      </x:c>
+      <x:c r="E9" s="213" t="str">
+        <x:v>团队确认名单并取得优先考古资料</x:v>
+      </x:c>
+      <x:c r="F9" s="214" t="str">
+        <x:v>尺度与坐标缺口暂不推测</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="212" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+      <x:c r="B10" s="213" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C10" s="213" t="str">
+        <x:v>完成小型样例第1批：9条片段、13实体、6关系及道路/水渠/城门/尺度/规则专题记录</x:v>
+      </x:c>
+      <x:c r="D10" s="213" t="str">
+        <x:v>小型样例_第1批_文献片段与基础对象_v1.xlsx</x:v>
+      </x:c>
+      <x:c r="E10" s="213" t="str">
+        <x:v>扫描版核对并继续提取5坊</x:v>
+      </x:c>
+      <x:c r="F10" s="214" t="str">
+        <x:v>未填写坐标和米制换算，全部待审核</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R5b9ddf5a9ff34225"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R258c9ac137a84eb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R1b2964248bc54c31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R65dd0d5893834f59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R191f2fe0537f4dcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R6ed2f8e3ba034573"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R24dd7a77fbd24cb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Re6b1fcf94e8b49b4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc30ee2fc16894c5c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R028d0b2f86f347ba"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1374,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：阶段四小型样例已启动
-总体状态：第一批史料片段与基础对象已录入，全部保持待审核
-已完成：9条史料片段、13个实体、6条关系、2条道路、2条水渠、5座城门、1组尺度、1条候选规则</x:v>
+        <x:v>当前阶段：阶段四小型样例进行中
+总体状态：第一批样例已建立，坊与道路的历史复原网格位置字段已补充
+已完成：坊 grid_coordinate、道路 grid_position、转换规则和代码说明同步更新</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 对第一批原文逐条与扫描版核对。
-2. 继续提取平康坊、崇仁坊、兴庆坊、胜业坊、永嘉坊。
-3. 补充坊间空间关系，并检查专题表转通用表结果。</x:v>
+        <x:v>1. 确认使用哪一版唐长安城复原网格作为坐标基准。
+2. 继续提取5个坊并填写(x,y)。
+3. 根据同一复原图填写道路网格序位和坊间空间关系。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>本批次没有填写坐标或米制换算；所有记录均为“待审核”。候选功能规则必须继续寻找反例。</x:v>
+        <x:v>约定：坊(x,y)中x从西向东、y从南向北；南北向道路按自西向东编号，东西向道路按自南向北编号。不同复原图不得混用。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3901c6738564ad9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8e001f849304f14"/>
 </x:worksheet>
 </file>
 
@@ -3387,6 +3387,26 @@
         <x:v>未填写坐标和米制换算，全部待审核</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="212" t="str">
+        <x:v>2026-08-08</x:v>
+      </x:c>
+      <x:c r="B11" s="213" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C11" s="213" t="str">
+        <x:v>新增坊平面网格坐标与道路网格序位字段，并同步转换规则和样例</x:v>
+      </x:c>
+      <x:c r="D11" s="213" t="str">
+        <x:v>阶段二模板 / 第1批小样例</x:v>
+      </x:c>
+      <x:c r="E11" s="213" t="str">
+        <x:v>确认复原网格基准后填写具体序号</x:v>
+      </x:c>
+      <x:c r="F11" s="214" t="str">
+        <x:v>网格位置不等同经纬度</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R191f2fe0537f4dcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R6ed2f8e3ba034573"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R24dd7a77fbd24cb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Re6b1fcf94e8b49b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R64f4f48c93fa48f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R294f4af3726e428c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R575ab6b0713d43c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rfc408d9ed9a244b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R028d0b2f86f347ba"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1af9f14d54d49f1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1375,8 +1375,8 @@
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
         <x:v>当前阶段：阶段四小型样例进行中
-总体状态：第一批样例已建立，坊与道路的历史复原网格位置字段已补充
-已完成：坊 grid_coordinate、道路 grid_position、转换规则和代码说明同步更新</x:v>
+总体状态：坐标基准试行版已建立，并完成5个坊的逻辑网格试录
+已完成：SENO-8C-V0.1换算规则、底图来源字段、原图格号与5坊试录</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 确认使用哪一版唐长安城复原网格作为坐标基准。
-2. 继续提取5个坊并填写(x,y)。
-3. 根据同一复原图填写道路网格序位和坊间空间关系。</x:v>
+        <x:v>1. 人工核对修真、安定、修德、普宁、休祥五坊在图15中的格号。
+2. 查找妹尾达彦原书高清图，确认转载图细节。
+3. 试编主要道路序位，再评估是否扩大到108坊。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>约定：坊(x,y)中x从西向东、y从南向北；南北向道路按自西向东编号，东西向道路按自南向北编号。不同复原图不得混用。</x:v>
+        <x:v>试行规则：图15原列A—J换算为x=1—10；原行1—13自北向南，数据库y=14-原行号。坐标是逻辑网格，不是经纬度。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8e001f849304f14"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe182890fa634f43"/>
 </x:worksheet>
 </file>
 
@@ -3407,6 +3407,26 @@
         <x:v>网格位置不等同经纬度</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>2026-08-08</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>新增坊平面网格坐标与道路网格序位字段，并同步转换规则和样例</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>阶段二模板 / 第1批小样例</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>确认复原网格基准后填写具体序号</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>网格位置不等同经纬度</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R64f4f48c93fa48f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R294f4af3726e428c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R575ab6b0713d43c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rfc408d9ed9a244b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rfacec74ac74545d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rb533b1474f0e4cd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Ra904d0c6a1e545cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R69c920b1c98b45df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1af9f14d54d49f1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdf437850a1d04674"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1375,8 +1375,8 @@
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
         <x:v>当前阶段：阶段四小型样例进行中
-总体状态：坐标基准试行版已建立，并完成5个坊的逻辑网格试录
-已完成：SENO-8C-V0.1换算规则、底图来源字段、原图格号与5坊试录</x:v>
+总体状态：坊坐标与道路轴线试行规则均已建立
+已完成：9条南北向轴线、13条东西向轴线编号；横街与承天门街完成试编</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工核对修真、安定、修德、普宁、休祥五坊在图15中的格号。
-2. 查找妹尾达彦原书高清图，确认转载图细节。
-3. 试编主要道路序位，再评估是否扩大到108坊。</x:v>
+        <x:v>1. 人工核对横街EW-13、承天门街NS-05的轴线判断。
+2. 核对朱雀大街、安化门街等命名道路与轴线的对应。
+3. 规则确认后，再扩展其余坊和主要道路。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>试行规则：图15原列A—J换算为x=1—10；原行1—13自北向南，数据库y=14-原行号。坐标是逻辑网格，不是经纬度。</x:v>
+        <x:v>道路编号针对轴线，不直接等于道路实体：同轴的不同路段分别建实体；道路偏折、终止和时期变化须另行记录。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe182890fa634f43"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9638e09a2e2c41e8"/>
 </x:worksheet>
 </file>
 
@@ -3427,6 +3427,26 @@
         <x:v>网格位置不等同经纬度</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>2026-08-08</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>建立道路轴线序位规则并试编横街、承天门街</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>阶段二模板 / 第1批小样例</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>人工核对两条道路后扩展主要道路</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>轴线编号不等于道路实体</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rfacec74ac74545d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rb533b1474f0e4cd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Ra904d0c6a1e545cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R69c920b1c98b45df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rab42855772654cb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rdbc3f53cef9645fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R9ee8c30845864d7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rcdf0f3b53c374e68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdf437850a1d04674"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfe87a803cce245c8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1376,7 +1376,7 @@
       <x:c r="A11" s="152" t="str">
         <x:v>当前阶段：阶段四小型样例进行中
 总体状态：坊坐标与道路轴线试行规则均已建立
-已完成：9条南北向轴线、13条东西向轴线编号；横街与承天门街完成试编</x:v>
+已完成：9条南北向轴线、12条东西向坊间轴线；横街改为坊间序位不适用</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,7 +1412,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工核对横街EW-13、承天门街NS-05的轴线判断。
+        <x:v>1. 核对承天门街NS-05的轴线判断。
 2. 核对朱雀大街、安化门街等命名道路与轴线的对应。
 3. 规则确认后，再扩展其余坊和主要道路。</x:v>
       </x:c>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>道路编号针对轴线，不直接等于道路实体：同轴的不同路段分别建实体；道路偏折、终止和时期变化须另行记录。</x:v>
+        <x:v>东西向坊间道路只有12条。横街位于第1排坊北侧，不进入EW序位；同轴不同路段仍分别建立道路实体。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9638e09a2e2c41e8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2447a6c2d37746c6"/>
 </x:worksheet>
 </file>
 
@@ -3447,6 +3447,26 @@
         <x:v>轴线编号不等于道路实体</x:v>
       </x:c>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>2026-08-08</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>修正东西向坊间道路为12条，横街移出EW序位</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>阶段二模板 / 第1批小样例</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>继续核对主要命名道路</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>横街位于第1排坊北侧</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rab42855772654cb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rdbc3f53cef9645fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R9ee8c30845864d7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rcdf0f3b53c374e68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rf593ed062cba4b03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R74288910cef64845"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rf712a9abd96641a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R9f31758e24dd40af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfe87a803cce245c8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0b854f50dd3b41db"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1376,7 +1376,7 @@
       <x:c r="A11" s="152" t="str">
         <x:v>当前阶段：阶段四小型样例进行中
 总体状态：坊坐标与道路轴线试行规则均已建立
-已完成：9条南北向轴线、12条东西向坊间轴线；横街改为坊间序位不适用</x:v>
+已完成：朱雀大街NS-05、安化门北向道路NS-03、启夏门北向道路NS-07试编</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 核对承天门街NS-05的轴线判断。
-2. 核对朱雀大街、安化门街等命名道路与轴线的对应。
-3. 规则确认后，再扩展其余坊和主要道路。</x:v>
+        <x:v>1. 人工核对三条南城入城轴线。
+2. 从文献确认安化门、启夏门向北道路的正式名称。
+3. 规则确认后，开始扩充城门表及其连接道路。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>东西向坊间道路只有12条。横街位于第1排坊北侧，不进入EW序位；同轴不同路段仍分别建立道路实体。</x:v>
+        <x:v>安化门、启夏门向北道路目前使用项目暂名，只表示地图上的道路实体；正式名称未得到文献支持前不得作为史实名称引用。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2447a6c2d37746c6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R337ce3eddffc44ef"/>
 </x:worksheet>
 </file>
 
@@ -3467,6 +3467,26 @@
         <x:v>横街位于第1排坊北侧</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>2026-08-08</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>试编朱雀大街及安化门、启夏门向北道路</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>阶段二模板 / 第1批小样例</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>确认两条暂名道路的史料名称</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>三条轴线分别为NS-05、NS-03、NS-07</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rf593ed062cba4b03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R74288910cef64845"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rf712a9abd96641a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R9f31758e24dd40af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R9c51177729664900"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rb2c90c6043f441e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rf1a43e299474498f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R708f4fe950264a8d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0b854f50dd3b41db"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d93413bdb1e4b87"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1375,8 +1375,8 @@
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
         <x:v>当前阶段：阶段四小型样例进行中
-总体状态：坊坐标与道路轴线试行规则均已建立
-已完成：朱雀大街NS-05、安化门北向道路NS-03、启夏门北向道路NS-07试编</x:v>
+总体状态：南城主要道路轴线已经审核，城门—道路连接开始扩充
+已完成：新增安化门、启夏门2个实体及4条道路—城门连接关系</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工核对三条南城入城轴线。
-2. 从文献确认安化门、启夏门向北道路的正式名称。
-3. 规则确认后，开始扩充城门表及其连接道路。</x:v>
+        <x:v>1. 人工审核4条新增道路—城门关系。
+2. 继续检索安化门、启夏门向北道路的正式名称。
+3. 审核通过后，扩充其余外郭城门及相连道路。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R337ce3eddffc44ef"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30d86ce58343403e"/>
 </x:worksheet>
 </file>
 
@@ -3487,6 +3487,26 @@
         <x:v>三条轴线分别为NS-05、NS-03、NS-07</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>2026-08-08</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>补录安化门、启夏门及4条城门—道路连接关系</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>第1批小型样例</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>人工审核新增关系并扩充其余外郭城门</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>连接关系来自图15；两条道路仍使用项目暂名</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R9c51177729664900"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rb2c90c6043f441e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rf1a43e299474498f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R708f4fe950264a8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rc130cbc9fb7842f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R14d23b466318422a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R8eb6319037b6468a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R0ae7c3a9d9a048c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d93413bdb1e4b87"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R80cfabb1a2974d38"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1227,7 +1227,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-07</x:v>
+        <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-09</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -1275,31 +1275,31 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
       <x:c r="G6" s="96" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"进行中")</x:f>
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="97"/>
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.2619047619047619</x:v>
+        <x:v>0.2826086956521739</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1308,7 +1308,7 @@
       </x:c>
       <x:c r="O6" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N6)</x:f>
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1359,7 +1359,7 @@
       </x:c>
       <x:c r="O9" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N9)</x:f>
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1374,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：阶段四小型样例进行中
-总体状态：南城主要道路轴线已经审核，城门—道路连接开始扩充
-已完成：新增安化门、启夏门2个实体及4条道路—城门连接关系</x:v>
+        <x:v>当前阶段：阶段二字段扩展与阶段四小型样例并行
+总体状态：城门—道路连接已审核；基础事实层与研究解释层开始分开建设
+已完成：新增坊内平面规则表、研究结论表，并重排工作簿页签</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工审核4条新增道路—城门关系。
-2. 继续检索安化门、启夏门向北道路的正式名称。
-3. 审核通过后，扩充其余外郭城门及相连道路。</x:v>
+        <x:v>1. 选择“道路为何宽阔”作为首个科普研究专题。
+2. 收集3—5篇专项研究论文并登记来源。
+3. 用真实论文试录后再确认两张新表的最终字段。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>安化门、启夏门向北道路目前使用项目暂名，只表示地图上的道路实体；正式名称未得到文献支持前不得作为史实名称引用。</x:v>
+        <x:v>研究结论不能直接当作史料事实：必须记录提出者、论文片段、论证依据、适用范围、限制条件和观点状态；科普转述另列。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30d86ce58343403e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99a42599c57f4560"/>
 </x:worksheet>
 </file>
 
@@ -1748,7 +1748,7 @@
         <x:v>阶段二：字段规范</x:v>
       </x:c>
       <x:c r="C8" s="16" t="str">
-        <x:v>确定六张表公共字段</x:v>
+        <x:v>确定核心专题表公共字段</x:v>
       </x:c>
       <x:c r="D8" s="16" t="str">
         <x:v>共同</x:v>
@@ -2062,7 +2062,7 @@
         <x:v>阶段二：字段规范</x:v>
       </x:c>
       <x:c r="C17" s="16" t="str">
-        <x:v>确定六张专题表转实体表/关系表规则</x:v>
+        <x:v>确定专题表转实体表/关系表规则</x:v>
       </x:c>
       <x:c r="D17" s="16" t="str">
         <x:v>共同</x:v>
@@ -2100,7 +2100,7 @@
         <x:v>阶段二：字段规范</x:v>
       </x:c>
       <x:c r="C18" s="16" t="str">
-        <x:v>召开六张表字段联合评审</x:v>
+        <x:v>召开专题表字段联合评审</x:v>
       </x:c>
       <x:c r="D18" s="16" t="str">
         <x:v>共同</x:v>
@@ -2132,7 +2132,7 @@
         <x:v>阶段二：字段规范</x:v>
       </x:c>
       <x:c r="C19" s="16" t="str">
-        <x:v>冻结六张核心表字段规范v1</x:v>
+        <x:v>冻结核心专题表字段规范v1</x:v>
       </x:c>
       <x:c r="D19" s="16" t="str">
         <x:v>共同</x:v>
@@ -2198,7 +2198,7 @@
         <x:v>阶段三：文献建设</x:v>
       </x:c>
       <x:c r="C21" s="16" t="str">
-        <x:v>建立六类数据缺失文献需求表</x:v>
+        <x:v>建立专题数据缺失文献需求表</x:v>
       </x:c>
       <x:c r="D21" s="16" t="str">
         <x:v>共同</x:v>
@@ -2386,7 +2386,7 @@
         <x:v>阶段四：小型样例</x:v>
       </x:c>
       <x:c r="C27" s="16" t="str">
-        <x:v>完成六张样例表</x:v>
+        <x:v>完成专题样例表</x:v>
       </x:c>
       <x:c r="D27" s="16" t="str">
         <x:v>共同</x:v>
@@ -2448,7 +2448,7 @@
         <x:v>阶段五：Skill升级</x:v>
       </x:c>
       <x:c r="C29" s="16" t="str">
-        <x:v>升级提取Skill支持六张专题表</x:v>
+        <x:v>升级提取Skill支持专题表</x:v>
       </x:c>
       <x:c r="D29" s="16" t="str">
         <x:v>Codex</x:v>
@@ -2598,7 +2598,7 @@
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C34" s="16" t="str">
-        <x:v>编写六张专题表到实体/关系转换脚本</x:v>
+        <x:v>编写专题表到实体/关系转换脚本</x:v>
       </x:c>
       <x:c r="D34" s="16" t="str">
         <x:v>Codex</x:v>
@@ -2949,6 +2949,124 @@
         <x:v>正式发布</x:v>
       </x:c>
       <x:c r="L45" s="16"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>S2-13</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>阶段二：字段规范</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>建立坊内平面规则表占位字段</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>用论文样例确认字段</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>S2-14</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>阶段二：字段规范</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>建立研究结论表及转换框架</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>试录专项研究论文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>S2-15</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>阶段二：字段规范</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>根据论文样例确认两张新增表字段</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>共同</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="H48"/>
+      <x:c r="I48"/>
+      <x:c r="J48" t="str">
+        <x:v>先选择道路宽度专题</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>S3-06</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>阶段三：文献建设</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>收集专项研究论文并建立小型专题综述</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>我</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>尚未开始</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G49"/>
+      <x:c r="H49"/>
+      <x:c r="I49"/>
+      <x:c r="J49" t="str">
+        <x:v>每个专题先选3—5篇论文</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3507,6 +3625,26 @@
         <x:v>连接关系来自图15；两条道路仍使用项目暂名</x:v>
       </x:c>
     </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>新增坊内平面规则表与研究结论表，补充转换和代码规则并重排页签</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>阶段二模板 / 第1批小型样例</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>用3—5篇道路宽度论文试录字段</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>基础事实与研究解释分层存储</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rc130cbc9fb7842f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R14d23b466318422a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R8eb6319037b6468a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R0ae7c3a9d9a048c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R67ccc771ea914c01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R4f319ca1ce404da2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R8e937f73d3274450"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rfa54bf5a9cec4ddb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R80cfabb1a2974d38"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R242eb819d8d04d5b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1227,7 +1227,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-09</x:v>
+        <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-10</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -1293,7 +1293,7 @@
       <x:c r="F6" s="70"/>
       <x:c r="G6" s="96" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"进行中")</x:f>
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H6" s="97"/>
       <x:c r="I6" s="98"/>
@@ -1308,7 +1308,7 @@
       </x:c>
       <x:c r="O6" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N6)</x:f>
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1359,7 +1359,7 @@
       </x:c>
       <x:c r="O9" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N9)</x:f>
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1374,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：阶段二字段扩展与阶段四小型样例并行
-总体状态：城门—道路连接已审核；基础事实层与研究解释层开始分开建设
-已完成：新增坊内平面规则表、研究结论表，并重排工作簿页签</x:v>
+        <x:v>当前阶段：阶段三专项研究论文筛选与精读
+总体状态：相关论文12篇已完成初筛，确定首批精读5篇
+分组结果：2篇核心直接研究、3篇辅助机制、5篇后续备用、2篇本轮暂不采用</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 选择“道路为何宽阔”作为首个科普研究专题。
-2. 收集3—5篇专项研究论文并登记来源。
-3. 用真实论文试录后再确认两张新表的最终字段。</x:v>
+        <x:v>1. 精读贺从容《（隋大兴）唐长安城坊内的道路》。
+2. 精读张小娟《唐宋都城内部道路交通研究》。
+3. 用防火、绿化、基础设施3篇论文检验解释机制并试录研究结论。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>研究结论不能直接当作史料事实：必须记录提出者、论文片段、论证依据、适用范围、限制条件和观点状态；科普转述另列。</x:v>
+        <x:v>证据提醒：道路宽度、走向、等级是基础事实；“为何宽阔”是研究解释。防火、绿化等材料若未明确联系唐长安，只能记为间接支持或待验证假说，不能写成确定动因。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99a42599c57f4560"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f7c412d41e24349"/>
 </x:worksheet>
 </file>
 
@@ -3039,7 +3039,13 @@
       <x:c r="H48"/>
       <x:c r="I48"/>
       <x:c r="J48" t="str">
-        <x:v>先选择道路宽度专题</x:v>
+        <x:v>用道路宽度专题论文试录字段</x:v>
+      </x:c>
+      <x:c r="K48" t="str">
+        <x:v>道路宽度专题_论文筛选清单_v1.md</x:v>
+      </x:c>
+      <x:c r="L48" t="str">
+        <x:v>先用真实论文检验字段，再决定是否增删</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -3056,16 +3062,24 @@
         <x:v>我</x:v>
       </x:c>
       <x:c r="E49" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F49" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G49"/>
+      <x:c r="G49" t="str">
+        <x:v>2026-08-10</x:v>
+      </x:c>
       <x:c r="H49"/>
       <x:c r="I49"/>
       <x:c r="J49" t="str">
-        <x:v>每个专题先选3—5篇论文</x:v>
+        <x:v>精读首批5篇并建立研究结论条目</x:v>
+      </x:c>
+      <x:c r="K49" t="str">
+        <x:v>道路宽度专题_论文筛选清单_v1.md</x:v>
+      </x:c>
+      <x:c r="L49" t="str">
+        <x:v>12篇已初筛；2篇核心、3篇辅助</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3645,6 +3659,26 @@
         <x:v>基础事实与研究解释分层存储</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>2026-08-10</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>完成相关论文12篇初筛，确定道路宽度专题首批5篇</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>道路宽度专题_论文筛选清单_v1.md</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>精读贺从容、张小娟并试录研究结论</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>防火、绿化、基础设施材料仅作辅助证据</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R67ccc771ea914c01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R4f319ca1ce404da2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R8e937f73d3274450"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rfa54bf5a9cec4ddb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R11bb14d1028b48bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R6bf8f84019fd4d03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R3fdaf5de0af04067"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R1ca6b7ee60514bcf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R242eb819d8d04d5b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f1051c4f4484220"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1374,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：阶段三专项研究论文筛选与精读
-总体状态：相关论文12篇已完成初筛，确定首批精读5篇
-分组结果：2篇核心直接研究、3篇辅助机制、5篇后续备用、2篇本轮暂不采用</x:v>
+        <x:v>当前阶段：阶段三专项论文精读与研究结论试录
+总体状态：13篇论文已初筛，核心文献增至3篇；李瑞论文已完成首轮精读
+本次产出：登记1条来源、6段完整论文片段、6条可独立审核的研究结论</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 精读贺从容《（隋大兴）唐长安城坊内的道路》。
-2. 精读张小娟《唐宋都城内部道路交通研究》。
-3. 用防火、绿化、基础设施3篇论文检验解释机制并试录研究结论。</x:v>
+        <x:v>1. 人工审核李瑞论文的6条研究结论。
+2. 精读贺从容《（隋大兴）唐长安城坊内的道路》。
+3. 精读张小娟《唐宋都城内部道路交通研究》，与李瑞观点交叉验证。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>证据提醒：道路宽度、走向、等级是基础事实；“为何宽阔”是研究解释。防火、绿化等材料若未明确联系唐长安，只能记为间接支持或待验证假说，不能写成确定动因。</x:v>
+        <x:v>审核重点：道路宽度数字要继续追溯考古原始来源；“政治物化、缺少人性化、空间浪费”等属于李瑞的评价性观点，不得改写成无争议事实。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f7c412d41e24349"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bf6ea8dd12e436e"/>
 </x:worksheet>
 </file>
 
@@ -3039,13 +3039,13 @@
       <x:c r="H48"/>
       <x:c r="I48"/>
       <x:c r="J48" t="str">
-        <x:v>用道路宽度专题论文试录字段</x:v>
+        <x:v>审核李瑞论文试录，确认研究结论表字段是否够用</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v>道路宽度专题_论文筛选清单_v1.md</x:v>
+        <x:v>唐长安城知识图谱录入模板_阶段二_v1.xlsx</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v>先用真实论文检验字段，再决定是否增删</x:v>
+        <x:v>现有字段可以容纳首批6条结论，待人工审核</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -3073,13 +3073,13 @@
       <x:c r="H49"/>
       <x:c r="I49"/>
       <x:c r="J49" t="str">
-        <x:v>精读首批5篇并建立研究结论条目</x:v>
+        <x:v>审核李瑞论文6条试录结论，然后精读贺从容、张小娟</x:v>
       </x:c>
       <x:c r="K49" t="str">
-        <x:v>道路宽度专题_论文筛选清单_v1.md</x:v>
+        <x:v>李瑞2005_道路宽度专题精读与试录说明_v1.md</x:v>
       </x:c>
       <x:c r="L49" t="str">
-        <x:v>12篇已初筛；2篇核心、3篇辅助</x:v>
+        <x:v>13篇已初筛；核心3篇、辅助3篇；李瑞6条已试录</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3679,6 +3679,26 @@
         <x:v>防火、绿化、基础设施材料仅作辅助证据</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>2026-08-10</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>完成李瑞论文首轮精读并试录6条研究结论</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>阶段二录入模板 / 李瑞2005精读说明</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>人工审核6条结论，再精读贺从容和张小娟</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>评价性观点与基础事实分开保存</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R11bb14d1028b48bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R6bf8f84019fd4d03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R3fdaf5de0af04067"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R1ca6b7ee60514bcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rbb0cb888a0af4204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R40a060843bcd46e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R46c6fe7c2a0f498d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R9af17231720643ae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f1051c4f4484220"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1c0f294790bb4989"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1374,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：阶段三专项论文精读与研究结论试录
-总体状态：13篇论文已初筛，核心文献增至3篇；李瑞论文已完成首轮精读
-本次产出：登记1条来源、6段完整论文片段、6条可独立审核的研究结论</x:v>
+        <x:v>当前阶段：核心论文精读与新增表字段检验
+总体状态：李瑞、贺从容两篇已完成首轮精读
+本次产出：贺从容论文登记6段片段、5条坊内规则、5条研究结论</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工审核李瑞论文的6条研究结论。
-2. 精读贺从容《（隋大兴）唐长安城坊内的道路》。
-3. 精读张小娟《唐宋都城内部道路交通研究》，与李瑞观点交叉验证。</x:v>
+        <x:v>1. 人工审核贺从容的5条坊内规则和5条研究结论。
+2. 重点确认“小十字街非普遍”“循墙道路不连续”两项。
+3. 精读张小娟论文，与李瑞的道路解释交叉验证。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>审核重点：道路宽度数字要继续追溯考古原始来源；“政治物化、缺少人性化、空间浪费”等属于李瑞的评价性观点，不得改写成无争议事实。</x:v>
+        <x:v>证据提醒：十字街约15—20米有较直接考古支持；巷约6米、曲约1.5—3米主要为推测；十六分区不能作为所有坊的固定模板。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bf6ea8dd12e436e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R100a61ceed9b415f"/>
 </x:worksheet>
 </file>
 
@@ -3039,13 +3039,13 @@
       <x:c r="H48"/>
       <x:c r="I48"/>
       <x:c r="J48" t="str">
-        <x:v>审核李瑞论文试录，确认研究结论表字段是否够用</x:v>
+        <x:v>用张小娟论文继续检验研究结论字段</x:v>
       </x:c>
       <x:c r="K48" t="str">
         <x:v>唐长安城知识图谱录入模板_阶段二_v1.xlsx</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v>现有字段可以容纳首批6条结论，待人工审核</x:v>
+        <x:v>坊内平面规则字段可用；潜在新增字段暂记备注</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -3073,13 +3073,13 @@
       <x:c r="H49"/>
       <x:c r="I49"/>
       <x:c r="J49" t="str">
-        <x:v>审核李瑞论文6条试录结论，然后精读贺从容、张小娟</x:v>
+        <x:v>审核贺从容5条规则和5条结论，再精读张小娟</x:v>
       </x:c>
       <x:c r="K49" t="str">
-        <x:v>李瑞2005_道路宽度专题精读与试录说明_v1.md</x:v>
+        <x:v>贺从容_坊内道路专题精读与试录说明_v1.md</x:v>
       </x:c>
       <x:c r="L49" t="str">
-        <x:v>13篇已初筛；核心3篇、辅助3篇；李瑞6条已试录</x:v>
+        <x:v>贺从容已精读：6段片段、5条规则、5条结论</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3699,6 +3699,26 @@
         <x:v>评价性观点与基础事实分开保存</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>2026-08-10</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>完成贺从容论文精读并试录坊内规则和研究结论</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>阶段二录入模板 / 贺从容精读说明</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>人工审核后精读张小娟</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>十六分区与宽度推测均保留限制</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rbb0cb888a0af4204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R40a060843bcd46e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R46c6fe7c2a0f498d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R9af17231720643ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R82f792b0ee4b48dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R92bf2d7d247042d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R6a8ff4a7c35f403e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Ra77a890dc19c4297"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1c0f294790bb4989"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5b2aa91ee0f249a8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R100a61ceed9b415f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08549b2feaf040d2"/>
 </x:worksheet>
 </file>
 

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R82f792b0ee4b48dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R92bf2d7d247042d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R6a8ff4a7c35f403e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Ra77a890dc19c4297"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rf840700f3a2f4b55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Ra98644e3f7d642a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rc1144211b05f48c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R09f6b013d6dc4857"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5b2aa91ee0f249a8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R58efeee8c6bb4846"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1374,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：核心论文精读与新增表字段检验
-总体状态：李瑞、贺从容两篇已完成首轮精读
-本次产出：贺从容论文登记6段片段、5条坊内规则、5条研究结论</x:v>
+        <x:v>当前阶段：第三篇核心论文精读与交叉验证
+总体状态：李瑞、贺从容、张小娟三篇已完成首轮精读
+本次产出：贺从容10条审核通过；张小娟登记6段片段、1条坊内规则、5条研究结论</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工审核贺从容的5条坊内规则和5条研究结论。
-2. 重点确认“小十字街非普遍”“循墙道路不连续”两项。
-3. 精读张小娟论文，与李瑞的道路解释交叉验证。</x:v>
+        <x:v>1. 人工审核张小娟的1条坊内规则和5条研究结论。
+2. 重点确认‘两类坊内模型仅为常规复原’和‘门禁导致时间性可达’。
+3. 审核后做三篇核心论文的字段小结，再进入防火论文。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>证据提醒：十字街约15—20米有较直接考古支持；巷约6米、曲约1.5—3米主要为推测；十六分区不能作为所有坊的固定模板。</x:v>
+        <x:v>证据提醒：张文称东西向十四街，与项目当前十二条口径冲突，暂不改道路表；坊内两类路网只能作为常规模型，不能覆盖具体坊的例外。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08549b2feaf040d2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6b2f361188b442e"/>
 </x:worksheet>
 </file>
 
@@ -3039,13 +3039,13 @@
       <x:c r="H48"/>
       <x:c r="I48"/>
       <x:c r="J48" t="str">
-        <x:v>用张小娟论文继续检验研究结论字段</x:v>
+        <x:v>审核张小娟后，综合三篇核心论文进行字段评估</x:v>
       </x:c>
       <x:c r="K48" t="str">
         <x:v>唐长安城知识图谱录入模板_阶段二_v1.xlsx</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v>坊内平面规则字段可用；潜在新增字段暂记备注</x:v>
+        <x:v>现有字段可承载；开放时段、管理措施、模型适用范围暂记候选字段</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -3073,13 +3073,13 @@
       <x:c r="H49"/>
       <x:c r="I49"/>
       <x:c r="J49" t="str">
-        <x:v>审核贺从容5条规则和5条结论，再精读张小娟</x:v>
+        <x:v>人工审核张小娟新增1条坊内规则和5条研究结论</x:v>
       </x:c>
       <x:c r="K49" t="str">
-        <x:v>贺从容_坊内道路专题精读与试录说明_v1.md</x:v>
+        <x:v>张小娟_道路交通专题精读与试录说明_v1.md</x:v>
       </x:c>
       <x:c r="L49" t="str">
-        <x:v>贺从容已精读：6段片段、5条规则、5条结论</x:v>
+        <x:v>贺从容10条已审核通过；张小娟完成6段片段、1条规则、5条结论</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3719,6 +3719,26 @@
         <x:v>十六分区与宽度推测均保留限制</x:v>
       </x:c>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>2026-08-10</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>完成张小娟论文精读、交叉验证与试录</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>阶段二录入模板 / 张小娟精读说明</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>人工审核后进行三篇核心论文字段评估</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>道路数量冲突暂不修改；两类坊内模型保留适用限制</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rf840700f3a2f4b55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Ra98644e3f7d642a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rc1144211b05f48c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R09f6b013d6dc4857"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R95af585e76b54c55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R80cab47b45b849a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rfed742c126814dac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rc793bbe0d8634b3d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R58efeee8c6bb4846"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R003bbd03e4b4464e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1374,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：第三篇核心论文精读与交叉验证
-总体状态：李瑞、贺从容、张小娟三篇已完成首轮精读
-本次产出：贺从容10条审核通过；张小娟登记6段片段、1条坊内规则、5条研究结论</x:v>
+        <x:v>当前阶段：小型样例表中的论文试录与字段验证
+总体状态：李瑞、贺从容、张小娟三批试录已统一迁入小型样例表
+本次整理：迁移3条来源、18段片段、6条坊内规则、16条研究结论；正式模板已清理</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工审核张小娟的1条坊内规则和5条研究结论。
-2. 重点确认‘两类坊内模型仅为常规复原’和‘门禁导致时间性可达’。
-3. 审核后做三篇核心论文的字段小结，再进入防火论文。</x:v>
+        <x:v>1. 人工审核样例表中的张小娟1条坊内规则和5条研究结论。
+2. 对三篇核心论文做字段小结，确定候选新增字段。
+3. 样例验证稳定后，再决定哪些审核数据进入正式模板。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>证据提醒：张文称东西向十四街，与项目当前十二条口径冲突，暂不改道路表；坊内两类路网只能作为常规模型，不能覆盖具体坊的例外。</x:v>
+        <x:v>流程提醒：论文提取先进入小型样例表；审核与字段验证完成后，才合并到正式模板。迁移时已重编号片段并检查全部引用。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6b2f361188b442e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cd2f020dad4402c"/>
 </x:worksheet>
 </file>
 
@@ -3039,13 +3039,13 @@
       <x:c r="H48"/>
       <x:c r="I48"/>
       <x:c r="J48" t="str">
-        <x:v>审核张小娟后，综合三篇核心论文进行字段评估</x:v>
+        <x:v>在小型样例表完成三篇核心论文字段评估，再决定是否转入正式模板</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v>唐长安城知识图谱录入模板_阶段二_v1.xlsx</x:v>
+        <x:v>小型样例_第1批_文献片段与基础对象_v1.xlsx</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v>现有字段可承载；开放时段、管理措施、模型适用范围暂记候选字段</x:v>
+        <x:v>正式模板恢复为结构与非论文试录数据；论文试录统一在样例表迭代</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -3073,13 +3073,13 @@
       <x:c r="H49"/>
       <x:c r="I49"/>
       <x:c r="J49" t="str">
-        <x:v>人工审核张小娟新增1条坊内规则和5条研究结论</x:v>
+        <x:v>人工审核小型样例表中的张小娟1条规则和5条研究结论</x:v>
       </x:c>
       <x:c r="K49" t="str">
-        <x:v>张小娟_道路交通专题精读与试录说明_v1.md</x:v>
+        <x:v>小型样例_第1批_文献片段与基础对象_v1.xlsx</x:v>
       </x:c>
       <x:c r="L49" t="str">
-        <x:v>贺从容10条已审核通过；张小娟完成6段片段、1条规则、5条结论</x:v>
+        <x:v>三篇论文试录已从正式模板迁移到小型样例表；贺从容10条保持审核通过</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3739,6 +3739,26 @@
         <x:v>道路数量冲突暂不修改；两类坊内模型保留适用限制</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>2026-08-10</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>完成三篇论文试录数据迁移与编号整理</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>小型样例表 / 正式录入模板 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>审核张小娟并开展三篇论文字段小结</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>片段编号改为1000、1100、1200段，正式模板不再存放论文试录</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R95af585e76b54c55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R80cab47b45b849a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rfed742c126814dac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rc793bbe0d8634b3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R021890da66964097"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R531a80b87b6f461b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R78c516eb14834943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rc5bd2215e2c744fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R003bbd03e4b4464e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14b1bef2c06748f4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1227,7 +1227,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-10</x:v>
+        <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-11</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -1374,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：小型样例表中的论文试录与字段验证
-总体状态：李瑞、贺从容、张小娟三批试录已统一迁入小型样例表
-本次整理：迁移3条来源、18段片段、6条坊内规则、16条研究结论；正式模板已清理</x:v>
+        <x:v>当前阶段：平台迁移前的数据结构对齐
+总体状态：三篇论文试录已审核；坊坐标与道路编码已按同事全量表统一
+本次整理：主坐标改为TC-PLANAR-GRID-v1；道路改为实体连续编号；旧SENO轴线规则降为历史版本</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工审核样例表中的张小娟1条坊内规则和5条研究结论。
-2. 对三篇核心论文做字段小结，确定候选新增字段。
-3. 样例验证稳定后，再决定哪些审核数据进入正式模板。</x:v>
+        <x:v>1. 建立“正式数据工作簿”，保持录入模板为空。
+2. 汇入同事完成的108坊、25条主道路及现有已审核数据。
+3. 生成实体表、关系表和平台小规模试导入数据包。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>流程提醒：论文提取先进入小型样例表；审核与字段验证完成后，才合并到正式模板。迁移时已重编号片段并检查全部引用。</x:v>
+        <x:v>流程提醒：模板只保存结构，不作为数据仓库；小型样例用于测试。平台迁移以正式数据工作簿为唯一汇总来源，论文全量阅读可在试导入通过后继续。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cd2f020dad4402c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93d3752b0800483c"/>
 </x:worksheet>
 </file>
 

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R021890da66964097"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R531a80b87b6f461b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R78c516eb14834943"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rc5bd2215e2c744fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R77b88f1a6b914c97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R8bec24eb7fa94805"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rb710a9a569f44c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R283e92eeae84451d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14b1bef2c06748f4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R175a81452e534e16"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1374,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：平台迁移前的数据结构对齐
-总体状态：三篇论文试录已审核；坊坐标与道路编码已按同事全量表统一
-本次整理：主坐标改为TC-PLANAR-GRID-v1；道路改为实体连续编号；旧SENO轴线规则降为历史版本</x:v>
+        <x:v>当前阶段：平台迁移前的数据结构整理完成
+总体状态：模板、样例、专题层、证据层和图谱输出层的职责已经分开
+本次整理：正式模板已清空11条示范记录；新增18张工作表结构总览；结构版本更新为TC-SCHEMA-1.1</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 建立“正式数据工作簿”，保持录入模板为空。
-2. 汇入同事完成的108坊、25条主道路及现有已审核数据。
-3. 生成实体表、关系表和平台小规模试导入数据包。</x:v>
+        <x:v>1. 建立“唐长安城知识图谱_正式数据集_v1.xlsx”。
+2. 汇入同事完成的108坊、25条主道路及其他审核数据。
+3. 按转换规则生成实体表、关系表和平台试导入包。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>流程提醒：模板只保存结构，不作为数据仓库；小型样例用于测试。平台迁移以正式数据工作簿为唯一汇总来源，论文全量阅读可在试导入通过后继续。</x:v>
+        <x:v>结构提醒：录入模板只保存空白结构；小型样例保存测试数据；正式数据工作簿是平台迁移的唯一汇总来源。专题表以后仍可增减，但主键和已发布关系不要随意重排。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93d3752b0800483c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e9d1234745249d0"/>
 </x:worksheet>
 </file>
 

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R77b88f1a6b914c97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R8bec24eb7fa94805"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rb710a9a569f44c0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R283e92eeae84451d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R25ac82c1f3a64732"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R7b6336bedfdf42eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rfe3ec7f6336f4cd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R6dc57d30503c47d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -991,7 +991,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R175a81452e534e16"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0808b8e998184c0e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1374,9 +1374,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：平台迁移前的数据结构整理完成
-总体状态：模板、样例、专题层、证据层和图谱输出层的职责已经分开
-本次整理：正式模板已清空11条示范记录；新增18张工作表结构总览；结构版本更新为TC-SCHEMA-1.1</x:v>
+        <x:v>当前阶段：三层结构与科普表达层已经建立
+总体状态：八张核心空间专题表、研究结论系统和科普内容系统均已纳入结构
+本次整理：新增地形、重要建筑与设施、科普内容、科普依据关联四张表；结构版本更新为TC-SCHEMA-1.2</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1412,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 建立“唐长安城知识图谱_正式数据集_v1.xlsx”。
-2. 汇入同事完成的108坊、25条主道路及其他审核数据。
-3. 按转换规则生成实体表、关系表和平台试导入包。</x:v>
+        <x:v>1. 审核四张新增表的字段是否满足平台展示。
+2. 建立正式数据工作簿，汇入108坊、25条主道路及审核数据。
+3. 选择一个科普问题，测试“事实—解释—科普—证据回溯”闭环。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1458,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>结构提醒：录入模板只保存空白结构；小型样例保存测试数据；正式数据工作簿是平台迁移的唯一汇总来源。专题表以后仍可增减，但主键和已发布关系不要随意重排。</x:v>
+        <x:v>三层提醒：基础事实与研究解释分别保存；科普文字单独进入科普内容表，并通过科普依据关联连接多个实体、关系、结论、来源和史料片段。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1502,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e9d1234745249d0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff4a15d92ea34e57"/>
 </x:worksheet>
 </file>
 

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R25ac82c1f3a64732"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R7b6336bedfdf42eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rfe3ec7f6336f4cd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R6dc57d30503c47d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R702fceaf83c5426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R5ffb8c998ca54e07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Reea34d7e8c7345a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rff2924134505438a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -210,7 +210,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="215">
+  <x:cellXfs count="218">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -726,6 +726,13 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -991,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0808b8e998184c0e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3992785f69c14bdf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1293,7 +1300,7 @@
       <x:c r="F6" s="70"/>
       <x:c r="G6" s="96" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"进行中")</x:f>
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="97"/>
       <x:c r="I6" s="98"/>
@@ -1308,7 +1315,7 @@
       </x:c>
       <x:c r="O6" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N6)</x:f>
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1329,7 +1336,7 @@
       </x:c>
       <x:c r="O7" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N7)</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1374,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：三层结构与科普表达层已经建立
-总体状态：八张核心空间专题表、研究结论系统和科普内容系统均已纳入结构
-本次整理：新增地形、重要建筑与设施、科普内容、科普依据关联四张表；结构版本更新为TC-SCHEMA-1.2</x:v>
+        <x:v>当前阶段：首条科普内容闭环已经试录
+总体状态：已把道路基础事实、研究解释、限制条件和公众表达连接起来
+本次整理：在小型样例中新增“唐长安城的街道为什么宽得惊人？”v0.1及7条依据关联</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1412,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 审核四张新增表的字段是否满足平台展示。
-2. 建立正式数据工作簿，汇入108坊、25条主道路及审核数据。
-3. 选择一个科普问题，测试“事实—解释—科普—证据回溯”闭环。</x:v>
+        <x:v>1. 人工审核首条科普问答的科学性和表达方式。
+2. 审核7条依据的支撑角色、显示顺序与公开范围。
+3. 审核通过后，用这条数据测试平台的证据回溯展示。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1458,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>三层提醒：基础事实与研究解释分别保存；科普文字单独进入科普内容表，并通过科普依据关联连接多个实体、关系、结论、来源和史料片段。</x:v>
+        <x:v>审核提醒：本条是待审核样例。‘朱雀大街约150米’和礼仪成因来自现代研究转引；‘横街三百步、所以限隔二城’属于古代文献直述，两类证据不可混写。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1502,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff4a15d92ea34e57"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9bdd0929d6e4166"/>
 </x:worksheet>
 </file>
 
@@ -3048,38 +3055,38 @@
         <x:v>正式模板恢复为结构与非论文试录数据；论文试录统一在样例表迭代</x:v>
       </x:c>
     </x:row>
-    <x:row r="49">
-      <x:c r="A49" t="str">
-        <x:v>S3-06</x:v>
-      </x:c>
-      <x:c r="B49" t="str">
-        <x:v>阶段三：文献建设</x:v>
-      </x:c>
-      <x:c r="C49" t="str">
-        <x:v>收集专项研究论文并建立小型专题综述</x:v>
-      </x:c>
-      <x:c r="D49" t="str">
-        <x:v>我</x:v>
-      </x:c>
-      <x:c r="E49" t="str">
-        <x:v>进行中</x:v>
-      </x:c>
-      <x:c r="F49" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G49" t="str">
-        <x:v>2026-08-10</x:v>
-      </x:c>
-      <x:c r="H49"/>
-      <x:c r="I49"/>
-      <x:c r="J49" t="str">
-        <x:v>人工审核小型样例表中的张小娟1条规则和5条研究结论</x:v>
-      </x:c>
-      <x:c r="K49" t="str">
-        <x:v>小型样例_第1批_文献片段与基础对象_v1.xlsx</x:v>
-      </x:c>
-      <x:c r="L49" t="str">
-        <x:v>三篇论文试录已从正式模板迁移到小型样例表；贺从容10条保持审核通过</x:v>
+    <x:row r="49" ht="40" customHeight="1">
+      <x:c r="A49" s="216" t="str">
+        <x:v>S4-05</x:v>
+      </x:c>
+      <x:c r="B49" s="216" t="str">
+        <x:v>阶段四：小型样例</x:v>
+      </x:c>
+      <x:c r="C49" s="216" t="str">
+        <x:v>试做首条科普内容及证据回溯闭环</x:v>
+      </x:c>
+      <x:c r="D49" s="216" t="str">
+        <x:v>共同</x:v>
+      </x:c>
+      <x:c r="E49" s="216" t="str">
+        <x:v>等待确认</x:v>
+      </x:c>
+      <x:c r="F49" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G49" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="H49" s="217"/>
+      <x:c r="I49" s="217"/>
+      <x:c r="J49" s="216" t="str">
+        <x:v>审核科普文字和7条依据关联</x:v>
+      </x:c>
+      <x:c r="K49" s="216" t="str">
+        <x:v>TC-POPULAR-0001及TC-POPLINK-0001—0007</x:v>
+      </x:c>
+      <x:c r="L49" s="216" t="str">
+        <x:v>样例只录入小型样例表，不进入空白正式模板</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3759,6 +3766,26 @@
         <x:v>片段编号改为1000、1100、1200段，正式模板不再存放论文试录</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="40" customHeight="1">
+      <x:c r="A23" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="B23" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C23" s="216" t="str">
+        <x:v>建立首条科普问答及7条证据关联，完成三层闭环试录</x:v>
+      </x:c>
+      <x:c r="D23" s="216" t="str">
+        <x:v>小型样例表 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E23" s="216" t="str">
+        <x:v>人工审核科普文字、依据角色和公开范围</x:v>
+      </x:c>
+      <x:c r="F23" s="216" t="str">
+        <x:v>未修改空白正式模板；全部标记待审核</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R702fceaf83c5426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R5ffb8c998ca54e07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Reea34d7e8c7345a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rff2924134505438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R0fd4a088273f464f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rbb0b0c22fec945a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R2a19d62ff2eb4915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R2b27747c91e74800"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3992785f69c14bdf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfeb8308d09b341aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.2826086956521739</x:v>
+        <x:v>0.2978723404255319</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：首条科普内容闭环已经试录
-总体状态：已把道路基础事实、研究解释、限制条件和公众表达连接起来
-本次整理：在小型样例中新增“唐长安城的街道为什么宽得惊人？”v0.1及7条依据关联</x:v>
+        <x:v>当前阶段：平台迁移盘点已经完成
+总体状态：技术底座可保留，迁移重点是领域类型、页面文案、数据包和三层知识展示
+本次整理：形成“保留—替换—新增”清单；平台代码和青瓷演示数据均未修改</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工审核首条科普问答的科学性和表达方式。
-2. 审核7条依据的支撑角色、显示顺序与公开范围。
-3. 审核通过后，用这条数据测试平台的证据回溯展示。</x:v>
+        <x:v>1. 确定唐长安平台数据契约v1。
+2. 明确Excel各表到sources、source_chunks、entities、relations的映射。
+3. 用现有小型样例生成首个可校验导入包。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>审核提醒：本条是待审核样例。‘朱雀大街约150米’和礼仪成因来自现代研究转引；‘横街三百步、所以限隔二城’属于古代文献直述，两类证据不可混写。</x:v>
+        <x:v>迁移提醒：不要先删除青瓷数据。先让唐长安小样例通过导入、检索、图谱和证据回溯测试，再清理旧种子和青瓷专属页面。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9bdd0929d6e4166"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26b2dfe242b14d80"/>
 </x:worksheet>
 </file>
 
@@ -2560,12 +2560,14 @@
       <x:c r="H32" s="17"/>
       <x:c r="I32" s="17"/>
       <x:c r="J32" s="16" t="str">
-        <x:v>保留通用技术架构</x:v>
+        <x:v>唐长安小样例验收后再清理</x:v>
       </x:c>
       <x:c r="K32" s="16" t="str">
         <x:v>唐长安城平台基线</x:v>
       </x:c>
-      <x:c r="L32" s="16"/>
+      <x:c r="L32" s="16" t="str">
+        <x:v>清理顺序调整：先导入验证，后删除青瓷演示数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="16" t="str">
@@ -3087,6 +3089,44 @@
       </x:c>
       <x:c r="L49" s="216" t="str">
         <x:v>样例只录入小型样例表，不进入空白正式模板</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="40" customHeight="1">
+      <x:c r="A50" s="216" t="str">
+        <x:v>S6-05</x:v>
+      </x:c>
+      <x:c r="B50" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C50" s="216" t="str">
+        <x:v>盘点青瓷平台并形成唐长安迁移清单</x:v>
+      </x:c>
+      <x:c r="D50" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E50" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F50" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G50" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="H50" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="I50" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="J50" s="216" t="str">
+        <x:v>确定唐长安平台数据契约v1</x:v>
+      </x:c>
+      <x:c r="K50" s="216" t="str">
+        <x:v>唐长安城平台迁移盘点与实施清单_v1.md</x:v>
+      </x:c>
+      <x:c r="L50" s="216" t="str">
+        <x:v>只读检查；未修改平台代码和演示数据</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3786,6 +3826,26 @@
         <x:v>未修改空白正式模板；全部标记待审核</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" ht="40" customHeight="1">
+      <x:c r="A24" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="B24" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C24" s="216" t="str">
+        <x:v>完成平台只读盘点，形成保留、替换、新增及六步实施清单</x:v>
+      </x:c>
+      <x:c r="D24" s="216" t="str">
+        <x:v>平台迁移盘点与实施清单v1 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E24" s="216" t="str">
+        <x:v>确定唐长安平台数据契约v1</x:v>
+      </x:c>
+      <x:c r="F24" s="216" t="str">
+        <x:v>平台代码未修改；发现一个百度云同步临时文件并保持不动</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R0fd4a088273f464f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rbb0b0c22fec945a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R2a19d62ff2eb4915"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R2b27747c91e74800"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R93efc77c45784207"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rd86d23c52d6e4c91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R47b3f38e70c94f4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R3d08a50723024f0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfeb8308d09b341aa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re779d36c309841bb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.2978723404255319</x:v>
+        <x:v>0.3125</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：平台迁移盘点已经完成
-总体状态：技术底座可保留，迁移重点是领域类型、页面文案、数据包和三层知识展示
-本次整理：形成“保留—替换—新增”清单；平台代码和青瓷演示数据均未修改</x:v>
+        <x:v>当前阶段：唐长安平台数据契约v1已经建立
+总体状态：Excel数据进入平台的四类落点、三层标识、审核状态和导入顺序已经明确
+本次整理：采用现有数据库兼容方案，暂不新增专用表，也不修改平台代码</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 确定唐长安平台数据契约v1。
-2. 明确Excel各表到sources、source_chunks、entities、relations的映射。
-3. 用现有小型样例生成首个可校验导入包。</x:v>
+        <x:v>1. 编写小型样例Excel转换程序。
+2. 生成首个唐长安平台导入包和错误报告。
+3. 人工核对数量、编号、证据和悬空关系后再进入平台。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>迁移提醒：不要先删除青瓷数据。先让唐长安小样例通过导入、检索、图谱和证据回溯测试，再清理旧种子和青瓷专属页面。</x:v>
+        <x:v>契约提醒：平台关系只能连接实体。原文片段写入source_ids；研究结论和审核科普成品作为实体；即时AI回答不写入知识库。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26b2dfe242b14d80"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4602b9e98624e05"/>
 </x:worksheet>
 </file>
 
@@ -3127,6 +3127,44 @@
       </x:c>
       <x:c r="L50" s="216" t="str">
         <x:v>只读检查；未修改平台代码和演示数据</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="40" customHeight="1">
+      <x:c r="A51" s="216" t="str">
+        <x:v>S6-06</x:v>
+      </x:c>
+      <x:c r="B51" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C51" s="216" t="str">
+        <x:v>制定唐长安平台数据契约v1</x:v>
+      </x:c>
+      <x:c r="D51" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E51" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F51" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G51" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="H51" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="I51" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="J51" s="216" t="str">
+        <x:v>编写小型样例Excel转换程序</x:v>
+      </x:c>
+      <x:c r="K51" s="216" t="str">
+        <x:v>平台数据契约v1 / 导入包结构示例v1</x:v>
+      </x:c>
+      <x:c r="L51" s="216" t="str">
+        <x:v>兼容现有四类核心表；小样例先行</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3846,6 +3884,26 @@
         <x:v>平台代码未修改；发现一个百度云同步临时文件并保持不动</x:v>
       </x:c>
     </x:row>
+    <x:row r="25" ht="40" customHeight="1">
+      <x:c r="A25" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="B25" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C25" s="216" t="str">
+        <x:v>完成平台数据契约v1，确定四类数据、三层标识、状态映射和导入顺序</x:v>
+      </x:c>
+      <x:c r="D25" s="216" t="str">
+        <x:v>平台数据契约v1 / 导入包结构示例v1 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E25" s="216" t="str">
+        <x:v>编写小型样例Excel转换程序</x:v>
+      </x:c>
+      <x:c r="F25" s="216" t="str">
+        <x:v>v1优先兼容现有数据库；不自动发布数据</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R93efc77c45784207"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rd86d23c52d6e4c91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R47b3f38e70c94f4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R3d08a50723024f0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Ra575df1efbe044a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R90660f22e4df4b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R5d2642ba54774055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Ra4cf915e4c704a22"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re779d36c309841bb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4696903f68964d5c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.3125</x:v>
+        <x:v>0.32653061224489793</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：唐长安平台数据契约v1已经建立
-总体状态：Excel数据进入平台的四类落点、三层标识、审核状态和导入顺序已经明确
-本次整理：采用现有数据库兼容方案，暂不新增专用表，也不修改平台代码</x:v>
+        <x:v>当前阶段：首个唐长安平台导入包已经生成
+总体状态：6来源、29片段、47实体、32关系通过结构校验；无悬空关系
+本次整理：UUID重复生成保持一致；没有记录被自动发布；科普样例仍为pending_review</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 编写小型样例Excel转换程序。
-2. 生成首个唐长安平台导入包和错误报告。
-3. 人工核对数量、编号、证据和悬空关系后再进入平台。</x:v>
+        <x:v>1. 人工审核导入校验报告中的数量和状态。
+2. 抽查实体、关系、研究结论和科普依据的证据回溯。
+3. 审核通过后，才在测试数据库执行首次导入。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>契约提醒：平台关系只能连接实体。原文片段写入source_ids；研究结论和审核科普成品作为实体；即时AI回答不写入知识库。</x:v>
+        <x:v>安全提醒：当前只生成导入文件，尚未写入平台数据库。首次导入必须使用测试环境，并保留现有青瓷演示数据作为回退。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4602b9e98624e05"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde605999bb944361"/>
 </x:worksheet>
 </file>
 
@@ -3165,6 +3165,44 @@
       </x:c>
       <x:c r="L51" s="216" t="str">
         <x:v>兼容现有四类核心表；小样例先行</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="40" customHeight="1">
+      <x:c r="A52" s="216" t="str">
+        <x:v>S6-07</x:v>
+      </x:c>
+      <x:c r="B52" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C52" s="216" t="str">
+        <x:v>编写小型样例转换程序并生成首个导入包</x:v>
+      </x:c>
+      <x:c r="D52" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E52" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F52" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G52" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="H52" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="I52" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="J52" s="216" t="str">
+        <x:v>人工复核导入包和校验报告</x:v>
+      </x:c>
+      <x:c r="K52" s="216" t="str">
+        <x:v>6来源 / 29片段 / 47实体 / 32关系</x:v>
+      </x:c>
+      <x:c r="L52" s="216" t="str">
+        <x:v>0错误、0警告、0悬空关系；未写入数据库</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3904,6 +3942,26 @@
         <x:v>v1优先兼容现有数据库；不自动发布数据</x:v>
       </x:c>
     </x:row>
+    <x:row r="26" ht="40" customHeight="1">
+      <x:c r="A26" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="B26" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C26" s="216" t="str">
+        <x:v>完成Excel转换程序、首个真实导入包和校验报告</x:v>
+      </x:c>
+      <x:c r="D26" s="216" t="str">
+        <x:v>转换程序 / 平台导入包 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E26" s="216" t="str">
+        <x:v>人工复核后在测试数据库首次导入</x:v>
+      </x:c>
+      <x:c r="F26" s="216" t="str">
+        <x:v>UUID稳定；0悬空关系；科普样例保持待审核</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Ra575df1efbe044a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R90660f22e4df4b9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R5d2642ba54774055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Ra4cf915e4c704a22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R9d1a02bf73544995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R2fc349c833cf41b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R6b3f9b53ee9c4f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R66e1da3dfaeb4c6e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4696903f68964d5c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1d2ebce984d4522"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.32653061224489793</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：首个唐长安平台导入包已经生成
-总体状态：6来源、29片段、47实体、32关系通过结构校验；无悬空关系
-本次整理：UUID重复生成保持一致；没有记录被自动发布；科普样例仍为pending_review</x:v>
+        <x:v>当前阶段：首个导入包人工复核已经完成
+总体状态：结构校验通过，但人工复核退回修正；发现2项P0和5项P1
+本次整理：主要问题是研究结论对象误连、基础实体类型错误及平台显示元数据缺失</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工审核导入校验报告中的数量和状态。
-2. 抽查实体、关系、研究结论和科普依据的证据回溯。
-3. 审核通过后，才在测试数据库执行首次导入。</x:v>
+        <x:v>1. 修正10条研究结论的指向对象。
+2. 修正宫城、皇城、龙首池的实体类型。
+3. 统一审核依赖并修正日期、页码、中文标签和科普直接证据元数据。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>安全提醒：当前只生成导入文件，尚未写入平台数据库。首次导入必须使用测试环境，并保留现有青瓷演示数据作为回退。</x:v>
+        <x:v>人工复核提醒：当前导入包不得进入测试数据库。原始Excel和平台数据库均未修改；修正后必须重新生成并复核。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde605999bb944361"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb07f65290c554cf3"/>
 </x:worksheet>
 </file>
 
@@ -3203,6 +3203,44 @@
       </x:c>
       <x:c r="L52" s="216" t="str">
         <x:v>0错误、0警告、0悬空关系；未写入数据库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="40" customHeight="1">
+      <x:c r="A53" s="216" t="str">
+        <x:v>S6-08</x:v>
+      </x:c>
+      <x:c r="B53" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C53" s="216" t="str">
+        <x:v>人工复核首个平台导入包</x:v>
+      </x:c>
+      <x:c r="D53" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E53" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F53" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G53" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="H53" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="I53" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="J53" s="216" t="str">
+        <x:v>修正MR-001—MR-007后重新生成导入包</x:v>
+      </x:c>
+      <x:c r="K53" s="216" t="str">
+        <x:v>人工复核报告v1 / 7项问题</x:v>
+      </x:c>
+      <x:c r="L53" s="216" t="str">
+        <x:v>人工复核退回：2项P0、5项P1；尚未导入数据库</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3962,6 +4000,26 @@
         <x:v>UUID稳定；0悬空关系；科普样例保持待审核</x:v>
       </x:c>
     </x:row>
+    <x:row r="27" ht="40" customHeight="1">
+      <x:c r="A27" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="B27" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C27" s="216" t="str">
+        <x:v>完成人工复核并形成问题清单</x:v>
+      </x:c>
+      <x:c r="D27" s="216" t="str">
+        <x:v>人工复核报告 / 复核问题JSON / 项目看板</x:v>
+      </x:c>
+      <x:c r="E27" s="216" t="str">
+        <x:v>修正7项问题后重新生成并复核</x:v>
+      </x:c>
+      <x:c r="F27" s="216" t="str">
+        <x:v>结构通过；人工复核退回；2项P0、5项P1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R9d1a02bf73544995"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R2fc349c833cf41b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R6b3f9b53ee9c4f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R66e1da3dfaeb4c6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R807225bbfc4f4e91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R10d90fbadc204f23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rceefc970a637454c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Re25d45858b38408b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1d2ebce984d4522"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R877fa5fed0fb470d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.34</x:v>
+        <x:v>0.35294117647058826</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：首个导入包人工复核已经完成
-总体状态：结构校验通过，但人工复核退回修正；发现2项P0和5项P1
-本次整理：主要问题是研究结论对象误连、基础实体类型错误及平台显示元数据缺失</x:v>
+        <x:v>当前阶段：首个平台导入包修正与第二轮人工复核已经完成
+总体状态：2项P0和5项P1全部关闭；自动校验0错误、0警告
+本次整理：新增道路网络实体，修正结论指向、实体类型、审核依赖和平台显示元数据</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 修正10条研究结论的指向对象。
-2. 修正宫城、皇城、龙首池的实体类型。
-3. 统一审核依赖并修正日期、页码、中文标签和科普直接证据元数据。</x:v>
+        <x:v>1. 确认测试数据库及青瓷演示数据的回退方式。
+2. 将修正后的导入包写入测试数据库。
+3. 核对数量、搜索、图谱关系、证据回溯和科普内容显示。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>人工复核提醒：当前导入包不得进入测试数据库。原始Excel和平台数据库均未修改；修正后必须重新生成并复核。</x:v>
+        <x:v>安全提醒：人工复核已经通过，但尚未写入平台数据库。首次导入只在测试环境进行，验证通过前不替换正式演示数据。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb07f65290c554cf3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb69246f953d94699"/>
 </x:worksheet>
 </file>
 
@@ -3241,6 +3241,44 @@
       </x:c>
       <x:c r="L53" s="216" t="str">
         <x:v>人工复核退回：2项P0、5项P1；尚未导入数据库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="40" customHeight="1">
+      <x:c r="A54" s="216" t="str">
+        <x:v>S6-09</x:v>
+      </x:c>
+      <x:c r="B54" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C54" s="216" t="str">
+        <x:v>修正人工复核问题并完成第二轮复核</x:v>
+      </x:c>
+      <x:c r="D54" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E54" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F54" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G54" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="H54" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="I54" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="J54" s="216" t="str">
+        <x:v>确认测试环境后执行首次数据库导入</x:v>
+      </x:c>
+      <x:c r="K54" s="216" t="str">
+        <x:v>小型样例v2 / 人工复核报告v2</x:v>
+      </x:c>
+      <x:c r="L54" s="216" t="str">
+        <x:v>MR-001—MR-007全部关闭；0错误、0警告；允许测试导入</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4020,6 +4058,26 @@
         <x:v>结构通过；人工复核退回；2项P0、5项P1</x:v>
       </x:c>
     </x:row>
+    <x:row r="28" ht="40" customHeight="1">
+      <x:c r="A28" s="217" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="B28" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C28" s="216" t="str">
+        <x:v>关闭7项人工复核问题并通过第二轮复核</x:v>
+      </x:c>
+      <x:c r="D28" s="216" t="str">
+        <x:v>小型样例v2 / 转换程序 / 数据契约 / 导入包 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E28" s="216" t="str">
+        <x:v>在测试数据库执行首次导入</x:v>
+      </x:c>
+      <x:c r="F28" s="216" t="str">
+        <x:v>新增RoadNetwork；6条原文片段标记审核通过；0错误、0警告</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R807225bbfc4f4e91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R10d90fbadc204f23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rceefc970a637454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Re25d45858b38408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R737847e2d612432d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Ra061f26ef894456d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Ra402d42a77c1431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rd08cdfa1e38b49f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R877fa5fed0fb470d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9b3a0c5db8904ba6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.35294117647058826</x:v>
+        <x:v>0.36538461538461536</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：首个平台导入包修正与第二轮人工复核已经完成
-总体状态：2项P0和5项P1全部关闭；自动校验0错误、0警告
-本次整理：新增道路网络实体，修正结论指向、实体类型、审核依赖和平台显示元数据</x:v>
+        <x:v>当前阶段：首个平台导入包补充复核已经完成
+总体状态：TC-CHUNK-1102已改连TC-LAYOUT-0005；自动校验0错误、0警告
+本次整理：证据片段、坊内道路宽度规则、研究结论与图谱关系的证据链已经一致</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1420,7 +1420,7 @@
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
         <x:v>1. 确认测试数据库及青瓷演示数据的回退方式。
-2. 将修正后的导入包写入测试数据库。
+2. 使用小型样例v3生成的导入包执行首次测试导入。
 3. 核对数量、搜索、图谱关系、证据回溯和科普内容显示。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>安全提醒：人工复核已经通过，但尚未写入平台数据库。首次导入只在测试环境进行，验证通过前不替换正式演示数据。</x:v>
+        <x:v>当前有效版本：小型样例v3、人工复核报告v3。v1和v2仅用于追踪修改历史；平台数据库仍未写入。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb69246f953d94699"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafcdf6ab9ca24d85"/>
 </x:worksheet>
 </file>
 
@@ -3279,6 +3279,44 @@
       </x:c>
       <x:c r="L54" s="216" t="str">
         <x:v>MR-001—MR-007全部关闭；0错误、0警告；允许测试导入</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="40" customHeight="1">
+      <x:c r="A55" s="216" t="str">
+        <x:v>S6-10</x:v>
+      </x:c>
+      <x:c r="B55" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C55" s="216" t="str">
+        <x:v>修正TC-CHUNK-1102与坊内规则的证据连接</x:v>
+      </x:c>
+      <x:c r="D55" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E55" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F55" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G55" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H55" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I55" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="J55" s="216" t="str">
+        <x:v>确认测试环境后执行首次数据库导入</x:v>
+      </x:c>
+      <x:c r="K55" s="216" t="str">
+        <x:v>小型样例v3 / 人工复核报告v3</x:v>
+      </x:c>
+      <x:c r="L55" s="216" t="str">
+        <x:v>TC-CHUNK-1102改连TC-LAYOUT-0005；证据链复核通过</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4078,6 +4116,26 @@
         <x:v>新增RoadNetwork；6条原文片段标记审核通过；0错误、0警告</x:v>
       </x:c>
     </x:row>
+    <x:row r="29" ht="40" customHeight="1">
+      <x:c r="A29" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B29" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C29" s="216" t="str">
+        <x:v>修正TC-CHUNK-1102证据对象并完成补充复核</x:v>
+      </x:c>
+      <x:c r="D29" s="216" t="str">
+        <x:v>小型样例v3 / 导入包 / 人工复核报告v3 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E29" s="216" t="str">
+        <x:v>在测试数据库执行首次导入</x:v>
+      </x:c>
+      <x:c r="F29" s="216" t="str">
+        <x:v>改连TC-LAYOUT-0005；0错误、0警告</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R737847e2d612432d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Ra061f26ef894456d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Ra402d42a77c1431d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rd08cdfa1e38b49f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rcf5b427d35fc4263"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rf71a9ddbf2a84a83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R3419842a54334f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Reb4aacb815da45b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9b3a0c5db8904ba6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10eda2ccb6d84518"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.36538461538461536</x:v>
+        <x:v>0.37735849056603776</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：首个平台导入包补充复核已经完成
-总体状态：TC-CHUNK-1102已改连TC-LAYOUT-0005；自动校验0错误、0警告
-本次整理：证据片段、坊内道路宽度规则、研究结论与图谱关系的证据链已经一致</x:v>
+        <x:v>当前阶段：首个唐长安测试数据库导入已经通过
+总体状态：独立测试库6来源、29片段、48实体、32关系；0重复编号
+本次整理：修复旧平台页码和校订状态兼容；原青瓷演示库数量完全不变</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 确认测试数据库及青瓷演示数据的回退方式。
-2. 使用小型样例v3生成的导入包执行首次测试导入。
-3. 核对数量、搜索、图谱关系、证据回溯和科普内容显示。</x:v>
+        <x:v>1. 启动连接唐长安测试库的API服务。
+2. 在管理端核对实体、关系、来源和审核状态。
+3. 检查证据卡片、图谱关系及科普内容后台展示。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>当前有效版本：小型样例v3、人工复核报告v3。v1和v2仅用于追踪修改历史；平台数据库仍未写入。</x:v>
+        <x:v>测试提醒：公众搜索当前为0条是正确结果，因为本批数据尚未发布。测试容器暂时保留，正式发布前不得自动改为published。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafcdf6ab9ca24d85"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6985b2d779042a9"/>
 </x:worksheet>
 </file>
 
@@ -3317,6 +3317,44 @@
       </x:c>
       <x:c r="L55" s="216" t="str">
         <x:v>TC-CHUNK-1102改连TC-LAYOUT-0005；证据链复核通过</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="40" customHeight="1">
+      <x:c r="A56" s="216" t="str">
+        <x:v>S6-11</x:v>
+      </x:c>
+      <x:c r="B56" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C56" s="216" t="str">
+        <x:v>完成首个唐长安测试数据库导入与验收</x:v>
+      </x:c>
+      <x:c r="D56" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E56" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F56" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G56" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H56" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I56" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="J56" s="216" t="str">
+        <x:v>启动测试API与页面，检查管理端和证据展示</x:v>
+      </x:c>
+      <x:c r="K56" s="216" t="str">
+        <x:v>首次测试导入报告v1 / 旧平台兼容包v1</x:v>
+      </x:c>
+      <x:c r="L56" s="216" t="str">
+        <x:v>独立测试库6来源/29片段/48实体/32关系；0重复；原青瓷库未变化</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4136,6 +4174,26 @@
         <x:v>改连TC-LAYOUT-0005；0错误、0警告</x:v>
       </x:c>
     </x:row>
+    <x:row r="30" ht="40" customHeight="1">
+      <x:c r="A30" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B30" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C30" s="216" t="str">
+        <x:v>完成隔离测试环境、首次导入和数据库/图谱/检索验收</x:v>
+      </x:c>
+      <x:c r="D30" s="216" t="str">
+        <x:v>测试数据库 / 兼容转换脚本 / 导入报告 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E30" s="216" t="str">
+        <x:v>启动测试API与页面进行界面验收</x:v>
+      </x:c>
+      <x:c r="F30" s="216" t="str">
+        <x:v>重复导入幂等；未发布数据不进入公众搜索；青瓷库未变化</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rcf5b427d35fc4263"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rf71a9ddbf2a84a83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R3419842a54334f0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Reb4aacb815da45b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R8a6fed614c344454"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R5fc512fe6a9d41cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R9f592f3fb43843f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rfd07cf2577f34eee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10eda2ccb6d84518"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9efd77285da24045"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.37735849056603776</x:v>
+        <x:v>0.3888888888888889</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：首个唐长安测试数据库导入已经通过
-总体状态：独立测试库6来源、29片段、48实体、32关系；0重复编号
-本次整理：修复旧平台页码和校订状态兼容；原青瓷演示库数量完全不变</x:v>
+        <x:v>当前阶段：唐长安隔离测试平台已经启动，管理端页面验收通过
+总体状态：页面正确显示48实体、32关系、6来源；五项基础服务全部正常
+本次发现：公众前台仍保留青瓷品牌与固定演示数字；一条来源显示0个片段</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 启动连接唐长安测试库的API服务。
-2. 在管理端核对实体、关系、来源和审核状态。
-3. 检查证据卡片、图谱关系及科普内容后台展示。</x:v>
+        <x:v>1. 将前端品牌、首页文案和专属模块改为隋唐长安城。
+2. 将首页统计改为实时读取当前数据库。
+3. 确认两条《唐两京城坊考》的合并或版本规则。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>测试提醒：公众搜索当前为0条是正确结果，因为本批数据尚未发布。测试容器暂时保留，正式发布前不得自动改为published。</x:v>
+        <x:v>测试入口：http://127.0.0.1:18081/。管理端已接入唐长安测试库；尚未发布任何数据，因此公众搜索和公众图谱为空是正确结果。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6985b2d779042a9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4135669f8db4f46"/>
 </x:worksheet>
 </file>
 
@@ -3355,6 +3355,44 @@
       </x:c>
       <x:c r="L56" s="216" t="str">
         <x:v>独立测试库6来源/29片段/48实体/32关系；0重复；原青瓷库未变化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="40" customHeight="1">
+      <x:c r="A57" s="216" t="str">
+        <x:v>S6-12</x:v>
+      </x:c>
+      <x:c r="B57" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C57" s="216" t="str">
+        <x:v>启动唐长安隔离测试平台并完成功能页面验收</x:v>
+      </x:c>
+      <x:c r="D57" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E57" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F57" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G57" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H57" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I57" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="J57" s="216" t="str">
+        <x:v>改造公众前台品牌、首页统计和长安城专题入口</x:v>
+      </x:c>
+      <x:c r="K57" s="216" t="str">
+        <x:v>平台页面验收报告v1 / 唐长安测试平台</x:v>
+      </x:c>
+      <x:c r="L57" s="216" t="str">
+        <x:v>API与管理端通过；48实体/32关系/6来源；前台仍需迁移</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4194,6 +4232,26 @@
         <x:v>重复导入幂等；未发布数据不进入公众搜索；青瓷库未变化</x:v>
       </x:c>
     </x:row>
+    <x:row r="31" ht="40" customHeight="1">
+      <x:c r="A31" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B31" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C31" s="216" t="str">
+        <x:v>启动唐长安隔离测试平台并完成管理端页面验收</x:v>
+      </x:c>
+      <x:c r="D31" s="216" t="str">
+        <x:v>测试API / 测试网页 / 页面验收报告 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E31" s="216" t="str">
+        <x:v>迁移前端品牌和首页数据逻辑</x:v>
+      </x:c>
+      <x:c r="F31" s="216" t="str">
+        <x:v>管理端数据正确；前台仍是青瓷主题；来源题名待去重判断</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R8a6fed614c344454"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R5fc512fe6a9d41cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R9f592f3fb43843f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rfd07cf2577f34eee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R059df3bf32764b71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R2fefb8022d1f4b37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R2d2d654fdb4d4d28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R2825cf4edca843c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9efd77285da24045"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R73e517b784c2480d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.3888888888888889</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：唐长安隔离测试平台已经启动，管理端页面验收通过
-总体状态：页面正确显示48实体、32关系、6来源；五项基础服务全部正常
-本次发现：公众前台仍保留青瓷品牌与固定演示数字；一条来源显示0个片段</x:v>
+        <x:v>当前阶段：唐长安前端第一轮换壳与实时统计已经通过验收
+总体状态：首页实时显示48实体、32关系、6来源、29片段；公众数据仍为0
+本次完成：全局品牌、搜索示例、AI提示词、API名称及公开图谱安全降级已迁移</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 将前端品牌、首页文案和专属模块改为隋唐长安城。
-2. 将首页统计改为实时读取当前数据库。
-3. 确认两条《唐两京城坊考》的合并或版本规则。</x:v>
+        <x:v>1. 确定首次测试发布的小型实体—关系—证据闭环。
+2. 明确审核通过到正式公开发布的操作规则。
+3. 测试公众搜索、图谱关系和证据卡片。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>测试入口：http://127.0.0.1:18081/。管理端已接入唐长安测试库；尚未发布任何数据，因此公众搜索和公众图谱为空是正确结果。</x:v>
+        <x:v>测试入口：http://127.0.0.1:18081/。首页统计已实时连接唐长安库；目前未发布数据，所以公众搜索与图谱保持为空。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4135669f8db4f46"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bd6fca87c9842d2"/>
 </x:worksheet>
 </file>
 
@@ -3393,6 +3393,44 @@
       </x:c>
       <x:c r="L57" s="216" t="str">
         <x:v>API与管理端通过；48实体/32关系/6来源；前台仍需迁移</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="40" customHeight="1">
+      <x:c r="A58" s="216" t="str">
+        <x:v>S6-13</x:v>
+      </x:c>
+      <x:c r="B58" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C58" s="216" t="str">
+        <x:v>完成唐长安前端第一轮换壳与实时统计改造</x:v>
+      </x:c>
+      <x:c r="D58" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E58" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F58" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G58" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H58" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I58" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="J58" s="216" t="str">
+        <x:v>设计并执行首批小型测试发布</x:v>
+      </x:c>
+      <x:c r="K58" s="216" t="str">
+        <x:v>前端换壳与实时统计验收报告v1 / 平台提交3a4b019</x:v>
+      </x:c>
+      <x:c r="L58" s="216" t="str">
+        <x:v>品牌与数据统计迁移通过；公开端仍严格限制published+public</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4252,6 +4290,26 @@
         <x:v>管理端数据正确；前台仍是青瓷主题；来源题名待去重判断</x:v>
       </x:c>
     </x:row>
+    <x:row r="32" ht="40" customHeight="1">
+      <x:c r="A32" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B32" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C32" s="216" t="str">
+        <x:v>完成唐长安前端换壳、实时统计和公开数据安全验收</x:v>
+      </x:c>
+      <x:c r="D32" s="216" t="str">
+        <x:v>平台前端 / API / 验收报告 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E32" s="216" t="str">
+        <x:v>选定并执行首次小型测试发布</x:v>
+      </x:c>
+      <x:c r="F32" s="216" t="str">
+        <x:v>48/32/6/29实时一致；7项测试通过；未发布数据未公开</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R059df3bf32764b71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R2fefb8022d1f4b37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R2d2d654fdb4d4d28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R2825cf4edca843c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Ra3857f1e6d474fdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rb3a1bf5aa97a42fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R1bbb8b759e8f4a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R9ba1b57dfc8644b8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R73e517b784c2480d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb9419decc0ae4c5f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.4</x:v>
+        <x:v>0.40350877192982454</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：唐长安前端第一轮换壳与实时统计已经通过验收
-总体状态：首页实时显示48实体、32关系、6来源、29片段；公众数据仍为0
-本次完成：全局品牌、搜索示例、AI提示词、API名称及公开图谱安全降级已迁移</x:v>
+        <x:v>当前阶段：首次小型闭环发布已完成人工审核
+总体状态：2实体、1关系、1来源、2片段已公开；图谱连接与公众呈现审核通过
+本次确认：研究解释 → 阐释 → 平面规则的方向和内容正确</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 确定首次测试发布的小型实体—关系—证据闭环。
-2. 明确审核通过到正式公开发布的操作规则。
-3. 测试公众搜索、图谱关系和证据卡片。</x:v>
+        <x:v>1. 人工审核第二批4个候选闭环。
+2. 确认“细化/阐释”关系类型及两条推测性措辞。
+3. 审核通过后执行第二批发布，不自动扩大公开范围。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>测试入口：http://127.0.0.1:18081/。首页统计已实时连接唐长安库；目前未发布数据，所以公众搜索与图谱保持为空。</x:v>
+        <x:v>第二批候选：4个闭环，共8实体、4关系、4片段；全部来自已经公开的同一来源。依赖检查通过，尚未发布，等待人工确认。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bd6fca87c9842d2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d7790592ab24777"/>
 </x:worksheet>
 </file>
 
@@ -3431,6 +3431,80 @@
       </x:c>
       <x:c r="L58" s="216" t="str">
         <x:v>品牌与数据统计迁移通过；公开端仍严格限制published+public</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="44" customHeight="1">
+      <x:c r="A59" s="216" t="str">
+        <x:v>S6-14</x:v>
+      </x:c>
+      <x:c r="B59" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C59" s="216" t="str">
+        <x:v>完成首次小型闭环测试发布与公众端验收</x:v>
+      </x:c>
+      <x:c r="D59" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E59" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F59" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G59" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H59" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I59" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="J59" s="216" t="str">
+        <x:v>人工审核公众搜索、图谱和证据卡片展示，再确定第二批发布范围</x:v>
+      </x:c>
+      <x:c r="K59" s="216" t="str">
+        <x:v>首次小型测试发布报告v1 / 发布版本v1</x:v>
+      </x:c>
+      <x:c r="L59" s="216" t="str">
+        <x:v>2实体/1关系/1来源/2片段；检索4文档；依赖校验与回滚快照通过</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="44" customHeight="1">
+      <x:c r="A60" s="216" t="str">
+        <x:v>S6-15</x:v>
+      </x:c>
+      <x:c r="B60" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C60" s="216" t="str">
+        <x:v>完成首次小型发布人工审核并启动第二批候选筛选</x:v>
+      </x:c>
+      <x:c r="D60" s="216" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="E60" s="216" t="str">
+        <x:v>待审核</x:v>
+      </x:c>
+      <x:c r="F60" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G60" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H60" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I60" s="217"/>
+      <x:c r="J60" s="216" t="str">
+        <x:v>人工审核第二批4个候选闭环，确认关系类型和推测性措辞</x:v>
+      </x:c>
+      <x:c r="K60" s="216" t="str">
+        <x:v>首次发布人工审核记录 / 第二批平台发布候选清单v1</x:v>
+      </x:c>
+      <x:c r="L60" s="216" t="str">
+        <x:v>候选为8实体/4关系/4片段；依赖检查通过，等待人工确认</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4310,6 +4384,66 @@
         <x:v>48/32/6/29实时一致；7项测试通过；未发布数据未公开</x:v>
       </x:c>
     </x:row>
+    <x:row r="33" ht="44" customHeight="1">
+      <x:c r="A33" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B33" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C33" s="216" t="str">
+        <x:v>完成选择性发布、依赖保护、公开图谱与检索同步及证据回溯验收</x:v>
+      </x:c>
+      <x:c r="D33" s="216" t="str">
+        <x:v>隔离测试平台 / 首次小型测试发布报告 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E33" s="216" t="str">
+        <x:v>人工复核公众呈现并确定第二批发布范围</x:v>
+      </x:c>
+      <x:c r="F33" s="216" t="str">
+        <x:v>发布v1：2实体、1关系、1来源、2片段；4个检索文档；其余记录未变</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="44" customHeight="1">
+      <x:c r="A34" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B34" s="216" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="C34" s="216" t="str">
+        <x:v>首次小型发布人工审核通过，图谱连接与公众呈现确认无误</x:v>
+      </x:c>
+      <x:c r="D34" s="216" t="str">
+        <x:v>公众检索 / 知识图谱 / 发布报告 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E34" s="216" t="str">
+        <x:v>筛选第二批可发布的证据闭环</x:v>
+      </x:c>
+      <x:c r="F34" s="216" t="str">
+        <x:v>继续保持先审核、后发布；本次未新增公开记录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="44" customHeight="1">
+      <x:c r="A35" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B35" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C35" s="216" t="str">
+        <x:v>完成第二批4个候选闭环筛选与依赖核对</x:v>
+      </x:c>
+      <x:c r="D35" s="216" t="str">
+        <x:v>隔离测试数据库 / 第二批平台发布候选清单v1 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E35" s="216" t="str">
+        <x:v>人工确认4个闭环后执行第二批发布</x:v>
+      </x:c>
+      <x:c r="F35" s="216" t="str">
+        <x:v>8实体、4关系、4片段；同一已公开来源；尚未新增公开记录</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Ra3857f1e6d474fdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rb3a1bf5aa97a42fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R1bbb8b759e8f4a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R9ba1b57dfc8644b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R138f7abfcb8c4ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rcfb4a26da23949f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rfdfd03cfdd964d20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R9aea17466fa84f1a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb9419decc0ae4c5f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R273556cc333f4bde"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.40350877192982454</x:v>
+        <x:v>0.41379310344827586</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：首次小型闭环发布已完成人工审核
-总体状态：2实体、1关系、1来源、2片段已公开；图谱连接与公众呈现审核通过
-本次确认：研究解释 → 阐释 → 平面规则的方向和内容正确</x:v>
+        <x:v>当前阶段：第二批坊内道路规则已经正式发布
+总体状态：公开10实体、5关系、1来源、6片段；检索索引16文档
+本次完成：4个新闭环发布、图谱与证据验收、检索摘要自然语言化</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工审核第二批4个候选闭环。
-2. 确认“细化/阐释”关系类型及两条推测性措辞。
-3. 审核通过后执行第二批发布，不自动扩大公开范围。</x:v>
+        <x:v>1. 人工抽查第二批4个新图谱闭环。
+2. 确认后结束小型试发阶段。
+3. 确定正式迁移优先级并分批审核其余数据。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>第二批候选：4个闭环，共8实体、4关系、4片段；全部来自已经公开的同一来源。依赖检查通过，尚未发布，等待人工确认。</x:v>
+        <x:v>第二批发布v2：8实体、4关系、4片段；与首批合计公开10实体、5关系、1来源、6片段。其他38实体、27关系、5来源、23片段仍待审核。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d7790592ab24777"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a7eee83c26442f2"/>
 </x:worksheet>
 </file>
 
@@ -3485,7 +3485,7 @@
         <x:v>用户 / Codex</x:v>
       </x:c>
       <x:c r="E60" s="216" t="str">
-        <x:v>待审核</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F60" s="216" t="str">
         <x:v>P0</x:v>
@@ -3496,15 +3496,53 @@
       <x:c r="H60" s="217" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="I60" s="217"/>
+      <x:c r="I60" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
       <x:c r="J60" s="216" t="str">
-        <x:v>人工审核第二批4个候选闭环，确认关系类型和推测性措辞</x:v>
+        <x:v>人工抽查第二批公众图谱，再确定正式迁移优先级</x:v>
       </x:c>
       <x:c r="K60" s="216" t="str">
-        <x:v>首次发布人工审核记录 / 第二批平台发布候选清单v1</x:v>
+        <x:v>第二批平台发布报告v1 / 发布版本v2</x:v>
       </x:c>
       <x:c r="L60" s="216" t="str">
-        <x:v>候选为8实体/4关系/4片段；依赖检查通过，等待人工确认</x:v>
+        <x:v>发布8实体/4关系/4片段；公众总量10实体/5关系/1来源/6片段</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="44" customHeight="1">
+      <x:c r="A61" s="216" t="str">
+        <x:v>S6-16</x:v>
+      </x:c>
+      <x:c r="B61" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C61" s="216" t="str">
+        <x:v>人工抽查第二批发布并确定正式迁移优先级</x:v>
+      </x:c>
+      <x:c r="D61" s="216" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="E61" s="216" t="str">
+        <x:v>待审核</x:v>
+      </x:c>
+      <x:c r="F61" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G61" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H61" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I61" s="217"/>
+      <x:c r="J61" s="216" t="str">
+        <x:v>抽查4个新闭环；选择先迁移空间基础事实或先审核研究解释</x:v>
+      </x:c>
+      <x:c r="K61" s="216" t="str">
+        <x:v>第二批公众页面审核记录 / 正式迁移批次方案</x:v>
+      </x:c>
+      <x:c r="L61" s="216" t="str">
+        <x:v>小型试发技术链路已经连续两批通过</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4444,6 +4482,26 @@
         <x:v>8实体、4关系、4片段；同一已公开来源；尚未新增公开记录</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" ht="44" customHeight="1">
+      <x:c r="A36" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B36" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C36" s="216" t="str">
+        <x:v>完成第二批4个坊内道路规则闭环发布与公众端验收</x:v>
+      </x:c>
+      <x:c r="D36" s="216" t="str">
+        <x:v>发布版本v2 / 公开图谱 / 检索索引 / 第二批平台发布报告v1</x:v>
+      </x:c>
+      <x:c r="E36" s="216" t="str">
+        <x:v>人工抽查后确定正式迁移优先级</x:v>
+      </x:c>
+      <x:c r="F36" s="216" t="str">
+        <x:v>8实体、4关系、4片段发布；索引摘要改为自然语言；其余数据未变</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R138f7abfcb8c4ac7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rcfb4a26da23949f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rfdfd03cfdd964d20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R9aea17466fa84f1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R096725a30d5b4387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R7a2dd8eea54d409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R0eba975b99ef403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R87bb7353572e4a45"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R273556cc333f4bde"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R43db269fdc1c4456"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1234,7 +1234,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-11</x:v>
+        <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-12</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.41379310344827586</x:v>
+        <x:v>0.423728813559322</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：第二批坊内道路规则已经正式发布
-总体状态：公开10实体、5关系、1来源、6片段；检索索引16文档
-本次完成：4个新闭环发布、图谱与证据验收、检索摘要自然语言化</x:v>
+        <x:v>当前阶段：小型样例的实体表、关系表已经完成同步
+总体状态：实体表48条、关系表32条，与平台导入包一致
+本次完成：补写25个专题生成实体、22条专题生成关系；转换程序增加去重规则</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,8 +1419,8 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工抽查第二批4个新图谱闭环。
-2. 确认后结束小型试发阶段。
+        <x:v>1. 人工抽查v4新增的实体和关系。
+2. 后续专题表更新后，统一重新生成实体表和关系表。
 3. 确定正式迁移优先级并分批审核其余数据。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>第二批发布v2：8实体、4关系、4片段；与首批合计公开10实体、5关系、1来源、6片段。其他38实体、27关系、5来源、23片段仍待审核。</x:v>
+        <x:v>v1—v3保留为历史版本；v4是当前小型样例工作版本。实体表和关系表是由专题表汇总生成的通用核查输出，后续不需要与专题表重复手工维护。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a7eee83c26442f2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5225469494704ba3"/>
 </x:worksheet>
 </file>
 
@@ -3543,6 +3543,44 @@
       </x:c>
       <x:c r="L61" s="216" t="str">
         <x:v>小型试发技术链路已经连续两批通过</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="48" customHeight="1">
+      <x:c r="A62" s="216" t="str">
+        <x:v>S6-17</x:v>
+      </x:c>
+      <x:c r="B62" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C62" s="216" t="str">
+        <x:v>同步小型样例实体表与关系表，并修复转换去重</x:v>
+      </x:c>
+      <x:c r="D62" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E62" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F62" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G62" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H62" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I62" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="J62" s="216" t="str">
+        <x:v>人工抽查v4；后续以v4作为小型样例唯一工作版本</x:v>
+      </x:c>
+      <x:c r="K62" s="216" t="str">
+        <x:v>小型样例v4 / 转换程序去重修复</x:v>
+      </x:c>
+      <x:c r="L62" s="216" t="str">
+        <x:v>实体表23→48，关系表10→32；重新转换0错误、0警告、0重复</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4502,6 +4540,26 @@
         <x:v>8实体、4关系、4片段发布；索引摘要改为自然语言；其余数据未变</x:v>
       </x:c>
     </x:row>
+    <x:row r="37" ht="44" customHeight="1">
+      <x:c r="A37" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B37" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C37" s="216" t="str">
+        <x:v>同步小型样例的实体表与关系表</x:v>
+      </x:c>
+      <x:c r="D37" s="216" t="str">
+        <x:v>小型样例v4 / 转换程序</x:v>
+      </x:c>
+      <x:c r="E37" s="216" t="str">
+        <x:v>人工抽查v4新增记录</x:v>
+      </x:c>
+      <x:c r="F37" s="216" t="str">
+        <x:v>补写25实体、22关系；转换验证为48实体、32关系、0错误、0警告</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R096725a30d5b4387"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R7a2dd8eea54d409e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R0eba975b99ef403d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R87bb7353572e4a45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rf90e4837e68348dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R95edab6afa0c45ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R7abf1ccd6441410c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R4dc1dcce837e43c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R43db269fdc1c4456"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R66bd8c2439c74d87"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.423728813559322</x:v>
+        <x:v>0.43333333333333335</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：小型样例的实体表、关系表已经完成同步
-总体状态：实体表48条、关系表32条，与平台导入包一致
-本次完成：补写25个专题生成实体、22条专题生成关系；转换程序增加去重规则</x:v>
+        <x:v>当前阶段：小型样例专题关系反向审计与修正完成
+总体状态：实体表48条、关系表43条；专题关系转换已自动化
+本次完成：补写11条可靠关系；示例和待补数据由程序主动阻断</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,8 +1419,8 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工抽查v4新增的实体和关系。
-2. 后续专题表更新后，统一重新生成实体表和关系表。
+        <x:v>1. 人工抽查v5新增的11条关系。
+2. 补齐平康坊示例、永安渠六坊编号和外郭城区域编号。
 3. 确定正式迁移优先级并分批审核其余数据。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>v1—v3保留为历史版本；v4是当前小型样例工作版本。实体表和关系表是由专题表汇总生成的通用核查输出，后续不需要与专题表重复手工维护。</x:v>
+        <x:v>v5是当前小型样例工作版本。重新转换结果：48实体、43关系、0错误；11条警告均为示例行、待补编号或无效证据片段，已阻断进入导入包。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5225469494704ba3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc89b68618bdc4155"/>
 </x:worksheet>
 </file>
 
@@ -3581,6 +3581,44 @@
       </x:c>
       <x:c r="L62" s="216" t="str">
         <x:v>实体表23→48，关系表10→32；重新转换0错误、0警告、0重复</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="48" customHeight="1">
+      <x:c r="A63" s="216" t="str">
+        <x:v>S6-18</x:v>
+      </x:c>
+      <x:c r="B63" s="216" t="str">
+        <x:v>阶段六：平台迁移</x:v>
+      </x:c>
+      <x:c r="C63" s="216" t="str">
+        <x:v>补齐专题表遗漏关系并完善自动转换阻断</x:v>
+      </x:c>
+      <x:c r="D63" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E63" s="216" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F63" s="216" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G63" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H63" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I63" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="J63" s="216" t="str">
+        <x:v>人工抽查v5新增11条关系</x:v>
+      </x:c>
+      <x:c r="K63" s="216" t="str">
+        <x:v>小型样例v5 / 专题关系自动转换</x:v>
+      </x:c>
+      <x:c r="L63" s="216" t="str">
+        <x:v>关系表32→43；转换0错误；11条不完整记录被主动阻断</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4560,6 +4598,26 @@
         <x:v>补写25实体、22关系；转换验证为48实体、32关系、0错误、0警告</x:v>
       </x:c>
     </x:row>
+    <x:row r="38" ht="44" customHeight="1">
+      <x:c r="A38" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="B38" s="216" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C38" s="216" t="str">
+        <x:v>完成专题关系反向审计、补写与转换程序修正</x:v>
+      </x:c>
+      <x:c r="D38" s="216" t="str">
+        <x:v>小型样例v5 / 转换程序 / 校验报告</x:v>
+      </x:c>
+      <x:c r="E38" s="216" t="str">
+        <x:v>人工抽查11条新增关系</x:v>
+      </x:c>
+      <x:c r="F38" s="216" t="str">
+        <x:v>补写11关系；48实体、43关系；0错误；11条不完整记录阻断警告</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rf90e4837e68348dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R95edab6afa0c45ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R7abf1ccd6441410c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R4dc1dcce837e43c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R73b6b4f1b0524fd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R789a1de2057c4be2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R63311772b39d4a83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R44f870a4466746c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -998,7 +998,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R66bd8c2439c74d87"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R869f4847c1cd4cfd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1282,19 +1282,19 @@
       </x:c>
       <x:c r="O5" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="40" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B6" s="41"/>
       <x:c r="C6" s="42"/>
       <x:c r="D6" s="68" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E6" s="69"/>
       <x:c r="F6" s="70"/>
@@ -1306,7 +1306,7 @@
       <x:c r="I6" s="98"/>
       <x:c r="J6" s="133" t="n">
         <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.43333333333333335</x:v>
+        <x:v>0.4918032786885246</x:v>
       </x:c>
       <x:c r="K6" s="134"/>
       <x:c r="L6" s="135"/>
@@ -1366,7 +1366,7 @@
       </x:c>
       <x:c r="O9" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$100,N9)</x:f>
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1381,9 +1381,9 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：小型样例专题关系反向审计与修正完成
-总体状态：实体表48条、关系表43条；专题关系转换已自动化
-本次完成：补写11条可靠关系；示例和待补数据由程序主动阻断</x:v>
+        <x:v>当前阶段：第三批空间基础事实已正式发布并通过网页验收
+总体状态：数据库48实体、43关系、6来源、29片段；公开21实体、16关系、2来源、12片段
+本次完成：11条专题关系、11个端点实体及6条证据片段进入发布版本v3，索引同步完成</x:v>
       </x:c>
       <x:c r="B11" s="153"/>
       <x:c r="C11" s="153"/>
@@ -1419,9 +1419,9 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="170" t="str">
-        <x:v>1. 人工抽查v5新增的11条关系。
-2. 补齐平康坊示例、永安渠六坊编号和外郭城区域编号。
-3. 确定正式迁移优先级并分批审核其余数据。</x:v>
+        <x:v>1. 补齐外郭城区域编号、永安渠所经六坊编号和平康坊演示数据。
+2. 用v6及三批验收经验升级knowledge-graph-extraction Skill。
+3. 按“基础事实→研究解释”的顺序开始正式全量迁移。</x:v>
       </x:c>
       <x:c r="B16" s="171"/>
       <x:c r="C16" s="171"/>
@@ -1465,7 +1465,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="196" t="str">
-        <x:v>v5是当前小型样例工作版本。重新转换结果：48实体、43关系、0错误；11条警告均为示例行、待补编号或无效证据片段，已阻断进入导入包。</x:v>
+        <x:v>v6是当前小型样例工作版本；平台导入包v2为当前导入基线。第三批发布v3已完成，公开检索与图谱均可见。尚未补齐的示例行、外郭城编号和永安渠六坊编号继续被转换程序阻断，不会误入平台。</x:v>
       </x:c>
       <x:c r="B22" s="197"/>
       <x:c r="C22" s="197"/>
@@ -1509,7 +1509,7 @@
     <x:mergeCell ref="A22:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc89b68618bdc4155"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R465a05d707bb4b27"/>
 </x:worksheet>
 </file>
 
@@ -2165,357 +2165,369 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="16" t="str">
-        <x:v>S3-01</x:v>
+        <x:v>S2-13</x:v>
       </x:c>
       <x:c r="B20" s="16" t="str">
-        <x:v>阶段三：文献建设</x:v>
+        <x:v>阶段二：字段规范</x:v>
       </x:c>
       <x:c r="C20" s="16" t="str">
-        <x:v>盘点现有文献并分配TC-REF编号</x:v>
+        <x:v>建立坊内平面规则表占位字段</x:v>
       </x:c>
       <x:c r="D20" s="16" t="str">
-        <x:v>我</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E20" s="16" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F20" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="G20" s="17" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
-      <x:c r="H20" s="17"/>
-      <x:c r="I20" s="17"/>
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="H20" s="17" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="I20" s="17" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
       <x:c r="J20" s="16" t="str">
-        <x:v>核对3份现有文献并补齐来源编号</x:v>
-      </x:c>
-      <x:c r="K20" s="16" t="str">
-        <x:v>小型样例文献选择方案v1</x:v>
-      </x:c>
-      <x:c r="L20" s="16" t="str">
-        <x:v>已完成初选，待正式登记来源表</x:v>
-      </x:c>
+        <x:v>用论文样例确认字段</x:v>
+      </x:c>
+      <x:c r="K20" s="16"/>
+      <x:c r="L20" s="16"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="16" t="str">
-        <x:v>S3-02</x:v>
+        <x:v>S2-14</x:v>
       </x:c>
       <x:c r="B21" s="16" t="str">
-        <x:v>阶段三：文献建设</x:v>
+        <x:v>阶段二：字段规范</x:v>
       </x:c>
       <x:c r="C21" s="16" t="str">
-        <x:v>建立专题数据缺失文献需求表</x:v>
+        <x:v>建立研究结论表及转换框架</x:v>
       </x:c>
       <x:c r="D21" s="16" t="str">
-        <x:v>共同</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E21" s="16" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F21" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="G21" s="17" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
-      <x:c r="H21" s="17"/>
-      <x:c r="I21" s="17"/>
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="H21" s="17" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
+      <x:c r="I21" s="17" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
       <x:c r="J21" s="16" t="str">
-        <x:v>确认考古、尺度、水系资料的取得顺序</x:v>
-      </x:c>
-      <x:c r="K21" s="16" t="str">
-        <x:v>初步文献缺口与优先级</x:v>
-      </x:c>
-      <x:c r="L21" s="16" t="str">
-        <x:v>优先取得《隋唐长安城遗址·考古资料编》</x:v>
-      </x:c>
+        <x:v>试录专项研究论文</x:v>
+      </x:c>
+      <x:c r="K21" s="16"/>
+      <x:c r="L21" s="16"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="16" t="str">
-        <x:v>S3-03</x:v>
+        <x:v>S2-15</x:v>
       </x:c>
       <x:c r="B22" s="16" t="str">
-        <x:v>阶段三：文献建设</x:v>
+        <x:v>阶段二：字段规范</x:v>
       </x:c>
       <x:c r="C22" s="16" t="str">
-        <x:v>补充城门、道路、水渠考古资料</x:v>
+        <x:v>根据论文样例确认两张新增表字段</x:v>
       </x:c>
       <x:c r="D22" s="16" t="str">
         <x:v>共同</x:v>
       </x:c>
       <x:c r="E22" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F22" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G22" s="17"/>
+      <x:c r="G22" s="17" t="str">
+        <x:v>2026-08-09</x:v>
+      </x:c>
       <x:c r="H22" s="17"/>
       <x:c r="I22" s="17"/>
       <x:c r="J22" s="16" t="str">
-        <x:v>优先权威考古报告</x:v>
+        <x:v>在小型样例表完成三篇核心论文字段评估，再决定是否转入正式模板</x:v>
       </x:c>
       <x:c r="K22" s="16" t="str">
-        <x:v>新增文献</x:v>
-      </x:c>
-      <x:c r="L22" s="16"/>
+        <x:v>小型样例_第1批_文献片段与基础对象_v1.xlsx</x:v>
+      </x:c>
+      <x:c r="L22" s="16" t="str">
+        <x:v>正式模板恢复为结构与非论文试录数据；论文试录统一在样例表迭代</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="16" t="str">
-        <x:v>S3-04</x:v>
+        <x:v>S3-01</x:v>
       </x:c>
       <x:c r="B23" s="16" t="str">
         <x:v>阶段三：文献建设</x:v>
       </x:c>
       <x:c r="C23" s="16" t="str">
-        <x:v>补充度量衡、复原图和GIS资料</x:v>
+        <x:v>盘点现有文献并分配TC-REF编号</x:v>
       </x:c>
       <x:c r="D23" s="16" t="str">
         <x:v>我</x:v>
       </x:c>
       <x:c r="E23" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F23" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G23" s="17"/>
+      <x:c r="G23" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="H23" s="17"/>
       <x:c r="I23" s="17"/>
       <x:c r="J23" s="16" t="str">
-        <x:v>用于尺度和坐标</x:v>
+        <x:v>核对3份现有文献并补齐来源编号</x:v>
       </x:c>
       <x:c r="K23" s="16" t="str">
-        <x:v>新增文献</x:v>
-      </x:c>
-      <x:c r="L23" s="16"/>
+        <x:v>小型样例文献选择方案v1</x:v>
+      </x:c>
+      <x:c r="L23" s="16" t="str">
+        <x:v>已完成初选，待正式登记来源表</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="16" t="str">
-        <x:v>S3-05</x:v>
+        <x:v>S3-02</x:v>
       </x:c>
       <x:c r="B24" s="16" t="str">
         <x:v>阶段三：文献建设</x:v>
       </x:c>
       <x:c r="C24" s="16" t="str">
-        <x:v>建立文献质量等级A-D</x:v>
+        <x:v>建立专题数据缺失文献需求表</x:v>
       </x:c>
       <x:c r="D24" s="16" t="str">
         <x:v>共同</x:v>
       </x:c>
       <x:c r="E24" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F24" s="16" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G24" s="17"/>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="H24" s="17"/>
       <x:c r="I24" s="17"/>
       <x:c r="J24" s="16" t="str">
-        <x:v>明确可用于坐标和尺度的来源</x:v>
+        <x:v>确认考古、尺度、水系资料的取得顺序</x:v>
       </x:c>
       <x:c r="K24" s="16" t="str">
-        <x:v>质量分级规则</x:v>
-      </x:c>
-      <x:c r="L24" s="16"/>
+        <x:v>初步文献缺口与优先级</x:v>
+      </x:c>
+      <x:c r="L24" s="16" t="str">
+        <x:v>优先取得《隋唐长安城遗址·考古资料编》</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="16" t="str">
-        <x:v>S4-01</x:v>
+        <x:v>S3-03</x:v>
       </x:c>
       <x:c r="B25" s="16" t="str">
-        <x:v>阶段四：小型样例</x:v>
+        <x:v>阶段三：文献建设</x:v>
       </x:c>
       <x:c r="C25" s="16" t="str">
-        <x:v>选择5坊、3道路、2水渠、5城门</x:v>
+        <x:v>补充城门、道路、水渠考古资料</x:v>
       </x:c>
       <x:c r="D25" s="16" t="str">
         <x:v>共同</x:v>
       </x:c>
       <x:c r="E25" s="16" t="str">
-        <x:v>进行中</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F25" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G25" s="17" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
+      <x:c r="G25" s="17"/>
       <x:c r="H25" s="17"/>
       <x:c r="I25" s="17"/>
       <x:c r="J25" s="16" t="str">
-        <x:v>继续补齐5坊样例</x:v>
+        <x:v>优先权威考古报告</x:v>
       </x:c>
       <x:c r="K25" s="16" t="str">
-        <x:v>第一批基础对象已录入</x:v>
+        <x:v>新增文献</x:v>
       </x:c>
       <x:c r="L25" s="16"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="16" t="str">
-        <x:v>S4-02</x:v>
+        <x:v>S3-04</x:v>
       </x:c>
       <x:c r="B26" s="16" t="str">
-        <x:v>阶段四：小型样例</x:v>
+        <x:v>阶段三：文献建设</x:v>
       </x:c>
       <x:c r="C26" s="16" t="str">
-        <x:v>制作3组尺度比较和3条功能规则</x:v>
+        <x:v>补充度量衡、复原图和GIS资料</x:v>
       </x:c>
       <x:c r="D26" s="16" t="str">
         <x:v>我</x:v>
       </x:c>
       <x:c r="E26" s="16" t="str">
-        <x:v>进行中</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F26" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G26" s="17" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
+      <x:c r="G26" s="17"/>
       <x:c r="H26" s="17"/>
       <x:c r="I26" s="17"/>
       <x:c r="J26" s="16" t="str">
-        <x:v>补充2组尺度和2条规则</x:v>
+        <x:v>用于尺度和坐标</x:v>
       </x:c>
       <x:c r="K26" s="16" t="str">
-        <x:v>1组尺度、1条候选规则</x:v>
+        <x:v>新增文献</x:v>
       </x:c>
       <x:c r="L26" s="16"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="16" t="str">
-        <x:v>S4-03</x:v>
+        <x:v>S3-05</x:v>
       </x:c>
       <x:c r="B27" s="16" t="str">
-        <x:v>阶段四：小型样例</x:v>
+        <x:v>阶段三：文献建设</x:v>
       </x:c>
       <x:c r="C27" s="16" t="str">
-        <x:v>完成专题样例表</x:v>
+        <x:v>建立文献质量等级A-D</x:v>
       </x:c>
       <x:c r="D27" s="16" t="str">
         <x:v>共同</x:v>
       </x:c>
       <x:c r="E27" s="16" t="str">
-        <x:v>进行中</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F27" s="16" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G27" s="17" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G27" s="17"/>
       <x:c r="H27" s="17"/>
       <x:c r="I27" s="17"/>
       <x:c r="J27" s="16" t="str">
-        <x:v>继续填写坊功能与坊间空间关系</x:v>
+        <x:v>明确可用于坐标和尺度的来源</x:v>
       </x:c>
       <x:c r="K27" s="16" t="str">
-        <x:v>第1批小样例工作簿</x:v>
+        <x:v>质量分级规则</x:v>
       </x:c>
       <x:c r="L27" s="16"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="16" t="str">
-        <x:v>S4-04</x:v>
+        <x:v>S4-01</x:v>
       </x:c>
       <x:c r="B28" s="16" t="str">
         <x:v>阶段四：小型样例</x:v>
       </x:c>
       <x:c r="C28" s="16" t="str">
-        <x:v>审核编号、来源、单位、坐标和推导</x:v>
+        <x:v>选择5坊、3道路、2水渠、5城门</x:v>
       </x:c>
       <x:c r="D28" s="16" t="str">
         <x:v>共同</x:v>
       </x:c>
       <x:c r="E28" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F28" s="16" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G28" s="17"/>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="H28" s="17"/>
       <x:c r="I28" s="17"/>
       <x:c r="J28" s="16" t="str">
-        <x:v>逐条审核</x:v>
+        <x:v>继续补齐5坊样例</x:v>
       </x:c>
       <x:c r="K28" s="16" t="str">
-        <x:v>样例审核记录</x:v>
+        <x:v>第一批基础对象已录入</x:v>
       </x:c>
       <x:c r="L28" s="16"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="16" t="str">
-        <x:v>S5-01</x:v>
+        <x:v>S4-02</x:v>
       </x:c>
       <x:c r="B29" s="16" t="str">
-        <x:v>阶段五：Skill升级</x:v>
+        <x:v>阶段四：小型样例</x:v>
       </x:c>
       <x:c r="C29" s="16" t="str">
-        <x:v>升级提取Skill支持专题表</x:v>
+        <x:v>制作3组尺度比较和3条功能规则</x:v>
       </x:c>
       <x:c r="D29" s="16" t="str">
-        <x:v>Codex</x:v>
+        <x:v>我</x:v>
       </x:c>
       <x:c r="E29" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F29" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G29" s="17"/>
+      <x:c r="G29" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="H29" s="17"/>
       <x:c r="I29" s="17"/>
       <x:c r="J29" s="16" t="str">
-        <x:v>样例通过后升级</x:v>
+        <x:v>补充2组尺度和2条规则</x:v>
       </x:c>
       <x:c r="K29" s="16" t="str">
-        <x:v>knowledge-graph-extraction v2</x:v>
+        <x:v>1组尺度、1条候选规则</x:v>
       </x:c>
       <x:c r="L29" s="16"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="16" t="str">
-        <x:v>S5-02</x:v>
+        <x:v>S4-03</x:v>
       </x:c>
       <x:c r="B30" s="16" t="str">
-        <x:v>阶段五：Skill升级</x:v>
+        <x:v>阶段四：小型样例</x:v>
       </x:c>
       <x:c r="C30" s="16" t="str">
-        <x:v>加入定量、单位、坐标和规则提取规范</x:v>
+        <x:v>完成专题样例表</x:v>
       </x:c>
       <x:c r="D30" s="16" t="str">
-        <x:v>Codex</x:v>
+        <x:v>共同</x:v>
       </x:c>
       <x:c r="E30" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F30" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G30" s="17"/>
+      <x:c r="G30" s="17" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
       <x:c r="H30" s="17"/>
       <x:c r="I30" s="17"/>
       <x:c r="J30" s="16" t="str">
-        <x:v>与字段规范一致</x:v>
+        <x:v>继续填写坊功能与坊间空间关系</x:v>
       </x:c>
       <x:c r="K30" s="16" t="str">
-        <x:v>提取规范v2</x:v>
+        <x:v>第1批小样例工作簿</x:v>
       </x:c>
       <x:c r="L30" s="16"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="16" t="str">
-        <x:v>S5-03</x:v>
+        <x:v>S4-04</x:v>
       </x:c>
       <x:c r="B31" s="16" t="str">
-        <x:v>阶段五：Skill升级</x:v>
+        <x:v>阶段四：小型样例</x:v>
       </x:c>
       <x:c r="C31" s="16" t="str">
-        <x:v>使用小型样例测试Skill</x:v>
+        <x:v>审核编号、来源、单位、坐标和推导</x:v>
       </x:c>
       <x:c r="D31" s="16" t="str">
         <x:v>共同</x:v>
@@ -2524,60 +2536,62 @@
         <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F31" s="16" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G31" s="17"/>
       <x:c r="H31" s="17"/>
       <x:c r="I31" s="17"/>
       <x:c r="J31" s="16" t="str">
-        <x:v>比较人工审核结果</x:v>
+        <x:v>逐条审核</x:v>
       </x:c>
       <x:c r="K31" s="16" t="str">
-        <x:v>测试报告</x:v>
+        <x:v>样例审核记录</x:v>
       </x:c>
       <x:c r="L31" s="16"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="16" t="str">
-        <x:v>S6-01</x:v>
+        <x:v>S4-05</x:v>
       </x:c>
       <x:c r="B32" s="16" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段四：小型样例</x:v>
       </x:c>
       <x:c r="C32" s="16" t="str">
-        <x:v>清理新平台青瓷模拟数据和文案</x:v>
+        <x:v>试做首条科普内容及证据回溯闭环</x:v>
       </x:c>
       <x:c r="D32" s="16" t="str">
-        <x:v>Codex</x:v>
+        <x:v>共同</x:v>
       </x:c>
       <x:c r="E32" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>等待确认</x:v>
       </x:c>
       <x:c r="F32" s="16" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G32" s="17"/>
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G32" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
       <x:c r="H32" s="17"/>
       <x:c r="I32" s="17"/>
       <x:c r="J32" s="16" t="str">
-        <x:v>唐长安小样例验收后再清理</x:v>
+        <x:v>审核科普文字和7条依据关联</x:v>
       </x:c>
       <x:c r="K32" s="16" t="str">
-        <x:v>唐长安城平台基线</x:v>
+        <x:v>TC-POPULAR-0001及TC-POPLINK-0001—0007</x:v>
       </x:c>
       <x:c r="L32" s="16" t="str">
-        <x:v>清理顺序调整：先导入验证，后删除青瓷演示数据</x:v>
+        <x:v>样例只录入小型样例表，不进入空白正式模板</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="16" t="str">
-        <x:v>S6-02</x:v>
+        <x:v>S5-01</x:v>
       </x:c>
       <x:c r="B33" s="16" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段五：Skill升级</x:v>
       </x:c>
       <x:c r="C33" s="16" t="str">
-        <x:v>更新唐长安城实体与关系Schema</x:v>
+        <x:v>升级提取Skill支持专题表</x:v>
       </x:c>
       <x:c r="D33" s="16" t="str">
         <x:v>Codex</x:v>
@@ -2592,22 +2606,22 @@
       <x:c r="H33" s="17"/>
       <x:c r="I33" s="17"/>
       <x:c r="J33" s="16" t="str">
-        <x:v>依据字段规范</x:v>
+        <x:v>样例通过后升级</x:v>
       </x:c>
       <x:c r="K33" s="16" t="str">
-        <x:v>JSON Schema</x:v>
+        <x:v>knowledge-graph-extraction v2</x:v>
       </x:c>
       <x:c r="L33" s="16"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="16" t="str">
-        <x:v>S6-03</x:v>
+        <x:v>S5-02</x:v>
       </x:c>
       <x:c r="B34" s="16" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段五：Skill升级</x:v>
       </x:c>
       <x:c r="C34" s="16" t="str">
-        <x:v>编写专题表到实体/关系转换脚本</x:v>
+        <x:v>加入定量、单位、坐标和规则提取规范</x:v>
       </x:c>
       <x:c r="D34" s="16" t="str">
         <x:v>Codex</x:v>
@@ -2616,28 +2630,28 @@
         <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F34" s="16" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G34" s="17"/>
       <x:c r="H34" s="17"/>
       <x:c r="I34" s="17"/>
       <x:c r="J34" s="16" t="str">
-        <x:v>先支持小型样例</x:v>
+        <x:v>与字段规范一致</x:v>
       </x:c>
       <x:c r="K34" s="16" t="str">
-        <x:v>转换脚本</x:v>
+        <x:v>提取规范v2</x:v>
       </x:c>
       <x:c r="L34" s="16"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="16" t="str">
-        <x:v>S6-04</x:v>
+        <x:v>S5-03</x:v>
       </x:c>
       <x:c r="B35" s="16" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段五：Skill升级</x:v>
       </x:c>
       <x:c r="C35" s="16" t="str">
-        <x:v>导入样例并验证检索、图谱和AI问答</x:v>
+        <x:v>使用小型样例测试Skill</x:v>
       </x:c>
       <x:c r="D35" s="16" t="str">
         <x:v>共同</x:v>
@@ -2646,31 +2660,31 @@
         <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F35" s="16" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G35" s="17"/>
       <x:c r="H35" s="17"/>
       <x:c r="I35" s="17"/>
       <x:c r="J35" s="16" t="str">
-        <x:v>逐项验收</x:v>
+        <x:v>比较人工审核结果</x:v>
       </x:c>
       <x:c r="K35" s="16" t="str">
-        <x:v>平台样例验收报告</x:v>
+        <x:v>测试报告</x:v>
       </x:c>
       <x:c r="L35" s="16"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="16" t="str">
-        <x:v>S7-01</x:v>
+        <x:v>S6-01</x:v>
       </x:c>
       <x:c r="B36" s="16" t="str">
-        <x:v>阶段七：全量提取</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C36" s="16" t="str">
-        <x:v>完成108坊功能数据</x:v>
+        <x:v>清理新平台青瓷模拟数据和文案</x:v>
       </x:c>
       <x:c r="D36" s="16" t="str">
-        <x:v>同事</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E36" s="16" t="str">
         <x:v>尚未开始</x:v>
@@ -2682,25 +2696,27 @@
       <x:c r="H36" s="17"/>
       <x:c r="I36" s="17"/>
       <x:c r="J36" s="16" t="str">
-        <x:v>小样例通过后分批提取</x:v>
+        <x:v>唐长安小样例验收后再清理</x:v>
       </x:c>
       <x:c r="K36" s="16" t="str">
-        <x:v>坊功能全量表</x:v>
-      </x:c>
-      <x:c r="L36" s="16"/>
+        <x:v>唐长安城平台基线</x:v>
+      </x:c>
+      <x:c r="L36" s="16" t="str">
+        <x:v>清理顺序调整：先导入验证，后删除青瓷演示数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="16" t="str">
-        <x:v>S7-02</x:v>
+        <x:v>S6-02</x:v>
       </x:c>
       <x:c r="B37" s="16" t="str">
-        <x:v>阶段七：全量提取</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C37" s="16" t="str">
-        <x:v>完成道路分级数据</x:v>
+        <x:v>更新唐长安城实体与关系Schema</x:v>
       </x:c>
       <x:c r="D37" s="16" t="str">
-        <x:v>同事</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E37" s="16" t="str">
         <x:v>尚未开始</x:v>
@@ -2712,262 +2728,326 @@
       <x:c r="H37" s="17"/>
       <x:c r="I37" s="17"/>
       <x:c r="J37" s="16" t="str">
-        <x:v>分批提取与审核</x:v>
+        <x:v>依据字段规范</x:v>
       </x:c>
       <x:c r="K37" s="16" t="str">
-        <x:v>道路全量表</x:v>
+        <x:v>JSON Schema</x:v>
       </x:c>
       <x:c r="L37" s="16"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="16" t="str">
-        <x:v>S7-03</x:v>
+        <x:v>S6-03</x:v>
       </x:c>
       <x:c r="B38" s="16" t="str">
-        <x:v>阶段七：全量提取</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C38" s="16" t="str">
-        <x:v>完成水渠数据</x:v>
+        <x:v>编写专题表到实体/关系转换脚本</x:v>
       </x:c>
       <x:c r="D38" s="16" t="str">
-        <x:v>同事</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E38" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F38" s="16" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G38" s="17"/>
-      <x:c r="H38" s="17"/>
-      <x:c r="I38" s="17"/>
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G38" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="H38" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="I38" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
       <x:c r="J38" s="16" t="str">
-        <x:v>分批提取与审核</x:v>
+        <x:v>转换程序随字段规范和Skill继续维护</x:v>
       </x:c>
       <x:c r="K38" s="16" t="str">
-        <x:v>水渠全量表</x:v>
-      </x:c>
-      <x:c r="L38" s="16"/>
+        <x:v>转换程序 / 平台导入包v2</x:v>
+      </x:c>
+      <x:c r="L38" s="16" t="str">
+        <x:v>默认工作版本已切换为小型样例v6</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="16" t="str">
-        <x:v>S7-04</x:v>
+        <x:v>S6-04</x:v>
       </x:c>
       <x:c r="B39" s="16" t="str">
-        <x:v>阶段七：全量提取</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C39" s="16" t="str">
-        <x:v>完成城门数据</x:v>
+        <x:v>导入样例并验证检索、图谱和AI问答</x:v>
       </x:c>
       <x:c r="D39" s="16" t="str">
-        <x:v>我</x:v>
+        <x:v>共同</x:v>
       </x:c>
       <x:c r="E39" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F39" s="16" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G39" s="17"/>
-      <x:c r="H39" s="17"/>
-      <x:c r="I39" s="17"/>
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G39" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="H39" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="I39" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
       <x:c r="J39" s="16" t="str">
-        <x:v>严格区分城门与内门</x:v>
+        <x:v>继续按审核批次执行正式迁移</x:v>
       </x:c>
       <x:c r="K39" s="16" t="str">
-        <x:v>城门全量表</x:v>
-      </x:c>
-      <x:c r="L39" s="16"/>
+        <x:v>第三批平台发布与网页验收报告v1</x:v>
+      </x:c>
+      <x:c r="L39" s="16" t="str">
+        <x:v>检索、图谱、证据片段和发布依赖均通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="16" t="str">
-        <x:v>S7-05</x:v>
+        <x:v>S6-05</x:v>
       </x:c>
       <x:c r="B40" s="16" t="str">
-        <x:v>阶段七：全量提取</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C40" s="16" t="str">
-        <x:v>完成尺度关系数据</x:v>
+        <x:v>盘点青瓷平台并形成唐长安迁移清单</x:v>
       </x:c>
       <x:c r="D40" s="16" t="str">
-        <x:v>我</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E40" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F40" s="16" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G40" s="17"/>
-      <x:c r="H40" s="17"/>
-      <x:c r="I40" s="17"/>
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G40" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="H40" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="I40" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
       <x:c r="J40" s="16" t="str">
-        <x:v>全部公式人工复核</x:v>
+        <x:v>确定唐长安平台数据契约v1</x:v>
       </x:c>
       <x:c r="K40" s="16" t="str">
-        <x:v>尺度关系全量表</x:v>
-      </x:c>
-      <x:c r="L40" s="16"/>
+        <x:v>唐长安城平台迁移盘点与实施清单_v1.md</x:v>
+      </x:c>
+      <x:c r="L40" s="16" t="str">
+        <x:v>只读检查；未修改平台代码和演示数据</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="16" t="str">
-        <x:v>S7-06</x:v>
+        <x:v>S6-06</x:v>
       </x:c>
       <x:c r="B41" s="16" t="str">
-        <x:v>阶段七：全量提取</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C41" s="16" t="str">
-        <x:v>完成功能分区规则</x:v>
+        <x:v>制定唐长安平台数据契约v1</x:v>
       </x:c>
       <x:c r="D41" s="16" t="str">
-        <x:v>我</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E41" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F41" s="16" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G41" s="17"/>
-      <x:c r="H41" s="17"/>
-      <x:c r="I41" s="17"/>
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G41" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="H41" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="I41" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
       <x:c r="J41" s="16" t="str">
-        <x:v>必须检索反例</x:v>
+        <x:v>编写小型样例Excel转换程序</x:v>
       </x:c>
       <x:c r="K41" s="16" t="str">
-        <x:v>规则全量表</x:v>
-      </x:c>
-      <x:c r="L41" s="16"/>
+        <x:v>平台数据契约v1 / 导入包结构示例v1</x:v>
+      </x:c>
+      <x:c r="L41" s="16" t="str">
+        <x:v>兼容现有四类核心表；小样例先行</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="16" t="str">
-        <x:v>S8-01</x:v>
+        <x:v>S6-07</x:v>
       </x:c>
       <x:c r="B42" s="16" t="str">
-        <x:v>阶段八：质量检查</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C42" s="16" t="str">
-        <x:v>完成数据完整性、历史语义和数值检查</x:v>
+        <x:v>编写小型样例转换程序并生成首个导入包</x:v>
       </x:c>
       <x:c r="D42" s="16" t="str">
-        <x:v>共同</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E42" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F42" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G42" s="17"/>
-      <x:c r="H42" s="17"/>
-      <x:c r="I42" s="17"/>
+      <x:c r="G42" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="H42" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="I42" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
       <x:c r="J42" s="16" t="str">
-        <x:v>全量导入前完成</x:v>
+        <x:v>人工复核导入包和校验报告</x:v>
       </x:c>
       <x:c r="K42" s="16" t="str">
-        <x:v>质量报告</x:v>
-      </x:c>
-      <x:c r="L42" s="16"/>
+        <x:v>6来源 / 29片段 / 47实体 / 32关系</x:v>
+      </x:c>
+      <x:c r="L42" s="16" t="str">
+        <x:v>0错误、0警告、0悬空关系；未写入数据库</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="16" t="str">
-        <x:v>S8-02</x:v>
+        <x:v>S6-08</x:v>
       </x:c>
       <x:c r="B43" s="16" t="str">
-        <x:v>阶段八：质量检查</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C43" s="16" t="str">
-        <x:v>完成系统测试与重复导入测试</x:v>
+        <x:v>人工复核首个平台导入包</x:v>
       </x:c>
       <x:c r="D43" s="16" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="E43" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F43" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G43" s="17"/>
-      <x:c r="H43" s="17"/>
-      <x:c r="I43" s="17"/>
+      <x:c r="G43" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="H43" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="I43" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
       <x:c r="J43" s="16" t="str">
-        <x:v>发布前完成</x:v>
+        <x:v>修正MR-001—MR-007后重新生成导入包</x:v>
       </x:c>
       <x:c r="K43" s="16" t="str">
-        <x:v>系统测试报告</x:v>
-      </x:c>
-      <x:c r="L43" s="16"/>
+        <x:v>人工复核报告v1 / 7项问题</x:v>
+      </x:c>
+      <x:c r="L43" s="16" t="str">
+        <x:v>人工复核退回：2项P0、5项P1；尚未导入数据库</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="16" t="str">
-        <x:v>S9-01</x:v>
+        <x:v>S6-09</x:v>
       </x:c>
       <x:c r="B44" s="16" t="str">
-        <x:v>阶段九：发布交付</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C44" s="16" t="str">
-        <x:v>冻结第一版数据并生成文档</x:v>
+        <x:v>修正人工复核问题并完成第二轮复核</x:v>
       </x:c>
       <x:c r="D44" s="16" t="str">
-        <x:v>共同</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E44" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F44" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G44" s="17"/>
-      <x:c r="H44" s="17"/>
-      <x:c r="I44" s="17"/>
+      <x:c r="G44" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="H44" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="I44" s="17" t="n">
+        <x:v>46245</x:v>
+      </x:c>
       <x:c r="J44" s="16" t="str">
-        <x:v>完成最终审核</x:v>
+        <x:v>确认测试环境后执行首次数据库导入</x:v>
       </x:c>
       <x:c r="K44" s="16" t="str">
-        <x:v>tang_changan_v1</x:v>
-      </x:c>
-      <x:c r="L44" s="16"/>
+        <x:v>小型样例v2 / 人工复核报告v2</x:v>
+      </x:c>
+      <x:c r="L44" s="16" t="str">
+        <x:v>MR-001—MR-007全部关闭；0错误、0警告；允许测试导入</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="16" t="str">
-        <x:v>S9-02</x:v>
+        <x:v>S6-10</x:v>
       </x:c>
       <x:c r="B45" s="16" t="str">
-        <x:v>阶段九：发布交付</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C45" s="16" t="str">
-        <x:v>发布v1并建立Git标签v1.0.0</x:v>
+        <x:v>修正TC-CHUNK-1102与坊内规则的证据连接</x:v>
       </x:c>
       <x:c r="D45" s="16" t="str">
-        <x:v>共同</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E45" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F45" s="16" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G45" s="17"/>
-      <x:c r="H45" s="17"/>
-      <x:c r="I45" s="17"/>
+      <x:c r="G45" s="17" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H45" s="17" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I45" s="17" t="n">
+        <x:v>46246</x:v>
+      </x:c>
       <x:c r="J45" s="16" t="str">
-        <x:v>检查权限与版权</x:v>
+        <x:v>确认测试环境后执行首次数据库导入</x:v>
       </x:c>
       <x:c r="K45" s="16" t="str">
-        <x:v>正式发布</x:v>
-      </x:c>
-      <x:c r="L45" s="16"/>
+        <x:v>小型样例v3 / 人工复核报告v3</x:v>
+      </x:c>
+      <x:c r="L45" s="16" t="str">
+        <x:v>TC-CHUNK-1102改连TC-LAYOUT-0005；证据链复核通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
-        <x:v>S2-13</x:v>
+        <x:v>S6-11</x:v>
       </x:c>
       <x:c r="B46" t="str">
-        <x:v>阶段二：字段规范</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>建立坊内平面规则表占位字段</x:v>
+        <x:v>完成首个唐长安测试数据库导入与验收</x:v>
       </x:c>
       <x:c r="D46" t="str">
         <x:v>Codex</x:v>
@@ -2976,30 +3056,36 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="F46" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G46" t="str">
-        <x:v>2026-08-09</x:v>
-      </x:c>
-      <x:c r="H46" t="str">
-        <x:v>2026-08-09</x:v>
-      </x:c>
-      <x:c r="I46" t="str">
-        <x:v>2026-08-09</x:v>
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I46" t="n">
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="J46" t="str">
-        <x:v>用论文样例确认字段</x:v>
+        <x:v>启动测试API与页面，检查管理端和证据展示</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>首次测试导入报告v1 / 旧平台兼容包v1</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>独立测试库6来源/29片段/48实体/32关系；0重复；原青瓷库未变化</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
-        <x:v>S2-14</x:v>
+        <x:v>S6-12</x:v>
       </x:c>
       <x:c r="B47" t="str">
-        <x:v>阶段二：字段规范</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C47" t="str">
-        <x:v>建立研究结论表及转换框架</x:v>
+        <x:v>启动唐长安隔离测试平台并完成功能页面验收</x:v>
       </x:c>
       <x:c r="D47" t="str">
         <x:v>Codex</x:v>
@@ -3008,101 +3094,115 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="F47" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G47" t="str">
-        <x:v>2026-08-09</x:v>
-      </x:c>
-      <x:c r="H47" t="str">
-        <x:v>2026-08-09</x:v>
-      </x:c>
-      <x:c r="I47" t="str">
-        <x:v>2026-08-09</x:v>
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I47" t="n">
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="J47" t="str">
-        <x:v>试录专项研究论文</x:v>
+        <x:v>改造公众前台品牌、首页统计和长安城专题入口</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>平台页面验收报告v1 / 唐长安测试平台</x:v>
+      </x:c>
+      <x:c r="L47" t="str">
+        <x:v>API与管理端通过；48实体/32关系/6来源；前台仍需迁移</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
-        <x:v>S2-15</x:v>
+        <x:v>S6-13</x:v>
       </x:c>
       <x:c r="B48" t="str">
-        <x:v>阶段二：字段规范</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C48" t="str">
-        <x:v>根据论文样例确认两张新增表字段</x:v>
+        <x:v>完成唐长安前端第一轮换壳与实时统计改造</x:v>
       </x:c>
       <x:c r="D48" t="str">
-        <x:v>共同</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E48" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F48" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G48" t="str">
-        <x:v>2026-08-09</x:v>
-      </x:c>
-      <x:c r="H48"/>
-      <x:c r="I48"/>
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G48" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H48" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I48" t="n">
+        <x:v>46246</x:v>
+      </x:c>
       <x:c r="J48" t="str">
-        <x:v>在小型样例表完成三篇核心论文字段评估，再决定是否转入正式模板</x:v>
+        <x:v>设计并执行首批小型测试发布</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v>小型样例_第1批_文献片段与基础对象_v1.xlsx</x:v>
+        <x:v>前端换壳与实时统计验收报告v1 / 平台提交3a4b019</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v>正式模板恢复为结构与非论文试录数据；论文试录统一在样例表迭代</x:v>
+        <x:v>品牌与数据统计迁移通过；公开端仍严格限制published+public</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="40" customHeight="1">
       <x:c r="A49" s="216" t="str">
-        <x:v>S4-05</x:v>
+        <x:v>S6-14</x:v>
       </x:c>
       <x:c r="B49" s="216" t="str">
-        <x:v>阶段四：小型样例</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C49" s="216" t="str">
-        <x:v>试做首条科普内容及证据回溯闭环</x:v>
+        <x:v>完成首次小型闭环测试发布与公众端验收</x:v>
       </x:c>
       <x:c r="D49" s="216" t="str">
-        <x:v>共同</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E49" s="216" t="str">
-        <x:v>等待确认</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F49" s="216" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G49" s="217" t="n">
-        <x:v>46245</x:v>
-      </x:c>
-      <x:c r="H49" s="217"/>
-      <x:c r="I49" s="217"/>
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="H49" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I49" s="217" t="n">
+        <x:v>46246</x:v>
+      </x:c>
       <x:c r="J49" s="216" t="str">
-        <x:v>审核科普文字和7条依据关联</x:v>
+        <x:v>人工审核公众搜索、图谱和证据卡片展示，再确定第二批发布范围</x:v>
       </x:c>
       <x:c r="K49" s="216" t="str">
-        <x:v>TC-POPULAR-0001及TC-POPLINK-0001—0007</x:v>
+        <x:v>首次小型测试发布报告v1 / 发布版本v1</x:v>
       </x:c>
       <x:c r="L49" s="216" t="str">
-        <x:v>样例只录入小型样例表，不进入空白正式模板</x:v>
+        <x:v>2实体/1关系/1来源/2片段；检索4文档；依赖校验与回滚快照通过</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="40" customHeight="1">
       <x:c r="A50" s="216" t="str">
-        <x:v>S6-05</x:v>
+        <x:v>S6-15</x:v>
       </x:c>
       <x:c r="B50" s="216" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C50" s="216" t="str">
-        <x:v>盘点青瓷平台并形成唐长安迁移清单</x:v>
+        <x:v>完成首次小型发布人工审核并启动第二批候选筛选</x:v>
       </x:c>
       <x:c r="D50" s="216" t="str">
-        <x:v>Codex</x:v>
+        <x:v>用户 / Codex</x:v>
       </x:c>
       <x:c r="E50" s="216" t="str">
         <x:v>已完成</x:v>
@@ -3111,36 +3211,36 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G50" s="217" t="n">
-        <x:v>46245</x:v>
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="H50" s="217" t="n">
-        <x:v>46245</x:v>
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="I50" s="217" t="n">
-        <x:v>46245</x:v>
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="J50" s="216" t="str">
-        <x:v>确定唐长安平台数据契约v1</x:v>
+        <x:v>人工抽查第二批公众图谱，再确定正式迁移优先级</x:v>
       </x:c>
       <x:c r="K50" s="216" t="str">
-        <x:v>唐长安城平台迁移盘点与实施清单_v1.md</x:v>
+        <x:v>第二批平台发布报告v1 / 发布版本v2</x:v>
       </x:c>
       <x:c r="L50" s="216" t="str">
-        <x:v>只读检查；未修改平台代码和演示数据</x:v>
+        <x:v>发布8实体/4关系/4片段；公众总量10实体/5关系/1来源/6片段</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="40" customHeight="1">
       <x:c r="A51" s="216" t="str">
-        <x:v>S6-06</x:v>
+        <x:v>S6-16</x:v>
       </x:c>
       <x:c r="B51" s="216" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C51" s="216" t="str">
-        <x:v>制定唐长安平台数据契约v1</x:v>
+        <x:v>人工抽查第二批发布并确定正式迁移优先级</x:v>
       </x:c>
       <x:c r="D51" s="216" t="str">
-        <x:v>Codex</x:v>
+        <x:v>用户 / Codex</x:v>
       </x:c>
       <x:c r="E51" s="216" t="str">
         <x:v>已完成</x:v>
@@ -3149,33 +3249,33 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G51" s="217" t="n">
-        <x:v>46245</x:v>
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="H51" s="217" t="n">
-        <x:v>46245</x:v>
-      </x:c>
-      <x:c r="I51" s="217" t="n">
-        <x:v>46245</x:v>
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I51" s="217" t="str">
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="J51" s="216" t="str">
-        <x:v>编写小型样例Excel转换程序</x:v>
+        <x:v>进入正式迁移前的P0结构补全</x:v>
       </x:c>
       <x:c r="K51" s="216" t="str">
-        <x:v>平台数据契约v1 / 导入包结构示例v1</x:v>
+        <x:v>第二批公众页面审核记录 / 正式迁移顺序</x:v>
       </x:c>
       <x:c r="L51" s="216" t="str">
-        <x:v>兼容现有四类核心表；小样例先行</x:v>
+        <x:v>用户审核通过；确定先发布空间基础事实</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="40" customHeight="1">
       <x:c r="A52" s="216" t="str">
-        <x:v>S6-07</x:v>
+        <x:v>S6-17</x:v>
       </x:c>
       <x:c r="B52" s="216" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C52" s="216" t="str">
-        <x:v>编写小型样例转换程序并生成首个导入包</x:v>
+        <x:v>同步小型样例实体表与关系表，并修复转换去重</x:v>
       </x:c>
       <x:c r="D52" s="216" t="str">
         <x:v>Codex</x:v>
@@ -3187,33 +3287,33 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G52" s="217" t="n">
-        <x:v>46245</x:v>
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="H52" s="217" t="n">
-        <x:v>46245</x:v>
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="I52" s="217" t="n">
-        <x:v>46245</x:v>
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="J52" s="216" t="str">
-        <x:v>人工复核导入包和校验报告</x:v>
+        <x:v>人工抽查v4；后续以v4作为小型样例唯一工作版本</x:v>
       </x:c>
       <x:c r="K52" s="216" t="str">
-        <x:v>6来源 / 29片段 / 47实体 / 32关系</x:v>
+        <x:v>小型样例v4 / 转换程序去重修复</x:v>
       </x:c>
       <x:c r="L52" s="216" t="str">
-        <x:v>0错误、0警告、0悬空关系；未写入数据库</x:v>
+        <x:v>实体表23→48，关系表10→32；重新转换0错误、0警告、0重复</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="40" customHeight="1">
       <x:c r="A53" s="216" t="str">
-        <x:v>S6-08</x:v>
+        <x:v>S6-18</x:v>
       </x:c>
       <x:c r="B53" s="216" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C53" s="216" t="str">
-        <x:v>人工复核首个平台导入包</x:v>
+        <x:v>补齐专题表遗漏关系并完善自动转换阻断</x:v>
       </x:c>
       <x:c r="D53" s="216" t="str">
         <x:v>Codex</x:v>
@@ -3225,36 +3325,36 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G53" s="217" t="n">
-        <x:v>46245</x:v>
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="H53" s="217" t="n">
-        <x:v>46245</x:v>
-      </x:c>
-      <x:c r="I53" s="217" t="n">
-        <x:v>46245</x:v>
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="I53" s="217" t="str">
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="J53" s="216" t="str">
-        <x:v>修正MR-001—MR-007后重新生成导入包</x:v>
+        <x:v>以v6和平台导入包v2为后续基线</x:v>
       </x:c>
       <x:c r="K53" s="216" t="str">
-        <x:v>人工复核报告v1 / 7项问题</x:v>
+        <x:v>小型样例v6 / 专题关系自动转换</x:v>
       </x:c>
       <x:c r="L53" s="216" t="str">
-        <x:v>人工复核退回：2项P0、5项P1；尚未导入数据库</x:v>
+        <x:v>11条新增关系均已审核并发布</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="40" customHeight="1">
       <x:c r="A54" s="216" t="str">
-        <x:v>S6-09</x:v>
+        <x:v>S6-19</x:v>
       </x:c>
       <x:c r="B54" s="216" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C54" s="216" t="str">
-        <x:v>修正人工复核问题并完成第二轮复核</x:v>
+        <x:v>完成第三批空间基础事实发布与网页验收</x:v>
       </x:c>
       <x:c r="D54" s="216" t="str">
-        <x:v>Codex</x:v>
+        <x:v>用户 / Codex</x:v>
       </x:c>
       <x:c r="E54" s="216" t="str">
         <x:v>已完成</x:v>
@@ -3262,364 +3362,324 @@
       <x:c r="F54" s="216" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G54" s="217" t="n">
-        <x:v>46245</x:v>
-      </x:c>
-      <x:c r="H54" s="217" t="n">
-        <x:v>46245</x:v>
-      </x:c>
-      <x:c r="I54" s="217" t="n">
-        <x:v>46245</x:v>
+      <x:c r="G54" s="217" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="H54" s="217" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="I54" s="217" t="str">
+        <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="J54" s="216" t="str">
-        <x:v>确认测试环境后执行首次数据库导入</x:v>
+        <x:v>补齐外郭城区域、永安渠六坊编号和平康坊演示数据</x:v>
       </x:c>
       <x:c r="K54" s="216" t="str">
-        <x:v>小型样例v2 / 人工复核报告v2</x:v>
+        <x:v>发布版本v3 / 第三批发布与网页验收报告v1</x:v>
       </x:c>
       <x:c r="L54" s="216" t="str">
-        <x:v>MR-001—MR-007全部关闭；0错误、0警告；允许测试导入</x:v>
+        <x:v>发布11实体、11关系、1来源、6片段；公开总量21实体/16关系/2来源/12片段；搜索索引33文档</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="40" customHeight="1">
       <x:c r="A55" s="216" t="str">
-        <x:v>S6-10</x:v>
+        <x:v>S7-01</x:v>
       </x:c>
       <x:c r="B55" s="216" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C55" s="216" t="str">
-        <x:v>修正TC-CHUNK-1102与坊内规则的证据连接</x:v>
+        <x:v>完成108坊功能数据</x:v>
       </x:c>
       <x:c r="D55" s="216" t="str">
-        <x:v>Codex</x:v>
+        <x:v>同事</x:v>
       </x:c>
       <x:c r="E55" s="216" t="str">
-        <x:v>已完成</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F55" s="216" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G55" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="H55" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="I55" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G55" s="217"/>
+      <x:c r="H55" s="217"/>
+      <x:c r="I55" s="217"/>
       <x:c r="J55" s="216" t="str">
-        <x:v>确认测试环境后执行首次数据库导入</x:v>
+        <x:v>小样例通过后分批提取</x:v>
       </x:c>
       <x:c r="K55" s="216" t="str">
-        <x:v>小型样例v3 / 人工复核报告v3</x:v>
-      </x:c>
-      <x:c r="L55" s="216" t="str">
-        <x:v>TC-CHUNK-1102改连TC-LAYOUT-0005；证据链复核通过</x:v>
-      </x:c>
+        <x:v>坊功能全量表</x:v>
+      </x:c>
+      <x:c r="L55" s="216"/>
     </x:row>
     <x:row r="56" ht="40" customHeight="1">
       <x:c r="A56" s="216" t="str">
-        <x:v>S6-11</x:v>
+        <x:v>S7-02</x:v>
       </x:c>
       <x:c r="B56" s="216" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C56" s="216" t="str">
-        <x:v>完成首个唐长安测试数据库导入与验收</x:v>
+        <x:v>完成道路分级数据</x:v>
       </x:c>
       <x:c r="D56" s="216" t="str">
-        <x:v>Codex</x:v>
+        <x:v>同事</x:v>
       </x:c>
       <x:c r="E56" s="216" t="str">
-        <x:v>已完成</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F56" s="216" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G56" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="H56" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="I56" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G56" s="217"/>
+      <x:c r="H56" s="217"/>
+      <x:c r="I56" s="217"/>
       <x:c r="J56" s="216" t="str">
-        <x:v>启动测试API与页面，检查管理端和证据展示</x:v>
+        <x:v>分批提取与审核</x:v>
       </x:c>
       <x:c r="K56" s="216" t="str">
-        <x:v>首次测试导入报告v1 / 旧平台兼容包v1</x:v>
-      </x:c>
-      <x:c r="L56" s="216" t="str">
-        <x:v>独立测试库6来源/29片段/48实体/32关系；0重复；原青瓷库未变化</x:v>
-      </x:c>
+        <x:v>道路全量表</x:v>
+      </x:c>
+      <x:c r="L56" s="216"/>
     </x:row>
     <x:row r="57" ht="40" customHeight="1">
       <x:c r="A57" s="216" t="str">
-        <x:v>S6-12</x:v>
+        <x:v>S7-03</x:v>
       </x:c>
       <x:c r="B57" s="216" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C57" s="216" t="str">
-        <x:v>启动唐长安隔离测试平台并完成功能页面验收</x:v>
+        <x:v>完成水渠数据</x:v>
       </x:c>
       <x:c r="D57" s="216" t="str">
-        <x:v>Codex</x:v>
+        <x:v>同事</x:v>
       </x:c>
       <x:c r="E57" s="216" t="str">
-        <x:v>已完成</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F57" s="216" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G57" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="H57" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="I57" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G57" s="217"/>
+      <x:c r="H57" s="217"/>
+      <x:c r="I57" s="217"/>
       <x:c r="J57" s="216" t="str">
-        <x:v>改造公众前台品牌、首页统计和长安城专题入口</x:v>
+        <x:v>分批提取与审核</x:v>
       </x:c>
       <x:c r="K57" s="216" t="str">
-        <x:v>平台页面验收报告v1 / 唐长安测试平台</x:v>
-      </x:c>
-      <x:c r="L57" s="216" t="str">
-        <x:v>API与管理端通过；48实体/32关系/6来源；前台仍需迁移</x:v>
-      </x:c>
+        <x:v>水渠全量表</x:v>
+      </x:c>
+      <x:c r="L57" s="216"/>
     </x:row>
     <x:row r="58" ht="40" customHeight="1">
       <x:c r="A58" s="216" t="str">
-        <x:v>S6-13</x:v>
+        <x:v>S7-04</x:v>
       </x:c>
       <x:c r="B58" s="216" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C58" s="216" t="str">
-        <x:v>完成唐长安前端第一轮换壳与实时统计改造</x:v>
+        <x:v>完成城门数据</x:v>
       </x:c>
       <x:c r="D58" s="216" t="str">
-        <x:v>Codex</x:v>
+        <x:v>我</x:v>
       </x:c>
       <x:c r="E58" s="216" t="str">
-        <x:v>已完成</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F58" s="216" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G58" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="H58" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="I58" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G58" s="217"/>
+      <x:c r="H58" s="217"/>
+      <x:c r="I58" s="217"/>
       <x:c r="J58" s="216" t="str">
-        <x:v>设计并执行首批小型测试发布</x:v>
+        <x:v>严格区分城门与内门</x:v>
       </x:c>
       <x:c r="K58" s="216" t="str">
-        <x:v>前端换壳与实时统计验收报告v1 / 平台提交3a4b019</x:v>
-      </x:c>
-      <x:c r="L58" s="216" t="str">
-        <x:v>品牌与数据统计迁移通过；公开端仍严格限制published+public</x:v>
-      </x:c>
+        <x:v>城门全量表</x:v>
+      </x:c>
+      <x:c r="L58" s="216"/>
     </x:row>
     <x:row r="59" ht="44" customHeight="1">
       <x:c r="A59" s="216" t="str">
-        <x:v>S6-14</x:v>
+        <x:v>S7-05</x:v>
       </x:c>
       <x:c r="B59" s="216" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C59" s="216" t="str">
-        <x:v>完成首次小型闭环测试发布与公众端验收</x:v>
+        <x:v>完成尺度关系数据</x:v>
       </x:c>
       <x:c r="D59" s="216" t="str">
-        <x:v>Codex</x:v>
+        <x:v>我</x:v>
       </x:c>
       <x:c r="E59" s="216" t="str">
-        <x:v>已完成</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F59" s="216" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G59" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="H59" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="I59" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G59" s="217"/>
+      <x:c r="H59" s="217"/>
+      <x:c r="I59" s="217"/>
       <x:c r="J59" s="216" t="str">
-        <x:v>人工审核公众搜索、图谱和证据卡片展示，再确定第二批发布范围</x:v>
+        <x:v>全部公式人工复核</x:v>
       </x:c>
       <x:c r="K59" s="216" t="str">
-        <x:v>首次小型测试发布报告v1 / 发布版本v1</x:v>
-      </x:c>
-      <x:c r="L59" s="216" t="str">
-        <x:v>2实体/1关系/1来源/2片段；检索4文档；依赖校验与回滚快照通过</x:v>
-      </x:c>
+        <x:v>尺度关系全量表</x:v>
+      </x:c>
+      <x:c r="L59" s="216"/>
     </x:row>
     <x:row r="60" ht="44" customHeight="1">
       <x:c r="A60" s="216" t="str">
-        <x:v>S6-15</x:v>
+        <x:v>S7-06</x:v>
       </x:c>
       <x:c r="B60" s="216" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C60" s="216" t="str">
-        <x:v>完成首次小型发布人工审核并启动第二批候选筛选</x:v>
+        <x:v>完成功能分区规则</x:v>
       </x:c>
       <x:c r="D60" s="216" t="str">
-        <x:v>用户 / Codex</x:v>
+        <x:v>我</x:v>
       </x:c>
       <x:c r="E60" s="216" t="str">
-        <x:v>已完成</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F60" s="216" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G60" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="H60" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="I60" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G60" s="217"/>
+      <x:c r="H60" s="217"/>
+      <x:c r="I60" s="217"/>
       <x:c r="J60" s="216" t="str">
-        <x:v>人工抽查第二批公众图谱，再确定正式迁移优先级</x:v>
+        <x:v>必须检索反例</x:v>
       </x:c>
       <x:c r="K60" s="216" t="str">
-        <x:v>第二批平台发布报告v1 / 发布版本v2</x:v>
-      </x:c>
-      <x:c r="L60" s="216" t="str">
-        <x:v>发布8实体/4关系/4片段；公众总量10实体/5关系/1来源/6片段</x:v>
-      </x:c>
+        <x:v>规则全量表</x:v>
+      </x:c>
+      <x:c r="L60" s="216"/>
     </x:row>
     <x:row r="61" ht="44" customHeight="1">
       <x:c r="A61" s="216" t="str">
-        <x:v>S6-16</x:v>
+        <x:v>S8-01</x:v>
       </x:c>
       <x:c r="B61" s="216" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段八：质量检查</x:v>
       </x:c>
       <x:c r="C61" s="216" t="str">
-        <x:v>人工抽查第二批发布并确定正式迁移优先级</x:v>
+        <x:v>完成数据完整性、历史语义和数值检查</x:v>
       </x:c>
       <x:c r="D61" s="216" t="str">
-        <x:v>用户 / Codex</x:v>
+        <x:v>共同</x:v>
       </x:c>
       <x:c r="E61" s="216" t="str">
-        <x:v>待审核</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F61" s="216" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G61" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="H61" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
+      <x:c r="G61" s="217"/>
+      <x:c r="H61" s="217"/>
       <x:c r="I61" s="217"/>
       <x:c r="J61" s="216" t="str">
-        <x:v>抽查4个新闭环；选择先迁移空间基础事实或先审核研究解释</x:v>
+        <x:v>全量导入前完成</x:v>
       </x:c>
       <x:c r="K61" s="216" t="str">
-        <x:v>第二批公众页面审核记录 / 正式迁移批次方案</x:v>
-      </x:c>
-      <x:c r="L61" s="216" t="str">
-        <x:v>小型试发技术链路已经连续两批通过</x:v>
-      </x:c>
+        <x:v>质量报告</x:v>
+      </x:c>
+      <x:c r="L61" s="216"/>
     </x:row>
     <x:row r="62" ht="48" customHeight="1">
       <x:c r="A62" s="216" t="str">
-        <x:v>S6-17</x:v>
+        <x:v>S8-02</x:v>
       </x:c>
       <x:c r="B62" s="216" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段八：质量检查</x:v>
       </x:c>
       <x:c r="C62" s="216" t="str">
-        <x:v>同步小型样例实体表与关系表，并修复转换去重</x:v>
+        <x:v>完成系统测试与重复导入测试</x:v>
       </x:c>
       <x:c r="D62" s="216" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="E62" s="216" t="str">
-        <x:v>已完成</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F62" s="216" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G62" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="H62" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="I62" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
+      <x:c r="G62" s="217"/>
+      <x:c r="H62" s="217"/>
+      <x:c r="I62" s="217"/>
       <x:c r="J62" s="216" t="str">
-        <x:v>人工抽查v4；后续以v4作为小型样例唯一工作版本</x:v>
+        <x:v>发布前完成</x:v>
       </x:c>
       <x:c r="K62" s="216" t="str">
-        <x:v>小型样例v4 / 转换程序去重修复</x:v>
-      </x:c>
-      <x:c r="L62" s="216" t="str">
-        <x:v>实体表23→48，关系表10→32；重新转换0错误、0警告、0重复</x:v>
-      </x:c>
+        <x:v>系统测试报告</x:v>
+      </x:c>
+      <x:c r="L62" s="216"/>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
       <x:c r="A63" s="216" t="str">
-        <x:v>S6-18</x:v>
+        <x:v>S9-01</x:v>
       </x:c>
       <x:c r="B63" s="216" t="str">
-        <x:v>阶段六：平台迁移</x:v>
+        <x:v>阶段九：发布交付</x:v>
       </x:c>
       <x:c r="C63" s="216" t="str">
-        <x:v>补齐专题表遗漏关系并完善自动转换阻断</x:v>
+        <x:v>冻结第一版数据并生成文档</x:v>
       </x:c>
       <x:c r="D63" s="216" t="str">
-        <x:v>Codex</x:v>
+        <x:v>共同</x:v>
       </x:c>
       <x:c r="E63" s="216" t="str">
-        <x:v>已完成</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F63" s="216" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G63" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="H63" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
-      <x:c r="I63" s="217" t="n">
-        <x:v>46246</x:v>
-      </x:c>
+      <x:c r="G63" s="217"/>
+      <x:c r="H63" s="217"/>
+      <x:c r="I63" s="217"/>
       <x:c r="J63" s="216" t="str">
-        <x:v>人工抽查v5新增11条关系</x:v>
+        <x:v>完成最终审核</x:v>
       </x:c>
       <x:c r="K63" s="216" t="str">
-        <x:v>小型样例v5 / 专题关系自动转换</x:v>
-      </x:c>
-      <x:c r="L63" s="216" t="str">
-        <x:v>关系表32→43；转换0错误；11条不完整记录被主动阻断</x:v>
-      </x:c>
+        <x:v>tang_changan_v1</x:v>
+      </x:c>
+      <x:c r="L63" s="216"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>S9-02</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>阶段九：发布交付</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>发布v1并建立Git标签v1.0.0</x:v>
+      </x:c>
+      <x:c r="D64" t="str">
+        <x:v>共同</x:v>
+      </x:c>
+      <x:c r="E64" t="str">
+        <x:v>尚未开始</x:v>
+      </x:c>
+      <x:c r="F64" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G64"/>
+      <x:c r="H64"/>
+      <x:c r="I64"/>
+      <x:c r="J64" t="str">
+        <x:v>检查权限与版权</x:v>
+      </x:c>
+      <x:c r="K64" t="str">
+        <x:v>正式发布</x:v>
+      </x:c>
+      <x:c r="L64"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4618,6 +4678,26 @@
         <x:v>补写11关系；48实体、43关系；0错误；11条不完整记录阻断警告</x:v>
       </x:c>
     </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>审核通过11条专题关系，完成第三批空间基础事实发布、索引同步与网页验收</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>小型样例v6 / 平台导入包v2 / 发布版本v3 / 网页验收报告v1 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>补齐3项P0结构数据后升级提取Skill并进入正式全量迁移</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>公开21实体、16关系、2来源、12片段；搜索索引33文档；工作清单已按任务编号重排</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R73b6b4f1b0524fd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R789a1de2057c4be2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R63311772b39d4a83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R44f870a4466746c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Ra5bbd8064b864423"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Re4cd9d4b08a54f91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R834528c94f6e4ef1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rf8116534fb464b07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="10">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -76,8 +76,13 @@
       <x:sz val="10"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF333333"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -117,6 +122,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF4CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF173F5F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F3E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF4EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EEF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F766E"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -210,7 +245,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="218">
+  <x:cellXfs count="326">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -734,6 +769,248 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -998,7 +1275,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R869f4847c1cd4cfd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6b7f53debab44831"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1202,276 +1479,342 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="221" t="str">
         <x:v>唐长安城知识图谱 · 今日进度看板</x:v>
       </x:c>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
-      <x:c r="F1" s="3"/>
-      <x:c r="G1" s="3"/>
-      <x:c r="H1" s="3"/>
-      <x:c r="I1" s="3"/>
-      <x:c r="J1" s="3"/>
-      <x:c r="K1" s="3"/>
-      <x:c r="L1" s="3"/>
-    </x:row>
-    <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="18" t="str">
+      <x:c r="B1" s="221"/>
+      <x:c r="C1" s="221"/>
+      <x:c r="D1" s="221"/>
+      <x:c r="E1" s="221"/>
+      <x:c r="F1" s="221"/>
+      <x:c r="G1" s="221"/>
+      <x:c r="H1" s="221"/>
+      <x:c r="I1" s="221"/>
+      <x:c r="J1" s="221"/>
+      <x:c r="K1" s="221"/>
+      <x:c r="L1" s="221"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="224" t="str">
         <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-12</x:v>
       </x:c>
-      <x:c r="B3" s="18"/>
-      <x:c r="C3" s="18"/>
-      <x:c r="D3" s="18"/>
-      <x:c r="E3" s="18"/>
-      <x:c r="F3" s="18"/>
-      <x:c r="G3" s="18"/>
-      <x:c r="H3" s="18"/>
-      <x:c r="I3" s="18"/>
-      <x:c r="J3" s="18"/>
-      <x:c r="K3" s="18"/>
-      <x:c r="L3" s="18"/>
+      <x:c r="B3" s="224"/>
+      <x:c r="C3" s="224"/>
+      <x:c r="D3" s="224"/>
+      <x:c r="E3" s="224"/>
+      <x:c r="F3" s="224"/>
+      <x:c r="G3" s="224"/>
+      <x:c r="H3" s="224"/>
+      <x:c r="I3" s="224"/>
+      <x:c r="J3" s="224"/>
+      <x:c r="K3" s="224"/>
+      <x:c r="L3" s="224"/>
     </x:row>
     <x:row r="4">
-      <x:c r="N4" t="str">
-        <x:v>状态</x:v>
-      </x:c>
-      <x:c r="O4" t="str">
-        <x:v>任务数</x:v>
-      </x:c>
+      <x:c r="N4"/>
+      <x:c r="O4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="20" t="str">
+      <x:c r="A5" s="226" t="str">
         <x:v>总任务数</x:v>
       </x:c>
-      <x:c r="B5" s="20"/>
-      <x:c r="C5" s="20"/>
-      <x:c r="D5" s="20" t="str">
+      <x:c r="B5" s="226"/>
+      <x:c r="C5" s="226"/>
+      <x:c r="D5" s="226" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="E5" s="20"/>
-      <x:c r="F5" s="20"/>
-      <x:c r="G5" s="20" t="str">
+      <x:c r="E5" s="226"/>
+      <x:c r="F5" s="226"/>
+      <x:c r="G5" s="226" t="str">
         <x:v>进行中</x:v>
       </x:c>
-      <x:c r="H5" s="20"/>
-      <x:c r="I5" s="20"/>
-      <x:c r="J5" s="20" t="str">
+      <x:c r="H5" s="226"/>
+      <x:c r="I5" s="226"/>
+      <x:c r="J5" s="226" t="str">
         <x:v>完成率</x:v>
       </x:c>
-      <x:c r="K5" s="20"/>
-      <x:c r="L5" s="20"/>
-      <x:c r="N5" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="O5" t="n">
-        <x:f>COUNTIF('工作清单'!$E$4:$E$100,N5)</x:f>
+      <x:c r="K5" s="226"/>
+      <x:c r="L5" s="226"/>
+      <x:c r="N5"/>
+      <x:c r="O5"/>
+    </x:row>
+    <x:row r="6" ht="32" customHeight="1">
+      <x:c r="A6" s="230" t="n">
+        <x:f>COUNTA('工作清单'!$A$4:$A$200)</x:f>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B6" s="230"/>
+      <x:c r="C6" s="230"/>
+      <x:c r="D6" s="230" t="n">
+        <x:f>COUNTIF('工作清单'!$E$4:$E$200,"已完成")</x:f>
         <x:v>30</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="40" t="n">
-        <x:f>COUNTA('工作清单'!$A$4:$A$100)</x:f>
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B6" s="41"/>
-      <x:c r="C6" s="42"/>
-      <x:c r="D6" s="68" t="n">
-        <x:f>COUNTIF('工作清单'!$E$4:$E$100,"已完成")</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E6" s="69"/>
-      <x:c r="F6" s="70"/>
-      <x:c r="G6" s="96" t="n">
-        <x:f>COUNTIF('工作清单'!$E$4:$E$100,"进行中")</x:f>
+      <x:c r="E6" s="230"/>
+      <x:c r="F6" s="230"/>
+      <x:c r="G6" s="234" t="n">
+        <x:f>COUNTIF('工作清单'!$E$4:$E$200,"进行中")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H6" s="97"/>
-      <x:c r="I6" s="98"/>
-      <x:c r="J6" s="133" t="n">
-        <x:f>IFERROR(COUNTIF('工作清单'!$E$4:$E$100,"已完成")/COUNTA('工作清单'!$A$4:$A$100),0)</x:f>
-        <x:v>0.4918032786885246</x:v>
-      </x:c>
-      <x:c r="K6" s="134"/>
-      <x:c r="L6" s="135"/>
-      <x:c r="N6" t="str">
-        <x:v>进行中</x:v>
-      </x:c>
-      <x:c r="O6" t="n">
-        <x:f>COUNTIF('工作清单'!$E$4:$E$100,N6)</x:f>
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="H6" s="234"/>
+      <x:c r="I6" s="234"/>
+      <x:c r="J6" s="239" t="n">
+        <x:f>IFERROR(D6/A6,0)</x:f>
+        <x:v>0.4838709677419355</x:v>
+      </x:c>
+      <x:c r="K6" s="239"/>
+      <x:c r="L6" s="239"/>
+      <x:c r="N6"/>
+      <x:c r="O6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="43"/>
-      <x:c r="B7" s="44"/>
-      <x:c r="C7" s="45"/>
-      <x:c r="D7" s="71"/>
-      <x:c r="E7" s="72"/>
-      <x:c r="F7" s="73"/>
-      <x:c r="G7" s="99"/>
-      <x:c r="H7" s="100"/>
-      <x:c r="I7" s="101"/>
-      <x:c r="J7" s="136"/>
-      <x:c r="K7" s="137"/>
-      <x:c r="L7" s="138"/>
-      <x:c r="N7" t="str">
-        <x:v>等待确认</x:v>
-      </x:c>
-      <x:c r="O7" t="n">
-        <x:f>COUNTIF('工作清单'!$E$4:$E$100,N7)</x:f>
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
+      <x:c r="N7"/>
+      <x:c r="O7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="46"/>
-      <x:c r="B8" s="47"/>
-      <x:c r="C8" s="48"/>
-      <x:c r="D8" s="74"/>
-      <x:c r="E8" s="75"/>
-      <x:c r="F8" s="76"/>
-      <x:c r="G8" s="102"/>
-      <x:c r="H8" s="103"/>
-      <x:c r="I8" s="104"/>
-      <x:c r="J8" s="139"/>
-      <x:c r="K8" s="140"/>
-      <x:c r="L8" s="141"/>
-      <x:c r="N8" t="str">
-        <x:v>遇到问题</x:v>
-      </x:c>
-      <x:c r="O8" t="n">
-        <x:f>COUNTIF('工作清单'!$E$4:$E$100,N8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="A8"/>
+      <x:c r="B8"/>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+      <x:c r="N8"/>
+      <x:c r="O8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="N9" t="str">
-        <x:v>尚未开始</x:v>
-      </x:c>
-      <x:c r="O9" t="n">
-        <x:f>COUNTIF('工作清单'!$E$4:$E$100,N9)</x:f>
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="142" t="str">
+      <x:c r="A9" s="243" t="str">
         <x:v>现在做到哪里</x:v>
       </x:c>
-      <x:c r="B10" s="142"/>
-      <x:c r="C10" s="142"/>
-      <x:c r="D10" s="142"/>
-      <x:c r="E10" s="142"/>
-      <x:c r="F10" s="142"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="152" t="str">
-        <x:v>当前阶段：第三批空间基础事实已正式发布并通过网页验收
-总体状态：数据库48实体、43关系、6来源、29片段；公开21实体、16关系、2来源、12片段
-本次完成：11条专题关系、11个端点实体及6条证据片段进入发布版本v3，索引同步完成</x:v>
-      </x:c>
-      <x:c r="B11" s="153"/>
-      <x:c r="C11" s="153"/>
-      <x:c r="D11" s="153"/>
-      <x:c r="E11" s="153"/>
-      <x:c r="F11" s="154"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="155"/>
-      <x:c r="B12" s="156"/>
-      <x:c r="C12" s="156"/>
-      <x:c r="D12" s="156"/>
-      <x:c r="E12" s="156"/>
-      <x:c r="F12" s="157"/>
+      <x:c r="B9" s="243"/>
+      <x:c r="C9" s="243"/>
+      <x:c r="D9" s="243"/>
+      <x:c r="E9" s="243"/>
+      <x:c r="F9" s="243"/>
+      <x:c r="G9" s="243"/>
+      <x:c r="H9" s="243"/>
+      <x:c r="I9" s="243"/>
+      <x:c r="J9" s="243"/>
+      <x:c r="K9" s="243"/>
+      <x:c r="L9" s="243"/>
+      <x:c r="N9"/>
+      <x:c r="O9"/>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
+      <x:c r="A10" s="262" t="str">
+        <x:v>当前阶段：正式迁移前P0结构补全已完成，等待人工审核
+总体状态：v7包含7来源、31片段、57实体、62关系；结构校验0错误、0警告
+本次完成：建立外郭城实体、补齐永安渠六坊编号、替换平康坊占位记录，并修正其与崇仁坊的南北方向</x:v>
+      </x:c>
+      <x:c r="B10" s="263"/>
+      <x:c r="C10" s="263"/>
+      <x:c r="D10" s="263"/>
+      <x:c r="E10" s="263"/>
+      <x:c r="F10" s="263"/>
+      <x:c r="G10" s="263"/>
+      <x:c r="H10" s="263"/>
+      <x:c r="I10" s="263"/>
+      <x:c r="J10" s="263"/>
+      <x:c r="K10" s="263"/>
+      <x:c r="L10" s="264"/>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="265"/>
+      <x:c r="B11" s="266"/>
+      <x:c r="C11" s="266"/>
+      <x:c r="D11" s="266"/>
+      <x:c r="E11" s="266"/>
+      <x:c r="F11" s="266"/>
+      <x:c r="G11" s="266"/>
+      <x:c r="H11" s="266"/>
+      <x:c r="I11" s="266"/>
+      <x:c r="J11" s="266"/>
+      <x:c r="K11" s="266"/>
+      <x:c r="L11" s="267"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="268"/>
+      <x:c r="B12" s="269"/>
+      <x:c r="C12" s="269"/>
+      <x:c r="D12" s="269"/>
+      <x:c r="E12" s="269"/>
+      <x:c r="F12" s="269"/>
+      <x:c r="G12" s="269"/>
+      <x:c r="H12" s="269"/>
+      <x:c r="I12" s="269"/>
+      <x:c r="J12" s="269"/>
+      <x:c r="K12" s="269"/>
+      <x:c r="L12" s="270"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="158"/>
-      <x:c r="B13" s="159"/>
-      <x:c r="C13" s="159"/>
-      <x:c r="D13" s="159"/>
-      <x:c r="E13" s="159"/>
-      <x:c r="F13" s="160"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="142" t="str">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="243" t="str">
         <x:v>下一步只做这三件事</x:v>
       </x:c>
-      <x:c r="B15" s="142"/>
-      <x:c r="C15" s="142"/>
-      <x:c r="D15" s="142"/>
-      <x:c r="E15" s="142"/>
-      <x:c r="F15" s="142"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="170" t="str">
-        <x:v>1. 补齐外郭城区域编号、永安渠所经六坊编号和平康坊演示数据。
-2. 用v6及三批验收经验升级knowledge-graph-extraction Skill。
-3. 按“基础事实→研究解释”的顺序开始正式全量迁移。</x:v>
-      </x:c>
-      <x:c r="B16" s="171"/>
-      <x:c r="C16" s="171"/>
-      <x:c r="D16" s="171"/>
-      <x:c r="E16" s="171"/>
-      <x:c r="F16" s="172"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="173"/>
-      <x:c r="B17" s="174"/>
-      <x:c r="C17" s="174"/>
-      <x:c r="D17" s="174"/>
-      <x:c r="E17" s="174"/>
-      <x:c r="F17" s="175"/>
+      <x:c r="B14" s="243"/>
+      <x:c r="C14" s="243"/>
+      <x:c r="D14" s="243"/>
+      <x:c r="E14" s="243"/>
+      <x:c r="F14" s="243"/>
+      <x:c r="G14" s="243"/>
+      <x:c r="H14" s="243"/>
+      <x:c r="I14" s="243"/>
+      <x:c r="J14" s="243"/>
+      <x:c r="K14" s="243"/>
+      <x:c r="L14" s="243"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="289" t="str">
+        <x:v>1. 审核外郭城TC-AREA-0003及5个城门归属关系。
+2. 审核永安渠六坊关系，重点确认‘廷福/延福’异文。
+3. 审核平康坊SOUTH_OF崇仁坊及两坊邻近TC-ROAD-0004；通过后升级提取Skill。</x:v>
+      </x:c>
+      <x:c r="B15" s="290"/>
+      <x:c r="C15" s="290"/>
+      <x:c r="D15" s="290"/>
+      <x:c r="E15" s="290"/>
+      <x:c r="F15" s="290"/>
+      <x:c r="G15" s="290"/>
+      <x:c r="H15" s="290"/>
+      <x:c r="I15" s="290"/>
+      <x:c r="J15" s="290"/>
+      <x:c r="K15" s="290"/>
+      <x:c r="L15" s="291"/>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="292"/>
+      <x:c r="B16" s="293"/>
+      <x:c r="C16" s="293"/>
+      <x:c r="D16" s="293"/>
+      <x:c r="E16" s="293"/>
+      <x:c r="F16" s="293"/>
+      <x:c r="G16" s="293"/>
+      <x:c r="H16" s="293"/>
+      <x:c r="I16" s="293"/>
+      <x:c r="J16" s="293"/>
+      <x:c r="K16" s="293"/>
+      <x:c r="L16" s="294"/>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="295"/>
+      <x:c r="B17" s="296"/>
+      <x:c r="C17" s="296"/>
+      <x:c r="D17" s="296"/>
+      <x:c r="E17" s="296"/>
+      <x:c r="F17" s="296"/>
+      <x:c r="G17" s="296"/>
+      <x:c r="H17" s="296"/>
+      <x:c r="I17" s="296"/>
+      <x:c r="J17" s="296"/>
+      <x:c r="K17" s="296"/>
+      <x:c r="L17" s="297"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="173"/>
-      <x:c r="B18" s="174"/>
-      <x:c r="C18" s="174"/>
-      <x:c r="D18" s="174"/>
-      <x:c r="E18" s="174"/>
-      <x:c r="F18" s="175"/>
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="176"/>
-      <x:c r="B19" s="177"/>
-      <x:c r="C19" s="177"/>
-      <x:c r="D19" s="177"/>
-      <x:c r="E19" s="177"/>
-      <x:c r="F19" s="178"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="19" t="str">
+      <x:c r="A19" s="243" t="str">
         <x:v>重要提醒</x:v>
       </x:c>
-      <x:c r="B21" s="19"/>
-      <x:c r="C21" s="19"/>
-      <x:c r="D21" s="19"/>
-      <x:c r="E21" s="19"/>
-      <x:c r="F21" s="19"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="196" t="str">
-        <x:v>v6是当前小型样例工作版本；平台导入包v2为当前导入基线。第三批发布v3已完成，公开检索与图谱均可见。尚未补齐的示例行、外郭城编号和永安渠六坊编号继续被转换程序阻断，不会误入平台。</x:v>
-      </x:c>
-      <x:c r="B22" s="197"/>
-      <x:c r="C22" s="197"/>
-      <x:c r="D22" s="197"/>
-      <x:c r="E22" s="197"/>
-      <x:c r="F22" s="198"/>
+      <x:c r="B19" s="243"/>
+      <x:c r="C19" s="243"/>
+      <x:c r="D19" s="243"/>
+      <x:c r="E19" s="243"/>
+      <x:c r="F19" s="243"/>
+      <x:c r="G19" s="243"/>
+      <x:c r="H19" s="243"/>
+      <x:c r="I19" s="243"/>
+      <x:c r="J19" s="243"/>
+      <x:c r="K19" s="243"/>
+      <x:c r="L19" s="243"/>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
+      <x:c r="A20" s="317" t="str">
+        <x:v>v7是当前小型样例工作版本，平台导入包v3为待审核导入基线。本次新增数据均为待审核，尚未写入或发布到平台。
+注意：项目坐标y值向南递增，所以平康坊(3,1)位于崇仁坊(3,0)南侧。</x:v>
+      </x:c>
+      <x:c r="B20" s="318"/>
+      <x:c r="C20" s="318"/>
+      <x:c r="D20" s="318"/>
+      <x:c r="E20" s="318"/>
+      <x:c r="F20" s="318"/>
+      <x:c r="G20" s="318"/>
+      <x:c r="H20" s="318"/>
+      <x:c r="I20" s="318"/>
+      <x:c r="J20" s="318"/>
+      <x:c r="K20" s="318"/>
+      <x:c r="L20" s="319"/>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21" s="320"/>
+      <x:c r="B21" s="321"/>
+      <x:c r="C21" s="321"/>
+      <x:c r="D21" s="321"/>
+      <x:c r="E21" s="321"/>
+      <x:c r="F21" s="321"/>
+      <x:c r="G21" s="321"/>
+      <x:c r="H21" s="321"/>
+      <x:c r="I21" s="321"/>
+      <x:c r="J21" s="321"/>
+      <x:c r="K21" s="321"/>
+      <x:c r="L21" s="322"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="323"/>
+      <x:c r="B22" s="324"/>
+      <x:c r="C22" s="324"/>
+      <x:c r="D22" s="324"/>
+      <x:c r="E22" s="324"/>
+      <x:c r="F22" s="324"/>
+      <x:c r="G22" s="324"/>
+      <x:c r="H22" s="324"/>
+      <x:c r="I22" s="324"/>
+      <x:c r="J22" s="324"/>
+      <x:c r="K22" s="324"/>
+      <x:c r="L22" s="325"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="199"/>
@@ -1494,22 +1837,22 @@
     <x:mergeCell ref="A1:L1"/>
     <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A5:C5"/>
-    <x:mergeCell ref="A6:C8"/>
     <x:mergeCell ref="D5:F5"/>
-    <x:mergeCell ref="D6:F8"/>
     <x:mergeCell ref="G5:I5"/>
-    <x:mergeCell ref="G6:I8"/>
     <x:mergeCell ref="J5:L5"/>
-    <x:mergeCell ref="J6:L8"/>
-    <x:mergeCell ref="A10:F10"/>
-    <x:mergeCell ref="A11:F13"/>
-    <x:mergeCell ref="A15:F15"/>
-    <x:mergeCell ref="A16:F19"/>
-    <x:mergeCell ref="A21:F21"/>
-    <x:mergeCell ref="A22:F24"/>
+    <x:mergeCell ref="A6:C6"/>
+    <x:mergeCell ref="D6:F6"/>
+    <x:mergeCell ref="G6:I6"/>
+    <x:mergeCell ref="J6:L6"/>
+    <x:mergeCell ref="A9:L9"/>
+    <x:mergeCell ref="A10:L12"/>
+    <x:mergeCell ref="A14:L14"/>
+    <x:mergeCell ref="A15:L17"/>
+    <x:mergeCell ref="A19:L19"/>
+    <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R465a05d707bb4b27"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb21ec5a2cc042e2"/>
 </x:worksheet>
 </file>
 
@@ -3372,7 +3715,7 @@
         <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="J54" s="216" t="str">
-        <x:v>补齐外郭城区域、永安渠六坊编号和平康坊演示数据</x:v>
+        <x:v>人工审核v7新增的外郭城、永安渠六坊和平康坊空间关系</x:v>
       </x:c>
       <x:c r="K54" s="216" t="str">
         <x:v>发布版本v3 / 第三批发布与网页验收报告v1</x:v>
@@ -3383,43 +3726,49 @@
     </x:row>
     <x:row r="55" ht="40" customHeight="1">
       <x:c r="A55" s="216" t="str">
-        <x:v>S7-01</x:v>
+        <x:v>S6-20</x:v>
       </x:c>
       <x:c r="B55" s="216" t="str">
-        <x:v>阶段七：全量提取</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C55" s="216" t="str">
-        <x:v>完成108坊功能数据</x:v>
+        <x:v>补齐正式迁移前P0结构端点并修正平康坊方向</x:v>
       </x:c>
       <x:c r="D55" s="216" t="str">
-        <x:v>同事</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E55" s="216" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>待审核</x:v>
       </x:c>
       <x:c r="F55" s="216" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G55" s="217"/>
-      <x:c r="H55" s="217"/>
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G55" s="217" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="H55" s="217" t="str">
+        <x:v>2026-08-13</x:v>
+      </x:c>
       <x:c r="I55" s="217"/>
       <x:c r="J55" s="216" t="str">
-        <x:v>小样例通过后分批提取</x:v>
+        <x:v>依次审核外郭城归属、永安渠六坊、平康坊空间关系</x:v>
       </x:c>
       <x:c r="K55" s="216" t="str">
-        <x:v>坊功能全量表</x:v>
-      </x:c>
-      <x:c r="L55" s="216"/>
+        <x:v>小型样例v7 / 平台导入包v3 / P0结构补全说明v1</x:v>
+      </x:c>
+      <x:c r="L55" s="216" t="str">
+        <x:v>新增9实体、14关系、1来源、2片段；57实体/62关系；0错误、0警告；未导入平台</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="40" customHeight="1">
       <x:c r="A56" s="216" t="str">
-        <x:v>S7-02</x:v>
+        <x:v>S7-01</x:v>
       </x:c>
       <x:c r="B56" s="216" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C56" s="216" t="str">
-        <x:v>完成道路分级数据</x:v>
+        <x:v>完成108坊功能数据</x:v>
       </x:c>
       <x:c r="D56" s="216" t="str">
         <x:v>同事</x:v>
@@ -3434,22 +3783,22 @@
       <x:c r="H56" s="217"/>
       <x:c r="I56" s="217"/>
       <x:c r="J56" s="216" t="str">
-        <x:v>分批提取与审核</x:v>
+        <x:v>小样例通过后分批提取</x:v>
       </x:c>
       <x:c r="K56" s="216" t="str">
-        <x:v>道路全量表</x:v>
+        <x:v>坊功能全量表</x:v>
       </x:c>
       <x:c r="L56" s="216"/>
     </x:row>
     <x:row r="57" ht="40" customHeight="1">
       <x:c r="A57" s="216" t="str">
-        <x:v>S7-03</x:v>
+        <x:v>S7-02</x:v>
       </x:c>
       <x:c r="B57" s="216" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C57" s="216" t="str">
-        <x:v>完成水渠数据</x:v>
+        <x:v>完成道路分级数据</x:v>
       </x:c>
       <x:c r="D57" s="216" t="str">
         <x:v>同事</x:v>
@@ -3467,22 +3816,22 @@
         <x:v>分批提取与审核</x:v>
       </x:c>
       <x:c r="K57" s="216" t="str">
-        <x:v>水渠全量表</x:v>
+        <x:v>道路全量表</x:v>
       </x:c>
       <x:c r="L57" s="216"/>
     </x:row>
     <x:row r="58" ht="40" customHeight="1">
       <x:c r="A58" s="216" t="str">
-        <x:v>S7-04</x:v>
+        <x:v>S7-03</x:v>
       </x:c>
       <x:c r="B58" s="216" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C58" s="216" t="str">
-        <x:v>完成城门数据</x:v>
+        <x:v>完成水渠数据</x:v>
       </x:c>
       <x:c r="D58" s="216" t="str">
-        <x:v>我</x:v>
+        <x:v>同事</x:v>
       </x:c>
       <x:c r="E58" s="216" t="str">
         <x:v>尚未开始</x:v>
@@ -3494,22 +3843,22 @@
       <x:c r="H58" s="217"/>
       <x:c r="I58" s="217"/>
       <x:c r="J58" s="216" t="str">
-        <x:v>严格区分城门与内门</x:v>
+        <x:v>分批提取与审核</x:v>
       </x:c>
       <x:c r="K58" s="216" t="str">
-        <x:v>城门全量表</x:v>
+        <x:v>水渠全量表</x:v>
       </x:c>
       <x:c r="L58" s="216"/>
     </x:row>
     <x:row r="59" ht="44" customHeight="1">
       <x:c r="A59" s="216" t="str">
-        <x:v>S7-05</x:v>
+        <x:v>S7-04</x:v>
       </x:c>
       <x:c r="B59" s="216" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C59" s="216" t="str">
-        <x:v>完成尺度关系数据</x:v>
+        <x:v>完成城门数据</x:v>
       </x:c>
       <x:c r="D59" s="216" t="str">
         <x:v>我</x:v>
@@ -3524,22 +3873,22 @@
       <x:c r="H59" s="217"/>
       <x:c r="I59" s="217"/>
       <x:c r="J59" s="216" t="str">
-        <x:v>全部公式人工复核</x:v>
+        <x:v>严格区分城门与内门</x:v>
       </x:c>
       <x:c r="K59" s="216" t="str">
-        <x:v>尺度关系全量表</x:v>
+        <x:v>城门全量表</x:v>
       </x:c>
       <x:c r="L59" s="216"/>
     </x:row>
     <x:row r="60" ht="44" customHeight="1">
       <x:c r="A60" s="216" t="str">
-        <x:v>S7-06</x:v>
+        <x:v>S7-05</x:v>
       </x:c>
       <x:c r="B60" s="216" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C60" s="216" t="str">
-        <x:v>完成功能分区规则</x:v>
+        <x:v>完成尺度关系数据</x:v>
       </x:c>
       <x:c r="D60" s="216" t="str">
         <x:v>我</x:v>
@@ -3554,55 +3903,55 @@
       <x:c r="H60" s="217"/>
       <x:c r="I60" s="217"/>
       <x:c r="J60" s="216" t="str">
-        <x:v>必须检索反例</x:v>
+        <x:v>全部公式人工复核</x:v>
       </x:c>
       <x:c r="K60" s="216" t="str">
-        <x:v>规则全量表</x:v>
+        <x:v>尺度关系全量表</x:v>
       </x:c>
       <x:c r="L60" s="216"/>
     </x:row>
     <x:row r="61" ht="44" customHeight="1">
       <x:c r="A61" s="216" t="str">
-        <x:v>S8-01</x:v>
+        <x:v>S7-06</x:v>
       </x:c>
       <x:c r="B61" s="216" t="str">
-        <x:v>阶段八：质量检查</x:v>
+        <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C61" s="216" t="str">
-        <x:v>完成数据完整性、历史语义和数值检查</x:v>
+        <x:v>完成功能分区规则</x:v>
       </x:c>
       <x:c r="D61" s="216" t="str">
-        <x:v>共同</x:v>
+        <x:v>我</x:v>
       </x:c>
       <x:c r="E61" s="216" t="str">
         <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F61" s="216" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G61" s="217"/>
       <x:c r="H61" s="217"/>
       <x:c r="I61" s="217"/>
       <x:c r="J61" s="216" t="str">
-        <x:v>全量导入前完成</x:v>
+        <x:v>必须检索反例</x:v>
       </x:c>
       <x:c r="K61" s="216" t="str">
-        <x:v>质量报告</x:v>
+        <x:v>规则全量表</x:v>
       </x:c>
       <x:c r="L61" s="216"/>
     </x:row>
     <x:row r="62" ht="48" customHeight="1">
       <x:c r="A62" s="216" t="str">
-        <x:v>S8-02</x:v>
+        <x:v>S8-01</x:v>
       </x:c>
       <x:c r="B62" s="216" t="str">
         <x:v>阶段八：质量检查</x:v>
       </x:c>
       <x:c r="C62" s="216" t="str">
-        <x:v>完成系统测试与重复导入测试</x:v>
+        <x:v>完成数据完整性、历史语义和数值检查</x:v>
       </x:c>
       <x:c r="D62" s="216" t="str">
-        <x:v>Codex</x:v>
+        <x:v>共同</x:v>
       </x:c>
       <x:c r="E62" s="216" t="str">
         <x:v>尚未开始</x:v>
@@ -3614,25 +3963,25 @@
       <x:c r="H62" s="217"/>
       <x:c r="I62" s="217"/>
       <x:c r="J62" s="216" t="str">
-        <x:v>发布前完成</x:v>
+        <x:v>全量导入前完成</x:v>
       </x:c>
       <x:c r="K62" s="216" t="str">
-        <x:v>系统测试报告</x:v>
+        <x:v>质量报告</x:v>
       </x:c>
       <x:c r="L62" s="216"/>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
       <x:c r="A63" s="216" t="str">
-        <x:v>S9-01</x:v>
+        <x:v>S8-02</x:v>
       </x:c>
       <x:c r="B63" s="216" t="str">
-        <x:v>阶段九：发布交付</x:v>
+        <x:v>阶段八：质量检查</x:v>
       </x:c>
       <x:c r="C63" s="216" t="str">
-        <x:v>冻结第一版数据并生成文档</x:v>
+        <x:v>完成系统测试与重复导入测试</x:v>
       </x:c>
       <x:c r="D63" s="216" t="str">
-        <x:v>共同</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E63" s="216" t="str">
         <x:v>尚未开始</x:v>
@@ -3644,22 +3993,22 @@
       <x:c r="H63" s="217"/>
       <x:c r="I63" s="217"/>
       <x:c r="J63" s="216" t="str">
-        <x:v>完成最终审核</x:v>
+        <x:v>发布前完成</x:v>
       </x:c>
       <x:c r="K63" s="216" t="str">
-        <x:v>tang_changan_v1</x:v>
+        <x:v>系统测试报告</x:v>
       </x:c>
       <x:c r="L63" s="216"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
-        <x:v>S9-02</x:v>
+        <x:v>S9-01</x:v>
       </x:c>
       <x:c r="B64" t="str">
         <x:v>阶段九：发布交付</x:v>
       </x:c>
       <x:c r="C64" t="str">
-        <x:v>发布v1并建立Git标签v1.0.0</x:v>
+        <x:v>冻结第一版数据并生成文档</x:v>
       </x:c>
       <x:c r="D64" t="str">
         <x:v>共同</x:v>
@@ -3674,12 +4023,42 @@
       <x:c r="H64"/>
       <x:c r="I64"/>
       <x:c r="J64" t="str">
+        <x:v>完成最终审核</x:v>
+      </x:c>
+      <x:c r="K64" t="str">
+        <x:v>tang_changan_v1</x:v>
+      </x:c>
+      <x:c r="L64"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>S9-02</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>阶段九：发布交付</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>发布v1并建立Git标签v1.0.0</x:v>
+      </x:c>
+      <x:c r="D65" t="str">
+        <x:v>共同</x:v>
+      </x:c>
+      <x:c r="E65" t="str">
+        <x:v>尚未开始</x:v>
+      </x:c>
+      <x:c r="F65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G65"/>
+      <x:c r="H65"/>
+      <x:c r="I65"/>
+      <x:c r="J65" t="str">
         <x:v>检查权限与版权</x:v>
       </x:c>
-      <x:c r="K64" t="str">
+      <x:c r="K65" t="str">
         <x:v>正式发布</x:v>
       </x:c>
-      <x:c r="L64"/>
+      <x:c r="L65"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4698,6 +5077,26 @@
         <x:v>公开21实体、16关系、2来源、12片段；搜索索引33文档；工作清单已按任务编号重排</x:v>
       </x:c>
     </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>补齐正式迁移前3项P0结构缺口，并发现、修正平康坊空间方向错误</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>小型样例v7 / 平台导入包v3 / P0结构补全说明v1 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>人工审核外郭城归属、永安渠六坊和两坊空间关系；通过后升级提取Skill</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>新增9实体、14关系、1来源、2片段；57实体/62关系；0错误、0警告；未导入平台</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Ra5bbd8064b864423"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Re4cd9d4b08a54f91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R834528c94f6e4ef1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rf8116534fb464b07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Re1b14d90ac7842b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R0b89e2960b7a47ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rd046b499ff0d40d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R784279888e714b15"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -81,8 +81,13 @@
       <x:color rgb="FF333333"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF333333"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="21">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -122,6 +127,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF4CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF173F5F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F3E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF4EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EEF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F766E"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -245,7 +280,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="326">
+  <x:cellXfs count="434">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1010,6 +1045,250 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1275,7 +1554,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6b7f53debab44831"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re7b80a8767ef426d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1494,90 +1773,90 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="221" t="str">
+      <x:c r="A1" s="329" t="str">
         <x:v>唐长安城知识图谱 · 今日进度看板</x:v>
       </x:c>
-      <x:c r="B1" s="221"/>
-      <x:c r="C1" s="221"/>
-      <x:c r="D1" s="221"/>
-      <x:c r="E1" s="221"/>
-      <x:c r="F1" s="221"/>
-      <x:c r="G1" s="221"/>
-      <x:c r="H1" s="221"/>
-      <x:c r="I1" s="221"/>
-      <x:c r="J1" s="221"/>
-      <x:c r="K1" s="221"/>
-      <x:c r="L1" s="221"/>
+      <x:c r="B1" s="329"/>
+      <x:c r="C1" s="329"/>
+      <x:c r="D1" s="329"/>
+      <x:c r="E1" s="329"/>
+      <x:c r="F1" s="329"/>
+      <x:c r="G1" s="329"/>
+      <x:c r="H1" s="329"/>
+      <x:c r="I1" s="329"/>
+      <x:c r="J1" s="329"/>
+      <x:c r="K1" s="329"/>
+      <x:c r="L1" s="329"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="224" t="str">
+      <x:c r="A3" s="332" t="str">
         <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-12</x:v>
       </x:c>
-      <x:c r="B3" s="224"/>
-      <x:c r="C3" s="224"/>
-      <x:c r="D3" s="224"/>
-      <x:c r="E3" s="224"/>
-      <x:c r="F3" s="224"/>
-      <x:c r="G3" s="224"/>
-      <x:c r="H3" s="224"/>
-      <x:c r="I3" s="224"/>
-      <x:c r="J3" s="224"/>
-      <x:c r="K3" s="224"/>
-      <x:c r="L3" s="224"/>
+      <x:c r="B3" s="332"/>
+      <x:c r="C3" s="332"/>
+      <x:c r="D3" s="332"/>
+      <x:c r="E3" s="332"/>
+      <x:c r="F3" s="332"/>
+      <x:c r="G3" s="332"/>
+      <x:c r="H3" s="332"/>
+      <x:c r="I3" s="332"/>
+      <x:c r="J3" s="332"/>
+      <x:c r="K3" s="332"/>
+      <x:c r="L3" s="332"/>
     </x:row>
     <x:row r="4">
       <x:c r="N4"/>
       <x:c r="O4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="226" t="str">
+      <x:c r="A5" s="334" t="str">
         <x:v>总任务数</x:v>
       </x:c>
-      <x:c r="B5" s="226"/>
-      <x:c r="C5" s="226"/>
-      <x:c r="D5" s="226" t="str">
+      <x:c r="B5" s="334"/>
+      <x:c r="C5" s="334"/>
+      <x:c r="D5" s="334" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="E5" s="226"/>
-      <x:c r="F5" s="226"/>
-      <x:c r="G5" s="226" t="str">
+      <x:c r="E5" s="334"/>
+      <x:c r="F5" s="334"/>
+      <x:c r="G5" s="334" t="str">
         <x:v>进行中</x:v>
       </x:c>
-      <x:c r="H5" s="226"/>
-      <x:c r="I5" s="226"/>
-      <x:c r="J5" s="226" t="str">
+      <x:c r="H5" s="334"/>
+      <x:c r="I5" s="334"/>
+      <x:c r="J5" s="334" t="str">
         <x:v>完成率</x:v>
       </x:c>
-      <x:c r="K5" s="226"/>
-      <x:c r="L5" s="226"/>
+      <x:c r="K5" s="334"/>
+      <x:c r="L5" s="334"/>
       <x:c r="N5"/>
       <x:c r="O5"/>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="230" t="n">
+      <x:c r="A6" s="338" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$200)</x:f>
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B6" s="230"/>
-      <x:c r="C6" s="230"/>
-      <x:c r="D6" s="230" t="n">
+      <x:c r="B6" s="338"/>
+      <x:c r="C6" s="338"/>
+      <x:c r="D6" s="338" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$200,"已完成")</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E6" s="230"/>
-      <x:c r="F6" s="230"/>
-      <x:c r="G6" s="234" t="n">
+      <x:c r="E6" s="338"/>
+      <x:c r="F6" s="338"/>
+      <x:c r="G6" s="342" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$200,"进行中")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H6" s="234"/>
-      <x:c r="I6" s="234"/>
-      <x:c r="J6" s="239" t="n">
+      <x:c r="H6" s="342"/>
+      <x:c r="I6" s="342"/>
+      <x:c r="J6" s="347" t="n">
         <x:f>IFERROR(D6/A6,0)</x:f>
         <x:v>0.4838709677419355</x:v>
       </x:c>
-      <x:c r="K6" s="239"/>
-      <x:c r="L6" s="239"/>
+      <x:c r="K6" s="347"/>
+      <x:c r="L6" s="347"/>
       <x:c r="N6"/>
       <x:c r="O6"/>
     </x:row>
@@ -1614,68 +1893,68 @@
       <x:c r="O8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="243" t="str">
+      <x:c r="A9" s="351" t="str">
         <x:v>现在做到哪里</x:v>
       </x:c>
-      <x:c r="B9" s="243"/>
-      <x:c r="C9" s="243"/>
-      <x:c r="D9" s="243"/>
-      <x:c r="E9" s="243"/>
-      <x:c r="F9" s="243"/>
-      <x:c r="G9" s="243"/>
-      <x:c r="H9" s="243"/>
-      <x:c r="I9" s="243"/>
-      <x:c r="J9" s="243"/>
-      <x:c r="K9" s="243"/>
-      <x:c r="L9" s="243"/>
+      <x:c r="B9" s="351"/>
+      <x:c r="C9" s="351"/>
+      <x:c r="D9" s="351"/>
+      <x:c r="E9" s="351"/>
+      <x:c r="F9" s="351"/>
+      <x:c r="G9" s="351"/>
+      <x:c r="H9" s="351"/>
+      <x:c r="I9" s="351"/>
+      <x:c r="J9" s="351"/>
+      <x:c r="K9" s="351"/>
+      <x:c r="L9" s="351"/>
       <x:c r="N9"/>
       <x:c r="O9"/>
     </x:row>
-    <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="262" t="str">
-        <x:v>当前阶段：正式迁移前P0结构补全已完成，等待人工审核
-总体状态：v7包含7来源、31片段、57实体、62关系；结构校验0错误、0警告
-本次完成：建立外郭城实体、补齐永安渠六坊编号、替换平康坊占位记录，并修正其与崇仁坊的南北方向</x:v>
-      </x:c>
-      <x:c r="B10" s="263"/>
-      <x:c r="C10" s="263"/>
-      <x:c r="D10" s="263"/>
-      <x:c r="E10" s="263"/>
-      <x:c r="F10" s="263"/>
-      <x:c r="G10" s="263"/>
-      <x:c r="H10" s="263"/>
-      <x:c r="I10" s="263"/>
-      <x:c r="J10" s="263"/>
-      <x:c r="K10" s="263"/>
-      <x:c r="L10" s="264"/>
-    </x:row>
-    <x:row r="11" ht="22" customHeight="1">
-      <x:c r="A11" s="265"/>
-      <x:c r="B11" s="266"/>
-      <x:c r="C11" s="266"/>
-      <x:c r="D11" s="266"/>
-      <x:c r="E11" s="266"/>
-      <x:c r="F11" s="266"/>
-      <x:c r="G11" s="266"/>
-      <x:c r="H11" s="266"/>
-      <x:c r="I11" s="266"/>
-      <x:c r="J11" s="266"/>
-      <x:c r="K11" s="266"/>
-      <x:c r="L11" s="267"/>
-    </x:row>
-    <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="268"/>
-      <x:c r="B12" s="269"/>
-      <x:c r="C12" s="269"/>
-      <x:c r="D12" s="269"/>
-      <x:c r="E12" s="269"/>
-      <x:c r="F12" s="269"/>
-      <x:c r="G12" s="269"/>
-      <x:c r="H12" s="269"/>
-      <x:c r="I12" s="269"/>
-      <x:c r="J12" s="269"/>
-      <x:c r="K12" s="269"/>
-      <x:c r="L12" s="270"/>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="370" t="str">
+        <x:v>当前阶段：正式迁移前P0样例已完成第二轮修正，等待最后一处人工复核
+总体状态：v8包含7来源、32片段、59实体、77关系；结构校验0错误、0警告
+本次修正：ROAD-0004/0009名称仍为东/西第三街；x=±3坊列area改为第二街与第三街之间，并补齐两侧边界道路关系</x:v>
+      </x:c>
+      <x:c r="B10" s="371"/>
+      <x:c r="C10" s="371"/>
+      <x:c r="D10" s="371"/>
+      <x:c r="E10" s="371"/>
+      <x:c r="F10" s="371"/>
+      <x:c r="G10" s="371"/>
+      <x:c r="H10" s="371"/>
+      <x:c r="I10" s="371"/>
+      <x:c r="J10" s="371"/>
+      <x:c r="K10" s="371"/>
+      <x:c r="L10" s="372"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="373"/>
+      <x:c r="B11" s="374"/>
+      <x:c r="C11" s="374"/>
+      <x:c r="D11" s="374"/>
+      <x:c r="E11" s="374"/>
+      <x:c r="F11" s="374"/>
+      <x:c r="G11" s="374"/>
+      <x:c r="H11" s="374"/>
+      <x:c r="I11" s="374"/>
+      <x:c r="J11" s="374"/>
+      <x:c r="K11" s="374"/>
+      <x:c r="L11" s="375"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="376"/>
+      <x:c r="B12" s="377"/>
+      <x:c r="C12" s="377"/>
+      <x:c r="D12" s="377"/>
+      <x:c r="E12" s="377"/>
+      <x:c r="F12" s="377"/>
+      <x:c r="G12" s="377"/>
+      <x:c r="H12" s="377"/>
+      <x:c r="I12" s="377"/>
+      <x:c r="J12" s="377"/>
+      <x:c r="K12" s="377"/>
+      <x:c r="L12" s="378"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13"/>
@@ -1686,66 +1965,66 @@
       <x:c r="F13"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="243" t="str">
+      <x:c r="A14" s="351" t="str">
         <x:v>下一步只做这三件事</x:v>
       </x:c>
-      <x:c r="B14" s="243"/>
-      <x:c r="C14" s="243"/>
-      <x:c r="D14" s="243"/>
-      <x:c r="E14" s="243"/>
-      <x:c r="F14" s="243"/>
-      <x:c r="G14" s="243"/>
-      <x:c r="H14" s="243"/>
-      <x:c r="I14" s="243"/>
-      <x:c r="J14" s="243"/>
-      <x:c r="K14" s="243"/>
-      <x:c r="L14" s="243"/>
-    </x:row>
-    <x:row r="15" ht="22" customHeight="1">
-      <x:c r="A15" s="289" t="str">
-        <x:v>1. 审核外郭城TC-AREA-0003及5个城门归属关系。
-2. 审核永安渠六坊关系，重点确认‘廷福/延福’异文。
-3. 审核平康坊SOUTH_OF崇仁坊及两坊邻近TC-ROAD-0004；通过后升级提取Skill。</x:v>
-      </x:c>
-      <x:c r="B15" s="290"/>
-      <x:c r="C15" s="290"/>
-      <x:c r="D15" s="290"/>
-      <x:c r="E15" s="290"/>
-      <x:c r="F15" s="290"/>
-      <x:c r="G15" s="290"/>
-      <x:c r="H15" s="290"/>
-      <x:c r="I15" s="290"/>
-      <x:c r="J15" s="290"/>
-      <x:c r="K15" s="290"/>
-      <x:c r="L15" s="291"/>
-    </x:row>
-    <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="292"/>
-      <x:c r="B16" s="293"/>
-      <x:c r="C16" s="293"/>
-      <x:c r="D16" s="293"/>
-      <x:c r="E16" s="293"/>
-      <x:c r="F16" s="293"/>
-      <x:c r="G16" s="293"/>
-      <x:c r="H16" s="293"/>
-      <x:c r="I16" s="293"/>
-      <x:c r="J16" s="293"/>
-      <x:c r="K16" s="293"/>
-      <x:c r="L16" s="294"/>
-    </x:row>
-    <x:row r="17" ht="22" customHeight="1">
-      <x:c r="A17" s="295"/>
-      <x:c r="B17" s="296"/>
-      <x:c r="C17" s="296"/>
-      <x:c r="D17" s="296"/>
-      <x:c r="E17" s="296"/>
-      <x:c r="F17" s="296"/>
-      <x:c r="G17" s="296"/>
-      <x:c r="H17" s="296"/>
-      <x:c r="I17" s="296"/>
-      <x:c r="J17" s="296"/>
-      <x:c r="K17" s="296"/>
-      <x:c r="L17" s="297"/>
+      <x:c r="B14" s="351"/>
+      <x:c r="C14" s="351"/>
+      <x:c r="D14" s="351"/>
+      <x:c r="E14" s="351"/>
+      <x:c r="F14" s="351"/>
+      <x:c r="G14" s="351"/>
+      <x:c r="H14" s="351"/>
+      <x:c r="I14" s="351"/>
+      <x:c r="J14" s="351"/>
+      <x:c r="K14" s="351"/>
+      <x:c r="L14" s="351"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="397" t="str">
+        <x:v>1. 只核对崇仁坊、平康坊的area是否为‘东第二街与东第三街之间’。
+2. 只核对延康坊至大通坊六坊的area是否为‘西第二街与西第三街之间’。
+3. 通过后再将本批待审核记录转为审核通过，并进入平台导入与Skill升级。</x:v>
+      </x:c>
+      <x:c r="B15" s="398"/>
+      <x:c r="C15" s="398"/>
+      <x:c r="D15" s="398"/>
+      <x:c r="E15" s="398"/>
+      <x:c r="F15" s="398"/>
+      <x:c r="G15" s="398"/>
+      <x:c r="H15" s="398"/>
+      <x:c r="I15" s="398"/>
+      <x:c r="J15" s="398"/>
+      <x:c r="K15" s="398"/>
+      <x:c r="L15" s="399"/>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="400"/>
+      <x:c r="B16" s="401"/>
+      <x:c r="C16" s="401"/>
+      <x:c r="D16" s="401"/>
+      <x:c r="E16" s="401"/>
+      <x:c r="F16" s="401"/>
+      <x:c r="G16" s="401"/>
+      <x:c r="H16" s="401"/>
+      <x:c r="I16" s="401"/>
+      <x:c r="J16" s="401"/>
+      <x:c r="K16" s="401"/>
+      <x:c r="L16" s="402"/>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="403"/>
+      <x:c r="B17" s="404"/>
+      <x:c r="C17" s="404"/>
+      <x:c r="D17" s="404"/>
+      <x:c r="E17" s="404"/>
+      <x:c r="F17" s="404"/>
+      <x:c r="G17" s="404"/>
+      <x:c r="H17" s="404"/>
+      <x:c r="I17" s="404"/>
+      <x:c r="J17" s="404"/>
+      <x:c r="K17" s="404"/>
+      <x:c r="L17" s="405"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18"/>
@@ -1756,81 +2035,80 @@
       <x:c r="F18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="243" t="str">
+      <x:c r="A19" s="351" t="str">
         <x:v>重要提醒</x:v>
       </x:c>
-      <x:c r="B19" s="243"/>
-      <x:c r="C19" s="243"/>
-      <x:c r="D19" s="243"/>
-      <x:c r="E19" s="243"/>
-      <x:c r="F19" s="243"/>
-      <x:c r="G19" s="243"/>
-      <x:c r="H19" s="243"/>
-      <x:c r="I19" s="243"/>
-      <x:c r="J19" s="243"/>
-      <x:c r="K19" s="243"/>
-      <x:c r="L19" s="243"/>
-    </x:row>
-    <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="317" t="str">
-        <x:v>v7是当前小型样例工作版本，平台导入包v3为待审核导入基线。本次新增数据均为待审核，尚未写入或发布到平台。
-注意：项目坐标y值向南递增，所以平康坊(3,1)位于崇仁坊(3,0)南侧。</x:v>
-      </x:c>
-      <x:c r="B20" s="318"/>
-      <x:c r="C20" s="318"/>
-      <x:c r="D20" s="318"/>
-      <x:c r="E20" s="318"/>
-      <x:c r="F20" s="318"/>
-      <x:c r="G20" s="318"/>
-      <x:c r="H20" s="318"/>
-      <x:c r="I20" s="318"/>
-      <x:c r="J20" s="318"/>
-      <x:c r="K20" s="318"/>
-      <x:c r="L20" s="319"/>
-    </x:row>
-    <x:row r="21" ht="22" customHeight="1">
-      <x:c r="A21" s="320"/>
-      <x:c r="B21" s="321"/>
-      <x:c r="C21" s="321"/>
-      <x:c r="D21" s="321"/>
-      <x:c r="E21" s="321"/>
-      <x:c r="F21" s="321"/>
-      <x:c r="G21" s="321"/>
-      <x:c r="H21" s="321"/>
-      <x:c r="I21" s="321"/>
-      <x:c r="J21" s="321"/>
-      <x:c r="K21" s="321"/>
-      <x:c r="L21" s="322"/>
-    </x:row>
-    <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="323"/>
-      <x:c r="B22" s="324"/>
-      <x:c r="C22" s="324"/>
-      <x:c r="D22" s="324"/>
-      <x:c r="E22" s="324"/>
-      <x:c r="F22" s="324"/>
-      <x:c r="G22" s="324"/>
-      <x:c r="H22" s="324"/>
-      <x:c r="I22" s="324"/>
-      <x:c r="J22" s="324"/>
-      <x:c r="K22" s="324"/>
-      <x:c r="L22" s="325"/>
+      <x:c r="B19" s="351"/>
+      <x:c r="C19" s="351"/>
+      <x:c r="D19" s="351"/>
+      <x:c r="E19" s="351"/>
+      <x:c r="F19" s="351"/>
+      <x:c r="G19" s="351"/>
+      <x:c r="H19" s="351"/>
+      <x:c r="I19" s="351"/>
+      <x:c r="J19" s="351"/>
+      <x:c r="K19" s="351"/>
+      <x:c r="L19" s="351"/>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="425" t="str">
+        <x:v>v8是当前小型样例工作版本，平台导入包v4已通过结构校验，但尚未写入平台。用户已确认v7其余内容无问题；本轮只等待道路边界与area修正复核。ROAD-0004/0009并未改名，它们分别是x=3与x=-3坊列的一侧边界。</x:v>
+      </x:c>
+      <x:c r="B20" s="426"/>
+      <x:c r="C20" s="426"/>
+      <x:c r="D20" s="426"/>
+      <x:c r="E20" s="426"/>
+      <x:c r="F20" s="426"/>
+      <x:c r="G20" s="426"/>
+      <x:c r="H20" s="426"/>
+      <x:c r="I20" s="426"/>
+      <x:c r="J20" s="426"/>
+      <x:c r="K20" s="426"/>
+      <x:c r="L20" s="427"/>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="428"/>
+      <x:c r="B21" s="429"/>
+      <x:c r="C21" s="429"/>
+      <x:c r="D21" s="429"/>
+      <x:c r="E21" s="429"/>
+      <x:c r="F21" s="429"/>
+      <x:c r="G21" s="429"/>
+      <x:c r="H21" s="429"/>
+      <x:c r="I21" s="429"/>
+      <x:c r="J21" s="429"/>
+      <x:c r="K21" s="429"/>
+      <x:c r="L21" s="430"/>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="431"/>
+      <x:c r="B22" s="432"/>
+      <x:c r="C22" s="432"/>
+      <x:c r="D22" s="432"/>
+      <x:c r="E22" s="432"/>
+      <x:c r="F22" s="432"/>
+      <x:c r="G22" s="432"/>
+      <x:c r="H22" s="432"/>
+      <x:c r="I22" s="432"/>
+      <x:c r="J22" s="432"/>
+      <x:c r="K22" s="432"/>
+      <x:c r="L22" s="433"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="199"/>
-      <x:c r="B23" s="200"/>
-      <x:c r="C23" s="200"/>
-      <x:c r="D23" s="200"/>
-      <x:c r="E23" s="200"/>
-      <x:c r="F23" s="201"/>
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="202"/>
-      <x:c r="B24" s="203"/>
-      <x:c r="C24" s="203"/>
-      <x:c r="D24" s="203"/>
-      <x:c r="E24" s="203"/>
-      <x:c r="F24" s="204"/>
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1852,7 +2130,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb21ec5a2cc042e2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b9f9b79d8bc464e"/>
 </x:worksheet>
 </file>
 
@@ -3732,10 +4010,10 @@
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C55" s="216" t="str">
-        <x:v>补齐正式迁移前P0结构端点并修正平康坊方向</x:v>
+        <x:v>补齐正式迁移前P0结构端点，修正平康坊方向及x=±3坊列道路边界</x:v>
       </x:c>
       <x:c r="D55" s="216" t="str">
-        <x:v>Codex</x:v>
+        <x:v>用户 / Codex</x:v>
       </x:c>
       <x:c r="E55" s="216" t="str">
         <x:v>待审核</x:v>
@@ -3751,13 +4029,13 @@
       </x:c>
       <x:c r="I55" s="217"/>
       <x:c r="J55" s="216" t="str">
-        <x:v>依次审核外郭城归属、永安渠六坊、平康坊空间关系</x:v>
+        <x:v>只复核v8中x=±3坊列area及第二、第三街双边界关系；其余内容用户已确认无问题</x:v>
       </x:c>
       <x:c r="K55" s="216" t="str">
-        <x:v>小型样例v7 / 平台导入包v3 / P0结构补全说明v1</x:v>
+        <x:v>小型样例v8 / 平台导入包v4 / P0结构补全说明v1</x:v>
       </x:c>
       <x:c r="L55" s="216" t="str">
-        <x:v>新增9实体、14关系、1来源、2片段；57实体/62关系；0错误、0警告；未导入平台</x:v>
+        <x:v>补入ROAD-0003/0008；area改为第二街与第三街之间；59实体/77关系/32片段；0错误、0警告；未导入平台</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="40" customHeight="1">
@@ -5097,6 +5375,26 @@
         <x:v>新增9实体、14关系、1来源、2片段；57实体/62关系；0错误、0警告；未导入平台</x:v>
       </x:c>
     </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>核对ROAD-0004/0009与坊功能area，修正x=±3坊列为第二街与第三街之间，并补齐双边界关系</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>小型样例v8 / 平台导入包v4 / P0结构补全说明v1 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>只需人工复核本轮area和边界关系；通过后执行平台导入并升级提取Skill</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>新增2道路实体、14坊—道路关系、1解释片段；59实体/77关系；0错误、0警告；未导入平台</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Re1b14d90ac7842b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R0b89e2960b7a47ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rd046b499ff0d40d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R784279888e714b15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Red9d5e3307a84fc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R587521ef2e914bc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R3374ed9f69e94ef3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R910b6e0ea6aa47a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1554,7 +1554,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re7b80a8767ef426d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra29c2e4db76344f5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1841,7 +1841,7 @@
       <x:c r="C6" s="338"/>
       <x:c r="D6" s="338" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$200,"已完成")</x:f>
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E6" s="338"/>
       <x:c r="F6" s="338"/>
@@ -1853,7 +1853,7 @@
       <x:c r="I6" s="342"/>
       <x:c r="J6" s="347" t="n">
         <x:f>IFERROR(D6/A6,0)</x:f>
-        <x:v>0.4838709677419355</x:v>
+        <x:v>0.5483870967741935</x:v>
       </x:c>
       <x:c r="K6" s="347"/>
       <x:c r="L6" s="347"/>
@@ -1912,9 +1912,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="370" t="str">
-        <x:v>当前阶段：正式迁移前P0样例已完成第二轮修正，等待最后一处人工复核
-总体状态：v8包含7来源、32片段、59实体、77关系；结构校验0错误、0警告
-本次修正：ROAD-0004/0009名称仍为东/西第三街；x=±3坊列area改为第二街与第三街之间，并补齐两侧边界道路关系</x:v>
+        <x:v>当前阶段：平台迁移P0样例与知识提取Skill v2均已完成
+稳定基线：小型样例v9为7来源、32片段、59实体、77关系；结构校验0错误、0警告
+公众端：39实体、50关系、4来源、19片段；发布v4、网页验收和Skill回归均通过</x:v>
       </x:c>
       <x:c r="B10" s="371"/>
       <x:c r="C10" s="371"/>
@@ -1982,9 +1982,9 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="397" t="str">
-        <x:v>1. 只核对崇仁坊、平康坊的area是否为‘东第二街与东第三街之间’。
-2. 只核对延康坊至大通坊六坊的area是否为‘西第二街与西第三街之间’。
-3. 通过后再将本批待审核记录转为审核通过，并进入平台导入与Skill升级。</x:v>
+        <x:v>1. 进入阶段七全量提取，先确定下一批资料与负责人。
+2. 同事继续坊功能、道路、水渠；你负责城门、尺度关系和功能分区规则。
+3. 新论文可在全量阶段逐批精读；每批仍按Skill v2走小批量审核与发布流程。</x:v>
       </x:c>
       <x:c r="B15" s="398"/>
       <x:c r="C15" s="398"/>
@@ -2052,7 +2052,7 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="425" t="str">
-        <x:v>v8是当前小型样例工作版本，平台导入包v4已通过结构校验，但尚未写入平台。用户已确认v7其余内容无问题；本轮只等待道路边界与area修正复核。ROAD-0004/0009并未改名，它们分别是x=3与x=-3坊列的一侧边界。</x:v>
+        <x:v>当前稳定基线：小型样例v9、平台导入包v5、平台发布v4、knowledge-graph-extraction v2。正式模板保持结构用途；试录数据进入小型样例。任何新增专题字段都可以版本化调整，但必须同步转换规则、实体/关系出口和回归校验。</x:v>
       </x:c>
       <x:c r="B20" s="426"/>
       <x:c r="C20" s="426"/>
@@ -2130,7 +2130,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b9f9b79d8bc464e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R145492e249374e7a"/>
 </x:worksheet>
 </file>
 
@@ -3218,21 +3218,29 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="E33" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F33" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G33" s="17"/>
-      <x:c r="H33" s="17"/>
-      <x:c r="I33" s="17"/>
+      <x:c r="G33" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="H33" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="I33" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
       <x:c r="J33" s="16" t="str">
-        <x:v>样例通过后升级</x:v>
+        <x:v>以Skill v2执行下一批全量提取</x:v>
       </x:c>
       <x:c r="K33" s="16" t="str">
         <x:v>knowledge-graph-extraction v2</x:v>
       </x:c>
-      <x:c r="L33" s="16"/>
+      <x:c r="L33" s="16" t="str">
+        <x:v>已覆盖空间专题、三层知识、证据回溯、审核白名单和平台验收流程</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="16" t="str">
@@ -3248,21 +3256,29 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="E34" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F34" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G34" s="17"/>
-      <x:c r="H34" s="17"/>
-      <x:c r="I34" s="17"/>
+      <x:c r="G34" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="H34" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="I34" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
       <x:c r="J34" s="16" t="str">
-        <x:v>与字段规范一致</x:v>
+        <x:v>全量提取时继续检查单位换算与坐标依据</x:v>
       </x:c>
       <x:c r="K34" s="16" t="str">
-        <x:v>提取规范v2</x:v>
-      </x:c>
-      <x:c r="L34" s="16"/>
+        <x:v>Skill v2 data-model / quality-and-release</x:v>
+      </x:c>
+      <x:c r="L34" s="16" t="str">
+        <x:v>已固化坐标、双边界道路、尺度与推论分层规则</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="16" t="str">
@@ -3275,24 +3291,32 @@
         <x:v>使用小型样例测试Skill</x:v>
       </x:c>
       <x:c r="D35" s="16" t="str">
-        <x:v>共同</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E35" s="16" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F35" s="16" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G35" s="17"/>
-      <x:c r="H35" s="17"/>
-      <x:c r="I35" s="17"/>
+      <x:c r="G35" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="H35" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="I35" s="17" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
       <x:c r="J35" s="16" t="str">
-        <x:v>比较人工审核结果</x:v>
+        <x:v>用下一篇论文做首次真实批次测试</x:v>
       </x:c>
       <x:c r="K35" s="16" t="str">
-        <x:v>测试报告</x:v>
-      </x:c>
-      <x:c r="L35" s="16"/>
+        <x:v>v9回归基线 / Skill v2压缩包</x:v>
+      </x:c>
+      <x:c r="L35" s="16" t="str">
+        <x:v>v9为7来源/32片段/59实体/77关系；0错误、0警告</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="16" t="str">
@@ -4016,7 +4040,7 @@
         <x:v>用户 / Codex</x:v>
       </x:c>
       <x:c r="E55" s="216" t="str">
-        <x:v>待审核</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F55" s="216" t="str">
         <x:v>P0</x:v>
@@ -4025,17 +4049,19 @@
         <x:v>2026-08-12</x:v>
       </x:c>
       <x:c r="H55" s="217" t="str">
-        <x:v>2026-08-13</x:v>
-      </x:c>
-      <x:c r="I55" s="217"/>
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="I55" s="217" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
       <x:c r="J55" s="216" t="str">
-        <x:v>只复核v8中x=±3坊列area及第二、第三街双边界关系；其余内容用户已确认无问题</x:v>
+        <x:v>以小型样例v9和发布v4作为Skill升级的稳定样例基线</x:v>
       </x:c>
       <x:c r="K55" s="216" t="str">
-        <x:v>小型样例v8 / 平台导入包v4 / P0结构补全说明v1</x:v>
+        <x:v>小型样例v9 / 平台导入包v5 / 发布版本v4 / 第四批平台发布与网页验收报告v1</x:v>
       </x:c>
       <x:c r="L55" s="216" t="str">
-        <x:v>补入ROAD-0003/0008；area改为第二街与第三街之间；59实体/77关系/32片段；0错误、0警告；未导入平台</x:v>
+        <x:v>用户审核通过；公开39实体/50关系/4来源/19片段；图谱与检索验收通过</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="40" customHeight="1">
@@ -5395,6 +5421,46 @@
         <x:v>新增2道路实体、14坊—道路关系、1解释片段；59实体/77关系；0错误、0警告；未导入平台</x:v>
       </x:c>
     </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>审核通过P0修正，完成第四批白名单导入、选择性发布、检索索引和网页图谱验收</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>小型样例v9 / 平台导入包v5 / 发布版本v4 / 第四批平台发布与网页验收报告v1 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>升级knowledge-graph-extraction Skill，并用v9执行回归测试</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>总库59实体/77关系/7来源/32片段；公开39实体/50关系/4来源/19片段；结构0错误、0警告</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>升级并打包knowledge-graph-extraction v2，完成v9规则回归检查</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>06-Skill/knowledge-graph-extraction / knowledge-graph-extraction-v2.skill / 项目看板</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>进入阶段七全量提取，按团队分工选择下一批资料</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>固化专题表转换、三层知识、双边界道路、证据依赖、审核白名单和网页验收规则</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Red9d5e3307a84fc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R587521ef2e914bc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R3374ed9f69e94ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R910b6e0ea6aa47a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R0cf1872713a74694"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R0458e9e71603442f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R505b2756b1594a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R2edf4de07d98498a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1554,7 +1554,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra29c2e4db76344f5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R613f16ac474742ce"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1912,9 +1912,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="370" t="str">
-        <x:v>当前阶段：平台迁移P0样例与知识提取Skill v2均已完成
-稳定基线：小型样例v9为7来源、32片段、59实体、77关系；结构校验0错误、0警告
-公众端：39实体、50关系、4来源、19片段；发布v4、网页验收和Skill回归均通过</x:v>
+        <x:v>当前阶段：RoadNetwork研究解释闭环已补发并完成网页验收
+稳定基线：小型样例v10为7来源、32片段、59实体、77关系；结构校验0错误、0警告
+公众端：48实体、58关系、6来源、27片段；发布v5中RoadNetwork一跳为9节点、8关系</x:v>
       </x:c>
       <x:c r="B10" s="371"/>
       <x:c r="C10" s="371"/>
@@ -1982,9 +1982,9 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="397" t="str">
-        <x:v>1. 进入阶段七全量提取，先确定下一批资料与负责人。
-2. 同事继续坊功能、道路、水渠；你负责城门、尺度关系和功能分区规则。
-3. 新论文可在全量阶段逐批精读；每批仍按Skill v2走小批量审核与发布流程。</x:v>
+        <x:v>1. 请在图谱页查看‘唐长安道路网络’及8条研究解释关系。
+2. 确认呈现方式后进入阶段七全量提取。
+3. 科普问答TC-POPULAR-0001继续保持待审核，不会因本次补发自动公开。</x:v>
       </x:c>
       <x:c r="B15" s="398"/>
       <x:c r="C15" s="398"/>
@@ -2052,7 +2052,7 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="425" t="str">
-        <x:v>当前稳定基线：小型样例v9、平台导入包v5、平台发布v4、knowledge-graph-extraction v2。正式模板保持结构用途；试录数据进入小型样例。任何新增专题字段都可以版本化调整，但必须同步转换规则、实体/关系出口和回归校验。</x:v>
+        <x:v>当前稳定基线：小型样例v10、平台导入包v6、平台发布v5、knowledge-graph-extraction v2。RoadNetwork此前不是漏建，而是待审核状态未进入公众图谱；今后审核研究结论时必须同时检查承载对象、关系、片段和来源的状态。</x:v>
       </x:c>
       <x:c r="B20" s="426"/>
       <x:c r="C20" s="426"/>
@@ -2130,7 +2130,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R145492e249374e7a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R105c7ef4934741e6"/>
 </x:worksheet>
 </file>
 
@@ -5461,6 +5461,26 @@
         <x:v>固化专题表转换、三层知识、双边界道路、证据依赖、审核白名单和网页验收规则</x:v>
       </x:c>
     </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>补发RoadNetwork实体及8条研究结论关系，完成公众图谱验收</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>小型样例v10 / 平台导入包v6 / 发布版本v5 / 第五批发布报告v1</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>人工查看RoadNetwork图谱后进入全量提取</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>公开48实体/58关系/6来源/27片段；RoadNetwork为9节点/8关系；科普候选仍未审核</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R0cf1872713a74694"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R0458e9e71603442f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R505b2756b1594a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R2edf4de07d98498a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Re145defa8c9b4b3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R04cdbba6507b4d21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rc815b97acc834145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R72b24a4dbddf4875"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1554,7 +1554,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R613f16ac474742ce"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2769b1e64d714f31"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1912,9 +1912,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="370" t="str">
-        <x:v>当前阶段：RoadNetwork研究解释闭环已补发并完成网页验收
-稳定基线：小型样例v10为7来源、32片段、59实体、77关系；结构校验0错误、0警告
-公众端：48实体、58关系、6来源、27片段；发布v5中RoadNetwork一跳为9节点、8关系</x:v>
+        <x:v>当前阶段：唐长安测试平台导航故障已修复并完成网页验收
+稳定基线：小型样例v10、平台导入包v6、平台发布v5、knowledge-graph-extraction v2
+本次修复：第四个“空间知识检索”按钮已可用，空间检索与全局检索、来源证据已分开</x:v>
       </x:c>
       <x:c r="B10" s="371"/>
       <x:c r="C10" s="371"/>
@@ -1982,9 +1982,9 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="397" t="str">
-        <x:v>1. 请在图谱页查看‘唐长安道路网络’及8条研究解释关系。
-2. 确认呈现方式后进入阶段七全量提取。
-3. 科普问答TC-POPULAR-0001继续保持待审核，不会因本次补发自动公开。</x:v>
+        <x:v>1. 在测试平台继续抽查空间检索、来源证据和知识图谱之间的跳转。
+2. 确认平台呈现无误后，进入阶段七全量提取。
+3. 科普问答TC-POPULAR-0001继续保持待审核，不会自动公开。</x:v>
       </x:c>
       <x:c r="B15" s="398"/>
       <x:c r="C15" s="398"/>
@@ -2052,7 +2052,7 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="425" t="str">
-        <x:v>当前稳定基线：小型样例v10、平台导入包v6、平台发布v5、knowledge-graph-extraction v2。RoadNetwork此前不是漏建，而是待审核状态未进入公众图谱；今后审核研究结论时必须同时检查承载对象、关系、片段和来源的状态。</x:v>
+        <x:v>导航修复说明：原第四按钮与第二按钮使用同一路由，且搜索页在客户端切换查询参数时没有同步刷新。现已将第四按钮设为“长安空间知识检索”，并按查询类型分别高亮；数据库和知识数据均未改动。</x:v>
       </x:c>
       <x:c r="B20" s="426"/>
       <x:c r="C20" s="426"/>
@@ -2130,7 +2130,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R105c7ef4934741e6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd58bc99548d440a4"/>
 </x:worksheet>
 </file>
 
@@ -5481,6 +5481,26 @@
         <x:v>公开48实体/58关系/6来源/27片段；RoadNetwork为9节点/8关系；科普候选仍未审核</x:v>
       </x:c>
     </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>修复第四个“空间知识检索”按钮不可用及搜索页状态不同步问题，并完成生产构建与网页验收</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>唐长安测试平台前端 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>确认平台呈现后进入阶段七全量提取</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>第四按钮现进入?q=长安；第五按钮仍为SourceChunk证据检索；数据库未改动</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Re145defa8c9b4b3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R04cdbba6507b4d21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rc815b97acc834145"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R72b24a4dbddf4875"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R4f0cac7c768f4d1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rc4eea8ddc8114373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rbd6e5bc7f5f649e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R876996ae9d2b4788"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1554,7 +1554,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2769b1e64d714f31"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5596723863654e3b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1912,9 +1912,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="370" t="str">
-        <x:v>当前阶段：唐长安测试平台导航故障已修复并完成网页验收
-稳定基线：小型样例v10、平台导入包v6、平台发布v5、knowledge-graph-extraction v2
-本次修复：第四个“空间知识检索”按钮已可用，空间检索与全局检索、来源证据已分开</x:v>
+        <x:v>当前阶段：多人全量提取 Skill v3 已整理完成
+稳定基线：小型样例v10、平台导入包v6、平台发布v5、knowledge-graph-extraction v3
+协作方式：按文献分配、按专题复核、集中查重合并；个人批次不得直接发布</x:v>
       </x:c>
       <x:c r="B10" s="371"/>
       <x:c r="C10" s="371"/>
@@ -1982,9 +1982,9 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="397" t="str">
-        <x:v>1. 在测试平台继续抽查空间检索、来源证据和知识图谱之间的跳转。
-2. 确认平台呈现无误后，进入阶段七全量提取。
-3. 科普问答TC-POPULAR-0001继续保持待审核，不会自动公开。</x:v>
+        <x:v>1. 将knowledge-graph-extraction-v3.skill发给参与全量提取的同事。
+2. 先填写包内的任务分配、编号段和主实体登记表，再分发文献。
+3. 每人先完成一个小批次，由项目负责人审核一致性后再扩大提取量。</x:v>
       </x:c>
       <x:c r="B15" s="398"/>
       <x:c r="C15" s="398"/>
@@ -2052,7 +2052,7 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="425" t="str">
-        <x:v>导航修复说明：原第四按钮与第二按钮使用同一路由，且搜索页在客户端切换查询参数时没有同步刷新。现已将第四按钮设为“长安空间知识检索”，并按查询类型分别高亮；数据库和知识数据均未改动。</x:v>
+        <x:v>Skill v3 已内置正式录入模板、小型样例v10和多人协作登记模板。分工以文献为单位，避免同一证据链被专题拆散；专题负责人只做横向复核，最终合并、审核和平台导入仍集中执行。</x:v>
       </x:c>
       <x:c r="B20" s="426"/>
       <x:c r="C20" s="426"/>
@@ -2130,7 +2130,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd58bc99548d440a4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reed0d40a9d5242dd"/>
 </x:worksheet>
 </file>
 
@@ -3236,10 +3236,10 @@
         <x:v>以Skill v2执行下一批全量提取</x:v>
       </x:c>
       <x:c r="K33" s="16" t="str">
-        <x:v>knowledge-graph-extraction v2</x:v>
+        <x:v>knowledge-graph-extraction v3</x:v>
       </x:c>
       <x:c r="L33" s="16" t="str">
-        <x:v>已覆盖空间专题、三层知识、证据回溯、审核白名单和平台验收流程</x:v>
+        <x:v>已加入按文献分工、专题复核、编号段管理、集中合并规范及三份配套资产</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -5501,6 +5501,26 @@
         <x:v>第四按钮现进入?q=长安；第五按钮仍为SourceChunk证据检索；数据库未改动</x:v>
       </x:c>
     </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>将知识提取Skill升级为v3，加入多人按文献分工、专题复核和集中合并规范，并打包完整协作资产</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>knowledge-graph-extraction-v3.skill / 项目看板</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>填写任务分配与编号段后，先让每位同事完成一个小批次</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>包内含正式模板、v10稳定样例、协作登记模板；个人批次不得直接发布</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R4f0cac7c768f4d1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Rc4eea8ddc8114373"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rbd6e5bc7f5f649e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R876996ae9d2b4788"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R43960c500f7d4cf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R1e70722e8b1d45f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R734d6990f27f4be2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R3df2e875ff454612"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1554,7 +1554,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5596723863654e3b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R32ee2d8416044ef2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1912,9 +1912,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="370" t="str">
-        <x:v>当前阶段：多人全量提取 Skill v3 已整理完成
-稳定基线：小型样例v10、平台导入包v6、平台发布v5、knowledge-graph-extraction v3
-协作方式：按文献分配、按专题复核、集中查重合并；个人批次不得直接发布</x:v>
+        <x:v>当前阶段：多人全量提取准备材料已完成
+公共实体登记：已预载108坊与25条道路，共133项，全部标记“待补字段”
+协作交付：Skill v3已重新打包，并新增可直接转发的多人全量提取操作手册v1</x:v>
       </x:c>
       <x:c r="B10" s="371"/>
       <x:c r="C10" s="371"/>
@@ -1982,9 +1982,9 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="397" t="str">
-        <x:v>1. 将knowledge-graph-extraction-v3.skill发给参与全量提取的同事。
-2. 先填写包内的任务分配、编号段和主实体登记表，再分发文献。
-3. 每人先完成一个小批次，由项目负责人审核一致性后再扩大提取量。</x:v>
+        <x:v>1. 由项目负责人填写任务分配表和编号段登记表。
+2. 将Skill v3、操作手册和指定文献发给同事。
+3. 每位同事先完成一篇文献或20—30条的小批次，审核一致后再扩大。</x:v>
       </x:c>
       <x:c r="B15" s="398"/>
       <x:c r="C15" s="398"/>
@@ -2052,7 +2052,7 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="425" t="str">
-        <x:v>Skill v3 已内置正式录入模板、小型样例v10和多人协作登记模板。分工以文献为单位，避免同一证据链被专题拆散；专题负责人只做横向复核，最终合并、审核和平台导入仍集中执行。</x:v>
+        <x:v>108坊与25条道路仅进入协作模板的主实体登记表，用于统一复用编号；未批量导入正式实体表。道路中的项目描述名/推导对象保留复核提示，后续须补齐片段级证据和缺失字段。</x:v>
       </x:c>
       <x:c r="B20" s="426"/>
       <x:c r="C20" s="426"/>
@@ -2130,7 +2130,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reed0d40a9d5242dd"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70a444ada7f54e40"/>
 </x:worksheet>
 </file>
 
@@ -5521,6 +5521,26 @@
         <x:v>包内含正式模板、v10稳定样例、协作登记模板；个人批次不得直接发布</x:v>
       </x:c>
     </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>2026-08-13</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>将同事表中的108坊和25条道路导入主实体登记表，并完成可直接转发的多人全量提取操作手册</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>协作登记模板 / 操作手册v1 / knowledge-graph-extraction-v3.skill</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>填写任务和编号段后，安排每人一个小批次试运行</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>133项均为待补字段；仅锁定公共编号，不进入正式实体表或自动审核</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R43960c500f7d4cf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R1e70722e8b1d45f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R734d6990f27f4be2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R3df2e875ff454612"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R800e5d2b4f0344d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R8cca5f3d8f6540ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R480a72ab565340bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R0ecee0025a904334"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1554,7 +1554,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R32ee2d8416044ef2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf83e5fba4a674ae2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1912,9 +1912,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="370" t="str">
-        <x:v>当前阶段：多人全量提取准备材料已完成
-公共实体登记：已预载108坊与25条道路，共133项，全部标记“待补字段”
-协作交付：Skill v3已重新打包，并新增可直接转发的多人全量提取操作手册v1</x:v>
+        <x:v>当前阶段：两人全量提取编号方案已确定并写入协作模板
+成员A（你）：来源0200段、片段/人工关系2000段、新实体2000—2499
+成员B（同事）：来源0300段、片段/人工关系3000段、新实体3000—3499</x:v>
       </x:c>
       <x:c r="B10" s="371"/>
       <x:c r="C10" s="371"/>
@@ -1982,9 +1982,9 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="397" t="str">
-        <x:v>1. 由项目负责人填写任务分配表和编号段登记表。
-2. 将Skill v3、操作手册和指定文献发给同事。
-3. 每位同事先完成一篇文献或20—30条的小批次，审核一致后再扩大。</x:v>
+        <x:v>1. 在任务分配表中为两人各安排第一篇试运行文献。
+2. 两人分别从自己的编号段起始编号连续使用，并及时更新“已用至”。
+3. 每人完成一篇或20—30条后集中审核，再决定是否扩大批次。</x:v>
       </x:c>
       <x:c r="B15" s="398"/>
       <x:c r="C15" s="398"/>
@@ -2052,7 +2052,7 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="425" t="str">
-        <x:v>108坊与25条道路仅进入协作模板的主实体登记表，用于统一复用编号；未批量导入正式实体表。道路中的项目描述名/推导对象保留复核提示，后续须补齐片段级证据和缺失字段。</x:v>
+        <x:v>公共对象继续复用原编号：108坊为TC-FANG-0001—0108，道路为TC-ROAD-0001—0025。自动关系由转换程序生成，不占人工TC-REL编号；1000段及以下不再分配给新批次。</x:v>
       </x:c>
       <x:c r="B20" s="426"/>
       <x:c r="C20" s="426"/>
@@ -2130,7 +2130,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70a444ada7f54e40"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3f74ef9206d4019"/>
 </x:worksheet>
 </file>
 
@@ -5541,6 +5541,26 @@
         <x:v>133项均为待补字段；仅锁定公共编号，不进入正式实体表或自动审核</x:v>
       </x:c>
     </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>2026-08-13</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>为两人全量提取设计并写入千位分区编号方案</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>协作登记模板_两人编号段版 / Skill v3 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>在任务分配表中安排两人的首篇试运行文献</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>成员A使用2000段、成员B使用3000段；公共坊/道路复用原编号；自动关系不人工分配</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R800e5d2b4f0344d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R8cca5f3d8f6540ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R480a72ab565340bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R0ecee0025a904334"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R017bb292dd964397"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R5e1fa8e2bcf04c48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Redb13692201244f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R21abdb4de15e4514"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -280,7 +280,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="434">
+  <x:cellXfs count="468">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1290,6 +1290,108 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1554,7 +1656,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf83e5fba4a674ae2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbd82a54903ed41f1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1773,58 +1875,80 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="329" t="str">
+      <x:c r="A1" s="445" t="str">
         <x:v>唐长安城知识图谱 · 今日进度看板</x:v>
       </x:c>
-      <x:c r="B1" s="329"/>
-      <x:c r="C1" s="329"/>
-      <x:c r="D1" s="329"/>
-      <x:c r="E1" s="329"/>
-      <x:c r="F1" s="329"/>
-      <x:c r="G1" s="329"/>
-      <x:c r="H1" s="329"/>
-      <x:c r="I1" s="329"/>
-      <x:c r="J1" s="329"/>
+      <x:c r="B1" s="445"/>
+      <x:c r="C1" s="445"/>
+      <x:c r="D1" s="445"/>
+      <x:c r="E1" s="445"/>
+      <x:c r="F1" s="445"/>
+      <x:c r="G1" s="445"/>
+      <x:c r="H1" s="445"/>
+      <x:c r="I1" s="445"/>
+      <x:c r="J1" s="445"/>
       <x:c r="K1" s="329"/>
       <x:c r="L1" s="329"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="446"/>
+      <x:c r="B2" s="446"/>
+      <x:c r="C2" s="446"/>
+      <x:c r="D2" s="446"/>
+      <x:c r="E2" s="446"/>
+      <x:c r="F2" s="446"/>
+      <x:c r="G2" s="446"/>
+      <x:c r="H2" s="446"/>
+      <x:c r="I2" s="446"/>
+      <x:c r="J2" s="446"/>
+    </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="332" t="str">
-        <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-12</x:v>
-      </x:c>
-      <x:c r="B3" s="332"/>
-      <x:c r="C3" s="332"/>
-      <x:c r="D3" s="332"/>
-      <x:c r="E3" s="332"/>
-      <x:c r="F3" s="332"/>
-      <x:c r="G3" s="332"/>
-      <x:c r="H3" s="332"/>
-      <x:c r="I3" s="332"/>
-      <x:c r="J3" s="332"/>
+      <x:c r="A3" s="447" t="str">
+        <x:v>只看这一页即可：它会根据“工作清单”的状态自动更新。最近更新：2026-08-13</x:v>
+      </x:c>
+      <x:c r="B3" s="447"/>
+      <x:c r="C3" s="447"/>
+      <x:c r="D3" s="447"/>
+      <x:c r="E3" s="447"/>
+      <x:c r="F3" s="447"/>
+      <x:c r="G3" s="447"/>
+      <x:c r="H3" s="447"/>
+      <x:c r="I3" s="447"/>
+      <x:c r="J3" s="447"/>
       <x:c r="K3" s="332"/>
       <x:c r="L3" s="332"/>
     </x:row>
     <x:row r="4">
+      <x:c r="A4" s="446"/>
+      <x:c r="B4" s="446"/>
+      <x:c r="C4" s="446"/>
+      <x:c r="D4" s="446"/>
+      <x:c r="E4" s="446"/>
+      <x:c r="F4" s="446"/>
+      <x:c r="G4" s="446"/>
+      <x:c r="H4" s="446"/>
+      <x:c r="I4" s="446"/>
+      <x:c r="J4" s="446"/>
       <x:c r="N4"/>
       <x:c r="O4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="334" t="str">
+      <x:c r="A5" s="448" t="str">
         <x:v>总任务数</x:v>
       </x:c>
-      <x:c r="B5" s="334"/>
-      <x:c r="C5" s="334"/>
-      <x:c r="D5" s="334" t="str">
+      <x:c r="B5" s="448"/>
+      <x:c r="C5" s="448"/>
+      <x:c r="D5" s="448" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="E5" s="334"/>
-      <x:c r="F5" s="334"/>
-      <x:c r="G5" s="334" t="str">
+      <x:c r="E5" s="448"/>
+      <x:c r="F5" s="448"/>
+      <x:c r="G5" s="448" t="str">
         <x:v>进行中</x:v>
       </x:c>
-      <x:c r="H5" s="334"/>
-      <x:c r="I5" s="334"/>
-      <x:c r="J5" s="334" t="str">
+      <x:c r="H5" s="448"/>
+      <x:c r="I5" s="448"/>
+      <x:c r="J5" s="448" t="str">
         <x:v>完成率</x:v>
       </x:c>
       <x:c r="K5" s="334"/>
@@ -1833,27 +1957,27 @@
       <x:c r="O5"/>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="338" t="n">
+      <x:c r="A6" s="449" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$200)</x:f>
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B6" s="338"/>
-      <x:c r="C6" s="338"/>
-      <x:c r="D6" s="338" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B6" s="449"/>
+      <x:c r="C6" s="449"/>
+      <x:c r="D6" s="449" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$200,"已完成")</x:f>
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E6" s="338"/>
-      <x:c r="F6" s="338"/>
-      <x:c r="G6" s="342" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E6" s="449"/>
+      <x:c r="F6" s="449"/>
+      <x:c r="G6" s="450" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$200,"进行中")</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="342"/>
-      <x:c r="I6" s="342"/>
-      <x:c r="J6" s="347" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H6" s="450"/>
+      <x:c r="I6" s="450"/>
+      <x:c r="J6" s="451" t="n">
         <x:f>IFERROR(D6/A6,0)</x:f>
-        <x:v>0.5483870967741935</x:v>
+        <x:v>0.5555555555555556</x:v>
       </x:c>
       <x:c r="K6" s="347"/>
       <x:c r="L6" s="347"/>
@@ -1861,208 +1985,216 @@
       <x:c r="O6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7"/>
-      <x:c r="B7"/>
-      <x:c r="C7"/>
-      <x:c r="D7"/>
-      <x:c r="E7"/>
-      <x:c r="F7"/>
-      <x:c r="G7"/>
-      <x:c r="H7"/>
-      <x:c r="I7"/>
-      <x:c r="J7"/>
+      <x:c r="A7" s="446"/>
+      <x:c r="B7" s="446"/>
+      <x:c r="C7" s="446"/>
+      <x:c r="D7" s="446"/>
+      <x:c r="E7" s="446"/>
+      <x:c r="F7" s="446"/>
+      <x:c r="G7" s="446"/>
+      <x:c r="H7" s="446"/>
+      <x:c r="I7" s="446"/>
+      <x:c r="J7" s="446"/>
       <x:c r="K7"/>
       <x:c r="L7"/>
       <x:c r="N7"/>
       <x:c r="O7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8"/>
-      <x:c r="B8"/>
-      <x:c r="C8"/>
-      <x:c r="D8"/>
-      <x:c r="E8"/>
-      <x:c r="F8"/>
-      <x:c r="G8"/>
-      <x:c r="H8"/>
-      <x:c r="I8"/>
-      <x:c r="J8"/>
+      <x:c r="A8" s="446"/>
+      <x:c r="B8" s="446"/>
+      <x:c r="C8" s="446"/>
+      <x:c r="D8" s="446"/>
+      <x:c r="E8" s="446"/>
+      <x:c r="F8" s="446"/>
+      <x:c r="G8" s="446"/>
+      <x:c r="H8" s="446"/>
+      <x:c r="I8" s="446"/>
+      <x:c r="J8" s="446"/>
       <x:c r="K8"/>
       <x:c r="L8"/>
       <x:c r="N8"/>
       <x:c r="O8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="351" t="str">
+      <x:c r="A9" s="452" t="str">
         <x:v>现在做到哪里</x:v>
       </x:c>
-      <x:c r="B9" s="351"/>
-      <x:c r="C9" s="351"/>
-      <x:c r="D9" s="351"/>
-      <x:c r="E9" s="351"/>
-      <x:c r="F9" s="351"/>
-      <x:c r="G9" s="351"/>
-      <x:c r="H9" s="351"/>
-      <x:c r="I9" s="351"/>
-      <x:c r="J9" s="351"/>
+      <x:c r="B9" s="452"/>
+      <x:c r="C9" s="452"/>
+      <x:c r="D9" s="452"/>
+      <x:c r="E9" s="452"/>
+      <x:c r="F9" s="452"/>
+      <x:c r="G9" s="452"/>
+      <x:c r="H9" s="452"/>
+      <x:c r="I9" s="452"/>
+      <x:c r="J9" s="452"/>
       <x:c r="K9" s="351"/>
       <x:c r="L9" s="351"/>
       <x:c r="N9"/>
       <x:c r="O9"/>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="370" t="str">
-        <x:v>当前阶段：两人全量提取编号方案已确定并写入协作模板
-成员A（你）：来源0200段、片段/人工关系2000段、新实体2000—2499
-成员B（同事）：来源0300段、片段/人工关系3000段、新实体3000—3499</x:v>
-      </x:c>
-      <x:c r="B10" s="371"/>
-      <x:c r="C10" s="371"/>
-      <x:c r="D10" s="371"/>
-      <x:c r="E10" s="371"/>
-      <x:c r="F10" s="371"/>
-      <x:c r="G10" s="371"/>
-      <x:c r="H10" s="371"/>
-      <x:c r="I10" s="371"/>
-      <x:c r="J10" s="371"/>
+      <x:c r="A10" s="453" t="str">
+        <x:v>当前阶段：成员A已完成《唐两京城坊考》卷一自主提取与全卷校验
+覆盖宫城、东宫、掖庭宫、皇城、大明宫、兴庆宫与三苑
+当前卷一工作簿：574个实体、886条关系、50个史料片段；基础一致性校验全部通过</x:v>
+      </x:c>
+      <x:c r="B10" s="454"/>
+      <x:c r="C10" s="454"/>
+      <x:c r="D10" s="454"/>
+      <x:c r="E10" s="454"/>
+      <x:c r="F10" s="454"/>
+      <x:c r="G10" s="454"/>
+      <x:c r="H10" s="454"/>
+      <x:c r="I10" s="454"/>
+      <x:c r="J10" s="454"/>
       <x:c r="K10" s="371"/>
       <x:c r="L10" s="372"/>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="373"/>
-      <x:c r="B11" s="374"/>
-      <x:c r="C11" s="374"/>
-      <x:c r="D11" s="374"/>
-      <x:c r="E11" s="374"/>
-      <x:c r="F11" s="374"/>
-      <x:c r="G11" s="374"/>
-      <x:c r="H11" s="374"/>
-      <x:c r="I11" s="374"/>
-      <x:c r="J11" s="374"/>
+      <x:c r="A11" s="455"/>
+      <x:c r="B11" s="456"/>
+      <x:c r="C11" s="456"/>
+      <x:c r="D11" s="456"/>
+      <x:c r="E11" s="456"/>
+      <x:c r="F11" s="456"/>
+      <x:c r="G11" s="456"/>
+      <x:c r="H11" s="456"/>
+      <x:c r="I11" s="456"/>
+      <x:c r="J11" s="456"/>
       <x:c r="K11" s="374"/>
       <x:c r="L11" s="375"/>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="376"/>
-      <x:c r="B12" s="377"/>
-      <x:c r="C12" s="377"/>
-      <x:c r="D12" s="377"/>
-      <x:c r="E12" s="377"/>
-      <x:c r="F12" s="377"/>
-      <x:c r="G12" s="377"/>
-      <x:c r="H12" s="377"/>
-      <x:c r="I12" s="377"/>
-      <x:c r="J12" s="377"/>
+      <x:c r="A12" s="457"/>
+      <x:c r="B12" s="458"/>
+      <x:c r="C12" s="458"/>
+      <x:c r="D12" s="458"/>
+      <x:c r="E12" s="458"/>
+      <x:c r="F12" s="458"/>
+      <x:c r="G12" s="458"/>
+      <x:c r="H12" s="458"/>
+      <x:c r="I12" s="458"/>
+      <x:c r="J12" s="458"/>
       <x:c r="K12" s="377"/>
       <x:c r="L12" s="378"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13"/>
-      <x:c r="B13"/>
-      <x:c r="C13"/>
-      <x:c r="D13"/>
-      <x:c r="E13"/>
-      <x:c r="F13"/>
+      <x:c r="A13" s="446"/>
+      <x:c r="B13" s="446"/>
+      <x:c r="C13" s="446"/>
+      <x:c r="D13" s="446"/>
+      <x:c r="E13" s="446"/>
+      <x:c r="F13" s="446"/>
+      <x:c r="G13" s="446"/>
+      <x:c r="H13" s="446"/>
+      <x:c r="I13" s="446"/>
+      <x:c r="J13" s="446"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="351" t="str">
+      <x:c r="A14" s="452" t="str">
         <x:v>下一步只做这三件事</x:v>
       </x:c>
-      <x:c r="B14" s="351"/>
-      <x:c r="C14" s="351"/>
-      <x:c r="D14" s="351"/>
-      <x:c r="E14" s="351"/>
-      <x:c r="F14" s="351"/>
-      <x:c r="G14" s="351"/>
-      <x:c r="H14" s="351"/>
-      <x:c r="I14" s="351"/>
-      <x:c r="J14" s="351"/>
+      <x:c r="B14" s="452"/>
+      <x:c r="C14" s="452"/>
+      <x:c r="D14" s="452"/>
+      <x:c r="E14" s="452"/>
+      <x:c r="F14" s="452"/>
+      <x:c r="G14" s="452"/>
+      <x:c r="H14" s="452"/>
+      <x:c r="I14" s="452"/>
+      <x:c r="J14" s="452"/>
       <x:c r="K14" s="351"/>
       <x:c r="L14" s="351"/>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="397" t="str">
-        <x:v>1. 在任务分配表中为两人各安排第一篇试运行文献。
-2. 两人分别从自己的编号段起始编号连续使用，并及时更新“已用至”。
-3. 每人完成一篇或20—30条后集中审核，再决定是否扩大批次。</x:v>
-      </x:c>
-      <x:c r="B15" s="398"/>
-      <x:c r="C15" s="398"/>
-      <x:c r="D15" s="398"/>
-      <x:c r="E15" s="398"/>
-      <x:c r="F15" s="398"/>
-      <x:c r="G15" s="398"/>
-      <x:c r="H15" s="398"/>
-      <x:c r="I15" s="398"/>
-      <x:c r="J15" s="398"/>
+      <x:c r="A15" s="459" t="str">
+        <x:v>1. 对卷一工作簿进行平台试导入与网页验收。
+2. 将本轮同名消歧、异文保留、位置不详对象处理规则更新到Skill。
+3. 成员A继续下一卷；成员B、C按文献提交独立批次，由A集中合并审核。</x:v>
+      </x:c>
+      <x:c r="B15" s="460"/>
+      <x:c r="C15" s="460"/>
+      <x:c r="D15" s="460"/>
+      <x:c r="E15" s="460"/>
+      <x:c r="F15" s="460"/>
+      <x:c r="G15" s="460"/>
+      <x:c r="H15" s="460"/>
+      <x:c r="I15" s="460"/>
+      <x:c r="J15" s="460"/>
       <x:c r="K15" s="398"/>
       <x:c r="L15" s="399"/>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="400"/>
-      <x:c r="B16" s="401"/>
-      <x:c r="C16" s="401"/>
-      <x:c r="D16" s="401"/>
-      <x:c r="E16" s="401"/>
-      <x:c r="F16" s="401"/>
-      <x:c r="G16" s="401"/>
-      <x:c r="H16" s="401"/>
-      <x:c r="I16" s="401"/>
-      <x:c r="J16" s="401"/>
+      <x:c r="A16" s="461"/>
+      <x:c r="B16" s="462"/>
+      <x:c r="C16" s="462"/>
+      <x:c r="D16" s="462"/>
+      <x:c r="E16" s="462"/>
+      <x:c r="F16" s="462"/>
+      <x:c r="G16" s="462"/>
+      <x:c r="H16" s="462"/>
+      <x:c r="I16" s="462"/>
+      <x:c r="J16" s="462"/>
       <x:c r="K16" s="401"/>
       <x:c r="L16" s="402"/>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="403"/>
-      <x:c r="B17" s="404"/>
-      <x:c r="C17" s="404"/>
-      <x:c r="D17" s="404"/>
-      <x:c r="E17" s="404"/>
-      <x:c r="F17" s="404"/>
-      <x:c r="G17" s="404"/>
-      <x:c r="H17" s="404"/>
-      <x:c r="I17" s="404"/>
-      <x:c r="J17" s="404"/>
+      <x:c r="A17" s="463"/>
+      <x:c r="B17" s="464"/>
+      <x:c r="C17" s="464"/>
+      <x:c r="D17" s="464"/>
+      <x:c r="E17" s="464"/>
+      <x:c r="F17" s="464"/>
+      <x:c r="G17" s="464"/>
+      <x:c r="H17" s="464"/>
+      <x:c r="I17" s="464"/>
+      <x:c r="J17" s="464"/>
       <x:c r="K17" s="404"/>
       <x:c r="L17" s="405"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
-      <x:c r="E18"/>
-      <x:c r="F18"/>
+      <x:c r="A18" s="446"/>
+      <x:c r="B18" s="446"/>
+      <x:c r="C18" s="446"/>
+      <x:c r="D18" s="446"/>
+      <x:c r="E18" s="446"/>
+      <x:c r="F18" s="446"/>
+      <x:c r="G18" s="446"/>
+      <x:c r="H18" s="446"/>
+      <x:c r="I18" s="446"/>
+      <x:c r="J18" s="446"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="351" t="str">
+      <x:c r="A19" s="452" t="str">
         <x:v>重要提醒</x:v>
       </x:c>
-      <x:c r="B19" s="351"/>
-      <x:c r="C19" s="351"/>
-      <x:c r="D19" s="351"/>
-      <x:c r="E19" s="351"/>
-      <x:c r="F19" s="351"/>
-      <x:c r="G19" s="351"/>
-      <x:c r="H19" s="351"/>
-      <x:c r="I19" s="351"/>
-      <x:c r="J19" s="351"/>
+      <x:c r="B19" s="452"/>
+      <x:c r="C19" s="452"/>
+      <x:c r="D19" s="452"/>
+      <x:c r="E19" s="452"/>
+      <x:c r="F19" s="452"/>
+      <x:c r="G19" s="452"/>
+      <x:c r="H19" s="452"/>
+      <x:c r="I19" s="452"/>
+      <x:c r="J19" s="452"/>
       <x:c r="K19" s="351"/>
       <x:c r="L19" s="351"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="425" t="str">
-        <x:v>公共对象继续复用原编号：108坊为TC-FANG-0001—0108，道路为TC-ROAD-0001—0025。自动关系由转换程序生成，不占人工TC-REL编号；1000段及以下不再分配给新批次。</x:v>
-      </x:c>
-      <x:c r="B20" s="426"/>
-      <x:c r="C20" s="426"/>
-      <x:c r="D20" s="426"/>
-      <x:c r="E20" s="426"/>
-      <x:c r="F20" s="426"/>
-      <x:c r="G20" s="426"/>
-      <x:c r="H20" s="426"/>
-      <x:c r="I20" s="426"/>
-      <x:c r="J20" s="426"/>
+      <x:c r="A20" s="465" t="str">
+        <x:v>重要提醒：公共对象由A、B、C共同复用；个人批次不得直接发布。成员A负责编号分配、集中合并、审批与平台导入；B、C按文献完成独立批次。</x:v>
+      </x:c>
+      <x:c r="B20" s="466"/>
+      <x:c r="C20" s="466"/>
+      <x:c r="D20" s="466"/>
+      <x:c r="E20" s="466"/>
+      <x:c r="F20" s="466"/>
+      <x:c r="G20" s="466"/>
+      <x:c r="H20" s="466"/>
+      <x:c r="I20" s="466"/>
+      <x:c r="J20" s="466"/>
       <x:c r="K20" s="426"/>
       <x:c r="L20" s="427"/>
     </x:row>
@@ -2130,7 +2262,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3f74ef9206d4019"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1407368238774e8d"/>
 </x:worksheet>
 </file>
 
@@ -3989,380 +4121,422 @@
       </x:c>
     </x:row>
     <x:row r="54" ht="40" customHeight="1">
-      <x:c r="A54" s="216" t="str">
+      <x:c r="A54" s="446" t="str">
         <x:v>S6-19</x:v>
       </x:c>
-      <x:c r="B54" s="216" t="str">
+      <x:c r="B54" s="446" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
-      <x:c r="C54" s="216" t="str">
+      <x:c r="C54" s="446" t="str">
         <x:v>完成第三批空间基础事实发布与网页验收</x:v>
       </x:c>
-      <x:c r="D54" s="216" t="str">
+      <x:c r="D54" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="E54" s="216" t="str">
+      <x:c r="E54" s="446" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="F54" s="216" t="str">
+      <x:c r="F54" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G54" s="217" t="str">
+      <x:c r="G54" s="467" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="H54" s="217" t="str">
+      <x:c r="H54" s="467" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="I54" s="217" t="str">
+      <x:c r="I54" s="467" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="J54" s="216" t="str">
+      <x:c r="J54" s="446" t="str">
         <x:v>人工审核v7新增的外郭城、永安渠六坊和平康坊空间关系</x:v>
       </x:c>
-      <x:c r="K54" s="216" t="str">
+      <x:c r="K54" s="446" t="str">
         <x:v>发布版本v3 / 第三批发布与网页验收报告v1</x:v>
       </x:c>
-      <x:c r="L54" s="216" t="str">
+      <x:c r="L54" s="446" t="str">
         <x:v>发布11实体、11关系、1来源、6片段；公开总量21实体/16关系/2来源/12片段；搜索索引33文档</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="40" customHeight="1">
-      <x:c r="A55" s="216" t="str">
+      <x:c r="A55" s="446" t="str">
         <x:v>S6-20</x:v>
       </x:c>
-      <x:c r="B55" s="216" t="str">
+      <x:c r="B55" s="446" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
-      <x:c r="C55" s="216" t="str">
+      <x:c r="C55" s="446" t="str">
         <x:v>补齐正式迁移前P0结构端点，修正平康坊方向及x=±3坊列道路边界</x:v>
       </x:c>
-      <x:c r="D55" s="216" t="str">
+      <x:c r="D55" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="E55" s="216" t="str">
+      <x:c r="E55" s="446" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="F55" s="216" t="str">
+      <x:c r="F55" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G55" s="217" t="str">
+      <x:c r="G55" s="467" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="H55" s="217" t="str">
+      <x:c r="H55" s="467" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="I55" s="217" t="str">
+      <x:c r="I55" s="467" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="J55" s="216" t="str">
+      <x:c r="J55" s="446" t="str">
         <x:v>以小型样例v9和发布v4作为Skill升级的稳定样例基线</x:v>
       </x:c>
-      <x:c r="K55" s="216" t="str">
+      <x:c r="K55" s="446" t="str">
         <x:v>小型样例v9 / 平台导入包v5 / 发布版本v4 / 第四批平台发布与网页验收报告v1</x:v>
       </x:c>
-      <x:c r="L55" s="216" t="str">
+      <x:c r="L55" s="446" t="str">
         <x:v>用户审核通过；公开39实体/50关系/4来源/19片段；图谱与检索验收通过</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="40" customHeight="1">
-      <x:c r="A56" s="216" t="str">
+      <x:c r="A56" s="446" t="str">
         <x:v>S7-01</x:v>
       </x:c>
-      <x:c r="B56" s="216" t="str">
+      <x:c r="B56" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
-      <x:c r="C56" s="216" t="str">
+      <x:c r="C56" s="446" t="str">
         <x:v>完成108坊功能数据</x:v>
       </x:c>
-      <x:c r="D56" s="216" t="str">
+      <x:c r="D56" s="446" t="str">
         <x:v>同事</x:v>
       </x:c>
-      <x:c r="E56" s="216" t="str">
+      <x:c r="E56" s="446" t="str">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="F56" s="446" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G56" s="467" t="str">
+        <x:v>2026-08-13</x:v>
+      </x:c>
+      <x:c r="H56" s="467"/>
+      <x:c r="I56" s="467"/>
+      <x:c r="J56" s="446" t="str">
+        <x:v>按协作包开始首篇试运行文献；复用108坊及公共对象编号</x:v>
+      </x:c>
+      <x:c r="K56" s="446" t="str">
+        <x:v>协作登记表 / 个人批次工作簿</x:v>
+      </x:c>
+      <x:c r="L56" s="446" t="str">
+        <x:v>108坊已登记为待补字段；先补证据和字段，不直接发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="40" customHeight="1">
+      <x:c r="A57" s="446" t="str">
+        <x:v>S7-02</x:v>
+      </x:c>
+      <x:c r="B57" s="446" t="str">
+        <x:v>阶段七：全量提取</x:v>
+      </x:c>
+      <x:c r="C57" s="446" t="str">
+        <x:v>完成道路分级数据</x:v>
+      </x:c>
+      <x:c r="D57" s="446" t="str">
+        <x:v>同事</x:v>
+      </x:c>
+      <x:c r="E57" s="446" t="str">
         <x:v>尚未开始</x:v>
       </x:c>
-      <x:c r="F56" s="216" t="str">
+      <x:c r="F57" s="446" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G56" s="217"/>
-      <x:c r="H56" s="217"/>
-      <x:c r="I56" s="217"/>
-      <x:c r="J56" s="216" t="str">
-        <x:v>小样例通过后分批提取</x:v>
-      </x:c>
-      <x:c r="K56" s="216" t="str">
-        <x:v>坊功能全量表</x:v>
-      </x:c>
-      <x:c r="L56" s="216"/>
-    </x:row>
-    <x:row r="57" ht="40" customHeight="1">
-      <x:c r="A57" s="216" t="str">
-        <x:v>S7-02</x:v>
-      </x:c>
-      <x:c r="B57" s="216" t="str">
+      <x:c r="G57" s="467"/>
+      <x:c r="H57" s="467"/>
+      <x:c r="I57" s="467"/>
+      <x:c r="J57" s="446" t="str">
+        <x:v>分批提取与审核</x:v>
+      </x:c>
+      <x:c r="K57" s="446" t="str">
+        <x:v>道路全量表</x:v>
+      </x:c>
+      <x:c r="L57" s="446"/>
+    </x:row>
+    <x:row r="58" ht="40" customHeight="1">
+      <x:c r="A58" s="446" t="str">
+        <x:v>S7-03</x:v>
+      </x:c>
+      <x:c r="B58" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
-      <x:c r="C57" s="216" t="str">
-        <x:v>完成道路分级数据</x:v>
-      </x:c>
-      <x:c r="D57" s="216" t="str">
+      <x:c r="C58" s="446" t="str">
+        <x:v>完成水渠数据</x:v>
+      </x:c>
+      <x:c r="D58" s="446" t="str">
         <x:v>同事</x:v>
       </x:c>
-      <x:c r="E57" s="216" t="str">
+      <x:c r="E58" s="446" t="str">
         <x:v>尚未开始</x:v>
       </x:c>
-      <x:c r="F57" s="216" t="str">
+      <x:c r="F58" s="446" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G57" s="217"/>
-      <x:c r="H57" s="217"/>
-      <x:c r="I57" s="217"/>
-      <x:c r="J57" s="216" t="str">
+      <x:c r="G58" s="467"/>
+      <x:c r="H58" s="467"/>
+      <x:c r="I58" s="467"/>
+      <x:c r="J58" s="446" t="str">
         <x:v>分批提取与审核</x:v>
       </x:c>
-      <x:c r="K57" s="216" t="str">
-        <x:v>道路全量表</x:v>
-      </x:c>
-      <x:c r="L57" s="216"/>
-    </x:row>
-    <x:row r="58" ht="40" customHeight="1">
-      <x:c r="A58" s="216" t="str">
-        <x:v>S7-03</x:v>
-      </x:c>
-      <x:c r="B58" s="216" t="str">
+      <x:c r="K58" s="446" t="str">
+        <x:v>水渠全量表</x:v>
+      </x:c>
+      <x:c r="L58" s="446"/>
+    </x:row>
+    <x:row r="59" ht="44" customHeight="1">
+      <x:c r="A59" s="446" t="str">
+        <x:v>S7-04</x:v>
+      </x:c>
+      <x:c r="B59" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
-      <x:c r="C58" s="216" t="str">
-        <x:v>完成水渠数据</x:v>
-      </x:c>
-      <x:c r="D58" s="216" t="str">
-        <x:v>同事</x:v>
-      </x:c>
-      <x:c r="E58" s="216" t="str">
+      <x:c r="C59" s="446" t="str">
+        <x:v>完成城门数据</x:v>
+      </x:c>
+      <x:c r="D59" s="446" t="str">
+        <x:v>我</x:v>
+      </x:c>
+      <x:c r="E59" s="446" t="str">
         <x:v>尚未开始</x:v>
       </x:c>
-      <x:c r="F58" s="216" t="str">
+      <x:c r="F59" s="446" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G58" s="217"/>
-      <x:c r="H58" s="217"/>
-      <x:c r="I58" s="217"/>
-      <x:c r="J58" s="216" t="str">
-        <x:v>分批提取与审核</x:v>
-      </x:c>
-      <x:c r="K58" s="216" t="str">
-        <x:v>水渠全量表</x:v>
-      </x:c>
-      <x:c r="L58" s="216"/>
-    </x:row>
-    <x:row r="59" ht="44" customHeight="1">
-      <x:c r="A59" s="216" t="str">
-        <x:v>S7-04</x:v>
-      </x:c>
-      <x:c r="B59" s="216" t="str">
+      <x:c r="G59" s="467"/>
+      <x:c r="H59" s="467"/>
+      <x:c r="I59" s="467"/>
+      <x:c r="J59" s="446" t="str">
+        <x:v>严格区分城门与内门</x:v>
+      </x:c>
+      <x:c r="K59" s="446" t="str">
+        <x:v>城门全量表</x:v>
+      </x:c>
+      <x:c r="L59" s="446"/>
+    </x:row>
+    <x:row r="60" ht="44" customHeight="1">
+      <x:c r="A60" s="446" t="str">
+        <x:v>S7-05</x:v>
+      </x:c>
+      <x:c r="B60" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
-      <x:c r="C59" s="216" t="str">
-        <x:v>完成城门数据</x:v>
-      </x:c>
-      <x:c r="D59" s="216" t="str">
+      <x:c r="C60" s="446" t="str">
+        <x:v>完成尺度关系数据</x:v>
+      </x:c>
+      <x:c r="D60" s="446" t="str">
         <x:v>我</x:v>
       </x:c>
-      <x:c r="E59" s="216" t="str">
+      <x:c r="E60" s="446" t="str">
         <x:v>尚未开始</x:v>
       </x:c>
-      <x:c r="F59" s="216" t="str">
+      <x:c r="F60" s="446" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G59" s="217"/>
-      <x:c r="H59" s="217"/>
-      <x:c r="I59" s="217"/>
-      <x:c r="J59" s="216" t="str">
-        <x:v>严格区分城门与内门</x:v>
-      </x:c>
-      <x:c r="K59" s="216" t="str">
-        <x:v>城门全量表</x:v>
-      </x:c>
-      <x:c r="L59" s="216"/>
-    </x:row>
-    <x:row r="60" ht="44" customHeight="1">
-      <x:c r="A60" s="216" t="str">
-        <x:v>S7-05</x:v>
-      </x:c>
-      <x:c r="B60" s="216" t="str">
+      <x:c r="G60" s="467"/>
+      <x:c r="H60" s="467"/>
+      <x:c r="I60" s="467"/>
+      <x:c r="J60" s="446" t="str">
+        <x:v>全部公式人工复核</x:v>
+      </x:c>
+      <x:c r="K60" s="446" t="str">
+        <x:v>尺度关系全量表</x:v>
+      </x:c>
+      <x:c r="L60" s="446"/>
+    </x:row>
+    <x:row r="61" ht="44" customHeight="1">
+      <x:c r="A61" s="446" t="str">
+        <x:v>S7-06</x:v>
+      </x:c>
+      <x:c r="B61" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
-      <x:c r="C60" s="216" t="str">
-        <x:v>完成尺度关系数据</x:v>
-      </x:c>
-      <x:c r="D60" s="216" t="str">
+      <x:c r="C61" s="446" t="str">
+        <x:v>完成功能分区规则</x:v>
+      </x:c>
+      <x:c r="D61" s="446" t="str">
         <x:v>我</x:v>
       </x:c>
-      <x:c r="E60" s="216" t="str">
+      <x:c r="E61" s="446" t="str">
         <x:v>尚未开始</x:v>
       </x:c>
-      <x:c r="F60" s="216" t="str">
+      <x:c r="F61" s="446" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G60" s="217"/>
-      <x:c r="H60" s="217"/>
-      <x:c r="I60" s="217"/>
-      <x:c r="J60" s="216" t="str">
-        <x:v>全部公式人工复核</x:v>
-      </x:c>
-      <x:c r="K60" s="216" t="str">
-        <x:v>尺度关系全量表</x:v>
-      </x:c>
-      <x:c r="L60" s="216"/>
-    </x:row>
-    <x:row r="61" ht="44" customHeight="1">
-      <x:c r="A61" s="216" t="str">
-        <x:v>S7-06</x:v>
-      </x:c>
-      <x:c r="B61" s="216" t="str">
+      <x:c r="G61" s="467"/>
+      <x:c r="H61" s="467"/>
+      <x:c r="I61" s="467"/>
+      <x:c r="J61" s="446" t="str">
+        <x:v>必须检索反例</x:v>
+      </x:c>
+      <x:c r="K61" s="446" t="str">
+        <x:v>规则全量表</x:v>
+      </x:c>
+      <x:c r="L61" s="446"/>
+    </x:row>
+    <x:row r="62" ht="48" customHeight="1">
+      <x:c r="A62" s="446" t="str">
+        <x:v>S7-07</x:v>
+      </x:c>
+      <x:c r="B62" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
-      <x:c r="C61" s="216" t="str">
-        <x:v>完成功能分区规则</x:v>
-      </x:c>
-      <x:c r="D61" s="216" t="str">
-        <x:v>我</x:v>
-      </x:c>
-      <x:c r="E61" s="216" t="str">
+      <x:c r="C62" s="446" t="str">
+        <x:v>完成《唐两京城坊考》卷一自主提取、实体关系转换与全卷校验</x:v>
+      </x:c>
+      <x:c r="D62" s="446" t="str">
+        <x:v>成员A / Codex</x:v>
+      </x:c>
+      <x:c r="E62" s="446" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F62" s="446" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G62" s="467" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="H62" s="467" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="I62" s="467" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="J62" s="446" t="str">
+        <x:v>平台试导入并将稳定规则更新到Skill</x:v>
+      </x:c>
+      <x:c r="K62" s="446" t="str">
+        <x:v>卷一工作簿 / 协作登记表 / 全卷校验记录</x:v>
+      </x:c>
+      <x:c r="L62" s="446" t="str">
+        <x:v>574实体、886关系、50片段；重复编号、重复边、悬空端点、错误引用、未登记关系类型、公式错误均为0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="48" customHeight="1">
+      <x:c r="A63" s="446" t="str">
+        <x:v>S8-01</x:v>
+      </x:c>
+      <x:c r="B63" s="446" t="str">
+        <x:v>阶段八：质量检查</x:v>
+      </x:c>
+      <x:c r="C63" s="446" t="str">
+        <x:v>完成数据完整性、历史语义和数值检查</x:v>
+      </x:c>
+      <x:c r="D63" s="446" t="str">
+        <x:v>共同</x:v>
+      </x:c>
+      <x:c r="E63" s="446" t="str">
         <x:v>尚未开始</x:v>
       </x:c>
-      <x:c r="F61" s="216" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G61" s="217"/>
-      <x:c r="H61" s="217"/>
-      <x:c r="I61" s="217"/>
-      <x:c r="J61" s="216" t="str">
-        <x:v>必须检索反例</x:v>
-      </x:c>
-      <x:c r="K61" s="216" t="str">
-        <x:v>规则全量表</x:v>
-      </x:c>
-      <x:c r="L61" s="216"/>
-    </x:row>
-    <x:row r="62" ht="48" customHeight="1">
-      <x:c r="A62" s="216" t="str">
-        <x:v>S8-01</x:v>
-      </x:c>
-      <x:c r="B62" s="216" t="str">
+      <x:c r="F63" s="446" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G63" s="467"/>
+      <x:c r="H63" s="467"/>
+      <x:c r="I63" s="467"/>
+      <x:c r="J63" s="446" t="str">
+        <x:v>全量导入前完成</x:v>
+      </x:c>
+      <x:c r="K63" s="446" t="str">
+        <x:v>质量报告</x:v>
+      </x:c>
+      <x:c r="L63" s="446"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="446" t="str">
+        <x:v>S8-02</x:v>
+      </x:c>
+      <x:c r="B64" s="446" t="str">
         <x:v>阶段八：质量检查</x:v>
       </x:c>
-      <x:c r="C62" s="216" t="str">
-        <x:v>完成数据完整性、历史语义和数值检查</x:v>
-      </x:c>
-      <x:c r="D62" s="216" t="str">
+      <x:c r="C64" s="446" t="str">
+        <x:v>完成系统测试与重复导入测试</x:v>
+      </x:c>
+      <x:c r="D64" s="446" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="E64" s="446" t="str">
+        <x:v>尚未开始</x:v>
+      </x:c>
+      <x:c r="F64" s="446" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G64" s="446"/>
+      <x:c r="H64" s="446"/>
+      <x:c r="I64" s="446"/>
+      <x:c r="J64" s="446" t="str">
+        <x:v>发布前完成</x:v>
+      </x:c>
+      <x:c r="K64" s="446" t="str">
+        <x:v>系统测试报告</x:v>
+      </x:c>
+      <x:c r="L64" s="446"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="446" t="str">
+        <x:v>S9-01</x:v>
+      </x:c>
+      <x:c r="B65" s="446" t="str">
+        <x:v>阶段九：发布交付</x:v>
+      </x:c>
+      <x:c r="C65" s="446" t="str">
+        <x:v>冻结第一版数据并生成文档</x:v>
+      </x:c>
+      <x:c r="D65" s="446" t="str">
         <x:v>共同</x:v>
       </x:c>
-      <x:c r="E62" s="216" t="str">
+      <x:c r="E65" s="446" t="str">
         <x:v>尚未开始</x:v>
       </x:c>
-      <x:c r="F62" s="216" t="str">
+      <x:c r="F65" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G62" s="217"/>
-      <x:c r="H62" s="217"/>
-      <x:c r="I62" s="217"/>
-      <x:c r="J62" s="216" t="str">
-        <x:v>全量导入前完成</x:v>
-      </x:c>
-      <x:c r="K62" s="216" t="str">
-        <x:v>质量报告</x:v>
-      </x:c>
-      <x:c r="L62" s="216"/>
-    </x:row>
-    <x:row r="63" ht="48" customHeight="1">
-      <x:c r="A63" s="216" t="str">
-        <x:v>S8-02</x:v>
-      </x:c>
-      <x:c r="B63" s="216" t="str">
-        <x:v>阶段八：质量检查</x:v>
-      </x:c>
-      <x:c r="C63" s="216" t="str">
-        <x:v>完成系统测试与重复导入测试</x:v>
-      </x:c>
-      <x:c r="D63" s="216" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
-      <x:c r="E63" s="216" t="str">
+      <x:c r="G65" s="446"/>
+      <x:c r="H65" s="446"/>
+      <x:c r="I65" s="446"/>
+      <x:c r="J65" s="446" t="str">
+        <x:v>完成最终审核</x:v>
+      </x:c>
+      <x:c r="K65" s="446" t="str">
+        <x:v>tang_changan_v1</x:v>
+      </x:c>
+      <x:c r="L65" s="446"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="446" t="str">
+        <x:v>S9-02</x:v>
+      </x:c>
+      <x:c r="B66" s="446" t="str">
+        <x:v>阶段九：发布交付</x:v>
+      </x:c>
+      <x:c r="C66" s="446" t="str">
+        <x:v>发布v1并建立Git标签v1.0.0</x:v>
+      </x:c>
+      <x:c r="D66" s="446" t="str">
+        <x:v>共同</x:v>
+      </x:c>
+      <x:c r="E66" s="446" t="str">
         <x:v>尚未开始</x:v>
       </x:c>
-      <x:c r="F63" s="216" t="str">
+      <x:c r="F66" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G63" s="217"/>
-      <x:c r="H63" s="217"/>
-      <x:c r="I63" s="217"/>
-      <x:c r="J63" s="216" t="str">
-        <x:v>发布前完成</x:v>
-      </x:c>
-      <x:c r="K63" s="216" t="str">
-        <x:v>系统测试报告</x:v>
-      </x:c>
-      <x:c r="L63" s="216"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="A64" t="str">
-        <x:v>S9-01</x:v>
-      </x:c>
-      <x:c r="B64" t="str">
-        <x:v>阶段九：发布交付</x:v>
-      </x:c>
-      <x:c r="C64" t="str">
-        <x:v>冻结第一版数据并生成文档</x:v>
-      </x:c>
-      <x:c r="D64" t="str">
-        <x:v>共同</x:v>
-      </x:c>
-      <x:c r="E64" t="str">
-        <x:v>尚未开始</x:v>
-      </x:c>
-      <x:c r="F64" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G64"/>
-      <x:c r="H64"/>
-      <x:c r="I64"/>
-      <x:c r="J64" t="str">
-        <x:v>完成最终审核</x:v>
-      </x:c>
-      <x:c r="K64" t="str">
-        <x:v>tang_changan_v1</x:v>
-      </x:c>
-      <x:c r="L64"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="A65" t="str">
-        <x:v>S9-02</x:v>
-      </x:c>
-      <x:c r="B65" t="str">
-        <x:v>阶段九：发布交付</x:v>
-      </x:c>
-      <x:c r="C65" t="str">
-        <x:v>发布v1并建立Git标签v1.0.0</x:v>
-      </x:c>
-      <x:c r="D65" t="str">
-        <x:v>共同</x:v>
-      </x:c>
-      <x:c r="E65" t="str">
-        <x:v>尚未开始</x:v>
-      </x:c>
-      <x:c r="F65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G65"/>
-      <x:c r="H65"/>
-      <x:c r="I65"/>
-      <x:c r="J65" t="str">
+      <x:c r="G66" s="446"/>
+      <x:c r="H66" s="446"/>
+      <x:c r="I66" s="446"/>
+      <x:c r="J66" s="446" t="str">
         <x:v>检查权限与版权</x:v>
       </x:c>
-      <x:c r="K65" t="str">
+      <x:c r="K66" s="446" t="str">
         <x:v>正式发布</x:v>
       </x:c>
-      <x:c r="L65"/>
+      <x:c r="L66" s="446"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5502,63 +5676,123 @@
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" t="str">
+      <x:c r="A46" s="446" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="B46" t="str">
+      <x:c r="B46" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="C46" t="str">
+      <x:c r="C46" s="446" t="str">
         <x:v>将知识提取Skill升级为v3，加入多人按文献分工、专题复核和集中合并规范，并打包完整协作资产</x:v>
       </x:c>
-      <x:c r="D46" t="str">
+      <x:c r="D46" s="446" t="str">
         <x:v>knowledge-graph-extraction-v3.skill / 项目看板</x:v>
       </x:c>
-      <x:c r="E46" t="str">
+      <x:c r="E46" s="446" t="str">
         <x:v>填写任务分配与编号段后，先让每位同事完成一个小批次</x:v>
       </x:c>
-      <x:c r="F46" t="str">
+      <x:c r="F46" s="446" t="str">
         <x:v>包内含正式模板、v10稳定样例、协作登记模板；个人批次不得直接发布</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" t="str">
+      <x:c r="A47" s="446" t="str">
         <x:v>2026-08-13</x:v>
       </x:c>
-      <x:c r="B47" t="str">
+      <x:c r="B47" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="C47" t="str">
+      <x:c r="C47" s="446" t="str">
         <x:v>将同事表中的108坊和25条道路导入主实体登记表，并完成可直接转发的多人全量提取操作手册</x:v>
       </x:c>
-      <x:c r="D47" t="str">
+      <x:c r="D47" s="446" t="str">
         <x:v>协作登记模板 / 操作手册v1 / knowledge-graph-extraction-v3.skill</x:v>
       </x:c>
-      <x:c r="E47" t="str">
+      <x:c r="E47" s="446" t="str">
         <x:v>填写任务和编号段后，安排每人一个小批次试运行</x:v>
       </x:c>
-      <x:c r="F47" t="str">
+      <x:c r="F47" s="446" t="str">
         <x:v>133项均为待补字段；仅锁定公共编号，不进入正式实体表或自动审核</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" t="str">
+      <x:c r="A48" s="446" t="str">
         <x:v>2026-08-13</x:v>
       </x:c>
-      <x:c r="B48" t="str">
+      <x:c r="B48" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="C48" t="str">
+      <x:c r="C48" s="446" t="str">
         <x:v>为两人全量提取设计并写入千位分区编号方案</x:v>
       </x:c>
-      <x:c r="D48" t="str">
+      <x:c r="D48" s="446" t="str">
         <x:v>协作登记模板_两人编号段版 / Skill v3 / 项目看板</x:v>
       </x:c>
-      <x:c r="E48" t="str">
+      <x:c r="E48" s="446" t="str">
         <x:v>在任务分配表中安排两人的首篇试运行文献</x:v>
       </x:c>
-      <x:c r="F48" t="str">
+      <x:c r="F48" s="446" t="str">
         <x:v>成员A使用2000段、成员B使用3000段；公共坊/道路复用原编号；自动关系不人工分配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="44" customHeight="1">
+      <x:c r="A49" s="467" t="str">
+        <x:v>2026-08-13</x:v>
+      </x:c>
+      <x:c r="B49" s="446" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="C49" s="446" t="str">
+        <x:v>更新多人协作 Skill、参考规范、操作手册和看板，并整理两人协作包</x:v>
+      </x:c>
+      <x:c r="D49" s="446" t="str">
+        <x:v>07-协作包/唐长安城知识图谱_两人协作包_v2_20260813</x:v>
+      </x:c>
+      <x:c r="E49" s="446" t="str">
+        <x:v>两人各领取一篇试运行文献，按公共编号复用并提交审核</x:v>
+      </x:c>
+      <x:c r="F49" s="446" t="str">
+        <x:v>协作登记表现有176个公共对象；新增43项均为待补字段，功能规则仅锁定编号和名称</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="44" customHeight="1">
+      <x:c r="A50" s="467" t="str">
+        <x:v>2026-08-13</x:v>
+      </x:c>
+      <x:c r="B50" s="446" t="str">
+        <x:v>用户 / Codex</x:v>
+      </x:c>
+      <x:c r="C50" s="446" t="str">
+        <x:v>将两人协作方案升级为三人制：成员A负责人，成员B、C协作者；新增C的4000编号段</x:v>
+      </x:c>
+      <x:c r="D50" s="446" t="str">
+        <x:v>07-协作包/唐长安城知识图谱_三人协作包_v1_20260813</x:v>
+      </x:c>
+      <x:c r="E50" s="446" t="str">
+        <x:v>由A为三人安排首篇试运行文献，B/C分别按文献完成批次</x:v>
+      </x:c>
+      <x:c r="F50" s="446" t="str">
+        <x:v>公共对象仍为176个；新增C来源0400段、片段/关系4000段、新实体4000—4499</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="446" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="B51" s="446" t="str">
+        <x:v>成员A / Codex</x:v>
+      </x:c>
+      <x:c r="C51" s="446" t="str">
+        <x:v>完成《唐两京城坊考》卷一逐段录入、自主审核、实体关系转换与全卷校验</x:v>
+      </x:c>
+      <x:c r="D51" s="446" t="str">
+        <x:v>卷一工作簿 / 协作登记表 / 项目规则日志</x:v>
+      </x:c>
+      <x:c r="E51" s="446" t="str">
+        <x:v>平台试导入、网页验收并更新Skill</x:v>
+      </x:c>
+      <x:c r="F51" s="446" t="str">
+        <x:v>覆盖宫城至三苑；574实体、886关系、50片段；保留异文候选及位置不详对象，统一关系类型代码</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R017bb292dd964397"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R5e1fa8e2bcf04c48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Redb13692201244f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R21abdb4de15e4514"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R3c2a4db7ca00408e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Raebd456779f34bbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rb10ced7c278a450a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R502bbb6958a34d35"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1656,7 +1656,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbd82a54903ed41f1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R25d5b301a76847fa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1959,13 +1959,13 @@
     <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" s="449" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$200)</x:f>
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B6" s="449"/>
       <x:c r="C6" s="449"/>
       <x:c r="D6" s="449" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$200,"已完成")</x:f>
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E6" s="449"/>
       <x:c r="F6" s="449"/>
@@ -1977,7 +1977,7 @@
       <x:c r="I6" s="450"/>
       <x:c r="J6" s="451" t="n">
         <x:f>IFERROR(D6/A6,0)</x:f>
-        <x:v>0.5555555555555556</x:v>
+        <x:v>0.5625</x:v>
       </x:c>
       <x:c r="K6" s="347"/>
       <x:c r="L6" s="347"/>
@@ -2036,9 +2036,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="453" t="str">
-        <x:v>当前阶段：成员A已完成《唐两京城坊考》卷一自主提取与全卷校验
-覆盖宫城、东宫、掖庭宫、皇城、大明宫、兴庆宫与三苑
-当前卷一工作簿：574个实体、886条关系、50个史料片段；基础一致性校验全部通过</x:v>
+        <x:v>当前阶段：《唐两京城坊考》卷一已完成平台导入、选择性发布与网页验收
+平台总量：626实体、963关系、7来源、82片段；v6发布565实体、870关系、1来源及50片段
+18条待考古或复原图核实记录保持草稿；v7已校正兴庆宫翰林院重复前缀</x:v>
       </x:c>
       <x:c r="B10" s="454"/>
       <x:c r="C10" s="454"/>
@@ -2110,9 +2110,9 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="459" t="str">
-        <x:v>1. 对卷一工作簿进行平台试导入与网页验收。
-2. 将本轮同名消歧、异文保留、位置不详对象处理规则更新到Skill。
-3. 成员A继续下一卷；成员B、C按文献提交独立批次，由A集中合并审核。</x:v>
+        <x:v>1. 卷一平台导入、选择性发布、网页验收及Skill v4更新均已完成。
+2. 下一步进入《唐两京城坊考》卷二，仍按连续片段→专题表→实体/关系权威出口→校验→平台发布处理。
+3. 卷五为东都洛阳，继续跳过；成员B、C按文献提交独立批次，由成员A集中合并。</x:v>
       </x:c>
       <x:c r="B15" s="460"/>
       <x:c r="C15" s="460"/>
@@ -2262,7 +2262,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1407368238774e8d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39222d4dbadc4dff"/>
 </x:worksheet>
 </file>
 
@@ -4198,77 +4198,85 @@
     </x:row>
     <x:row r="56" ht="40" customHeight="1">
       <x:c r="A56" s="446" t="str">
-        <x:v>S7-01</x:v>
+        <x:v>S6-21</x:v>
       </x:c>
       <x:c r="B56" s="446" t="str">
-        <x:v>阶段七：全量提取</x:v>
+        <x:v>阶段六：平台迁移</x:v>
       </x:c>
       <x:c r="C56" s="446" t="str">
-        <x:v>完成108坊功能数据</x:v>
+        <x:v>完成《唐两京城坊考》卷一全量导入、选择性发布与网页验收</x:v>
       </x:c>
       <x:c r="D56" s="446" t="str">
-        <x:v>同事</x:v>
+        <x:v>成员A / Codex</x:v>
       </x:c>
       <x:c r="E56" s="446" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F56" s="446" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G56" s="467" t="str">
-        <x:v>2026-08-13</x:v>
-      </x:c>
-      <x:c r="H56" s="467"/>
-      <x:c r="I56" s="467"/>
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="H56" s="467" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="I56" s="467" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
       <x:c r="J56" s="446" t="str">
-        <x:v>按协作包开始首篇试运行文献；复用108坊及公共对象编号</x:v>
+        <x:v>规则已固化到Skill v4；下一步进入卷二</x:v>
       </x:c>
       <x:c r="K56" s="446" t="str">
-        <x:v>协作登记表 / 个人批次工作簿</x:v>
+        <x:v>卷一平台导入包 / v6-v7发布 / 网页验收记录 / Skill v4</x:v>
       </x:c>
       <x:c r="L56" s="446" t="str">
-        <x:v>108坊已登记为待补字段；先补证据和字段，不直接发布</x:v>
+        <x:v>正确实例626实体、963关系、7来源、82片段；18条待核实保持草稿；检索、图谱、繁体原文证据通过</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="40" customHeight="1">
       <x:c r="A57" s="446" t="str">
-        <x:v>S7-02</x:v>
+        <x:v>S7-01</x:v>
       </x:c>
       <x:c r="B57" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C57" s="446" t="str">
-        <x:v>完成道路分级数据</x:v>
+        <x:v>完成108坊功能数据</x:v>
       </x:c>
       <x:c r="D57" s="446" t="str">
         <x:v>同事</x:v>
       </x:c>
       <x:c r="E57" s="446" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F57" s="446" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G57" s="467"/>
+      <x:c r="G57" s="467" t="str">
+        <x:v>2026-08-13</x:v>
+      </x:c>
       <x:c r="H57" s="467"/>
       <x:c r="I57" s="467"/>
       <x:c r="J57" s="446" t="str">
-        <x:v>分批提取与审核</x:v>
+        <x:v>按协作包开始首篇试运行文献；复用108坊及公共对象编号</x:v>
       </x:c>
       <x:c r="K57" s="446" t="str">
-        <x:v>道路全量表</x:v>
-      </x:c>
-      <x:c r="L57" s="446"/>
+        <x:v>协作登记表 / 个人批次工作簿</x:v>
+      </x:c>
+      <x:c r="L57" s="446" t="str">
+        <x:v>108坊已登记为待补字段；先补证据和字段，不直接发布</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="40" customHeight="1">
       <x:c r="A58" s="446" t="str">
-        <x:v>S7-03</x:v>
+        <x:v>S7-02</x:v>
       </x:c>
       <x:c r="B58" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C58" s="446" t="str">
-        <x:v>完成水渠数据</x:v>
+        <x:v>完成道路分级数据</x:v>
       </x:c>
       <x:c r="D58" s="446" t="str">
         <x:v>同事</x:v>
@@ -4286,22 +4294,22 @@
         <x:v>分批提取与审核</x:v>
       </x:c>
       <x:c r="K58" s="446" t="str">
-        <x:v>水渠全量表</x:v>
+        <x:v>道路全量表</x:v>
       </x:c>
       <x:c r="L58" s="446"/>
     </x:row>
     <x:row r="59" ht="44" customHeight="1">
       <x:c r="A59" s="446" t="str">
-        <x:v>S7-04</x:v>
+        <x:v>S7-03</x:v>
       </x:c>
       <x:c r="B59" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C59" s="446" t="str">
-        <x:v>完成城门数据</x:v>
+        <x:v>完成水渠数据</x:v>
       </x:c>
       <x:c r="D59" s="446" t="str">
-        <x:v>我</x:v>
+        <x:v>同事</x:v>
       </x:c>
       <x:c r="E59" s="446" t="str">
         <x:v>尚未开始</x:v>
@@ -4313,22 +4321,22 @@
       <x:c r="H59" s="467"/>
       <x:c r="I59" s="467"/>
       <x:c r="J59" s="446" t="str">
-        <x:v>严格区分城门与内门</x:v>
+        <x:v>分批提取与审核</x:v>
       </x:c>
       <x:c r="K59" s="446" t="str">
-        <x:v>城门全量表</x:v>
+        <x:v>水渠全量表</x:v>
       </x:c>
       <x:c r="L59" s="446"/>
     </x:row>
     <x:row r="60" ht="44" customHeight="1">
       <x:c r="A60" s="446" t="str">
-        <x:v>S7-05</x:v>
+        <x:v>S7-04</x:v>
       </x:c>
       <x:c r="B60" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C60" s="446" t="str">
-        <x:v>完成尺度关系数据</x:v>
+        <x:v>完成城门数据</x:v>
       </x:c>
       <x:c r="D60" s="446" t="str">
         <x:v>我</x:v>
@@ -4343,22 +4351,22 @@
       <x:c r="H60" s="467"/>
       <x:c r="I60" s="467"/>
       <x:c r="J60" s="446" t="str">
-        <x:v>全部公式人工复核</x:v>
+        <x:v>严格区分城门与内门</x:v>
       </x:c>
       <x:c r="K60" s="446" t="str">
-        <x:v>尺度关系全量表</x:v>
+        <x:v>城门全量表</x:v>
       </x:c>
       <x:c r="L60" s="446"/>
     </x:row>
     <x:row r="61" ht="44" customHeight="1">
       <x:c r="A61" s="446" t="str">
-        <x:v>S7-06</x:v>
+        <x:v>S7-05</x:v>
       </x:c>
       <x:c r="B61" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C61" s="446" t="str">
-        <x:v>完成功能分区规则</x:v>
+        <x:v>完成尺度关系数据</x:v>
       </x:c>
       <x:c r="D61" s="446" t="str">
         <x:v>我</x:v>
@@ -4373,93 +4381,93 @@
       <x:c r="H61" s="467"/>
       <x:c r="I61" s="467"/>
       <x:c r="J61" s="446" t="str">
-        <x:v>必须检索反例</x:v>
+        <x:v>全部公式人工复核</x:v>
       </x:c>
       <x:c r="K61" s="446" t="str">
-        <x:v>规则全量表</x:v>
+        <x:v>尺度关系全量表</x:v>
       </x:c>
       <x:c r="L61" s="446"/>
     </x:row>
     <x:row r="62" ht="48" customHeight="1">
       <x:c r="A62" s="446" t="str">
-        <x:v>S7-07</x:v>
+        <x:v>S7-06</x:v>
       </x:c>
       <x:c r="B62" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C62" s="446" t="str">
-        <x:v>完成《唐两京城坊考》卷一自主提取、实体关系转换与全卷校验</x:v>
+        <x:v>完成功能分区规则</x:v>
       </x:c>
       <x:c r="D62" s="446" t="str">
-        <x:v>成员A / Codex</x:v>
+        <x:v>我</x:v>
       </x:c>
       <x:c r="E62" s="446" t="str">
-        <x:v>已完成</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="F62" s="446" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G62" s="467" t="str">
-        <x:v>2026-08-14</x:v>
-      </x:c>
-      <x:c r="H62" s="467" t="str">
-        <x:v>2026-08-14</x:v>
-      </x:c>
-      <x:c r="I62" s="467" t="str">
-        <x:v>2026-08-14</x:v>
-      </x:c>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G62" s="467"/>
+      <x:c r="H62" s="467"/>
+      <x:c r="I62" s="467"/>
       <x:c r="J62" s="446" t="str">
-        <x:v>平台试导入并将稳定规则更新到Skill</x:v>
+        <x:v>必须检索反例</x:v>
       </x:c>
       <x:c r="K62" s="446" t="str">
-        <x:v>卷一工作簿 / 协作登记表 / 全卷校验记录</x:v>
-      </x:c>
-      <x:c r="L62" s="446" t="str">
-        <x:v>574实体、886关系、50片段；重复编号、重复边、悬空端点、错误引用、未登记关系类型、公式错误均为0</x:v>
-      </x:c>
+        <x:v>规则全量表</x:v>
+      </x:c>
+      <x:c r="L62" s="446"/>
     </x:row>
     <x:row r="63" ht="48" customHeight="1">
       <x:c r="A63" s="446" t="str">
-        <x:v>S8-01</x:v>
+        <x:v>S7-07</x:v>
       </x:c>
       <x:c r="B63" s="446" t="str">
-        <x:v>阶段八：质量检查</x:v>
+        <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C63" s="446" t="str">
-        <x:v>完成数据完整性、历史语义和数值检查</x:v>
+        <x:v>完成《唐两京城坊考》卷一自主提取、实体关系转换与全卷校验</x:v>
       </x:c>
       <x:c r="D63" s="446" t="str">
-        <x:v>共同</x:v>
+        <x:v>成员A / Codex</x:v>
       </x:c>
       <x:c r="E63" s="446" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F63" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G63" s="467"/>
-      <x:c r="H63" s="467"/>
-      <x:c r="I63" s="467"/>
+      <x:c r="G63" s="467" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="H63" s="467" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="I63" s="467" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
       <x:c r="J63" s="446" t="str">
-        <x:v>全量导入前完成</x:v>
+        <x:v>平台试导入并将稳定规则更新到Skill</x:v>
       </x:c>
       <x:c r="K63" s="446" t="str">
-        <x:v>质量报告</x:v>
-      </x:c>
-      <x:c r="L63" s="446"/>
+        <x:v>卷一工作簿 / 协作登记表 / 全卷校验记录</x:v>
+      </x:c>
+      <x:c r="L63" s="446" t="str">
+        <x:v>574实体、886关系、50片段；重复编号、重复边、悬空端点、错误引用、未登记关系类型、公式错误均为0</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="446" t="str">
-        <x:v>S8-02</x:v>
+        <x:v>S8-01</x:v>
       </x:c>
       <x:c r="B64" s="446" t="str">
         <x:v>阶段八：质量检查</x:v>
       </x:c>
       <x:c r="C64" s="446" t="str">
-        <x:v>完成系统测试与重复导入测试</x:v>
+        <x:v>完成数据完整性、历史语义和数值检查</x:v>
       </x:c>
       <x:c r="D64" s="446" t="str">
-        <x:v>Codex</x:v>
+        <x:v>共同</x:v>
       </x:c>
       <x:c r="E64" s="446" t="str">
         <x:v>尚未开始</x:v>
@@ -4471,25 +4479,25 @@
       <x:c r="H64" s="446"/>
       <x:c r="I64" s="446"/>
       <x:c r="J64" s="446" t="str">
-        <x:v>发布前完成</x:v>
+        <x:v>全量导入前完成</x:v>
       </x:c>
       <x:c r="K64" s="446" t="str">
-        <x:v>系统测试报告</x:v>
+        <x:v>质量报告</x:v>
       </x:c>
       <x:c r="L64" s="446"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="446" t="str">
-        <x:v>S9-01</x:v>
+        <x:v>S8-02</x:v>
       </x:c>
       <x:c r="B65" s="446" t="str">
-        <x:v>阶段九：发布交付</x:v>
+        <x:v>阶段八：质量检查</x:v>
       </x:c>
       <x:c r="C65" s="446" t="str">
-        <x:v>冻结第一版数据并生成文档</x:v>
+        <x:v>完成系统测试与重复导入测试</x:v>
       </x:c>
       <x:c r="D65" s="446" t="str">
-        <x:v>共同</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="E65" s="446" t="str">
         <x:v>尚未开始</x:v>
@@ -4501,22 +4509,22 @@
       <x:c r="H65" s="446"/>
       <x:c r="I65" s="446"/>
       <x:c r="J65" s="446" t="str">
-        <x:v>完成最终审核</x:v>
+        <x:v>发布前完成</x:v>
       </x:c>
       <x:c r="K65" s="446" t="str">
-        <x:v>tang_changan_v1</x:v>
+        <x:v>系统测试报告</x:v>
       </x:c>
       <x:c r="L65" s="446"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="446" t="str">
-        <x:v>S9-02</x:v>
+        <x:v>S9-01</x:v>
       </x:c>
       <x:c r="B66" s="446" t="str">
         <x:v>阶段九：发布交付</x:v>
       </x:c>
       <x:c r="C66" s="446" t="str">
-        <x:v>发布v1并建立Git标签v1.0.0</x:v>
+        <x:v>冻结第一版数据并生成文档</x:v>
       </x:c>
       <x:c r="D66" s="446" t="str">
         <x:v>共同</x:v>
@@ -4531,12 +4539,42 @@
       <x:c r="H66" s="446"/>
       <x:c r="I66" s="446"/>
       <x:c r="J66" s="446" t="str">
+        <x:v>完成最终审核</x:v>
+      </x:c>
+      <x:c r="K66" s="446" t="str">
+        <x:v>tang_changan_v1</x:v>
+      </x:c>
+      <x:c r="L66" s="446"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="446" t="str">
+        <x:v>S9-02</x:v>
+      </x:c>
+      <x:c r="B67" s="446" t="str">
+        <x:v>阶段九：发布交付</x:v>
+      </x:c>
+      <x:c r="C67" s="446" t="str">
+        <x:v>发布v1并建立Git标签v1.0.0</x:v>
+      </x:c>
+      <x:c r="D67" s="446" t="str">
+        <x:v>共同</x:v>
+      </x:c>
+      <x:c r="E67" s="446" t="str">
+        <x:v>尚未开始</x:v>
+      </x:c>
+      <x:c r="F67" s="446" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G67" s="446"/>
+      <x:c r="H67" s="446"/>
+      <x:c r="I67" s="446"/>
+      <x:c r="J67" s="446" t="str">
         <x:v>检查权限与版权</x:v>
       </x:c>
-      <x:c r="K66" s="446" t="str">
+      <x:c r="K67" s="446" t="str">
         <x:v>正式发布</x:v>
       </x:c>
-      <x:c r="L66" s="446"/>
+      <x:c r="L67" s="446"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5795,6 +5833,46 @@
         <x:v>覆盖宫城至三苑；574实体、886关系、50片段；保留异文候选及位置不详对象，统一关系类型代码</x:v>
       </x:c>
     </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="446" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="B52" s="446" t="str">
+        <x:v>成员A / Codex</x:v>
+      </x:c>
+      <x:c r="C52" s="446" t="str">
+        <x:v>完成卷一全量平台导入、外部审核登记、选择性发布及检索/图谱/证据验收；校正兴庆宫翰林院重复前缀</x:v>
+      </x:c>
+      <x:c r="D52" s="446" t="str">
+        <x:v>卷一平台导入包v1 / 发布v6-v7 / 导入与校正结果 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E52" s="446" t="str">
+        <x:v>更新knowledge-graph-extraction Skill后进入下一卷</x:v>
+      </x:c>
+      <x:c r="F52" s="446" t="str">
+        <x:v>导入包574实体、886关系、50片段，零错误零警告；平台复用2来源和7实体；18条待核实未发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="446" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="B53" s="446" t="str">
+        <x:v>成员A / Codex</x:v>
+      </x:c>
+      <x:c r="C53" s="446" t="str">
+        <x:v>将卷一全量实践固化到knowledge-graph-extraction Skill v4，并完成官方结构校验</x:v>
+      </x:c>
+      <x:c r="D53" s="446" t="str">
+        <x:v>Skill v4 / 质量与发布规范 / 项目规则日志 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E53" s="446" t="str">
+        <x:v>进入《唐两京城坊考》卷二；卷五东都洛阳继续跳过</x:v>
+      </x:c>
+      <x:c r="F53" s="446" t="str">
+        <x:v>新增权威关系表、实例预检、精确回滚、待核实不发布、繁简检索和重复前缀扫描规则</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R36bb66f8512040f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R4b2fc991f91f41ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R99cd1a07af8f4eea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rcef9414427af4aa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R84733953e6b54e0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R722d8e7b8bcc4427"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Ra0fd8796632149ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R1128cc83bbdb4cca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1656,7 +1656,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R72ce74d9fb354059"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3862034e9fb24d6e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1971,7 +1971,7 @@
       <x:c r="F6" s="449"/>
       <x:c r="G6" s="450" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$200,"进行中")</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H6" s="450"/>
       <x:c r="I6" s="450"/>
@@ -2036,9 +2036,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="453" t="str">
-        <x:v>当前阶段：《唐两京城坊考》卷一已完成平台导入、选择性发布与网页验收
-平台总量：626实体、963关系、7来源、82片段；v6发布565实体、870关系、1来源及50片段
-18条待考古或复原图核实记录保持草稿；v7已校正兴庆宫翰林院重复前缀</x:v>
+        <x:v>当前阶段：成员A开始《唐两京城坊考》卷二
+已完成外郭城总述单元：4个史料片段、12座城门、朱雀门街及实体关系转换
+普通事实已AI自主审核；疑似电子文本讹字保留原文并等待扫描版复核</x:v>
       </x:c>
       <x:c r="B10" s="454"/>
       <x:c r="C10" s="454"/>
@@ -2110,9 +2110,9 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="459" t="str">
-        <x:v>1. 卷一平台导入、选择性发布、网页验收及Skill v4更新均已完成。
-2. 下一步进入《唐两京城坊考》卷二，仍按连续片段→专题表→实体/关系权威出口→校验→平台发布处理。
-3. 卷五为东都洛阳，继续跳过；成员B、C按文献提交独立批次，由成员A集中合并。</x:v>
+        <x:v>1. 继续按卷二原文顺序录入朱雀门街东侧各坊。
+2. 每完成一组坊即校验专题表—实体表—关系表衔接。
+3. 对“周二四千一百二十步”“海里置里司”等文本集中用扫描版核字。</x:v>
       </x:c>
       <x:c r="B15" s="460"/>
       <x:c r="C15" s="460"/>
@@ -2262,7 +2262,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a12c5c3543849c6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54d325fd07ea4693"/>
 </x:worksheet>
 </file>
 
@@ -4548,33 +4548,37 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="446" t="str">
-        <x:v>S9-02</x:v>
+        <x:v>S7-08</x:v>
       </x:c>
       <x:c r="B67" s="446" t="str">
-        <x:v>阶段九：发布交付</x:v>
+        <x:v>阶段七：全量提取</x:v>
       </x:c>
       <x:c r="C67" s="446" t="str">
-        <x:v>发布v1并建立Git标签v1.0.0</x:v>
+        <x:v>启动《唐两京城坊考》卷二，完成外郭城总述单元</x:v>
       </x:c>
       <x:c r="D67" s="446" t="str">
-        <x:v>共同</x:v>
+        <x:v>成员A / Codex</x:v>
       </x:c>
       <x:c r="E67" s="446" t="str">
-        <x:v>尚未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="F67" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G67" s="446"/>
+      <x:c r="G67" s="446" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
       <x:c r="H67" s="446"/>
       <x:c r="I67" s="446"/>
       <x:c r="J67" s="446" t="str">
-        <x:v>检查权限与版权</x:v>
+        <x:v>继续朱雀门街东侧各坊</x:v>
       </x:c>
       <x:c r="K67" s="446" t="str">
-        <x:v>正式发布</x:v>
-      </x:c>
-      <x:c r="L67" s="446"/>
+        <x:v>BATCH-0201工作簿 / 协作登记表</x:v>
+      </x:c>
+      <x:c r="L67" s="446" t="str">
+        <x:v>4片段、12城门、1道路、14关系；明德门—朱雀门沿用既有边；2处文本类问题待扫描版复核</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5835,22 +5839,22 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="446" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="B52" s="446" t="str">
         <x:v>成员A / Codex</x:v>
       </x:c>
       <x:c r="C52" s="446" t="str">
-        <x:v>完成卷一全量平台导入、外部审核登记、选择性发布及检索/图谱/证据验收；校正兴庆宫翰林院重复前缀</x:v>
+        <x:v>启动卷二并完成外郭城总述的证据、专题与图谱转换</x:v>
       </x:c>
       <x:c r="D52" s="446" t="str">
-        <x:v>卷一平台导入包v1 / 发布v6-v7 / 导入与校正结果 / 项目看板</x:v>
+        <x:v>卷二工作簿 / 协作登记表 / 项目看板</x:v>
       </x:c>
       <x:c r="E52" s="446" t="str">
-        <x:v>更新knowledge-graph-extraction Skill后进入下一卷</x:v>
+        <x:v>继续按原文顺序录入各坊</x:v>
       </x:c>
       <x:c r="F52" s="446" t="str">
-        <x:v>导入包574实体、886关系、50片段，零错误零警告；平台复用2来源和7实体；18条待核实未发布</x:v>
+        <x:v>沿用当前协作登记表编号；不采用早期小型样例中的冲突城门编号</x:v>
       </x:c>
     </x:row>
     <x:row r="53">

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R84733953e6b54e0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R722d8e7b8bcc4427"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Ra0fd8796632149ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R1128cc83bbdb4cca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rda371f9c878c4553"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Ree069090a9374a0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Re253fc9b40054316"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rb7ef5d6c8d6748e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1656,7 +1656,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3862034e9fb24d6e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rac1f591428744c2c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2036,9 +2036,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="453" t="str">
-        <x:v>当前阶段：成员A开始《唐两京城坊考》卷二
-已完成外郭城总述单元：4个史料片段、12座城门、朱雀门街及实体关系转换
-普通事实已AI自主审核；疑似电子文本讹字保留原文并等待扫描版复核</x:v>
+        <x:v>当前阶段：成员A继续《唐两京城坊考》卷二
+已完成外郭城总述及朱雀门街东第一列九坊
+卷二当前累计：13个史料片段、74个实体、98条关系；普通事实已AI自主审核</x:v>
       </x:c>
       <x:c r="B10" s="454"/>
       <x:c r="C10" s="454"/>
@@ -2110,9 +2110,9 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="459" t="str">
-        <x:v>1. 继续按卷二原文顺序录入朱雀门街东侧各坊。
-2. 每完成一组坊即校验专题表—实体表—关系表衔接。
-3. 对“周二四千一百二十步”“海里置里司”等文本集中用扫描版核字。</x:v>
+        <x:v>1. 继续朱雀门街东第二列：务本坊至安德坊。
+2. 集中核对“昊天观/吳天觀”“崔垂林/崔垂休”等电子文本异文。
+3. 每列结束后继续执行专题—实体—关系闭环校验。</x:v>
       </x:c>
       <x:c r="B15" s="460"/>
       <x:c r="C15" s="460"/>
@@ -2262,7 +2262,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54d325fd07ea4693"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22ab4edbe7384c96"/>
 </x:worksheet>
 </file>
 
@@ -4577,7 +4577,7 @@
         <x:v>BATCH-0201工作簿 / 协作登记表</x:v>
       </x:c>
       <x:c r="L67" s="446" t="str">
-        <x:v>4片段、12城门、1道路、14关系；明德门—朱雀门沿用既有边；2处文本类问题待扫描版复核</x:v>
+        <x:v>卷二累计13片段、74实体、98关系；东第一列9坊及49处设施已录；2项名称待扫描版复核</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5859,22 +5859,22 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="446" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="B53" s="446" t="str">
         <x:v>成员A / Codex</x:v>
       </x:c>
       <x:c r="C53" s="446" t="str">
-        <x:v>将卷一全量实践固化到knowledge-graph-extraction Skill v4，并完成官方结构校验</x:v>
+        <x:v>完成卷二朱雀门街东第一列九坊的完整提取、自主审核与转换</x:v>
       </x:c>
       <x:c r="D53" s="446" t="str">
-        <x:v>Skill v4 / 质量与发布规范 / 项目规则日志 / 项目看板</x:v>
+        <x:v>卷二工作簿 / 协作登记表 / 项目看板</x:v>
       </x:c>
       <x:c r="E53" s="446" t="str">
-        <x:v>进入《唐两京城坊考》卷二；卷五东都洛阳继续跳过</x:v>
+        <x:v>继续东第二列九坊</x:v>
       </x:c>
       <x:c r="F53" s="446" t="str">
-        <x:v>新增权威关系表、实例预检、精确回滚、待核实不发布、繁简检索和重复前缀扫描规则</x:v>
+        <x:v>复用TC-FANG-0045—0053；新增49处设施；保留两项待扫描版核名记录</x:v>
       </x:c>
     </x:row>
     <x:row r="54">

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Rda371f9c878c4553"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Ree069090a9374a0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Re253fc9b40054316"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rb7ef5d6c8d6748e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Re24df0d16e134d66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R55a47fc0967f42bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R3882e279ced340ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R4353faf345284770"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1656,7 +1656,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rac1f591428744c2c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R745fa0a06efa4501"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2036,9 +2036,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="453" t="str">
-        <x:v>当前阶段：成员A继续《唐两京城坊考》卷二
-已完成外郭城总述及朱雀门街东第一列九坊
-卷二当前累计：13个史料片段、74个实体、98条关系；普通事实已AI自主审核</x:v>
+        <x:v>当前阶段：卷二朱雀门街东第二列
+已完成务本坊、崇义坊、长兴坊
+累计16片段、142实体、173关系；普通事实已AI自主审核</x:v>
       </x:c>
       <x:c r="B10" s="454"/>
       <x:c r="C10" s="454"/>
@@ -2110,9 +2110,7 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="459" t="str">
-        <x:v>1. 继续朱雀门街东第二列：务本坊至安德坊。
-2. 集中核对“昊天观/吳天觀”“崔垂林/崔垂休”等电子文本异文。
-3. 每列结束后继续执行专题—实体—关系闭环校验。</x:v>
+        <x:v>继续东第二列：永乐坊、靖安坊、安善坊、大业坊、昌乐坊、安德坊；随后完成整列校验。</x:v>
       </x:c>
       <x:c r="B15" s="460"/>
       <x:c r="C15" s="460"/>
@@ -2262,7 +2260,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22ab4edbe7384c96"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad5684e5e6b448ac"/>
 </x:worksheet>
 </file>
 

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="Re24df0d16e134d66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R55a47fc0967f42bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R3882e279ced340ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R4353faf345284770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R9b0ff3e52d024754"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Re82c5be822654f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R945bec89d75041d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Ra3bee3743fdb4275"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1656,7 +1656,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R745fa0a06efa4501"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f0aac7a722a4cdb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2036,9 +2036,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="453" t="str">
-        <x:v>当前阶段：卷二朱雀门街东第二列
-已完成务本坊、崇义坊、长兴坊
-累计16片段、142实体、173关系；普通事实已AI自主审核</x:v>
+        <x:v>当前阶段：《唐两京城坊考》卷二
+朱雀门街东第一、第二列共18坊已完成
+累计22片段、198实体、247关系；普通事实已AI自主审核</x:v>
       </x:c>
       <x:c r="B10" s="454"/>
       <x:c r="C10" s="454"/>
@@ -2110,7 +2110,7 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="459" t="str">
-        <x:v>继续东第二列：永乐坊、靖安坊、安善坊、大业坊、昌乐坊、安德坊；随后完成整列校验。</x:v>
+        <x:v>继续朱雀门街东第三列，自北第一坊开始；保持按列完成后校验。</x:v>
       </x:c>
       <x:c r="B15" s="460"/>
       <x:c r="C15" s="460"/>
@@ -2260,7 +2260,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad5684e5e6b448ac"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbddff13d3956496d"/>
 </x:worksheet>
 </file>
 

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R9b0ff3e52d024754"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="Re82c5be822654f70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R945bec89d75041d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Ra3bee3743fdb4275"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R8ab06800153d43d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R01a68dcc8b1642f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Ra1c622e160f44aad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R3555bc7c94794b3e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1656,7 +1656,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f0aac7a722a4cdb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd154ad05ca034eab"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2036,9 +2036,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="453" t="str">
-        <x:v>当前阶段：《唐两京城坊考》卷二
-朱雀门街东第一、第二列共18坊已完成
-累计22片段、198实体、247关系；普通事实已AI自主审核</x:v>
+        <x:v>当前阶段：《唐两京城坊考》卷二已完成
+朱雀门街东第一、第二街共18坊已录入
+全卷22片段、198实体、247关系；普通事实已AI自主审核，结构终检通过</x:v>
       </x:c>
       <x:c r="B10" s="454"/>
       <x:c r="C10" s="454"/>
@@ -2110,7 +2110,7 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="459" t="str">
-        <x:v>继续朱雀门街东第三列，自北第一坊开始；保持按列完成后校验。</x:v>
+        <x:v>下一步：建议先将卷二导入平台抽样验收，再开始卷三。</x:v>
       </x:c>
       <x:c r="B15" s="460"/>
       <x:c r="C15" s="460"/>
@@ -2260,7 +2260,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbddff13d3956496d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0557490e4a564bc5"/>
 </x:worksheet>
 </file>
 

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R8ab06800153d43d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R01a68dcc8b1642f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Ra1c622e160f44aad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="R3555bc7c94794b3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R9daafb6472ed41e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R3a42c3f39b6e4ab0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R1cc9542668834a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rc0cf334afc864143"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1656,7 +1656,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd154ad05ca034eab"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R26db6e3eb3ad448a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2036,9 +2036,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="453" t="str">
-        <x:v>当前阶段：《唐两京城坊考》卷二已完成
-朱雀门街东第一、第二街共18坊已录入
-全卷22片段、198实体、247关系；普通事实已AI自主审核，结构终检通过</x:v>
+        <x:v>《唐两京城坊考》卷一、卷二已联合导入18081平台
+联合包：765个去重实体、1128条去重关系、72个史料片段
+平台总量：812个实体、1205条关系、104个史料片段；已验收</x:v>
       </x:c>
       <x:c r="B10" s="454"/>
       <x:c r="C10" s="454"/>
@@ -2110,7 +2110,7 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="459" t="str">
-        <x:v>下一步：建议先将卷二导入平台抽样验收，再开始卷三。</x:v>
+        <x:v>下一步：在网页抽查卷二坊、建筑和跨卷双证据关系，然后开始卷三。</x:v>
       </x:c>
       <x:c r="B15" s="460"/>
       <x:c r="C15" s="460"/>
@@ -2260,7 +2260,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0557490e4a564bc5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R272a654ae9db43e6"/>
 </x:worksheet>
 </file>
 

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R9daafb6472ed41e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R3a42c3f39b6e4ab0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R1cc9542668834a03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rc0cf334afc864143"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R446bd1c839944d24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R36710fc17ea9411d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R95b4a19c0cfd4c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rcb0523960099494a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1656,7 +1656,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R26db6e3eb3ad448a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69de101977074714"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1959,7 +1959,7 @@
     <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" s="449" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$200)</x:f>
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B6" s="449"/>
       <x:c r="C6" s="449"/>
@@ -1971,13 +1971,13 @@
       <x:c r="F6" s="449"/>
       <x:c r="G6" s="450" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$200,"进行中")</x:f>
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H6" s="450"/>
       <x:c r="I6" s="450"/>
       <x:c r="J6" s="451" t="n">
         <x:f>IFERROR(D6/A6,0)</x:f>
-        <x:v>0.5625</x:v>
+        <x:v>0.5538461538461539</x:v>
       </x:c>
       <x:c r="K6" s="347"/>
       <x:c r="L6" s="347"/>
@@ -2036,9 +2036,9 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="453" t="str">
-        <x:v>《唐两京城坊考》卷一、卷二已联合导入18081平台
-联合包：765个去重实体、1128条去重关系、72个史料片段
-平台总量：812个实体、1205条关系、104个史料片段；已验收</x:v>
+        <x:v>当前阶段：成员A开始《唐两京城坊考》卷三
+首批完成翊善—光宅、永昌—来庭两组分坊沿革
+卷三当前：4个完整史料片段、2个稳定坊、20处建筑设施、23条关系；已自主审核并通过结构校验</x:v>
       </x:c>
       <x:c r="B10" s="454"/>
       <x:c r="C10" s="454"/>
@@ -2110,7 +2110,9 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="459" t="str">
-        <x:v>下一步：在网页抽查卷二坊、建筑和跨卷双证据关系，然后开始卷三。</x:v>
+        <x:v>1. 继续东第三街：永兴坊起，按原文顺序逐坊录入。
+2. 分坊沿革继续采用稳定坊编号＋历史名称证据的做法。
+3. 每批同步填写专题表、实体表、关系表并检查孤立实体与重复边。</x:v>
       </x:c>
       <x:c r="B15" s="460"/>
       <x:c r="C15" s="460"/>
@@ -2260,7 +2262,7 @@
     <x:mergeCell ref="A20:L22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R272a654ae9db43e6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3d600b45bab45ad"/>
 </x:worksheet>
 </file>
 
@@ -4576,6 +4578,40 @@
       </x:c>
       <x:c r="L67" s="446" t="str">
         <x:v>卷二累计13片段、74实体、98关系；东第一列9坊及49处设施已录；2项名称待扫描版复核</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>S7-09</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>阶段七：全量提取</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>启动《唐两京城坊考》卷三并完成首批分坊沿革</x:v>
+      </x:c>
+      <x:c r="D68" t="str">
+        <x:v>成员A / Codex</x:v>
+      </x:c>
+      <x:c r="E68" t="str">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="F68" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G68" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="H68"/>
+      <x:c r="I68"/>
+      <x:c r="J68" t="str">
+        <x:v>继续东第三街永兴坊以后条目</x:v>
+      </x:c>
+      <x:c r="K68" t="str">
+        <x:v>BATCH-0202工作簿 / 协作登记表</x:v>
+      </x:c>
+      <x:c r="L68" t="str">
+        <x:v>4片段、20设施、23关系；复用TC-FANG-0023/0024</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4895,7 +4931,7 @@
       <x:c r="E4" s="207" t="str">
         <x:v>复制并建立新平台仓库</x:v>
       </x:c>
-      <x:c r="F4" s="207" t="str"/>
+      <x:c r="F4" s="207"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="207" t="str">
@@ -4933,7 +4969,7 @@
       <x:c r="E6" s="207" t="str">
         <x:v>组织六张表字段联合评审</x:v>
       </x:c>
-      <x:c r="F6" s="207" t="str"/>
+      <x:c r="F6" s="207"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="207" t="str">
@@ -5893,6 +5929,26 @@
       </x:c>
       <x:c r="F54" s="446" t="str">
         <x:v>已移除包内v3.1 Skill和旧v1手册；5个Excel公式错误扫描均为0，Word三页版式检查通过</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>成员A / Codex</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>启动卷三并完成翊善—光宅、永昌—来庭首批提取</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
+        <x:v>卷三工作簿 / 协作登记表 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E55" t="str">
+        <x:v>继续东第三街后续各坊</x:v>
+      </x:c>
+      <x:c r="F55" t="str">
+        <x:v>四段原文独立保留；实体层复用两个稳定坊编号；新增20处设施</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R446bd1c839944d24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R36710fc17ea9411d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R95b4a19c0cfd4c87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rcb0523960099494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R034e1f087500450b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R697e5460a98341b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rc085725758e04211"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rd9794bbe0c954033"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -86,8 +86,14 @@
       <x:color rgb="FF333333"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17324D"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="21">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -189,6 +195,16 @@
         <x:fgColor rgb="FF0F766E"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F3E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F3E8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="13">
     <x:border/>
@@ -280,7 +296,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="468">
+  <x:cellXfs count="498">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1391,6 +1407,96 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1656,7 +1762,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69de101977074714"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R432aaa9fcf1a4272"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1965,19 +2071,19 @@
       <x:c r="C6" s="449"/>
       <x:c r="D6" s="449" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$200,"已完成")</x:f>
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E6" s="449"/>
       <x:c r="F6" s="449"/>
       <x:c r="G6" s="450" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$200,"进行中")</x:f>
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H6" s="450"/>
       <x:c r="I6" s="450"/>
       <x:c r="J6" s="451" t="n">
         <x:f>IFERROR(D6/A6,0)</x:f>
-        <x:v>0.5538461538461539</x:v>
+        <x:v>0.5692307692307692</x:v>
       </x:c>
       <x:c r="K6" s="347"/>
       <x:c r="L6" s="347"/>
@@ -2034,49 +2140,49 @@
       <x:c r="N9"/>
       <x:c r="O9"/>
     </x:row>
-    <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="453" t="str">
-        <x:v>当前阶段：成员A开始《唐两京城坊考》卷三
-首批完成翊善—光宅、永昌—来庭两组分坊沿革
-卷三当前：4个完整史料片段、2个稳定坊、20处建筑设施、23条关系；已自主审核并通过结构校验</x:v>
-      </x:c>
-      <x:c r="B10" s="454"/>
-      <x:c r="C10" s="454"/>
-      <x:c r="D10" s="454"/>
-      <x:c r="E10" s="454"/>
-      <x:c r="F10" s="454"/>
-      <x:c r="G10" s="454"/>
-      <x:c r="H10" s="454"/>
-      <x:c r="I10" s="454"/>
-      <x:c r="J10" s="454"/>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="492" t="str">
+        <x:v>当前阶段：《唐两京城坊考》卷三已完成
+全卷40个完整史料片段，35个坊，408处正文直述建筑/设施，451个实体，448条关系
+东市、曲江、芙蓉园已作为专题区域录入；普通事实已AI自主审核，下一步为平台联合验收</x:v>
+      </x:c>
+      <x:c r="B10" s="493"/>
+      <x:c r="C10" s="493"/>
+      <x:c r="D10" s="493"/>
+      <x:c r="E10" s="493"/>
+      <x:c r="F10" s="493"/>
+      <x:c r="G10" s="493"/>
+      <x:c r="H10" s="493"/>
+      <x:c r="I10" s="493"/>
+      <x:c r="J10" s="493"/>
       <x:c r="K10" s="371"/>
       <x:c r="L10" s="372"/>
     </x:row>
-    <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="455"/>
-      <x:c r="B11" s="456"/>
-      <x:c r="C11" s="456"/>
-      <x:c r="D11" s="456"/>
-      <x:c r="E11" s="456"/>
-      <x:c r="F11" s="456"/>
-      <x:c r="G11" s="456"/>
-      <x:c r="H11" s="456"/>
-      <x:c r="I11" s="456"/>
-      <x:c r="J11" s="456"/>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="494"/>
+      <x:c r="B11" s="495"/>
+      <x:c r="C11" s="495"/>
+      <x:c r="D11" s="495"/>
+      <x:c r="E11" s="495"/>
+      <x:c r="F11" s="495"/>
+      <x:c r="G11" s="495"/>
+      <x:c r="H11" s="495"/>
+      <x:c r="I11" s="495"/>
+      <x:c r="J11" s="495"/>
       <x:c r="K11" s="374"/>
       <x:c r="L11" s="375"/>
     </x:row>
-    <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="457"/>
-      <x:c r="B12" s="458"/>
-      <x:c r="C12" s="458"/>
-      <x:c r="D12" s="458"/>
-      <x:c r="E12" s="458"/>
-      <x:c r="F12" s="458"/>
-      <x:c r="G12" s="458"/>
-      <x:c r="H12" s="458"/>
-      <x:c r="I12" s="458"/>
-      <x:c r="J12" s="458"/>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="496"/>
+      <x:c r="B12" s="497"/>
+      <x:c r="C12" s="497"/>
+      <x:c r="D12" s="497"/>
+      <x:c r="E12" s="497"/>
+      <x:c r="F12" s="497"/>
+      <x:c r="G12" s="497"/>
+      <x:c r="H12" s="497"/>
+      <x:c r="I12" s="497"/>
+      <x:c r="J12" s="497"/>
       <x:c r="K12" s="377"/>
       <x:c r="L12" s="378"/>
     </x:row>
@@ -2108,49 +2214,49 @@
       <x:c r="K14" s="351"/>
       <x:c r="L14" s="351"/>
     </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="459" t="str">
-        <x:v>1. 继续东第三街：永兴坊起，按原文顺序逐坊录入。
-2. 分坊沿革继续采用稳定坊编号＋历史名称证据的做法。
-3. 每批同步填写专题表、实体表、关系表并检查孤立实体与重复边。</x:v>
-      </x:c>
-      <x:c r="B15" s="460"/>
-      <x:c r="C15" s="460"/>
-      <x:c r="D15" s="460"/>
-      <x:c r="E15" s="460"/>
-      <x:c r="F15" s="460"/>
-      <x:c r="G15" s="460"/>
-      <x:c r="H15" s="460"/>
-      <x:c r="I15" s="460"/>
-      <x:c r="J15" s="460"/>
+    <x:row r="15" ht="58" customHeight="1">
+      <x:c r="A15" s="492" t="str">
+        <x:v>1. 将卷三与卷一、卷二按稳定ID联合导入测试平台。
+2. 网页抽查东第三、第四、第五街及东市、曲江、芙蓉园。
+3. 对扫描页码和电子文本疑似讹字保留后续专项复核入口。</x:v>
+      </x:c>
+      <x:c r="B15" s="493"/>
+      <x:c r="C15" s="493"/>
+      <x:c r="D15" s="493"/>
+      <x:c r="E15" s="493"/>
+      <x:c r="F15" s="493"/>
+      <x:c r="G15" s="493"/>
+      <x:c r="H15" s="493"/>
+      <x:c r="I15" s="493"/>
+      <x:c r="J15" s="493"/>
       <x:c r="K15" s="398"/>
       <x:c r="L15" s="399"/>
     </x:row>
-    <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="461"/>
-      <x:c r="B16" s="462"/>
-      <x:c r="C16" s="462"/>
-      <x:c r="D16" s="462"/>
-      <x:c r="E16" s="462"/>
-      <x:c r="F16" s="462"/>
-      <x:c r="G16" s="462"/>
-      <x:c r="H16" s="462"/>
-      <x:c r="I16" s="462"/>
-      <x:c r="J16" s="462"/>
+    <x:row r="16" ht="58" customHeight="1">
+      <x:c r="A16" s="494"/>
+      <x:c r="B16" s="495"/>
+      <x:c r="C16" s="495"/>
+      <x:c r="D16" s="495"/>
+      <x:c r="E16" s="495"/>
+      <x:c r="F16" s="495"/>
+      <x:c r="G16" s="495"/>
+      <x:c r="H16" s="495"/>
+      <x:c r="I16" s="495"/>
+      <x:c r="J16" s="495"/>
       <x:c r="K16" s="401"/>
       <x:c r="L16" s="402"/>
     </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="463"/>
-      <x:c r="B17" s="464"/>
-      <x:c r="C17" s="464"/>
-      <x:c r="D17" s="464"/>
-      <x:c r="E17" s="464"/>
-      <x:c r="F17" s="464"/>
-      <x:c r="G17" s="464"/>
-      <x:c r="H17" s="464"/>
-      <x:c r="I17" s="464"/>
-      <x:c r="J17" s="464"/>
+    <x:row r="17" ht="58" customHeight="1">
+      <x:c r="A17" s="496"/>
+      <x:c r="B17" s="497"/>
+      <x:c r="C17" s="497"/>
+      <x:c r="D17" s="497"/>
+      <x:c r="E17" s="497"/>
+      <x:c r="F17" s="497"/>
+      <x:c r="G17" s="497"/>
+      <x:c r="H17" s="497"/>
+      <x:c r="I17" s="497"/>
+      <x:c r="J17" s="497"/>
       <x:c r="K17" s="404"/>
       <x:c r="L17" s="405"/>
     </x:row>
@@ -2255,14 +2361,14 @@
     <x:mergeCell ref="G6:I6"/>
     <x:mergeCell ref="J6:L6"/>
     <x:mergeCell ref="A9:L9"/>
-    <x:mergeCell ref="A10:L12"/>
     <x:mergeCell ref="A14:L14"/>
-    <x:mergeCell ref="A15:L17"/>
     <x:mergeCell ref="A19:L19"/>
     <x:mergeCell ref="A20:L22"/>
+    <x:mergeCell ref="A10:J12"/>
+    <x:mergeCell ref="A15:J17"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3d600b45bab45ad"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R206551128a224f8e"/>
 </x:worksheet>
 </file>
 
@@ -4594,7 +4700,7 @@
         <x:v>成员A / Codex</x:v>
       </x:c>
       <x:c r="E68" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="F68" t="str">
         <x:v>P0</x:v>
@@ -4605,13 +4711,13 @@
       <x:c r="H68"/>
       <x:c r="I68"/>
       <x:c r="J68" t="str">
-        <x:v>继续东第三街永兴坊以后条目</x:v>
+        <x:v>联合导入卷一至卷三并网页验收</x:v>
       </x:c>
       <x:c r="K68" t="str">
         <x:v>BATCH-0202工作簿 / 协作登记表</x:v>
       </x:c>
       <x:c r="L68" t="str">
-        <x:v>4片段、20设施、23关系；复用TC-FANG-0023/0024</x:v>
+        <x:v>卷三40片段、35坊、408设施、451实体、448关系；结构校验通过</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5951,6 +6057,26 @@
         <x:v>四段原文独立保留；实体层复用两个稳定坊编号；新增20处设施</x:v>
       </x:c>
     </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>成员A / Codex</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>完成《唐两京城坊考》卷三全卷提取、自主审核与图谱转换</x:v>
+      </x:c>
+      <x:c r="D56" t="str">
+        <x:v>卷三工作簿 / 协作登记表 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E56" t="str">
+        <x:v>卷一至卷三联合导入与网页验收</x:v>
+      </x:c>
+      <x:c r="F56" t="str">
+        <x:v>完成道路编号纠错；东市、曲江、芙蓉园新增Area实体；建筑编号用至TC-BUILDING-2943</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>

--- a/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
+++ b/00-项目总览/唐长安城知识图谱_项目进度看板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R034e1f087500450b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R697e5460a98341b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="Rc085725758e04211"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rd9794bbe0c954033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日看板" sheetId="1" r:id="R0131726225ef4a24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作清单" sheetId="2" r:id="R0a04a63331384fa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="3" r:id="R7287ab856c774ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="4" r:id="Rd8fdcd62b288401b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -296,7 +296,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="498">
+  <x:cellXfs count="525">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1497,6 +1497,87 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="22" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1762,7 +1843,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R432aaa9fcf1a4272"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd5073172c9b54ac2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1993,8 +2074,8 @@
       <x:c r="H1" s="445"/>
       <x:c r="I1" s="445"/>
       <x:c r="J1" s="445"/>
-      <x:c r="K1" s="329"/>
-      <x:c r="L1" s="329"/>
+      <x:c r="K1" s="445"/>
+      <x:c r="L1" s="445"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="446"/>
@@ -2007,6 +2088,8 @@
       <x:c r="H2" s="446"/>
       <x:c r="I2" s="446"/>
       <x:c r="J2" s="446"/>
+      <x:c r="K2" s="446"/>
+      <x:c r="L2" s="446"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="447" t="str">
@@ -2021,8 +2104,8 @@
       <x:c r="H3" s="447"/>
       <x:c r="I3" s="447"/>
       <x:c r="J3" s="447"/>
-      <x:c r="K3" s="332"/>
-      <x:c r="L3" s="332"/>
+      <x:c r="K3" s="447"/>
+      <x:c r="L3" s="447"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="446"/>
@@ -2035,6 +2118,8 @@
       <x:c r="H4" s="446"/>
       <x:c r="I4" s="446"/>
       <x:c r="J4" s="446"/>
+      <x:c r="K4" s="446"/>
+      <x:c r="L4" s="446"/>
       <x:c r="N4"/>
       <x:c r="O4"/>
     </x:row>
@@ -2057,21 +2142,21 @@
       <x:c r="J5" s="448" t="str">
         <x:v>完成率</x:v>
       </x:c>
-      <x:c r="K5" s="334"/>
-      <x:c r="L5" s="334"/>
+      <x:c r="K5" s="448"/>
+      <x:c r="L5" s="448"/>
       <x:c r="N5"/>
       <x:c r="O5"/>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" s="449" t="n">
         <x:f>COUNTA('工作清单'!$A$4:$A$200)</x:f>
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B6" s="449"/>
       <x:c r="C6" s="449"/>
       <x:c r="D6" s="449" t="n">
         <x:f>COUNTIF('工作清单'!$E$4:$E$200,"已完成")</x:f>
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E6" s="449"/>
       <x:c r="F6" s="449"/>
@@ -2083,10 +2168,10 @@
       <x:c r="I6" s="450"/>
       <x:c r="J6" s="451" t="n">
         <x:f>IFERROR(D6/A6,0)</x:f>
-        <x:v>0.5692307692307692</x:v>
-      </x:c>
-      <x:c r="K6" s="347"/>
-      <x:c r="L6" s="347"/>
+        <x:v>0.5757575757575758</x:v>
+      </x:c>
+      <x:c r="K6" s="451"/>
+      <x:c r="L6" s="451"/>
       <x:c r="N6"/>
       <x:c r="O6"/>
     </x:row>
@@ -2101,8 +2186,8 @@
       <x:c r="H7" s="446"/>
       <x:c r="I7" s="446"/>
       <x:c r="J7" s="446"/>
-      <x:c r="K7"/>
-      <x:c r="L7"/>
+      <x:c r="K7" s="446"/>
+      <x:c r="L7" s="446"/>
       <x:c r="N7"/>
       <x:c r="O7"/>
     </x:row>
@@ -2117,8 +2202,8 @@
       <x:c r="H8" s="446"/>
       <x:c r="I8" s="446"/>
       <x:c r="J8" s="446"/>
-      <x:c r="K8"/>
-      <x:c r="L8"/>
+      <x:c r="K8" s="446"/>
+      <x:c r="L8" s="446"/>
       <x:c r="N8"/>
       <x:c r="O8"/>
     </x:row>
@@ -2135,56 +2220,56 @@
       <x:c r="H9" s="452"/>
       <x:c r="I9" s="452"/>
       <x:c r="J9" s="452"/>
-      <x:c r="K9" s="351"/>
-      <x:c r="L9" s="351"/>
+      <x:c r="K9" s="452"/>
+      <x:c r="L9" s="452"/>
       <x:c r="N9"/>
       <x:c r="O9"/>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
-      <x:c r="A10" s="492" t="str">
-        <x:v>当前阶段：《唐两京城坊考》卷三已完成
-全卷40个完整史料片段，35个坊，408处正文直述建筑/设施，451个实体，448条关系
-东市、曲江、芙蓉园已作为专题区域录入；普通事实已AI自主审核，下一步为平台联合验收</x:v>
-      </x:c>
-      <x:c r="B10" s="493"/>
-      <x:c r="C10" s="493"/>
-      <x:c r="D10" s="493"/>
-      <x:c r="E10" s="493"/>
-      <x:c r="F10" s="493"/>
-      <x:c r="G10" s="493"/>
-      <x:c r="H10" s="493"/>
-      <x:c r="I10" s="493"/>
-      <x:c r="J10" s="493"/>
-      <x:c r="K10" s="371"/>
-      <x:c r="L10" s="372"/>
+      <x:c r="A10" s="486" t="str">
+        <x:v>当前阶段：卷一至卷三已完成联合导入与网页验收
+联合包：4来源、112史料片段、1212实体、1576关系；悬空关系和错误证据引用均为0
+测试平台现有：1256实体、1653关系、9来源、144片段（含此前试录数据）；永兴坊、曲江及来源关系抽查正常</x:v>
+      </x:c>
+      <x:c r="B10" s="487"/>
+      <x:c r="C10" s="487"/>
+      <x:c r="D10" s="487"/>
+      <x:c r="E10" s="487"/>
+      <x:c r="F10" s="487"/>
+      <x:c r="G10" s="487"/>
+      <x:c r="H10" s="487"/>
+      <x:c r="I10" s="487"/>
+      <x:c r="J10" s="487"/>
+      <x:c r="K10" s="454"/>
+      <x:c r="L10" s="505"/>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
-      <x:c r="A11" s="494"/>
-      <x:c r="B11" s="495"/>
-      <x:c r="C11" s="495"/>
-      <x:c r="D11" s="495"/>
-      <x:c r="E11" s="495"/>
-      <x:c r="F11" s="495"/>
-      <x:c r="G11" s="495"/>
-      <x:c r="H11" s="495"/>
-      <x:c r="I11" s="495"/>
-      <x:c r="J11" s="495"/>
-      <x:c r="K11" s="374"/>
-      <x:c r="L11" s="375"/>
+      <x:c r="A11" s="488"/>
+      <x:c r="B11" s="489"/>
+      <x:c r="C11" s="489"/>
+      <x:c r="D11" s="489"/>
+      <x:c r="E11" s="489"/>
+      <x:c r="F11" s="489"/>
+      <x:c r="G11" s="489"/>
+      <x:c r="H11" s="489"/>
+      <x:c r="I11" s="489"/>
+      <x:c r="J11" s="489"/>
+      <x:c r="K11" s="456"/>
+      <x:c r="L11" s="506"/>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
-      <x:c r="A12" s="496"/>
-      <x:c r="B12" s="497"/>
-      <x:c r="C12" s="497"/>
-      <x:c r="D12" s="497"/>
-      <x:c r="E12" s="497"/>
-      <x:c r="F12" s="497"/>
-      <x:c r="G12" s="497"/>
-      <x:c r="H12" s="497"/>
-      <x:c r="I12" s="497"/>
-      <x:c r="J12" s="497"/>
-      <x:c r="K12" s="377"/>
-      <x:c r="L12" s="378"/>
+      <x:c r="A12" s="490"/>
+      <x:c r="B12" s="491"/>
+      <x:c r="C12" s="491"/>
+      <x:c r="D12" s="491"/>
+      <x:c r="E12" s="491"/>
+      <x:c r="F12" s="491"/>
+      <x:c r="G12" s="491"/>
+      <x:c r="H12" s="491"/>
+      <x:c r="I12" s="491"/>
+      <x:c r="J12" s="491"/>
+      <x:c r="K12" s="458"/>
+      <x:c r="L12" s="507"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="446"/>
@@ -2197,6 +2282,8 @@
       <x:c r="H13" s="446"/>
       <x:c r="I13" s="446"/>
       <x:c r="J13" s="446"/>
+      <x:c r="K13" s="446"/>
+      <x:c r="L13" s="446"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="452" t="str">
@@ -2211,54 +2298,54 @@
       <x:c r="H14" s="452"/>
       <x:c r="I14" s="452"/>
       <x:c r="J14" s="452"/>
-      <x:c r="K14" s="351"/>
-      <x:c r="L14" s="351"/>
+      <x:c r="K14" s="452"/>
+      <x:c r="L14" s="452"/>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
-      <x:c r="A15" s="492" t="str">
-        <x:v>1. 将卷三与卷一、卷二按稳定ID联合导入测试平台。
-2. 网页抽查东第三、第四、第五街及东市、曲江、芙蓉园。
-3. 对扫描页码和电子文本疑似讹字保留后续专项复核入口。</x:v>
-      </x:c>
-      <x:c r="B15" s="493"/>
-      <x:c r="C15" s="493"/>
-      <x:c r="D15" s="493"/>
-      <x:c r="E15" s="493"/>
-      <x:c r="F15" s="493"/>
-      <x:c r="G15" s="493"/>
-      <x:c r="H15" s="493"/>
-      <x:c r="I15" s="493"/>
-      <x:c r="J15" s="493"/>
-      <x:c r="K15" s="398"/>
-      <x:c r="L15" s="399"/>
+      <x:c r="A15" s="486" t="str">
+        <x:v>1. 开始《唐两京城坊考》卷四，继续按卷建立独立工作簿并复用稳定实体编号。
+2. 成员A建筑编号段已扩展为TC-BUILDING-5000—5999；成员B、C原编号段不变。
+3. 卷五为东都洛阳，仍按既定范围暂不录入。</x:v>
+      </x:c>
+      <x:c r="B15" s="487"/>
+      <x:c r="C15" s="487"/>
+      <x:c r="D15" s="487"/>
+      <x:c r="E15" s="487"/>
+      <x:c r="F15" s="487"/>
+      <x:c r="G15" s="487"/>
+      <x:c r="H15" s="487"/>
+      <x:c r="I15" s="487"/>
+      <x:c r="J15" s="487"/>
+      <x:c r="K15" s="460"/>
+      <x:c r="L15" s="508"/>
     </x:row>
     <x:row r="16" ht="58" customHeight="1">
-      <x:c r="A16" s="494"/>
-      <x:c r="B16" s="495"/>
-      <x:c r="C16" s="495"/>
-      <x:c r="D16" s="495"/>
-      <x:c r="E16" s="495"/>
-      <x:c r="F16" s="495"/>
-      <x:c r="G16" s="495"/>
-      <x:c r="H16" s="495"/>
-      <x:c r="I16" s="495"/>
-      <x:c r="J16" s="495"/>
-      <x:c r="K16" s="401"/>
-      <x:c r="L16" s="402"/>
+      <x:c r="A16" s="488"/>
+      <x:c r="B16" s="489"/>
+      <x:c r="C16" s="489"/>
+      <x:c r="D16" s="489"/>
+      <x:c r="E16" s="489"/>
+      <x:c r="F16" s="489"/>
+      <x:c r="G16" s="489"/>
+      <x:c r="H16" s="489"/>
+      <x:c r="I16" s="489"/>
+      <x:c r="J16" s="489"/>
+      <x:c r="K16" s="462"/>
+      <x:c r="L16" s="509"/>
     </x:row>
     <x:row r="17" ht="58" customHeight="1">
-      <x:c r="A17" s="496"/>
-      <x:c r="B17" s="497"/>
-      <x:c r="C17" s="497"/>
-      <x:c r="D17" s="497"/>
-      <x:c r="E17" s="497"/>
-      <x:c r="F17" s="497"/>
-      <x:c r="G17" s="497"/>
-      <x:c r="H17" s="497"/>
-      <x:c r="I17" s="497"/>
-      <x:c r="J17" s="497"/>
-      <x:c r="K17" s="404"/>
-      <x:c r="L17" s="405"/>
+      <x:c r="A17" s="490"/>
+      <x:c r="B17" s="491"/>
+      <x:c r="C17" s="491"/>
+      <x:c r="D17" s="491"/>
+      <x:c r="E17" s="491"/>
+      <x:c r="F17" s="491"/>
+      <x:c r="G17" s="491"/>
+      <x:c r="H17" s="491"/>
+      <x:c r="I17" s="491"/>
+      <x:c r="J17" s="491"/>
+      <x:c r="K17" s="464"/>
+      <x:c r="L17" s="510"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="446"/>
@@ -2271,6 +2358,8 @@
       <x:c r="H18" s="446"/>
       <x:c r="I18" s="446"/>
       <x:c r="J18" s="446"/>
+      <x:c r="K18" s="446"/>
+      <x:c r="L18" s="446"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="452" t="str">
@@ -2285,8 +2374,8 @@
       <x:c r="H19" s="452"/>
       <x:c r="I19" s="452"/>
       <x:c r="J19" s="452"/>
-      <x:c r="K19" s="351"/>
-      <x:c r="L19" s="351"/>
+      <x:c r="K19" s="452"/>
+      <x:c r="L19" s="452"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="465" t="str">
@@ -2301,52 +2390,2528 @@
       <x:c r="H20" s="466"/>
       <x:c r="I20" s="466"/>
       <x:c r="J20" s="466"/>
-      <x:c r="K20" s="426"/>
-      <x:c r="L20" s="427"/>
+      <x:c r="K20" s="466"/>
+      <x:c r="L20" s="511"/>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
-      <x:c r="A21" s="428"/>
-      <x:c r="B21" s="429"/>
-      <x:c r="C21" s="429"/>
-      <x:c r="D21" s="429"/>
-      <x:c r="E21" s="429"/>
-      <x:c r="F21" s="429"/>
-      <x:c r="G21" s="429"/>
-      <x:c r="H21" s="429"/>
-      <x:c r="I21" s="429"/>
-      <x:c r="J21" s="429"/>
-      <x:c r="K21" s="429"/>
-      <x:c r="L21" s="430"/>
+      <x:c r="A21" s="512"/>
+      <x:c r="B21" s="513"/>
+      <x:c r="C21" s="513"/>
+      <x:c r="D21" s="513"/>
+      <x:c r="E21" s="513"/>
+      <x:c r="F21" s="513"/>
+      <x:c r="G21" s="513"/>
+      <x:c r="H21" s="513"/>
+      <x:c r="I21" s="513"/>
+      <x:c r="J21" s="513"/>
+      <x:c r="K21" s="513"/>
+      <x:c r="L21" s="514"/>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="431"/>
-      <x:c r="B22" s="432"/>
-      <x:c r="C22" s="432"/>
-      <x:c r="D22" s="432"/>
-      <x:c r="E22" s="432"/>
-      <x:c r="F22" s="432"/>
-      <x:c r="G22" s="432"/>
-      <x:c r="H22" s="432"/>
-      <x:c r="I22" s="432"/>
-      <x:c r="J22" s="432"/>
-      <x:c r="K22" s="432"/>
-      <x:c r="L22" s="433"/>
+      <x:c r="A22" s="515"/>
+      <x:c r="B22" s="516"/>
+      <x:c r="C22" s="516"/>
+      <x:c r="D22" s="516"/>
+      <x:c r="E22" s="516"/>
+      <x:c r="F22" s="516"/>
+      <x:c r="G22" s="516"/>
+      <x:c r="H22" s="516"/>
+      <x:c r="I22" s="516"/>
+      <x:c r="J22" s="516"/>
+      <x:c r="K22" s="516"/>
+      <x:c r="L22" s="517"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23"/>
-      <x:c r="C23"/>
-      <x:c r="D23"/>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
+      <x:c r="A23" s="446"/>
+      <x:c r="B23" s="446"/>
+      <x:c r="C23" s="446"/>
+      <x:c r="D23" s="446"/>
+      <x:c r="E23" s="446"/>
+      <x:c r="F23" s="446"/>
+      <x:c r="G23" s="446"/>
+      <x:c r="H23" s="446"/>
+      <x:c r="I23" s="446"/>
+      <x:c r="J23" s="446"/>
+      <x:c r="K23" s="446"/>
+      <x:c r="L23" s="446"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24"/>
-      <x:c r="B24"/>
-      <x:c r="C24"/>
-      <x:c r="D24"/>
-      <x:c r="E24"/>
-      <x:c r="F24"/>
+      <x:c r="A24" s="446"/>
+      <x:c r="B24" s="446"/>
+      <x:c r="C24" s="446"/>
+      <x:c r="D24" s="446"/>
+      <x:c r="E24" s="446"/>
+      <x:c r="F24" s="446"/>
+      <x:c r="G24" s="446"/>
+      <x:c r="H24" s="446"/>
+      <x:c r="I24" s="446"/>
+      <x:c r="J24" s="446"/>
+      <x:c r="K24" s="446"/>
+      <x:c r="L24" s="446"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="446"/>
+      <x:c r="B25" s="446"/>
+      <x:c r="C25" s="446"/>
+      <x:c r="D25" s="446"/>
+      <x:c r="E25" s="446"/>
+      <x:c r="F25" s="446"/>
+      <x:c r="G25" s="446"/>
+      <x:c r="H25" s="446"/>
+      <x:c r="I25" s="446"/>
+      <x:c r="J25" s="446"/>
+      <x:c r="K25" s="446"/>
+      <x:c r="L25" s="446"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="446"/>
+      <x:c r="B26" s="446"/>
+      <x:c r="C26" s="446"/>
+      <x:c r="D26" s="446"/>
+      <x:c r="E26" s="446"/>
+      <x:c r="F26" s="446"/>
+      <x:c r="G26" s="446"/>
+      <x:c r="H26" s="446"/>
+      <x:c r="I26" s="446"/>
+      <x:c r="J26" s="446"/>
+      <x:c r="K26" s="446"/>
+      <x:c r="L26" s="446"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="446"/>
+      <x:c r="B27" s="446"/>
+      <x:c r="C27" s="446"/>
+      <x:c r="D27" s="446"/>
+      <x:c r="E27" s="446"/>
+      <x:c r="F27" s="446"/>
+      <x:c r="G27" s="446"/>
+      <x:c r="H27" s="446"/>
+      <x:c r="I27" s="446"/>
+      <x:c r="J27" s="446"/>
+      <x:c r="K27" s="446"/>
+      <x:c r="L27" s="446"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="446"/>
+      <x:c r="B28" s="446"/>
+      <x:c r="C28" s="446"/>
+      <x:c r="D28" s="446"/>
+      <x:c r="E28" s="446"/>
+      <x:c r="F28" s="446"/>
+      <x:c r="G28" s="446"/>
+      <x:c r="H28" s="446"/>
+      <x:c r="I28" s="446"/>
+      <x:c r="J28" s="446"/>
+      <x:c r="K28" s="446"/>
+      <x:c r="L28" s="446"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="446"/>
+      <x:c r="B29" s="446"/>
+      <x:c r="C29" s="446"/>
+      <x:c r="D29" s="446"/>
+      <x:c r="E29" s="446"/>
+      <x:c r="F29" s="446"/>
+      <x:c r="G29" s="446"/>
+      <x:c r="H29" s="446"/>
+      <x:c r="I29" s="446"/>
+      <x:c r="J29" s="446"/>
+      <x:c r="K29" s="446"/>
+      <x:c r="L29" s="446"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="446"/>
+      <x:c r="B30" s="446"/>
+      <x:c r="C30" s="446"/>
+      <x:c r="D30" s="446"/>
+      <x:c r="E30" s="446"/>
+      <x:c r="F30" s="446"/>
+      <x:c r="G30" s="446"/>
+      <x:c r="H30" s="446"/>
+      <x:c r="I30" s="446"/>
+      <x:c r="J30" s="446"/>
+      <x:c r="K30" s="446"/>
+      <x:c r="L30" s="446"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="446"/>
+      <x:c r="B31" s="446"/>
+      <x:c r="C31" s="446"/>
+      <x:c r="D31" s="446"/>
+      <x:c r="E31" s="446"/>
+      <x:c r="F31" s="446"/>
+      <x:c r="G31" s="446"/>
+      <x:c r="H31" s="446"/>
+      <x:c r="I31" s="446"/>
+      <x:c r="J31" s="446"/>
+      <x:c r="K31" s="446"/>
+      <x:c r="L31" s="446"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="446"/>
+      <x:c r="B32" s="446"/>
+      <x:c r="C32" s="446"/>
+      <x:c r="D32" s="446"/>
+      <x:c r="E32" s="446"/>
+      <x:c r="F32" s="446"/>
+      <x:c r="G32" s="446"/>
+      <x:c r="H32" s="446"/>
+      <x:c r="I32" s="446"/>
+      <x:c r="J32" s="446"/>
+      <x:c r="K32" s="446"/>
+      <x:c r="L32" s="446"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="446"/>
+      <x:c r="B33" s="446"/>
+      <x:c r="C33" s="446"/>
+      <x:c r="D33" s="446"/>
+      <x:c r="E33" s="446"/>
+      <x:c r="F33" s="446"/>
+      <x:c r="G33" s="446"/>
+      <x:c r="H33" s="446"/>
+      <x:c r="I33" s="446"/>
+      <x:c r="J33" s="446"/>
+      <x:c r="K33" s="446"/>
+      <x:c r="L33" s="446"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="446"/>
+      <x:c r="B34" s="446"/>
+      <x:c r="C34" s="446"/>
+      <x:c r="D34" s="446"/>
+      <x:c r="E34" s="446"/>
+      <x:c r="F34" s="446"/>
+      <x:c r="G34" s="446"/>
+      <x:c r="H34" s="446"/>
+      <x:c r="I34" s="446"/>
+      <x:c r="J34" s="446"/>
+      <x:c r="K34" s="446"/>
+      <x:c r="L34" s="446"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="446"/>
+      <x:c r="B35" s="446"/>
+      <x:c r="C35" s="446"/>
+      <x:c r="D35" s="446"/>
+      <x:c r="E35" s="446"/>
+      <x:c r="F35" s="446"/>
+      <x:c r="G35" s="446"/>
+      <x:c r="H35" s="446"/>
+      <x:c r="I35" s="446"/>
+      <x:c r="J35" s="446"/>
+      <x:c r="K35" s="446"/>
+      <x:c r="L35" s="446"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="446"/>
+      <x:c r="B36" s="446"/>
+      <x:c r="C36" s="446"/>
+      <x:c r="D36" s="446"/>
+      <x:c r="E36" s="446"/>
+      <x:c r="F36" s="446"/>
+      <x:c r="G36" s="446"/>
+      <x:c r="H36" s="446"/>
+      <x:c r="I36" s="446"/>
+      <x:c r="J36" s="446"/>
+      <x:c r="K36" s="446"/>
+      <x:c r="L36" s="446"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="446"/>
+      <x:c r="B37" s="446"/>
+      <x:c r="C37" s="446"/>
+      <x:c r="D37" s="446"/>
+      <x:c r="E37" s="446"/>
+      <x:c r="F37" s="446"/>
+      <x:c r="G37" s="446"/>
+      <x:c r="H37" s="446"/>
+      <x:c r="I37" s="446"/>
+      <x:c r="J37" s="446"/>
+      <x:c r="K37" s="446"/>
+      <x:c r="L37" s="446"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="446"/>
+      <x:c r="B38" s="446"/>
+      <x:c r="C38" s="446"/>
+      <x:c r="D38" s="446"/>
+      <x:c r="E38" s="446"/>
+      <x:c r="F38" s="446"/>
+      <x:c r="G38" s="446"/>
+      <x:c r="H38" s="446"/>
+      <x:c r="I38" s="446"/>
+      <x:c r="J38" s="446"/>
+      <x:c r="K38" s="446"/>
+      <x:c r="L38" s="446"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="446"/>
+      <x:c r="B39" s="446"/>
+      <x:c r="C39" s="446"/>
+      <x:c r="D39" s="446"/>
+      <x:c r="E39" s="446"/>
+      <x:c r="F39" s="446"/>
+      <x:c r="G39" s="446"/>
+      <x:c r="H39" s="446"/>
+      <x:c r="I39" s="446"/>
+      <x:c r="J39" s="446"/>
+      <x:c r="K39" s="446"/>
+      <x:c r="L39" s="446"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="446"/>
+      <x:c r="B40" s="446"/>
+      <x:c r="C40" s="446"/>
+      <x:c r="D40" s="446"/>
+      <x:c r="E40" s="446"/>
+      <x:c r="F40" s="446"/>
+      <x:c r="G40" s="446"/>
+      <x:c r="H40" s="446"/>
+      <x:c r="I40" s="446"/>
+      <x:c r="J40" s="446"/>
+      <x:c r="K40" s="446"/>
+      <x:c r="L40" s="446"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="446"/>
+      <x:c r="B41" s="446"/>
+      <x:c r="C41" s="446"/>
+      <x:c r="D41" s="446"/>
+      <x:c r="E41" s="446"/>
+      <x:c r="F41" s="446"/>
+      <x:c r="G41" s="446"/>
+      <x:c r="H41" s="446"/>
+      <x:c r="I41" s="446"/>
+      <x:c r="J41" s="446"/>
+      <x:c r="K41" s="446"/>
+      <x:c r="L41" s="446"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="446"/>
+      <x:c r="B42" s="446"/>
+      <x:c r="C42" s="446"/>
+      <x:c r="D42" s="446"/>
+      <x:c r="E42" s="446"/>
+      <x:c r="F42" s="446"/>
+      <x:c r="G42" s="446"/>
+      <x:c r="H42" s="446"/>
+      <x:c r="I42" s="446"/>
+      <x:c r="J42" s="446"/>
+      <x:c r="K42" s="446"/>
+      <x:c r="L42" s="446"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="446"/>
+      <x:c r="B43" s="446"/>
+      <x:c r="C43" s="446"/>
+      <x:c r="D43" s="446"/>
+      <x:c r="E43" s="446"/>
+      <x:c r="F43" s="446"/>
+      <x:c r="G43" s="446"/>
+      <x:c r="H43" s="446"/>
+      <x:c r="I43" s="446"/>
+      <x:c r="J43" s="446"/>
+      <x:c r="K43" s="446"/>
+      <x:c r="L43" s="446"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="446"/>
+      <x:c r="B44" s="446"/>
+      <x:c r="C44" s="446"/>
+      <x:c r="D44" s="446"/>
+      <x:c r="E44" s="446"/>
+      <x:c r="F44" s="446"/>
+      <x:c r="G44" s="446"/>
+      <x:c r="H44" s="446"/>
+      <x:c r="I44" s="446"/>
+      <x:c r="J44" s="446"/>
+      <x:c r="K44" s="446"/>
+      <x:c r="L44" s="446"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="446"/>
+      <x:c r="B45" s="446"/>
+      <x:c r="C45" s="446"/>
+      <x:c r="D45" s="446"/>
+      <x:c r="E45" s="446"/>
+      <x:c r="F45" s="446"/>
+      <x:c r="G45" s="446"/>
+      <x:c r="H45" s="446"/>
+      <x:c r="I45" s="446"/>
+      <x:c r="J45" s="446"/>
+      <x:c r="K45" s="446"/>
+      <x:c r="L45" s="446"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="446"/>
+      <x:c r="B46" s="446"/>
+      <x:c r="C46" s="446"/>
+      <x:c r="D46" s="446"/>
+      <x:c r="E46" s="446"/>
+      <x:c r="F46" s="446"/>
+      <x:c r="G46" s="446"/>
+      <x:c r="H46" s="446"/>
+      <x:c r="I46" s="446"/>
+      <x:c r="J46" s="446"/>
+      <x:c r="K46" s="446"/>
+      <x:c r="L46" s="446"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="446"/>
+      <x:c r="B47" s="446"/>
+      <x:c r="C47" s="446"/>
+      <x:c r="D47" s="446"/>
+      <x:c r="E47" s="446"/>
+      <x:c r="F47" s="446"/>
+      <x:c r="G47" s="446"/>
+      <x:c r="H47" s="446"/>
+      <x:c r="I47" s="446"/>
+      <x:c r="J47" s="446"/>
+      <x:c r="K47" s="446"/>
+      <x:c r="L47" s="446"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="446"/>
+      <x:c r="B48" s="446"/>
+      <x:c r="C48" s="446"/>
+      <x:c r="D48" s="446"/>
+      <x:c r="E48" s="446"/>
+      <x:c r="F48" s="446"/>
+      <x:c r="G48" s="446"/>
+      <x:c r="H48" s="446"/>
+      <x:c r="I48" s="446"/>
+      <x:c r="J48" s="446"/>
+      <x:c r="K48" s="446"/>
+      <x:c r="L48" s="446"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="446"/>
+      <x:c r="B49" s="446"/>
+      <x:c r="C49" s="446"/>
+      <x:c r="D49" s="446"/>
+      <x:c r="E49" s="446"/>
+      <x:c r="F49" s="446"/>
+      <x:c r="G49" s="446"/>
+      <x:c r="H49" s="446"/>
+      <x:c r="I49" s="446"/>
+      <x:c r="J49" s="446"/>
+      <x:c r="K49" s="446"/>
+      <x:c r="L49" s="446"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="446"/>
+      <x:c r="B50" s="446"/>
+      <x:c r="C50" s="446"/>
+      <x:c r="D50" s="446"/>
+      <x:c r="E50" s="446"/>
+      <x:c r="F50" s="446"/>
+      <x:c r="G50" s="446"/>
+      <x:c r="H50" s="446"/>
+      <x:c r="I50" s="446"/>
+      <x:c r="J50" s="446"/>
+      <x:c r="K50" s="446"/>
+      <x:c r="L50" s="446"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="446"/>
+      <x:c r="B51" s="446"/>
+      <x:c r="C51" s="446"/>
+      <x:c r="D51" s="446"/>
+      <x:c r="E51" s="446"/>
+      <x:c r="F51" s="446"/>
+      <x:c r="G51" s="446"/>
+      <x:c r="H51" s="446"/>
+      <x:c r="I51" s="446"/>
+      <x:c r="J51" s="446"/>
+      <x:c r="K51" s="446"/>
+      <x:c r="L51" s="446"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="446"/>
+      <x:c r="B52" s="446"/>
+      <x:c r="C52" s="446"/>
+      <x:c r="D52" s="446"/>
+      <x:c r="E52" s="446"/>
+      <x:c r="F52" s="446"/>
+      <x:c r="G52" s="446"/>
+      <x:c r="H52" s="446"/>
+      <x:c r="I52" s="446"/>
+      <x:c r="J52" s="446"/>
+      <x:c r="K52" s="446"/>
+      <x:c r="L52" s="446"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="446"/>
+      <x:c r="B53" s="446"/>
+      <x:c r="C53" s="446"/>
+      <x:c r="D53" s="446"/>
+      <x:c r="E53" s="446"/>
+      <x:c r="F53" s="446"/>
+      <x:c r="G53" s="446"/>
+      <x:c r="H53" s="446"/>
+      <x:c r="I53" s="446"/>
+      <x:c r="J53" s="446"/>
+      <x:c r="K53" s="446"/>
+      <x:c r="L53" s="446"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="446"/>
+      <x:c r="B54" s="446"/>
+      <x:c r="C54" s="446"/>
+      <x:c r="D54" s="446"/>
+      <x:c r="E54" s="446"/>
+      <x:c r="F54" s="446"/>
+      <x:c r="G54" s="446"/>
+      <x:c r="H54" s="446"/>
+      <x:c r="I54" s="446"/>
+      <x:c r="J54" s="446"/>
+      <x:c r="K54" s="446"/>
+      <x:c r="L54" s="446"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="446"/>
+      <x:c r="B55" s="446"/>
+      <x:c r="C55" s="446"/>
+      <x:c r="D55" s="446"/>
+      <x:c r="E55" s="446"/>
+      <x:c r="F55" s="446"/>
+      <x:c r="G55" s="446"/>
+      <x:c r="H55" s="446"/>
+      <x:c r="I55" s="446"/>
+      <x:c r="J55" s="446"/>
+      <x:c r="K55" s="446"/>
+      <x:c r="L55" s="446"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="446"/>
+      <x:c r="B56" s="446"/>
+      <x:c r="C56" s="446"/>
+      <x:c r="D56" s="446"/>
+      <x:c r="E56" s="446"/>
+      <x:c r="F56" s="446"/>
+      <x:c r="G56" s="446"/>
+      <x:c r="H56" s="446"/>
+      <x:c r="I56" s="446"/>
+      <x:c r="J56" s="446"/>
+      <x:c r="K56" s="446"/>
+      <x:c r="L56" s="446"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="446"/>
+      <x:c r="B57" s="446"/>
+      <x:c r="C57" s="446"/>
+      <x:c r="D57" s="446"/>
+      <x:c r="E57" s="446"/>
+      <x:c r="F57" s="446"/>
+      <x:c r="G57" s="446"/>
+      <x:c r="H57" s="446"/>
+      <x:c r="I57" s="446"/>
+      <x:c r="J57" s="446"/>
+      <x:c r="K57" s="446"/>
+      <x:c r="L57" s="446"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="446"/>
+      <x:c r="B58" s="446"/>
+      <x:c r="C58" s="446"/>
+      <x:c r="D58" s="446"/>
+      <x:c r="E58" s="446"/>
+      <x:c r="F58" s="446"/>
+      <x:c r="G58" s="446"/>
+      <x:c r="H58" s="446"/>
+      <x:c r="I58" s="446"/>
+      <x:c r="J58" s="446"/>
+      <x:c r="K58" s="446"/>
+      <x:c r="L58" s="446"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="446"/>
+      <x:c r="B59" s="446"/>
+      <x:c r="C59" s="446"/>
+      <x:c r="D59" s="446"/>
+      <x:c r="E59" s="446"/>
+      <x:c r="F59" s="446"/>
+      <x:c r="G59" s="446"/>
+      <x:c r="H59" s="446"/>
+      <x:c r="I59" s="446"/>
+      <x:c r="J59" s="446"/>
+      <x:c r="K59" s="446"/>
+      <x:c r="L59" s="446"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="446"/>
+      <x:c r="B60" s="446"/>
+      <x:c r="C60" s="446"/>
+      <x:c r="D60" s="446"/>
+      <x:c r="E60" s="446"/>
+      <x:c r="F60" s="446"/>
+      <x:c r="G60" s="446"/>
+      <x:c r="H60" s="446"/>
+      <x:c r="I60" s="446"/>
+      <x:c r="J60" s="446"/>
+      <x:c r="K60" s="446"/>
+      <x:c r="L60" s="446"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="446"/>
+      <x:c r="B61" s="446"/>
+      <x:c r="C61" s="446"/>
+      <x:c r="D61" s="446"/>
+      <x:c r="E61" s="446"/>
+      <x:c r="F61" s="446"/>
+      <x:c r="G61" s="446"/>
+      <x:c r="H61" s="446"/>
+      <x:c r="I61" s="446"/>
+      <x:c r="J61" s="446"/>
+      <x:c r="K61" s="446"/>
+      <x:c r="L61" s="446"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="446"/>
+      <x:c r="B62" s="446"/>
+      <x:c r="C62" s="446"/>
+      <x:c r="D62" s="446"/>
+      <x:c r="E62" s="446"/>
+      <x:c r="F62" s="446"/>
+      <x:c r="G62" s="446"/>
+      <x:c r="H62" s="446"/>
+      <x:c r="I62" s="446"/>
+      <x:c r="J62" s="446"/>
+      <x:c r="K62" s="446"/>
+      <x:c r="L62" s="446"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="446"/>
+      <x:c r="B63" s="446"/>
+      <x:c r="C63" s="446"/>
+      <x:c r="D63" s="446"/>
+      <x:c r="E63" s="446"/>
+      <x:c r="F63" s="446"/>
+      <x:c r="G63" s="446"/>
+      <x:c r="H63" s="446"/>
+      <x:c r="I63" s="446"/>
+      <x:c r="J63" s="446"/>
+      <x:c r="K63" s="446"/>
+      <x:c r="L63" s="446"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="446"/>
+      <x:c r="B64" s="446"/>
+      <x:c r="C64" s="446"/>
+      <x:c r="D64" s="446"/>
+      <x:c r="E64" s="446"/>
+      <x:c r="F64" s="446"/>
+      <x:c r="G64" s="446"/>
+      <x:c r="H64" s="446"/>
+      <x:c r="I64" s="446"/>
+      <x:c r="J64" s="446"/>
+      <x:c r="K64" s="446"/>
+      <x:c r="L64" s="446"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="446"/>
+      <x:c r="B65" s="446"/>
+      <x:c r="C65" s="446"/>
+      <x:c r="D65" s="446"/>
+      <x:c r="E65" s="446"/>
+      <x:c r="F65" s="446"/>
+      <x:c r="G65" s="446"/>
+      <x:c r="H65" s="446"/>
+      <x:c r="I65" s="446"/>
+      <x:c r="J65" s="446"/>
+      <x:c r="K65" s="446"/>
+      <x:c r="L65" s="446"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="446"/>
+      <x:c r="B66" s="446"/>
+      <x:c r="C66" s="446"/>
+      <x:c r="D66" s="446"/>
+      <x:c r="E66" s="446"/>
+      <x:c r="F66" s="446"/>
+      <x:c r="G66" s="446"/>
+      <x:c r="H66" s="446"/>
+      <x:c r="I66" s="446"/>
+      <x:c r="J66" s="446"/>
+      <x:c r="K66" s="446"/>
+      <x:c r="L66" s="446"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="446"/>
+      <x:c r="B67" s="446"/>
+      <x:c r="C67" s="446"/>
+      <x:c r="D67" s="446"/>
+      <x:c r="E67" s="446"/>
+      <x:c r="F67" s="446"/>
+      <x:c r="G67" s="446"/>
+      <x:c r="H67" s="446"/>
+      <x:c r="I67" s="446"/>
+      <x:c r="J67" s="446"/>
+      <x:c r="K67" s="446"/>
+      <x:c r="L67" s="446"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="446"/>
+      <x:c r="B68" s="446"/>
+      <x:c r="C68" s="446"/>
+      <x:c r="D68" s="446"/>
+      <x:c r="E68" s="446"/>
+      <x:c r="F68" s="446"/>
+      <x:c r="G68" s="446"/>
+      <x:c r="H68" s="446"/>
+      <x:c r="I68" s="446"/>
+      <x:c r="J68" s="446"/>
+      <x:c r="K68" s="446"/>
+      <x:c r="L68" s="446"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="446"/>
+      <x:c r="B69" s="446"/>
+      <x:c r="C69" s="446"/>
+      <x:c r="D69" s="446"/>
+      <x:c r="E69" s="446"/>
+      <x:c r="F69" s="446"/>
+      <x:c r="G69" s="446"/>
+      <x:c r="H69" s="446"/>
+      <x:c r="I69" s="446"/>
+      <x:c r="J69" s="446"/>
+      <x:c r="K69" s="446"/>
+      <x:c r="L69" s="446"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="446"/>
+      <x:c r="B70" s="446"/>
+      <x:c r="C70" s="446"/>
+      <x:c r="D70" s="446"/>
+      <x:c r="E70" s="446"/>
+      <x:c r="F70" s="446"/>
+      <x:c r="G70" s="446"/>
+      <x:c r="H70" s="446"/>
+      <x:c r="I70" s="446"/>
+      <x:c r="J70" s="446"/>
+      <x:c r="K70" s="446"/>
+      <x:c r="L70" s="446"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="446"/>
+      <x:c r="B71" s="446"/>
+      <x:c r="C71" s="446"/>
+      <x:c r="D71" s="446"/>
+      <x:c r="E71" s="446"/>
+      <x:c r="F71" s="446"/>
+      <x:c r="G71" s="446"/>
+      <x:c r="H71" s="446"/>
+      <x:c r="I71" s="446"/>
+      <x:c r="J71" s="446"/>
+      <x:c r="K71" s="446"/>
+      <x:c r="L71" s="446"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="446"/>
+      <x:c r="B72" s="446"/>
+      <x:c r="C72" s="446"/>
+      <x:c r="D72" s="446"/>
+      <x:c r="E72" s="446"/>
+      <x:c r="F72" s="446"/>
+      <x:c r="G72" s="446"/>
+      <x:c r="H72" s="446"/>
+      <x:c r="I72" s="446"/>
+      <x:c r="J72" s="446"/>
+      <x:c r="K72" s="446"/>
+      <x:c r="L72" s="446"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="446"/>
+      <x:c r="B73" s="446"/>
+      <x:c r="C73" s="446"/>
+      <x:c r="D73" s="446"/>
+      <x:c r="E73" s="446"/>
+      <x:c r="F73" s="446"/>
+      <x:c r="G73" s="446"/>
+      <x:c r="H73" s="446"/>
+      <x:c r="I73" s="446"/>
+      <x:c r="J73" s="446"/>
+      <x:c r="K73" s="446"/>
+      <x:c r="L73" s="446"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="446"/>
+      <x:c r="B74" s="446"/>
+      <x:c r="C74" s="446"/>
+      <x:c r="D74" s="446"/>
+      <x:c r="E74" s="446"/>
+      <x:c r="F74" s="446"/>
+      <x:c r="G74" s="446"/>
+      <x:c r="H74" s="446"/>
+      <x:c r="I74" s="446"/>
+      <x:c r="J74" s="446"/>
+      <x:c r="K74" s="446"/>
+      <x:c r="L74" s="446"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="446"/>
+      <x:c r="B75" s="446"/>
+      <x:c r="C75" s="446"/>
+      <x:c r="D75" s="446"/>
+      <x:c r="E75" s="446"/>
+      <x:c r="F75" s="446"/>
+      <x:c r="G75" s="446"/>
+      <x:c r="H75" s="446"/>
+      <x:c r="I75" s="446"/>
+      <x:c r="J75" s="446"/>
+      <x:c r="K75" s="446"/>
+      <x:c r="L75" s="446"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="446"/>
+      <x:c r="B76" s="446"/>
+      <x:c r="C76" s="446"/>
+      <x:c r="D76" s="446"/>
+      <x:c r="E76" s="446"/>
+      <x:c r="F76" s="446"/>
+      <x:c r="G76" s="446"/>
+      <x:c r="H76" s="446"/>
+      <x:c r="I76" s="446"/>
+      <x:c r="J76" s="446"/>
+      <x:c r="K76" s="446"/>
+      <x:c r="L76" s="446"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="446"/>
+      <x:c r="B77" s="446"/>
+      <x:c r="C77" s="446"/>
+      <x:c r="D77" s="446"/>
+      <x:c r="E77" s="446"/>
+      <x:c r="F77" s="446"/>
+      <x:c r="G77" s="446"/>
+      <x:c r="H77" s="446"/>
+      <x:c r="I77" s="446"/>
+      <x:c r="J77" s="446"/>
+      <x:c r="K77" s="446"/>
+      <x:c r="L77" s="446"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="446"/>
+      <x:c r="B78" s="446"/>
+      <x:c r="C78" s="446"/>
+      <x:c r="D78" s="446"/>
+      <x:c r="E78" s="446"/>
+      <x:c r="F78" s="446"/>
+      <x:c r="G78" s="446"/>
+      <x:c r="H78" s="446"/>
+      <x:c r="I78" s="446"/>
+      <x:c r="J78" s="446"/>
+      <x:c r="K78" s="446"/>
+      <x:c r="L78" s="446"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="446"/>
+      <x:c r="B79" s="446"/>
+      <x:c r="C79" s="446"/>
+      <x:c r="D79" s="446"/>
+      <x:c r="E79" s="446"/>
+      <x:c r="F79" s="446"/>
+      <x:c r="G79" s="446"/>
+      <x:c r="H79" s="446"/>
+      <x:c r="I79" s="446"/>
+      <x:c r="J79" s="446"/>
+      <x:c r="K79" s="446"/>
+      <x:c r="L79" s="446"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="446"/>
+      <x:c r="B80" s="446"/>
+      <x:c r="C80" s="446"/>
+      <x:c r="D80" s="446"/>
+      <x:c r="E80" s="446"/>
+      <x:c r="F80" s="446"/>
+      <x:c r="G80" s="446"/>
+      <x:c r="H80" s="446"/>
+      <x:c r="I80" s="446"/>
+      <x:c r="J80" s="446"/>
+      <x:c r="K80" s="446"/>
+      <x:c r="L80" s="446"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="446"/>
+      <x:c r="B81" s="446"/>
+      <x:c r="C81" s="446"/>
+      <x:c r="D81" s="446"/>
+      <x:c r="E81" s="446"/>
+      <x:c r="F81" s="446"/>
+      <x:c r="G81" s="446"/>
+      <x:c r="H81" s="446"/>
+      <x:c r="I81" s="446"/>
+      <x:c r="J81" s="446"/>
+      <x:c r="K81" s="446"/>
+      <x:c r="L81" s="446"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="446"/>
+      <x:c r="B82" s="446"/>
+      <x:c r="C82" s="446"/>
+      <x:c r="D82" s="446"/>
+      <x:c r="E82" s="446"/>
+      <x:c r="F82" s="446"/>
+      <x:c r="G82" s="446"/>
+      <x:c r="H82" s="446"/>
+      <x:c r="I82" s="446"/>
+      <x:c r="J82" s="446"/>
+      <x:c r="K82" s="446"/>
+      <x:c r="L82" s="446"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="446"/>
+      <x:c r="B83" s="446"/>
+      <x:c r="C83" s="446"/>
+      <x:c r="D83" s="446"/>
+      <x:c r="E83" s="446"/>
+      <x:c r="F83" s="446"/>
+      <x:c r="G83" s="446"/>
+      <x:c r="H83" s="446"/>
+      <x:c r="I83" s="446"/>
+      <x:c r="J83" s="446"/>
+      <x:c r="K83" s="446"/>
+      <x:c r="L83" s="446"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="446"/>
+      <x:c r="B84" s="446"/>
+      <x:c r="C84" s="446"/>
+      <x:c r="D84" s="446"/>
+      <x:c r="E84" s="446"/>
+      <x:c r="F84" s="446"/>
+      <x:c r="G84" s="446"/>
+      <x:c r="H84" s="446"/>
+      <x:c r="I84" s="446"/>
+      <x:c r="J84" s="446"/>
+      <x:c r="K84" s="446"/>
+      <x:c r="L84" s="446"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="446"/>
+      <x:c r="B85" s="446"/>
+      <x:c r="C85" s="446"/>
+      <x:c r="D85" s="446"/>
+      <x:c r="E85" s="446"/>
+      <x:c r="F85" s="446"/>
+      <x:c r="G85" s="446"/>
+      <x:c r="H85" s="446"/>
+      <x:c r="I85" s="446"/>
+      <x:c r="J85" s="446"/>
+      <x:c r="K85" s="446"/>
+      <x:c r="L85" s="446"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="446"/>
+      <x:c r="B86" s="446"/>
+      <x:c r="C86" s="446"/>
+      <x:c r="D86" s="446"/>
+      <x:c r="E86" s="446"/>
+      <x:c r="F86" s="446"/>
+      <x:c r="G86" s="446"/>
+      <x:c r="H86" s="446"/>
+      <x:c r="I86" s="446"/>
+      <x:c r="J86" s="446"/>
+      <x:c r="K86" s="446"/>
+      <x:c r="L86" s="446"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="446"/>
+      <x:c r="B87" s="446"/>
+      <x:c r="C87" s="446"/>
+      <x:c r="D87" s="446"/>
+      <x:c r="E87" s="446"/>
+      <x:c r="F87" s="446"/>
+      <x:c r="G87" s="446"/>
+      <x:c r="H87" s="446"/>
+      <x:c r="I87" s="446"/>
+      <x:c r="J87" s="446"/>
+      <x:c r="K87" s="446"/>
+      <x:c r="L87" s="446"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="446"/>
+      <x:c r="B88" s="446"/>
+      <x:c r="C88" s="446"/>
+      <x:c r="D88" s="446"/>
+      <x:c r="E88" s="446"/>
+      <x:c r="F88" s="446"/>
+      <x:c r="G88" s="446"/>
+      <x:c r="H88" s="446"/>
+      <x:c r="I88" s="446"/>
+      <x:c r="J88" s="446"/>
+      <x:c r="K88" s="446"/>
+      <x:c r="L88" s="446"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="446"/>
+      <x:c r="B89" s="446"/>
+      <x:c r="C89" s="446"/>
+      <x:c r="D89" s="446"/>
+      <x:c r="E89" s="446"/>
+      <x:c r="F89" s="446"/>
+      <x:c r="G89" s="446"/>
+      <x:c r="H89" s="446"/>
+      <x:c r="I89" s="446"/>
+      <x:c r="J89" s="446"/>
+      <x:c r="K89" s="446"/>
+      <x:c r="L89" s="446"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="446"/>
+      <x:c r="B90" s="446"/>
+      <x:c r="C90" s="446"/>
+      <x:c r="D90" s="446"/>
+      <x:c r="E90" s="446"/>
+      <x:c r="F90" s="446"/>
+      <x:c r="G90" s="446"/>
+      <x:c r="H90" s="446"/>
+      <x:c r="I90" s="446"/>
+      <x:c r="J90" s="446"/>
+      <x:c r="K90" s="446"/>
+      <x:c r="L90" s="446"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="446"/>
+      <x:c r="B91" s="446"/>
+      <x:c r="C91" s="446"/>
+      <x:c r="D91" s="446"/>
+      <x:c r="E91" s="446"/>
+      <x:c r="F91" s="446"/>
+      <x:c r="G91" s="446"/>
+      <x:c r="H91" s="446"/>
+      <x:c r="I91" s="446"/>
+      <x:c r="J91" s="446"/>
+      <x:c r="K91" s="446"/>
+      <x:c r="L91" s="446"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="446"/>
+      <x:c r="B92" s="446"/>
+      <x:c r="C92" s="446"/>
+      <x:c r="D92" s="446"/>
+      <x:c r="E92" s="446"/>
+      <x:c r="F92" s="446"/>
+      <x:c r="G92" s="446"/>
+      <x:c r="H92" s="446"/>
+      <x:c r="I92" s="446"/>
+      <x:c r="J92" s="446"/>
+      <x:c r="K92" s="446"/>
+      <x:c r="L92" s="446"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="446"/>
+      <x:c r="B93" s="446"/>
+      <x:c r="C93" s="446"/>
+      <x:c r="D93" s="446"/>
+      <x:c r="E93" s="446"/>
+      <x:c r="F93" s="446"/>
+      <x:c r="G93" s="446"/>
+      <x:c r="H93" s="446"/>
+      <x:c r="I93" s="446"/>
+      <x:c r="J93" s="446"/>
+      <x:c r="K93" s="446"/>
+      <x:c r="L93" s="446"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="446"/>
+      <x:c r="B94" s="446"/>
+      <x:c r="C94" s="446"/>
+      <x:c r="D94" s="446"/>
+      <x:c r="E94" s="446"/>
+      <x:c r="F94" s="446"/>
+      <x:c r="G94" s="446"/>
+      <x:c r="H94" s="446"/>
+      <x:c r="I94" s="446"/>
+      <x:c r="J94" s="446"/>
+      <x:c r="K94" s="446"/>
+      <x:c r="L94" s="446"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="446"/>
+      <x:c r="B95" s="446"/>
+      <x:c r="C95" s="446"/>
+      <x:c r="D95" s="446"/>
+      <x:c r="E95" s="446"/>
+      <x:c r="F95" s="446"/>
+      <x:c r="G95" s="446"/>
+      <x:c r="H95" s="446"/>
+      <x:c r="I95" s="446"/>
+      <x:c r="J95" s="446"/>
+      <x:c r="K95" s="446"/>
+      <x:c r="L95" s="446"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="446"/>
+      <x:c r="B96" s="446"/>
+      <x:c r="C96" s="446"/>
+      <x:c r="D96" s="446"/>
+      <x:c r="E96" s="446"/>
+      <x:c r="F96" s="446"/>
+      <x:c r="G96" s="446"/>
+      <x:c r="H96" s="446"/>
+      <x:c r="I96" s="446"/>
+      <x:c r="J96" s="446"/>
+      <x:c r="K96" s="446"/>
+      <x:c r="L96" s="446"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="446"/>
+      <x:c r="B97" s="446"/>
+      <x:c r="C97" s="446"/>
+      <x:c r="D97" s="446"/>
+      <x:c r="E97" s="446"/>
+      <x:c r="F97" s="446"/>
+      <x:c r="G97" s="446"/>
+      <x:c r="H97" s="446"/>
+      <x:c r="I97" s="446"/>
+      <x:c r="J97" s="446"/>
+      <x:c r="K97" s="446"/>
+      <x:c r="L97" s="446"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="446"/>
+      <x:c r="B98" s="446"/>
+      <x:c r="C98" s="446"/>
+      <x:c r="D98" s="446"/>
+      <x:c r="E98" s="446"/>
+      <x:c r="F98" s="446"/>
+      <x:c r="G98" s="446"/>
+      <x:c r="H98" s="446"/>
+      <x:c r="I98" s="446"/>
+      <x:c r="J98" s="446"/>
+      <x:c r="K98" s="446"/>
+      <x:c r="L98" s="446"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="446"/>
+      <x:c r="B99" s="446"/>
+      <x:c r="C99" s="446"/>
+      <x:c r="D99" s="446"/>
+      <x:c r="E99" s="446"/>
+      <x:c r="F99" s="446"/>
+      <x:c r="G99" s="446"/>
+      <x:c r="H99" s="446"/>
+      <x:c r="I99" s="446"/>
+      <x:c r="J99" s="446"/>
+      <x:c r="K99" s="446"/>
+      <x:c r="L99" s="446"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="446"/>
+      <x:c r="B100" s="446"/>
+      <x:c r="C100" s="446"/>
+      <x:c r="D100" s="446"/>
+      <x:c r="E100" s="446"/>
+      <x:c r="F100" s="446"/>
+      <x:c r="G100" s="446"/>
+      <x:c r="H100" s="446"/>
+      <x:c r="I100" s="446"/>
+      <x:c r="J100" s="446"/>
+      <x:c r="K100" s="446"/>
+      <x:c r="L100" s="446"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="446"/>
+      <x:c r="B101" s="446"/>
+      <x:c r="C101" s="446"/>
+      <x:c r="D101" s="446"/>
+      <x:c r="E101" s="446"/>
+      <x:c r="F101" s="446"/>
+      <x:c r="G101" s="446"/>
+      <x:c r="H101" s="446"/>
+      <x:c r="I101" s="446"/>
+      <x:c r="J101" s="446"/>
+      <x:c r="K101" s="446"/>
+      <x:c r="L101" s="446"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="446"/>
+      <x:c r="B102" s="446"/>
+      <x:c r="C102" s="446"/>
+      <x:c r="D102" s="446"/>
+      <x:c r="E102" s="446"/>
+      <x:c r="F102" s="446"/>
+      <x:c r="G102" s="446"/>
+      <x:c r="H102" s="446"/>
+      <x:c r="I102" s="446"/>
+      <x:c r="J102" s="446"/>
+      <x:c r="K102" s="446"/>
+      <x:c r="L102" s="446"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="446"/>
+      <x:c r="B103" s="446"/>
+      <x:c r="C103" s="446"/>
+      <x:c r="D103" s="446"/>
+      <x:c r="E103" s="446"/>
+      <x:c r="F103" s="446"/>
+      <x:c r="G103" s="446"/>
+      <x:c r="H103" s="446"/>
+      <x:c r="I103" s="446"/>
+      <x:c r="J103" s="446"/>
+      <x:c r="K103" s="446"/>
+      <x:c r="L103" s="446"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="446"/>
+      <x:c r="B104" s="446"/>
+      <x:c r="C104" s="446"/>
+      <x:c r="D104" s="446"/>
+      <x:c r="E104" s="446"/>
+      <x:c r="F104" s="446"/>
+      <x:c r="G104" s="446"/>
+      <x:c r="H104" s="446"/>
+      <x:c r="I104" s="446"/>
+      <x:c r="J104" s="446"/>
+      <x:c r="K104" s="446"/>
+      <x:c r="L104" s="446"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="446"/>
+      <x:c r="B105" s="446"/>
+      <x:c r="C105" s="446"/>
+      <x:c r="D105" s="446"/>
+      <x:c r="E105" s="446"/>
+      <x:c r="F105" s="446"/>
+      <x:c r="G105" s="446"/>
+      <x:c r="H105" s="446"/>
+      <x:c r="I105" s="446"/>
+      <x:c r="J105" s="446"/>
+      <x:c r="K105" s="446"/>
+      <x:c r="L105" s="446"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="446"/>
+      <x:c r="B106" s="446"/>
+      <x:c r="C106" s="446"/>
+      <x:c r="D106" s="446"/>
+      <x:c r="E106" s="446"/>
+      <x:c r="F106" s="446"/>
+      <x:c r="G106" s="446"/>
+      <x:c r="H106" s="446"/>
+      <x:c r="I106" s="446"/>
+      <x:c r="J106" s="446"/>
+      <x:c r="K106" s="446"/>
+      <x:c r="L106" s="446"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="446"/>
+      <x:c r="B107" s="446"/>
+      <x:c r="C107" s="446"/>
+      <x:c r="D107" s="446"/>
+      <x:c r="E107" s="446"/>
+      <x:c r="F107" s="446"/>
+      <x:c r="G107" s="446"/>
+      <x:c r="H107" s="446"/>
+      <x:c r="I107" s="446"/>
+      <x:c r="J107" s="446"/>
+      <x:c r="K107" s="446"/>
+      <x:c r="L107" s="446"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="446"/>
+      <x:c r="B108" s="446"/>
+      <x:c r="C108" s="446"/>
+      <x:c r="D108" s="446"/>
+      <x:c r="E108" s="446"/>
+      <x:c r="F108" s="446"/>
+      <x:c r="G108" s="446"/>
+      <x:c r="H108" s="446"/>
+      <x:c r="I108" s="446"/>
+      <x:c r="J108" s="446"/>
+      <x:c r="K108" s="446"/>
+      <x:c r="L108" s="446"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="446"/>
+      <x:c r="B109" s="446"/>
+      <x:c r="C109" s="446"/>
+      <x:c r="D109" s="446"/>
+      <x:c r="E109" s="446"/>
+      <x:c r="F109" s="446"/>
+      <x:c r="G109" s="446"/>
+      <x:c r="H109" s="446"/>
+      <x:c r="I109" s="446"/>
+      <x:c r="J109" s="446"/>
+      <x:c r="K109" s="446"/>
+      <x:c r="L109" s="446"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="446"/>
+      <x:c r="B110" s="446"/>
+      <x:c r="C110" s="446"/>
+      <x:c r="D110" s="446"/>
+      <x:c r="E110" s="446"/>
+      <x:c r="F110" s="446"/>
+      <x:c r="G110" s="446"/>
+      <x:c r="H110" s="446"/>
+      <x:c r="I110" s="446"/>
+      <x:c r="J110" s="446"/>
+      <x:c r="K110" s="446"/>
+      <x:c r="L110" s="446"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="446"/>
+      <x:c r="B111" s="446"/>
+      <x:c r="C111" s="446"/>
+      <x:c r="D111" s="446"/>
+      <x:c r="E111" s="446"/>
+      <x:c r="F111" s="446"/>
+      <x:c r="G111" s="446"/>
+      <x:c r="H111" s="446"/>
+      <x:c r="I111" s="446"/>
+      <x:c r="J111" s="446"/>
+      <x:c r="K111" s="446"/>
+      <x:c r="L111" s="446"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="446"/>
+      <x:c r="B112" s="446"/>
+      <x:c r="C112" s="446"/>
+      <x:c r="D112" s="446"/>
+      <x:c r="E112" s="446"/>
+      <x:c r="F112" s="446"/>
+      <x:c r="G112" s="446"/>
+      <x:c r="H112" s="446"/>
+      <x:c r="I112" s="446"/>
+      <x:c r="J112" s="446"/>
+      <x:c r="K112" s="446"/>
+      <x:c r="L112" s="446"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="446"/>
+      <x:c r="B113" s="446"/>
+      <x:c r="C113" s="446"/>
+      <x:c r="D113" s="446"/>
+      <x:c r="E113" s="446"/>
+      <x:c r="F113" s="446"/>
+      <x:c r="G113" s="446"/>
+      <x:c r="H113" s="446"/>
+      <x:c r="I113" s="446"/>
+      <x:c r="J113" s="446"/>
+      <x:c r="K113" s="446"/>
+      <x:c r="L113" s="446"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="446"/>
+      <x:c r="B114" s="446"/>
+      <x:c r="C114" s="446"/>
+      <x:c r="D114" s="446"/>
+      <x:c r="E114" s="446"/>
+      <x:c r="F114" s="446"/>
+      <x:c r="G114" s="446"/>
+      <x:c r="H114" s="446"/>
+      <x:c r="I114" s="446"/>
+      <x:c r="J114" s="446"/>
+      <x:c r="K114" s="446"/>
+      <x:c r="L114" s="446"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="446"/>
+      <x:c r="B115" s="446"/>
+      <x:c r="C115" s="446"/>
+      <x:c r="D115" s="446"/>
+      <x:c r="E115" s="446"/>
+      <x:c r="F115" s="446"/>
+      <x:c r="G115" s="446"/>
+      <x:c r="H115" s="446"/>
+      <x:c r="I115" s="446"/>
+      <x:c r="J115" s="446"/>
+      <x:c r="K115" s="446"/>
+      <x:c r="L115" s="446"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="446"/>
+      <x:c r="B116" s="446"/>
+      <x:c r="C116" s="446"/>
+      <x:c r="D116" s="446"/>
+      <x:c r="E116" s="446"/>
+      <x:c r="F116" s="446"/>
+      <x:c r="G116" s="446"/>
+      <x:c r="H116" s="446"/>
+      <x:c r="I116" s="446"/>
+      <x:c r="J116" s="446"/>
+      <x:c r="K116" s="446"/>
+      <x:c r="L116" s="446"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="446"/>
+      <x:c r="B117" s="446"/>
+      <x:c r="C117" s="446"/>
+      <x:c r="D117" s="446"/>
+      <x:c r="E117" s="446"/>
+      <x:c r="F117" s="446"/>
+      <x:c r="G117" s="446"/>
+      <x:c r="H117" s="446"/>
+      <x:c r="I117" s="446"/>
+      <x:c r="J117" s="446"/>
+      <x:c r="K117" s="446"/>
+      <x:c r="L117" s="446"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="446"/>
+      <x:c r="B118" s="446"/>
+      <x:c r="C118" s="446"/>
+      <x:c r="D118" s="446"/>
+      <x:c r="E118" s="446"/>
+      <x:c r="F118" s="446"/>
+      <x:c r="G118" s="446"/>
+      <x:c r="H118" s="446"/>
+      <x:c r="I118" s="446"/>
+      <x:c r="J118" s="446"/>
+      <x:c r="K118" s="446"/>
+      <x:c r="L118" s="446"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="446"/>
+      <x:c r="B119" s="446"/>
+      <x:c r="C119" s="446"/>
+      <x:c r="D119" s="446"/>
+      <x:c r="E119" s="446"/>
+      <x:c r="F119" s="446"/>
+      <x:c r="G119" s="446"/>
+      <x:c r="H119" s="446"/>
+      <x:c r="I119" s="446"/>
+      <x:c r="J119" s="446"/>
+      <x:c r="K119" s="446"/>
+      <x:c r="L119" s="446"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="446"/>
+      <x:c r="B120" s="446"/>
+      <x:c r="C120" s="446"/>
+      <x:c r="D120" s="446"/>
+      <x:c r="E120" s="446"/>
+      <x:c r="F120" s="446"/>
+      <x:c r="G120" s="446"/>
+      <x:c r="H120" s="446"/>
+      <x:c r="I120" s="446"/>
+      <x:c r="J120" s="446"/>
+      <x:c r="K120" s="446"/>
+      <x:c r="L120" s="446"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="446"/>
+      <x:c r="B121" s="446"/>
+      <x:c r="C121" s="446"/>
+      <x:c r="D121" s="446"/>
+      <x:c r="E121" s="446"/>
+      <x:c r="F121" s="446"/>
+      <x:c r="G121" s="446"/>
+      <x:c r="H121" s="446"/>
+      <x:c r="I121" s="446"/>
+      <x:c r="J121" s="446"/>
+      <x:c r="K121" s="446"/>
+      <x:c r="L121" s="446"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="446"/>
+      <x:c r="B122" s="446"/>
+      <x:c r="C122" s="446"/>
+      <x:c r="D122" s="446"/>
+      <x:c r="E122" s="446"/>
+      <x:c r="F122" s="446"/>
+      <x:c r="G122" s="446"/>
+      <x:c r="H122" s="446"/>
+      <x:c r="I122" s="446"/>
+      <x:c r="J122" s="446"/>
+      <x:c r="K122" s="446"/>
+      <x:c r="L122" s="446"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="446"/>
+      <x:c r="B123" s="446"/>
+      <x:c r="C123" s="446"/>
+      <x:c r="D123" s="446"/>
+      <x:c r="E123" s="446"/>
+      <x:c r="F123" s="446"/>
+      <x:c r="G123" s="446"/>
+      <x:c r="H123" s="446"/>
+      <x:c r="I123" s="446"/>
+      <x:c r="J123" s="446"/>
+      <x:c r="K123" s="446"/>
+      <x:c r="L123" s="446"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="446"/>
+      <x:c r="B124" s="446"/>
+      <x:c r="C124" s="446"/>
+      <x:c r="D124" s="446"/>
+      <x:c r="E124" s="446"/>
+      <x:c r="F124" s="446"/>
+      <x:c r="G124" s="446"/>
+      <x:c r="H124" s="446"/>
+      <x:c r="I124" s="446"/>
+      <x:c r="J124" s="446"/>
+      <x:c r="K124" s="446"/>
+      <x:c r="L124" s="446"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="446"/>
+      <x:c r="B125" s="446"/>
+      <x:c r="C125" s="446"/>
+      <x:c r="D125" s="446"/>
+      <x:c r="E125" s="446"/>
+      <x:c r="F125" s="446"/>
+      <x:c r="G125" s="446"/>
+      <x:c r="H125" s="446"/>
+      <x:c r="I125" s="446"/>
+      <x:c r="J125" s="446"/>
+      <x:c r="K125" s="446"/>
+      <x:c r="L125" s="446"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="446"/>
+      <x:c r="B126" s="446"/>
+      <x:c r="C126" s="446"/>
+      <x:c r="D126" s="446"/>
+      <x:c r="E126" s="446"/>
+      <x:c r="F126" s="446"/>
+      <x:c r="G126" s="446"/>
+      <x:c r="H126" s="446"/>
+      <x:c r="I126" s="446"/>
+      <x:c r="J126" s="446"/>
+      <x:c r="K126" s="446"/>
+      <x:c r="L126" s="446"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="446"/>
+      <x:c r="B127" s="446"/>
+      <x:c r="C127" s="446"/>
+      <x:c r="D127" s="446"/>
+      <x:c r="E127" s="446"/>
+      <x:c r="F127" s="446"/>
+      <x:c r="G127" s="446"/>
+      <x:c r="H127" s="446"/>
+      <x:c r="I127" s="446"/>
+      <x:c r="J127" s="446"/>
+      <x:c r="K127" s="446"/>
+      <x:c r="L127" s="446"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="446"/>
+      <x:c r="B128" s="446"/>
+      <x:c r="C128" s="446"/>
+      <x:c r="D128" s="446"/>
+      <x:c r="E128" s="446"/>
+      <x:c r="F128" s="446"/>
+      <x:c r="G128" s="446"/>
+      <x:c r="H128" s="446"/>
+      <x:c r="I128" s="446"/>
+      <x:c r="J128" s="446"/>
+      <x:c r="K128" s="446"/>
+      <x:c r="L128" s="446"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="446"/>
+      <x:c r="B129" s="446"/>
+      <x:c r="C129" s="446"/>
+      <x:c r="D129" s="446"/>
+      <x:c r="E129" s="446"/>
+      <x:c r="F129" s="446"/>
+      <x:c r="G129" s="446"/>
+      <x:c r="H129" s="446"/>
+      <x:c r="I129" s="446"/>
+      <x:c r="J129" s="446"/>
+      <x:c r="K129" s="446"/>
+      <x:c r="L129" s="446"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="446"/>
+      <x:c r="B130" s="446"/>
+      <x:c r="C130" s="446"/>
+      <x:c r="D130" s="446"/>
+      <x:c r="E130" s="446"/>
+      <x:c r="F130" s="446"/>
+      <x:c r="G130" s="446"/>
+      <x:c r="H130" s="446"/>
+      <x:c r="I130" s="446"/>
+      <x:c r="J130" s="446"/>
+      <x:c r="K130" s="446"/>
+      <x:c r="L130" s="446"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="446"/>
+      <x:c r="B131" s="446"/>
+      <x:c r="C131" s="446"/>
+      <x:c r="D131" s="446"/>
+      <x:c r="E131" s="446"/>
+      <x:c r="F131" s="446"/>
+      <x:c r="G131" s="446"/>
+      <x:c r="H131" s="446"/>
+      <x:c r="I131" s="446"/>
+      <x:c r="J131" s="446"/>
+      <x:c r="K131" s="446"/>
+      <x:c r="L131" s="446"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="446"/>
+      <x:c r="B132" s="446"/>
+      <x:c r="C132" s="446"/>
+      <x:c r="D132" s="446"/>
+      <x:c r="E132" s="446"/>
+      <x:c r="F132" s="446"/>
+      <x:c r="G132" s="446"/>
+      <x:c r="H132" s="446"/>
+      <x:c r="I132" s="446"/>
+      <x:c r="J132" s="446"/>
+      <x:c r="K132" s="446"/>
+      <x:c r="L132" s="446"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="446"/>
+      <x:c r="B133" s="446"/>
+      <x:c r="C133" s="446"/>
+      <x:c r="D133" s="446"/>
+      <x:c r="E133" s="446"/>
+      <x:c r="F133" s="446"/>
+      <x:c r="G133" s="446"/>
+      <x:c r="H133" s="446"/>
+      <x:c r="I133" s="446"/>
+      <x:c r="J133" s="446"/>
+      <x:c r="K133" s="446"/>
+      <x:c r="L133" s="446"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="446"/>
+      <x:c r="B134" s="446"/>
+      <x:c r="C134" s="446"/>
+      <x:c r="D134" s="446"/>
+      <x:c r="E134" s="446"/>
+      <x:c r="F134" s="446"/>
+      <x:c r="G134" s="446"/>
+      <x:c r="H134" s="446"/>
+      <x:c r="I134" s="446"/>
+      <x:c r="J134" s="446"/>
+      <x:c r="K134" s="446"/>
+      <x:c r="L134" s="446"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="446"/>
+      <x:c r="B135" s="446"/>
+      <x:c r="C135" s="446"/>
+      <x:c r="D135" s="446"/>
+      <x:c r="E135" s="446"/>
+      <x:c r="F135" s="446"/>
+      <x:c r="G135" s="446"/>
+      <x:c r="H135" s="446"/>
+      <x:c r="I135" s="446"/>
+      <x:c r="J135" s="446"/>
+      <x:c r="K135" s="446"/>
+      <x:c r="L135" s="446"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="446"/>
+      <x:c r="B136" s="446"/>
+      <x:c r="C136" s="446"/>
+      <x:c r="D136" s="446"/>
+      <x:c r="E136" s="446"/>
+      <x:c r="F136" s="446"/>
+      <x:c r="G136" s="446"/>
+      <x:c r="H136" s="446"/>
+      <x:c r="I136" s="446"/>
+      <x:c r="J136" s="446"/>
+      <x:c r="K136" s="446"/>
+      <x:c r="L136" s="446"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="446"/>
+      <x:c r="B137" s="446"/>
+      <x:c r="C137" s="446"/>
+      <x:c r="D137" s="446"/>
+      <x:c r="E137" s="446"/>
+      <x:c r="F137" s="446"/>
+      <x:c r="G137" s="446"/>
+      <x:c r="H137" s="446"/>
+      <x:c r="I137" s="446"/>
+      <x:c r="J137" s="446"/>
+      <x:c r="K137" s="446"/>
+      <x:c r="L137" s="446"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="446"/>
+      <x:c r="B138" s="446"/>
+      <x:c r="C138" s="446"/>
+      <x:c r="D138" s="446"/>
+      <x:c r="E138" s="446"/>
+      <x:c r="F138" s="446"/>
+      <x:c r="G138" s="446"/>
+      <x:c r="H138" s="446"/>
+      <x:c r="I138" s="446"/>
+      <x:c r="J138" s="446"/>
+      <x:c r="K138" s="446"/>
+      <x:c r="L138" s="446"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="446"/>
+      <x:c r="B139" s="446"/>
+      <x:c r="C139" s="446"/>
+      <x:c r="D139" s="446"/>
+      <x:c r="E139" s="446"/>
+      <x:c r="F139" s="446"/>
+      <x:c r="G139" s="446"/>
+      <x:c r="H139" s="446"/>
+      <x:c r="I139" s="446"/>
+      <x:c r="J139" s="446"/>
+      <x:c r="K139" s="446"/>
+      <x:c r="L139" s="446"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="446"/>
+      <x:c r="B140" s="446"/>
+      <x:c r="C140" s="446"/>
+      <x:c r="D140" s="446"/>
+      <x:c r="E140" s="446"/>
+      <x:c r="F140" s="446"/>
+      <x:c r="G140" s="446"/>
+      <x:c r="H140" s="446"/>
+      <x:c r="I140" s="446"/>
+      <x:c r="J140" s="446"/>
+      <x:c r="K140" s="446"/>
+      <x:c r="L140" s="446"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="446"/>
+      <x:c r="B141" s="446"/>
+      <x:c r="C141" s="446"/>
+      <x:c r="D141" s="446"/>
+      <x:c r="E141" s="446"/>
+      <x:c r="F141" s="446"/>
+      <x:c r="G141" s="446"/>
+      <x:c r="H141" s="446"/>
+      <x:c r="I141" s="446"/>
+      <x:c r="J141" s="446"/>
+      <x:c r="K141" s="446"/>
+      <x:c r="L141" s="446"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="446"/>
+      <x:c r="B142" s="446"/>
+      <x:c r="C142" s="446"/>
+      <x:c r="D142" s="446"/>
+      <x:c r="E142" s="446"/>
+      <x:c r="F142" s="446"/>
+      <x:c r="G142" s="446"/>
+      <x:c r="H142" s="446"/>
+      <x:c r="I142" s="446"/>
+      <x:c r="J142" s="446"/>
+      <x:c r="K142" s="446"/>
+      <x:c r="L142" s="446"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="446"/>
+      <x:c r="B143" s="446"/>
+      <x:c r="C143" s="446"/>
+      <x:c r="D143" s="446"/>
+      <x:c r="E143" s="446"/>
+      <x:c r="F143" s="446"/>
+      <x:c r="G143" s="446"/>
+      <x:c r="H143" s="446"/>
+      <x:c r="I143" s="446"/>
+      <x:c r="J143" s="446"/>
+      <x:c r="K143" s="446"/>
+      <x:c r="L143" s="446"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="446"/>
+      <x:c r="B144" s="446"/>
+      <x:c r="C144" s="446"/>
+      <x:c r="D144" s="446"/>
+      <x:c r="E144" s="446"/>
+      <x:c r="F144" s="446"/>
+      <x:c r="G144" s="446"/>
+      <x:c r="H144" s="446"/>
+      <x:c r="I144" s="446"/>
+      <x:c r="J144" s="446"/>
+      <x:c r="K144" s="446"/>
+      <x:c r="L144" s="446"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="446"/>
+      <x:c r="B145" s="446"/>
+      <x:c r="C145" s="446"/>
+      <x:c r="D145" s="446"/>
+      <x:c r="E145" s="446"/>
+      <x:c r="F145" s="446"/>
+      <x:c r="G145" s="446"/>
+      <x:c r="H145" s="446"/>
+      <x:c r="I145" s="446"/>
+      <x:c r="J145" s="446"/>
+      <x:c r="K145" s="446"/>
+      <x:c r="L145" s="446"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="446"/>
+      <x:c r="B146" s="446"/>
+      <x:c r="C146" s="446"/>
+      <x:c r="D146" s="446"/>
+      <x:c r="E146" s="446"/>
+      <x:c r="F146" s="446"/>
+      <x:c r="G146" s="446"/>
+      <x:c r="H146" s="446"/>
+      <x:c r="I146" s="446"/>
+      <x:c r="J146" s="446"/>
+      <x:c r="K146" s="446"/>
+      <x:c r="L146" s="446"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="446"/>
+      <x:c r="B147" s="446"/>
+      <x:c r="C147" s="446"/>
+      <x:c r="D147" s="446"/>
+      <x:c r="E147" s="446"/>
+      <x:c r="F147" s="446"/>
+      <x:c r="G147" s="446"/>
+      <x:c r="H147" s="446"/>
+      <x:c r="I147" s="446"/>
+      <x:c r="J147" s="446"/>
+      <x:c r="K147" s="446"/>
+      <x:c r="L147" s="446"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="446"/>
+      <x:c r="B148" s="446"/>
+      <x:c r="C148" s="446"/>
+      <x:c r="D148" s="446"/>
+      <x:c r="E148" s="446"/>
+      <x:c r="F148" s="446"/>
+      <x:c r="G148" s="446"/>
+      <x:c r="H148" s="446"/>
+      <x:c r="I148" s="446"/>
+      <x:c r="J148" s="446"/>
+      <x:c r="K148" s="446"/>
+      <x:c r="L148" s="446"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="446"/>
+      <x:c r="B149" s="446"/>
+      <x:c r="C149" s="446"/>
+      <x:c r="D149" s="446"/>
+      <x:c r="E149" s="446"/>
+      <x:c r="F149" s="446"/>
+      <x:c r="G149" s="446"/>
+      <x:c r="H149" s="446"/>
+      <x:c r="I149" s="446"/>
+      <x:c r="J149" s="446"/>
+      <x:c r="K149" s="446"/>
+      <x:c r="L149" s="446"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="446"/>
+      <x:c r="B150" s="446"/>
+      <x:c r="C150" s="446"/>
+      <x:c r="D150" s="446"/>
+      <x:c r="E150" s="446"/>
+      <x:c r="F150" s="446"/>
+      <x:c r="G150" s="446"/>
+      <x:c r="H150" s="446"/>
+      <x:c r="I150" s="446"/>
+      <x:c r="J150" s="446"/>
+      <x:c r="K150" s="446"/>
+      <x:c r="L150" s="446"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="446"/>
+      <x:c r="B151" s="446"/>
+      <x:c r="C151" s="446"/>
+      <x:c r="D151" s="446"/>
+      <x:c r="E151" s="446"/>
+      <x:c r="F151" s="446"/>
+      <x:c r="G151" s="446"/>
+      <x:c r="H151" s="446"/>
+      <x:c r="I151" s="446"/>
+      <x:c r="J151" s="446"/>
+      <x:c r="K151" s="446"/>
+      <x:c r="L151" s="446"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="446"/>
+      <x:c r="B152" s="446"/>
+      <x:c r="C152" s="446"/>
+      <x:c r="D152" s="446"/>
+      <x:c r="E152" s="446"/>
+      <x:c r="F152" s="446"/>
+      <x:c r="G152" s="446"/>
+      <x:c r="H152" s="446"/>
+      <x:c r="I152" s="446"/>
+      <x:c r="J152" s="446"/>
+      <x:c r="K152" s="446"/>
+      <x:c r="L152" s="446"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="446"/>
+      <x:c r="B153" s="446"/>
+      <x:c r="C153" s="446"/>
+      <x:c r="D153" s="446"/>
+      <x:c r="E153" s="446"/>
+      <x:c r="F153" s="446"/>
+      <x:c r="G153" s="446"/>
+      <x:c r="H153" s="446"/>
+      <x:c r="I153" s="446"/>
+      <x:c r="J153" s="446"/>
+      <x:c r="K153" s="446"/>
+      <x:c r="L153" s="446"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="446"/>
+      <x:c r="B154" s="446"/>
+      <x:c r="C154" s="446"/>
+      <x:c r="D154" s="446"/>
+      <x:c r="E154" s="446"/>
+      <x:c r="F154" s="446"/>
+      <x:c r="G154" s="446"/>
+      <x:c r="H154" s="446"/>
+      <x:c r="I154" s="446"/>
+      <x:c r="J154" s="446"/>
+      <x:c r="K154" s="446"/>
+      <x:c r="L154" s="446"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="446"/>
+      <x:c r="B155" s="446"/>
+      <x:c r="C155" s="446"/>
+      <x:c r="D155" s="446"/>
+      <x:c r="E155" s="446"/>
+      <x:c r="F155" s="446"/>
+      <x:c r="G155" s="446"/>
+      <x:c r="H155" s="446"/>
+      <x:c r="I155" s="446"/>
+      <x:c r="J155" s="446"/>
+      <x:c r="K155" s="446"/>
+      <x:c r="L155" s="446"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="446"/>
+      <x:c r="B156" s="446"/>
+      <x:c r="C156" s="446"/>
+      <x:c r="D156" s="446"/>
+      <x:c r="E156" s="446"/>
+      <x:c r="F156" s="446"/>
+      <x:c r="G156" s="446"/>
+      <x:c r="H156" s="446"/>
+      <x:c r="I156" s="446"/>
+      <x:c r="J156" s="446"/>
+      <x:c r="K156" s="446"/>
+      <x:c r="L156" s="446"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="446"/>
+      <x:c r="B157" s="446"/>
+      <x:c r="C157" s="446"/>
+      <x:c r="D157" s="446"/>
+      <x:c r="E157" s="446"/>
+      <x:c r="F157" s="446"/>
+      <x:c r="G157" s="446"/>
+      <x:c r="H157" s="446"/>
+      <x:c r="I157" s="446"/>
+      <x:c r="J157" s="446"/>
+      <x:c r="K157" s="446"/>
+      <x:c r="L157" s="446"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="446"/>
+      <x:c r="B158" s="446"/>
+      <x:c r="C158" s="446"/>
+      <x:c r="D158" s="446"/>
+      <x:c r="E158" s="446"/>
+      <x:c r="F158" s="446"/>
+      <x:c r="G158" s="446"/>
+      <x:c r="H158" s="446"/>
+      <x:c r="I158" s="446"/>
+      <x:c r="J158" s="446"/>
+      <x:c r="K158" s="446"/>
+      <x:c r="L158" s="446"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="446"/>
+      <x:c r="B159" s="446"/>
+      <x:c r="C159" s="446"/>
+      <x:c r="D159" s="446"/>
+      <x:c r="E159" s="446"/>
+      <x:c r="F159" s="446"/>
+      <x:c r="G159" s="446"/>
+      <x:c r="H159" s="446"/>
+      <x:c r="I159" s="446"/>
+      <x:c r="J159" s="446"/>
+      <x:c r="K159" s="446"/>
+      <x:c r="L159" s="446"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="446"/>
+      <x:c r="B160" s="446"/>
+      <x:c r="C160" s="446"/>
+      <x:c r="D160" s="446"/>
+      <x:c r="E160" s="446"/>
+      <x:c r="F160" s="446"/>
+      <x:c r="G160" s="446"/>
+      <x:c r="H160" s="446"/>
+      <x:c r="I160" s="446"/>
+      <x:c r="J160" s="446"/>
+      <x:c r="K160" s="446"/>
+      <x:c r="L160" s="446"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="446"/>
+      <x:c r="B161" s="446"/>
+      <x:c r="C161" s="446"/>
+      <x:c r="D161" s="446"/>
+      <x:c r="E161" s="446"/>
+      <x:c r="F161" s="446"/>
+      <x:c r="G161" s="446"/>
+      <x:c r="H161" s="446"/>
+      <x:c r="I161" s="446"/>
+      <x:c r="J161" s="446"/>
+      <x:c r="K161" s="446"/>
+      <x:c r="L161" s="446"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="446"/>
+      <x:c r="B162" s="446"/>
+      <x:c r="C162" s="446"/>
+      <x:c r="D162" s="446"/>
+      <x:c r="E162" s="446"/>
+      <x:c r="F162" s="446"/>
+      <x:c r="G162" s="446"/>
+      <x:c r="H162" s="446"/>
+      <x:c r="I162" s="446"/>
+      <x:c r="J162" s="446"/>
+      <x:c r="K162" s="446"/>
+      <x:c r="L162" s="446"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="446"/>
+      <x:c r="B163" s="446"/>
+      <x:c r="C163" s="446"/>
+      <x:c r="D163" s="446"/>
+      <x:c r="E163" s="446"/>
+      <x:c r="F163" s="446"/>
+      <x:c r="G163" s="446"/>
+      <x:c r="H163" s="446"/>
+      <x:c r="I163" s="446"/>
+      <x:c r="J163" s="446"/>
+      <x:c r="K163" s="446"/>
+      <x:c r="L163" s="446"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="446"/>
+      <x:c r="B164" s="446"/>
+      <x:c r="C164" s="446"/>
+      <x:c r="D164" s="446"/>
+      <x:c r="E164" s="446"/>
+      <x:c r="F164" s="446"/>
+      <x:c r="G164" s="446"/>
+      <x:c r="H164" s="446"/>
+      <x:c r="I164" s="446"/>
+      <x:c r="J164" s="446"/>
+      <x:c r="K164" s="446"/>
+      <x:c r="L164" s="446"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="446"/>
+      <x:c r="B165" s="446"/>
+      <x:c r="C165" s="446"/>
+      <x:c r="D165" s="446"/>
+      <x:c r="E165" s="446"/>
+      <x:c r="F165" s="446"/>
+      <x:c r="G165" s="446"/>
+      <x:c r="H165" s="446"/>
+      <x:c r="I165" s="446"/>
+      <x:c r="J165" s="446"/>
+      <x:c r="K165" s="446"/>
+      <x:c r="L165" s="446"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="446"/>
+      <x:c r="B166" s="446"/>
+      <x:c r="C166" s="446"/>
+      <x:c r="D166" s="446"/>
+      <x:c r="E166" s="446"/>
+      <x:c r="F166" s="446"/>
+      <x:c r="G166" s="446"/>
+      <x:c r="H166" s="446"/>
+      <x:c r="I166" s="446"/>
+      <x:c r="J166" s="446"/>
+      <x:c r="K166" s="446"/>
+      <x:c r="L166" s="446"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="446"/>
+      <x:c r="B167" s="446"/>
+      <x:c r="C167" s="446"/>
+      <x:c r="D167" s="446"/>
+      <x:c r="E167" s="446"/>
+      <x:c r="F167" s="446"/>
+      <x:c r="G167" s="446"/>
+      <x:c r="H167" s="446"/>
+      <x:c r="I167" s="446"/>
+      <x:c r="J167" s="446"/>
+      <x:c r="K167" s="446"/>
+      <x:c r="L167" s="446"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="446"/>
+      <x:c r="B168" s="446"/>
+      <x:c r="C168" s="446"/>
+      <x:c r="D168" s="446"/>
+      <x:c r="E168" s="446"/>
+      <x:c r="F168" s="446"/>
+      <x:c r="G168" s="446"/>
+      <x:c r="H168" s="446"/>
+      <x:c r="I168" s="446"/>
+      <x:c r="J168" s="446"/>
+      <x:c r="K168" s="446"/>
+      <x:c r="L168" s="446"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="446"/>
+      <x:c r="B169" s="446"/>
+      <x:c r="C169" s="446"/>
+      <x:c r="D169" s="446"/>
+      <x:c r="E169" s="446"/>
+      <x:c r="F169" s="446"/>
+      <x:c r="G169" s="446"/>
+      <x:c r="H169" s="446"/>
+      <x:c r="I169" s="446"/>
+      <x:c r="J169" s="446"/>
+      <x:c r="K169" s="446"/>
+      <x:c r="L169" s="446"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="446"/>
+      <x:c r="B170" s="446"/>
+      <x:c r="C170" s="446"/>
+      <x:c r="D170" s="446"/>
+      <x:c r="E170" s="446"/>
+      <x:c r="F170" s="446"/>
+      <x:c r="G170" s="446"/>
+      <x:c r="H170" s="446"/>
+      <x:c r="I170" s="446"/>
+      <x:c r="J170" s="446"/>
+      <x:c r="K170" s="446"/>
+      <x:c r="L170" s="446"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="446"/>
+      <x:c r="B171" s="446"/>
+      <x:c r="C171" s="446"/>
+      <x:c r="D171" s="446"/>
+      <x:c r="E171" s="446"/>
+      <x:c r="F171" s="446"/>
+      <x:c r="G171" s="446"/>
+      <x:c r="H171" s="446"/>
+      <x:c r="I171" s="446"/>
+      <x:c r="J171" s="446"/>
+      <x:c r="K171" s="446"/>
+      <x:c r="L171" s="446"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="446"/>
+      <x:c r="B172" s="446"/>
+      <x:c r="C172" s="446"/>
+      <x:c r="D172" s="446"/>
+      <x:c r="E172" s="446"/>
+      <x:c r="F172" s="446"/>
+      <x:c r="G172" s="446"/>
+      <x:c r="H172" s="446"/>
+      <x:c r="I172" s="446"/>
+      <x:c r="J172" s="446"/>
+      <x:c r="K172" s="446"/>
+      <x:c r="L172" s="446"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="446"/>
+      <x:c r="B173" s="446"/>
+      <x:c r="C173" s="446"/>
+      <x:c r="D173" s="446"/>
+      <x:c r="E173" s="446"/>
+      <x:c r="F173" s="446"/>
+      <x:c r="G173" s="446"/>
+      <x:c r="H173" s="446"/>
+      <x:c r="I173" s="446"/>
+      <x:c r="J173" s="446"/>
+      <x:c r="K173" s="446"/>
+      <x:c r="L173" s="446"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="446"/>
+      <x:c r="B174" s="446"/>
+      <x:c r="C174" s="446"/>
+      <x:c r="D174" s="446"/>
+      <x:c r="E174" s="446"/>
+      <x:c r="F174" s="446"/>
+      <x:c r="G174" s="446"/>
+      <x:c r="H174" s="446"/>
+      <x:c r="I174" s="446"/>
+      <x:c r="J174" s="446"/>
+      <x:c r="K174" s="446"/>
+      <x:c r="L174" s="446"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="446"/>
+      <x:c r="B175" s="446"/>
+      <x:c r="C175" s="446"/>
+      <x:c r="D175" s="446"/>
+      <x:c r="E175" s="446"/>
+      <x:c r="F175" s="446"/>
+      <x:c r="G175" s="446"/>
+      <x:c r="H175" s="446"/>
+      <x:c r="I175" s="446"/>
+      <x:c r="J175" s="446"/>
+      <x:c r="K175" s="446"/>
+      <x:c r="L175" s="446"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="446"/>
+      <x:c r="B176" s="446"/>
+      <x:c r="C176" s="446"/>
+      <x:c r="D176" s="446"/>
+      <x:c r="E176" s="446"/>
+      <x:c r="F176" s="446"/>
+      <x:c r="G176" s="446"/>
+      <x:c r="H176" s="446"/>
+      <x:c r="I176" s="446"/>
+      <x:c r="J176" s="446"/>
+      <x:c r="K176" s="446"/>
+      <x:c r="L176" s="446"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="446"/>
+      <x:c r="B177" s="446"/>
+      <x:c r="C177" s="446"/>
+      <x:c r="D177" s="446"/>
+      <x:c r="E177" s="446"/>
+      <x:c r="F177" s="446"/>
+      <x:c r="G177" s="446"/>
+      <x:c r="H177" s="446"/>
+      <x:c r="I177" s="446"/>
+      <x:c r="J177" s="446"/>
+      <x:c r="K177" s="446"/>
+      <x:c r="L177" s="446"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="446"/>
+      <x:c r="B178" s="446"/>
+      <x:c r="C178" s="446"/>
+      <x:c r="D178" s="446"/>
+      <x:c r="E178" s="446"/>
+      <x:c r="F178" s="446"/>
+      <x:c r="G178" s="446"/>
+      <x:c r="H178" s="446"/>
+      <x:c r="I178" s="446"/>
+      <x:c r="J178" s="446"/>
+      <x:c r="K178" s="446"/>
+      <x:c r="L178" s="446"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="446"/>
+      <x:c r="B179" s="446"/>
+      <x:c r="C179" s="446"/>
+      <x:c r="D179" s="446"/>
+      <x:c r="E179" s="446"/>
+      <x:c r="F179" s="446"/>
+      <x:c r="G179" s="446"/>
+      <x:c r="H179" s="446"/>
+      <x:c r="I179" s="446"/>
+      <x:c r="J179" s="446"/>
+      <x:c r="K179" s="446"/>
+      <x:c r="L179" s="446"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="446"/>
+      <x:c r="B180" s="446"/>
+      <x:c r="C180" s="446"/>
+      <x:c r="D180" s="446"/>
+      <x:c r="E180" s="446"/>
+      <x:c r="F180" s="446"/>
+      <x:c r="G180" s="446"/>
+      <x:c r="H180" s="446"/>
+      <x:c r="I180" s="446"/>
+      <x:c r="J180" s="446"/>
+      <x:c r="K180" s="446"/>
+      <x:c r="L180" s="446"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="446"/>
+      <x:c r="B181" s="446"/>
+      <x:c r="C181" s="446"/>
+      <x:c r="D181" s="446"/>
+      <x:c r="E181" s="446"/>
+      <x:c r="F181" s="446"/>
+      <x:c r="G181" s="446"/>
+      <x:c r="H181" s="446"/>
+      <x:c r="I181" s="446"/>
+      <x:c r="J181" s="446"/>
+      <x:c r="K181" s="446"/>
+      <x:c r="L181" s="446"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="446"/>
+      <x:c r="B182" s="446"/>
+      <x:c r="C182" s="446"/>
+      <x:c r="D182" s="446"/>
+      <x:c r="E182" s="446"/>
+      <x:c r="F182" s="446"/>
+      <x:c r="G182" s="446"/>
+      <x:c r="H182" s="446"/>
+      <x:c r="I182" s="446"/>
+      <x:c r="J182" s="446"/>
+      <x:c r="K182" s="446"/>
+      <x:c r="L182" s="446"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="446"/>
+      <x:c r="B183" s="446"/>
+      <x:c r="C183" s="446"/>
+      <x:c r="D183" s="446"/>
+      <x:c r="E183" s="446"/>
+      <x:c r="F183" s="446"/>
+      <x:c r="G183" s="446"/>
+      <x:c r="H183" s="446"/>
+      <x:c r="I183" s="446"/>
+      <x:c r="J183" s="446"/>
+      <x:c r="K183" s="446"/>
+      <x:c r="L183" s="446"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="446"/>
+      <x:c r="B184" s="446"/>
+      <x:c r="C184" s="446"/>
+      <x:c r="D184" s="446"/>
+      <x:c r="E184" s="446"/>
+      <x:c r="F184" s="446"/>
+      <x:c r="G184" s="446"/>
+      <x:c r="H184" s="446"/>
+      <x:c r="I184" s="446"/>
+      <x:c r="J184" s="446"/>
+      <x:c r="K184" s="446"/>
+      <x:c r="L184" s="446"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="446"/>
+      <x:c r="B185" s="446"/>
+      <x:c r="C185" s="446"/>
+      <x:c r="D185" s="446"/>
+      <x:c r="E185" s="446"/>
+      <x:c r="F185" s="446"/>
+      <x:c r="G185" s="446"/>
+      <x:c r="H185" s="446"/>
+      <x:c r="I185" s="446"/>
+      <x:c r="J185" s="446"/>
+      <x:c r="K185" s="446"/>
+      <x:c r="L185" s="446"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="446"/>
+      <x:c r="B186" s="446"/>
+      <x:c r="C186" s="446"/>
+      <x:c r="D186" s="446"/>
+      <x:c r="E186" s="446"/>
+      <x:c r="F186" s="446"/>
+      <x:c r="G186" s="446"/>
+      <x:c r="H186" s="446"/>
+      <x:c r="I186" s="446"/>
+      <x:c r="J186" s="446"/>
+      <x:c r="K186" s="446"/>
+      <x:c r="L186" s="446"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="446"/>
+      <x:c r="B187" s="446"/>
+      <x:c r="C187" s="446"/>
+      <x:c r="D187" s="446"/>
+      <x:c r="E187" s="446"/>
+      <x:c r="F187" s="446"/>
+      <x:c r="G187" s="446"/>
+      <x:c r="H187" s="446"/>
+      <x:c r="I187" s="446"/>
+      <x:c r="J187" s="446"/>
+      <x:c r="K187" s="446"/>
+      <x:c r="L187" s="446"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="446"/>
+      <x:c r="B188" s="446"/>
+      <x:c r="C188" s="446"/>
+      <x:c r="D188" s="446"/>
+      <x:c r="E188" s="446"/>
+      <x:c r="F188" s="446"/>
+      <x:c r="G188" s="446"/>
+      <x:c r="H188" s="446"/>
+      <x:c r="I188" s="446"/>
+      <x:c r="J188" s="446"/>
+      <x:c r="K188" s="446"/>
+      <x:c r="L188" s="446"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="446"/>
+      <x:c r="B189" s="446"/>
+      <x:c r="C189" s="446"/>
+      <x:c r="D189" s="446"/>
+      <x:c r="E189" s="446"/>
+      <x:c r="F189" s="446"/>
+      <x:c r="G189" s="446"/>
+      <x:c r="H189" s="446"/>
+      <x:c r="I189" s="446"/>
+      <x:c r="J189" s="446"/>
+      <x:c r="K189" s="446"/>
+      <x:c r="L189" s="446"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="446"/>
+      <x:c r="B190" s="446"/>
+      <x:c r="C190" s="446"/>
+      <x:c r="D190" s="446"/>
+      <x:c r="E190" s="446"/>
+      <x:c r="F190" s="446"/>
+      <x:c r="G190" s="446"/>
+      <x:c r="H190" s="446"/>
+      <x:c r="I190" s="446"/>
+      <x:c r="J190" s="446"/>
+      <x:c r="K190" s="446"/>
+      <x:c r="L190" s="446"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="446"/>
+      <x:c r="B191" s="446"/>
+      <x:c r="C191" s="446"/>
+      <x:c r="D191" s="446"/>
+      <x:c r="E191" s="446"/>
+      <x:c r="F191" s="446"/>
+      <x:c r="G191" s="446"/>
+      <x:c r="H191" s="446"/>
+      <x:c r="I191" s="446"/>
+      <x:c r="J191" s="446"/>
+      <x:c r="K191" s="446"/>
+      <x:c r="L191" s="446"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="446"/>
+      <x:c r="B192" s="446"/>
+      <x:c r="C192" s="446"/>
+      <x:c r="D192" s="446"/>
+      <x:c r="E192" s="446"/>
+      <x:c r="F192" s="446"/>
+      <x:c r="G192" s="446"/>
+      <x:c r="H192" s="446"/>
+      <x:c r="I192" s="446"/>
+      <x:c r="J192" s="446"/>
+      <x:c r="K192" s="446"/>
+      <x:c r="L192" s="446"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="446"/>
+      <x:c r="B193" s="446"/>
+      <x:c r="C193" s="446"/>
+      <x:c r="D193" s="446"/>
+      <x:c r="E193" s="446"/>
+      <x:c r="F193" s="446"/>
+      <x:c r="G193" s="446"/>
+      <x:c r="H193" s="446"/>
+      <x:c r="I193" s="446"/>
+      <x:c r="J193" s="446"/>
+      <x:c r="K193" s="446"/>
+      <x:c r="L193" s="446"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="446"/>
+      <x:c r="B194" s="446"/>
+      <x:c r="C194" s="446"/>
+      <x:c r="D194" s="446"/>
+      <x:c r="E194" s="446"/>
+      <x:c r="F194" s="446"/>
+      <x:c r="G194" s="446"/>
+      <x:c r="H194" s="446"/>
+      <x:c r="I194" s="446"/>
+      <x:c r="J194" s="446"/>
+      <x:c r="K194" s="446"/>
+      <x:c r="L194" s="446"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="446"/>
+      <x:c r="B195" s="446"/>
+      <x:c r="C195" s="446"/>
+      <x:c r="D195" s="446"/>
+      <x:c r="E195" s="446"/>
+      <x:c r="F195" s="446"/>
+      <x:c r="G195" s="446"/>
+      <x:c r="H195" s="446"/>
+      <x:c r="I195" s="446"/>
+      <x:c r="J195" s="446"/>
+      <x:c r="K195" s="446"/>
+      <x:c r="L195" s="446"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="446"/>
+      <x:c r="B196" s="446"/>
+      <x:c r="C196" s="446"/>
+      <x:c r="D196" s="446"/>
+      <x:c r="E196" s="446"/>
+      <x:c r="F196" s="446"/>
+      <x:c r="G196" s="446"/>
+      <x:c r="H196" s="446"/>
+      <x:c r="I196" s="446"/>
+      <x:c r="J196" s="446"/>
+      <x:c r="K196" s="446"/>
+      <x:c r="L196" s="446"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="446"/>
+      <x:c r="B197" s="446"/>
+      <x:c r="C197" s="446"/>
+      <x:c r="D197" s="446"/>
+      <x:c r="E197" s="446"/>
+      <x:c r="F197" s="446"/>
+      <x:c r="G197" s="446"/>
+      <x:c r="H197" s="446"/>
+      <x:c r="I197" s="446"/>
+      <x:c r="J197" s="446"/>
+      <x:c r="K197" s="446"/>
+      <x:c r="L197" s="446"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="446"/>
+      <x:c r="B198" s="446"/>
+      <x:c r="C198" s="446"/>
+      <x:c r="D198" s="446"/>
+      <x:c r="E198" s="446"/>
+      <x:c r="F198" s="446"/>
+      <x:c r="G198" s="446"/>
+      <x:c r="H198" s="446"/>
+      <x:c r="I198" s="446"/>
+      <x:c r="J198" s="446"/>
+      <x:c r="K198" s="446"/>
+      <x:c r="L198" s="446"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="446"/>
+      <x:c r="B199" s="446"/>
+      <x:c r="C199" s="446"/>
+      <x:c r="D199" s="446"/>
+      <x:c r="E199" s="446"/>
+      <x:c r="F199" s="446"/>
+      <x:c r="G199" s="446"/>
+      <x:c r="H199" s="446"/>
+      <x:c r="I199" s="446"/>
+      <x:c r="J199" s="446"/>
+      <x:c r="K199" s="446"/>
+      <x:c r="L199" s="446"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="446"/>
+      <x:c r="B200" s="446"/>
+      <x:c r="C200" s="446"/>
+      <x:c r="D200" s="446"/>
+      <x:c r="E200" s="446"/>
+      <x:c r="F200" s="446"/>
+      <x:c r="G200" s="446"/>
+      <x:c r="H200" s="446"/>
+      <x:c r="I200" s="446"/>
+      <x:c r="J200" s="446"/>
+      <x:c r="K200" s="446"/>
+      <x:c r="L200" s="446"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2368,7 +4933,7 @@
     <x:mergeCell ref="A15:J17"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R206551128a224f8e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbb7f74810ba442b"/>
 </x:worksheet>
 </file>
 
@@ -2391,72 +4956,72 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="519" t="str">
         <x:v>唐长安城知识图谱 · 完整工作清单</x:v>
       </x:c>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
-      <x:c r="F1" s="3"/>
-      <x:c r="G1" s="3"/>
-      <x:c r="H1" s="3"/>
-      <x:c r="I1" s="3"/>
-      <x:c r="J1" s="3"/>
-      <x:c r="K1" s="3"/>
-      <x:c r="L1" s="3"/>
+      <x:c r="B1" s="519"/>
+      <x:c r="C1" s="519"/>
+      <x:c r="D1" s="519"/>
+      <x:c r="E1" s="519"/>
+      <x:c r="F1" s="519"/>
+      <x:c r="G1" s="519"/>
+      <x:c r="H1" s="519"/>
+      <x:c r="I1" s="519"/>
+      <x:c r="J1" s="519"/>
+      <x:c r="K1" s="519"/>
+      <x:c r="L1" s="519"/>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="520" t="str">
         <x:v>使用方法：平时只需修改“状态、负责人、日期、下一步”。首页会自动更新。带期限的日期是建议值，可以随实际情况调整。</x:v>
       </x:c>
-      <x:c r="B2" s="6"/>
-      <x:c r="C2" s="6"/>
-      <x:c r="D2" s="6"/>
-      <x:c r="E2" s="6"/>
-      <x:c r="F2" s="6"/>
-      <x:c r="G2" s="6"/>
-      <x:c r="H2" s="6"/>
-      <x:c r="I2" s="6"/>
-      <x:c r="J2" s="6"/>
-      <x:c r="K2" s="6"/>
-      <x:c r="L2" s="6"/>
+      <x:c r="B2" s="520"/>
+      <x:c r="C2" s="520"/>
+      <x:c r="D2" s="520"/>
+      <x:c r="E2" s="520"/>
+      <x:c r="F2" s="520"/>
+      <x:c r="G2" s="520"/>
+      <x:c r="H2" s="520"/>
+      <x:c r="I2" s="520"/>
+      <x:c r="J2" s="520"/>
+      <x:c r="K2" s="520"/>
+      <x:c r="L2" s="520"/>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="521" t="str">
         <x:v>任务编号</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="521" t="str">
         <x:v>阶段</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="521" t="str">
         <x:v>工作内容</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="521" t="str">
         <x:v>负责人</x:v>
       </x:c>
-      <x:c r="E3" s="12" t="str">
+      <x:c r="E3" s="521" t="str">
         <x:v>状态</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="str">
+      <x:c r="F3" s="521" t="str">
         <x:v>优先级</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="str">
+      <x:c r="G3" s="521" t="str">
         <x:v>开始日期</x:v>
       </x:c>
-      <x:c r="H3" s="12" t="str">
+      <x:c r="H3" s="521" t="str">
         <x:v>计划完成</x:v>
       </x:c>
-      <x:c r="I3" s="12" t="str">
+      <x:c r="I3" s="521" t="str">
         <x:v>实际完成</x:v>
       </x:c>
-      <x:c r="J3" s="12" t="str">
+      <x:c r="J3" s="521" t="str">
         <x:v>下一步</x:v>
       </x:c>
-      <x:c r="K3" s="12" t="str">
+      <x:c r="K3" s="521" t="str">
         <x:v>交付物</x:v>
       </x:c>
-      <x:c r="L3" s="12" t="str">
+      <x:c r="L3" s="521" t="str">
         <x:v>备注</x:v>
       </x:c>
     </x:row>
@@ -3923,306 +6488,306 @@
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" t="str">
+      <x:c r="A46" s="446" t="str">
         <x:v>S6-11</x:v>
       </x:c>
-      <x:c r="B46" t="str">
+      <x:c r="B46" s="446" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
-      <x:c r="C46" t="str">
+      <x:c r="C46" s="446" t="str">
         <x:v>完成首个唐长安测试数据库导入与验收</x:v>
       </x:c>
-      <x:c r="D46" t="str">
+      <x:c r="D46" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="E46" t="str">
+      <x:c r="E46" s="446" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="F46" t="str">
+      <x:c r="F46" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G46" t="n">
+      <x:c r="G46" s="446" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="H46" t="n">
+      <x:c r="H46" s="446" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="I46" t="n">
+      <x:c r="I46" s="446" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="J46" t="str">
+      <x:c r="J46" s="446" t="str">
         <x:v>启动测试API与页面，检查管理端和证据展示</x:v>
       </x:c>
-      <x:c r="K46" t="str">
+      <x:c r="K46" s="446" t="str">
         <x:v>首次测试导入报告v1 / 旧平台兼容包v1</x:v>
       </x:c>
-      <x:c r="L46" t="str">
+      <x:c r="L46" s="446" t="str">
         <x:v>独立测试库6来源/29片段/48实体/32关系；0重复；原青瓷库未变化</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" t="str">
+      <x:c r="A47" s="446" t="str">
         <x:v>S6-12</x:v>
       </x:c>
-      <x:c r="B47" t="str">
+      <x:c r="B47" s="446" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
-      <x:c r="C47" t="str">
+      <x:c r="C47" s="446" t="str">
         <x:v>启动唐长安隔离测试平台并完成功能页面验收</x:v>
       </x:c>
-      <x:c r="D47" t="str">
+      <x:c r="D47" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="E47" t="str">
+      <x:c r="E47" s="446" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="F47" t="str">
+      <x:c r="F47" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G47" t="n">
+      <x:c r="G47" s="446" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="H47" t="n">
+      <x:c r="H47" s="446" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="I47" t="n">
+      <x:c r="I47" s="446" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="J47" t="str">
+      <x:c r="J47" s="446" t="str">
         <x:v>改造公众前台品牌、首页统计和长安城专题入口</x:v>
       </x:c>
-      <x:c r="K47" t="str">
+      <x:c r="K47" s="446" t="str">
         <x:v>平台页面验收报告v1 / 唐长安测试平台</x:v>
       </x:c>
-      <x:c r="L47" t="str">
+      <x:c r="L47" s="446" t="str">
         <x:v>API与管理端通过；48实体/32关系/6来源；前台仍需迁移</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" t="str">
+      <x:c r="A48" s="446" t="str">
         <x:v>S6-13</x:v>
       </x:c>
-      <x:c r="B48" t="str">
+      <x:c r="B48" s="446" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
-      <x:c r="C48" t="str">
+      <x:c r="C48" s="446" t="str">
         <x:v>完成唐长安前端第一轮换壳与实时统计改造</x:v>
       </x:c>
-      <x:c r="D48" t="str">
+      <x:c r="D48" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="E48" t="str">
+      <x:c r="E48" s="446" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="F48" t="str">
+      <x:c r="F48" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G48" t="n">
+      <x:c r="G48" s="446" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="H48" t="n">
+      <x:c r="H48" s="446" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="I48" t="n">
+      <x:c r="I48" s="446" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="J48" t="str">
+      <x:c r="J48" s="446" t="str">
         <x:v>设计并执行首批小型测试发布</x:v>
       </x:c>
-      <x:c r="K48" t="str">
+      <x:c r="K48" s="446" t="str">
         <x:v>前端换壳与实时统计验收报告v1 / 平台提交3a4b019</x:v>
       </x:c>
-      <x:c r="L48" t="str">
+      <x:c r="L48" s="446" t="str">
         <x:v>品牌与数据统计迁移通过；公开端仍严格限制published+public</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="40" customHeight="1">
-      <x:c r="A49" s="216" t="str">
+      <x:c r="A49" s="446" t="str">
         <x:v>S6-14</x:v>
       </x:c>
-      <x:c r="B49" s="216" t="str">
+      <x:c r="B49" s="446" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
-      <x:c r="C49" s="216" t="str">
+      <x:c r="C49" s="446" t="str">
         <x:v>完成首次小型闭环测试发布与公众端验收</x:v>
       </x:c>
-      <x:c r="D49" s="216" t="str">
+      <x:c r="D49" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="E49" s="216" t="str">
+      <x:c r="E49" s="446" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="F49" s="216" t="str">
+      <x:c r="F49" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G49" s="217" t="n">
+      <x:c r="G49" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="H49" s="217" t="n">
+      <x:c r="H49" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="I49" s="217" t="n">
+      <x:c r="I49" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="J49" s="216" t="str">
+      <x:c r="J49" s="446" t="str">
         <x:v>人工审核公众搜索、图谱和证据卡片展示，再确定第二批发布范围</x:v>
       </x:c>
-      <x:c r="K49" s="216" t="str">
+      <x:c r="K49" s="446" t="str">
         <x:v>首次小型测试发布报告v1 / 发布版本v1</x:v>
       </x:c>
-      <x:c r="L49" s="216" t="str">
+      <x:c r="L49" s="446" t="str">
         <x:v>2实体/1关系/1来源/2片段；检索4文档；依赖校验与回滚快照通过</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="40" customHeight="1">
-      <x:c r="A50" s="216" t="str">
+      <x:c r="A50" s="446" t="str">
         <x:v>S6-15</x:v>
       </x:c>
-      <x:c r="B50" s="216" t="str">
+      <x:c r="B50" s="446" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
-      <x:c r="C50" s="216" t="str">
+      <x:c r="C50" s="446" t="str">
         <x:v>完成首次小型发布人工审核并启动第二批候选筛选</x:v>
       </x:c>
-      <x:c r="D50" s="216" t="str">
+      <x:c r="D50" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="E50" s="216" t="str">
+      <x:c r="E50" s="446" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="F50" s="216" t="str">
+      <x:c r="F50" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G50" s="217" t="n">
+      <x:c r="G50" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="H50" s="217" t="n">
+      <x:c r="H50" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="I50" s="217" t="n">
+      <x:c r="I50" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="J50" s="216" t="str">
+      <x:c r="J50" s="446" t="str">
         <x:v>人工抽查第二批公众图谱，再确定正式迁移优先级</x:v>
       </x:c>
-      <x:c r="K50" s="216" t="str">
+      <x:c r="K50" s="446" t="str">
         <x:v>第二批平台发布报告v1 / 发布版本v2</x:v>
       </x:c>
-      <x:c r="L50" s="216" t="str">
+      <x:c r="L50" s="446" t="str">
         <x:v>发布8实体/4关系/4片段；公众总量10实体/5关系/1来源/6片段</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="40" customHeight="1">
-      <x:c r="A51" s="216" t="str">
+      <x:c r="A51" s="446" t="str">
         <x:v>S6-16</x:v>
       </x:c>
-      <x:c r="B51" s="216" t="str">
+      <x:c r="B51" s="446" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
-      <x:c r="C51" s="216" t="str">
+      <x:c r="C51" s="446" t="str">
         <x:v>人工抽查第二批发布并确定正式迁移优先级</x:v>
       </x:c>
-      <x:c r="D51" s="216" t="str">
+      <x:c r="D51" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="E51" s="216" t="str">
+      <x:c r="E51" s="446" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="F51" s="216" t="str">
+      <x:c r="F51" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G51" s="217" t="n">
+      <x:c r="G51" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="H51" s="217" t="n">
+      <x:c r="H51" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="I51" s="217" t="str">
+      <x:c r="I51" s="467" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="J51" s="216" t="str">
+      <x:c r="J51" s="446" t="str">
         <x:v>进入正式迁移前的P0结构补全</x:v>
       </x:c>
-      <x:c r="K51" s="216" t="str">
+      <x:c r="K51" s="446" t="str">
         <x:v>第二批公众页面审核记录 / 正式迁移顺序</x:v>
       </x:c>
-      <x:c r="L51" s="216" t="str">
+      <x:c r="L51" s="446" t="str">
         <x:v>用户审核通过；确定先发布空间基础事实</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="40" customHeight="1">
-      <x:c r="A52" s="216" t="str">
+      <x:c r="A52" s="446" t="str">
         <x:v>S6-17</x:v>
       </x:c>
-      <x:c r="B52" s="216" t="str">
+      <x:c r="B52" s="446" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
-      <x:c r="C52" s="216" t="str">
+      <x:c r="C52" s="446" t="str">
         <x:v>同步小型样例实体表与关系表，并修复转换去重</x:v>
       </x:c>
-      <x:c r="D52" s="216" t="str">
+      <x:c r="D52" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="E52" s="216" t="str">
+      <x:c r="E52" s="446" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="F52" s="216" t="str">
+      <x:c r="F52" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G52" s="217" t="n">
+      <x:c r="G52" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="H52" s="217" t="n">
+      <x:c r="H52" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="I52" s="217" t="n">
+      <x:c r="I52" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="J52" s="216" t="str">
+      <x:c r="J52" s="446" t="str">
         <x:v>人工抽查v4；后续以v4作为小型样例唯一工作版本</x:v>
       </x:c>
-      <x:c r="K52" s="216" t="str">
+      <x:c r="K52" s="446" t="str">
         <x:v>小型样例v4 / 转换程序去重修复</x:v>
       </x:c>
-      <x:c r="L52" s="216" t="str">
+      <x:c r="L52" s="446" t="str">
         <x:v>实体表23→48，关系表10→32；重新转换0错误、0警告、0重复</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="40" customHeight="1">
-      <x:c r="A53" s="216" t="str">
+      <x:c r="A53" s="446" t="str">
         <x:v>S6-18</x:v>
       </x:c>
-      <x:c r="B53" s="216" t="str">
+      <x:c r="B53" s="446" t="str">
         <x:v>阶段六：平台迁移</x:v>
       </x:c>
-      <x:c r="C53" s="216" t="str">
+      <x:c r="C53" s="446" t="str">
         <x:v>补齐专题表遗漏关系并完善自动转换阻断</x:v>
       </x:c>
-      <x:c r="D53" s="216" t="str">
+      <x:c r="D53" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="E53" s="216" t="str">
+      <x:c r="E53" s="446" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="F53" s="216" t="str">
+      <x:c r="F53" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G53" s="217" t="n">
+      <x:c r="G53" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="H53" s="217" t="n">
+      <x:c r="H53" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="I53" s="217" t="str">
+      <x:c r="I53" s="467" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="J53" s="216" t="str">
+      <x:c r="J53" s="446" t="str">
         <x:v>以v6和平台导入包v2为后续基线</x:v>
       </x:c>
-      <x:c r="K53" s="216" t="str">
+      <x:c r="K53" s="446" t="str">
         <x:v>小型样例v6 / 专题关系自动转换</x:v>
       </x:c>
-      <x:c r="L53" s="216" t="str">
+      <x:c r="L53" s="446" t="str">
         <x:v>11条新增关系均已审核并发布</x:v>
       </x:c>
     </x:row>
@@ -4687,38 +7252,1910 @@
       </x:c>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" t="str">
+      <x:c r="A68" s="446" t="str">
         <x:v>S7-09</x:v>
       </x:c>
-      <x:c r="B68" t="str">
+      <x:c r="B68" s="446" t="str">
         <x:v>阶段七：全量提取</x:v>
       </x:c>
-      <x:c r="C68" t="str">
+      <x:c r="C68" s="446" t="str">
         <x:v>启动《唐两京城坊考》卷三并完成首批分坊沿革</x:v>
       </x:c>
-      <x:c r="D68" t="str">
+      <x:c r="D68" s="446" t="str">
         <x:v>成员A / Codex</x:v>
       </x:c>
-      <x:c r="E68" t="str">
+      <x:c r="E68" s="446" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="F68" t="str">
+      <x:c r="F68" s="446" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G68" t="str">
+      <x:c r="G68" s="446" t="str">
         <x:v>2026-08-16</x:v>
       </x:c>
-      <x:c r="H68"/>
-      <x:c r="I68"/>
-      <x:c r="J68" t="str">
+      <x:c r="H68" s="446"/>
+      <x:c r="I68" s="446"/>
+      <x:c r="J68" s="446" t="str">
         <x:v>联合导入卷一至卷三并网页验收</x:v>
       </x:c>
-      <x:c r="K68" t="str">
+      <x:c r="K68" s="446" t="str">
         <x:v>BATCH-0202工作簿 / 协作登记表</x:v>
       </x:c>
-      <x:c r="L68" t="str">
+      <x:c r="L68" s="446" t="str">
         <x:v>卷三40片段、35坊、408设施、451实体、448关系；结构校验通过</x:v>
       </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="446" t="str">
+        <x:v>S7-10</x:v>
+      </x:c>
+      <x:c r="B69" s="446" t="str">
+        <x:v>阶段七：全量提取</x:v>
+      </x:c>
+      <x:c r="C69" s="446" t="str">
+        <x:v>卷一至卷三联合导入测试平台并完成网页抽查</x:v>
+      </x:c>
+      <x:c r="D69" s="446" t="str">
+        <x:v>成员A / Codex</x:v>
+      </x:c>
+      <x:c r="E69" s="446" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="F69" s="446" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G69" s="446" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="H69" s="446" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="I69" s="446" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="J69" s="446" t="str">
+        <x:v>开始《唐两京城坊考》卷四</x:v>
+      </x:c>
+      <x:c r="K69" s="446" t="str">
+        <x:v>联合导入包 / 平台备份 / 网页验收记录</x:v>
+      </x:c>
+      <x:c r="L69" s="446" t="str">
+        <x:v>4来源、112片段、1212实体、1576关系；悬空关系0、错误证据引用0；平台抽查正常</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="446"/>
+      <x:c r="B70" s="446"/>
+      <x:c r="C70" s="446"/>
+      <x:c r="D70" s="446"/>
+      <x:c r="E70" s="446"/>
+      <x:c r="F70" s="446"/>
+      <x:c r="G70" s="446"/>
+      <x:c r="H70" s="446"/>
+      <x:c r="I70" s="446"/>
+      <x:c r="J70" s="446"/>
+      <x:c r="K70" s="446"/>
+      <x:c r="L70" s="446"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="446"/>
+      <x:c r="B71" s="446"/>
+      <x:c r="C71" s="446"/>
+      <x:c r="D71" s="446"/>
+      <x:c r="E71" s="446"/>
+      <x:c r="F71" s="446"/>
+      <x:c r="G71" s="446"/>
+      <x:c r="H71" s="446"/>
+      <x:c r="I71" s="446"/>
+      <x:c r="J71" s="446"/>
+      <x:c r="K71" s="446"/>
+      <x:c r="L71" s="446"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="446"/>
+      <x:c r="B72" s="446"/>
+      <x:c r="C72" s="446"/>
+      <x:c r="D72" s="446"/>
+      <x:c r="E72" s="446"/>
+      <x:c r="F72" s="446"/>
+      <x:c r="G72" s="446"/>
+      <x:c r="H72" s="446"/>
+      <x:c r="I72" s="446"/>
+      <x:c r="J72" s="446"/>
+      <x:c r="K72" s="446"/>
+      <x:c r="L72" s="446"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="446"/>
+      <x:c r="B73" s="446"/>
+      <x:c r="C73" s="446"/>
+      <x:c r="D73" s="446"/>
+      <x:c r="E73" s="446"/>
+      <x:c r="F73" s="446"/>
+      <x:c r="G73" s="446"/>
+      <x:c r="H73" s="446"/>
+      <x:c r="I73" s="446"/>
+      <x:c r="J73" s="446"/>
+      <x:c r="K73" s="446"/>
+      <x:c r="L73" s="446"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="446"/>
+      <x:c r="B74" s="446"/>
+      <x:c r="C74" s="446"/>
+      <x:c r="D74" s="446"/>
+      <x:c r="E74" s="446"/>
+      <x:c r="F74" s="446"/>
+      <x:c r="G74" s="446"/>
+      <x:c r="H74" s="446"/>
+      <x:c r="I74" s="446"/>
+      <x:c r="J74" s="446"/>
+      <x:c r="K74" s="446"/>
+      <x:c r="L74" s="446"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="446"/>
+      <x:c r="B75" s="446"/>
+      <x:c r="C75" s="446"/>
+      <x:c r="D75" s="446"/>
+      <x:c r="E75" s="446"/>
+      <x:c r="F75" s="446"/>
+      <x:c r="G75" s="446"/>
+      <x:c r="H75" s="446"/>
+      <x:c r="I75" s="446"/>
+      <x:c r="J75" s="446"/>
+      <x:c r="K75" s="446"/>
+      <x:c r="L75" s="446"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="446"/>
+      <x:c r="B76" s="446"/>
+      <x:c r="C76" s="446"/>
+      <x:c r="D76" s="446"/>
+      <x:c r="E76" s="446"/>
+      <x:c r="F76" s="446"/>
+      <x:c r="G76" s="446"/>
+      <x:c r="H76" s="446"/>
+      <x:c r="I76" s="446"/>
+      <x:c r="J76" s="446"/>
+      <x:c r="K76" s="446"/>
+      <x:c r="L76" s="446"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="446"/>
+      <x:c r="B77" s="446"/>
+      <x:c r="C77" s="446"/>
+      <x:c r="D77" s="446"/>
+      <x:c r="E77" s="446"/>
+      <x:c r="F77" s="446"/>
+      <x:c r="G77" s="446"/>
+      <x:c r="H77" s="446"/>
+      <x:c r="I77" s="446"/>
+      <x:c r="J77" s="446"/>
+      <x:c r="K77" s="446"/>
+      <x:c r="L77" s="446"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="446"/>
+      <x:c r="B78" s="446"/>
+      <x:c r="C78" s="446"/>
+      <x:c r="D78" s="446"/>
+      <x:c r="E78" s="446"/>
+      <x:c r="F78" s="446"/>
+      <x:c r="G78" s="446"/>
+      <x:c r="H78" s="446"/>
+      <x:c r="I78" s="446"/>
+      <x:c r="J78" s="446"/>
+      <x:c r="K78" s="446"/>
+      <x:c r="L78" s="446"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="446"/>
+      <x:c r="B79" s="446"/>
+      <x:c r="C79" s="446"/>
+      <x:c r="D79" s="446"/>
+      <x:c r="E79" s="446"/>
+      <x:c r="F79" s="446"/>
+      <x:c r="G79" s="446"/>
+      <x:c r="H79" s="446"/>
+      <x:c r="I79" s="446"/>
+      <x:c r="J79" s="446"/>
+      <x:c r="K79" s="446"/>
+      <x:c r="L79" s="446"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="446"/>
+      <x:c r="B80" s="446"/>
+      <x:c r="C80" s="446"/>
+      <x:c r="D80" s="446"/>
+      <x:c r="E80" s="446"/>
+      <x:c r="F80" s="446"/>
+      <x:c r="G80" s="446"/>
+      <x:c r="H80" s="446"/>
+      <x:c r="I80" s="446"/>
+      <x:c r="J80" s="446"/>
+      <x:c r="K80" s="446"/>
+      <x:c r="L80" s="446"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="446"/>
+      <x:c r="B81" s="446"/>
+      <x:c r="C81" s="446"/>
+      <x:c r="D81" s="446"/>
+      <x:c r="E81" s="446"/>
+      <x:c r="F81" s="446"/>
+      <x:c r="G81" s="446"/>
+      <x:c r="H81" s="446"/>
+      <x:c r="I81" s="446"/>
+      <x:c r="J81" s="446"/>
+      <x:c r="K81" s="446"/>
+      <x:c r="L81" s="446"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="446"/>
+      <x:c r="B82" s="446"/>
+      <x:c r="C82" s="446"/>
+      <x:c r="D82" s="446"/>
+      <x:c r="E82" s="446"/>
+      <x:c r="F82" s="446"/>
+      <x:c r="G82" s="446"/>
+      <x:c r="H82" s="446"/>
+      <x:c r="I82" s="446"/>
+      <x:c r="J82" s="446"/>
+      <x:c r="K82" s="446"/>
+      <x:c r="L82" s="446"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="446"/>
+      <x:c r="B83" s="446"/>
+      <x:c r="C83" s="446"/>
+      <x:c r="D83" s="446"/>
+      <x:c r="E83" s="446"/>
+      <x:c r="F83" s="446"/>
+      <x:c r="G83" s="446"/>
+      <x:c r="H83" s="446"/>
+      <x:c r="I83" s="446"/>
+      <x:c r="J83" s="446"/>
+      <x:c r="K83" s="446"/>
+      <x:c r="L83" s="446"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="446"/>
+      <x:c r="B84" s="446"/>
+      <x:c r="C84" s="446"/>
+      <x:c r="D84" s="446"/>
+      <x:c r="E84" s="446"/>
+      <x:c r="F84" s="446"/>
+      <x:c r="G84" s="446"/>
+      <x:c r="H84" s="446"/>
+      <x:c r="I84" s="446"/>
+      <x:c r="J84" s="446"/>
+      <x:c r="K84" s="446"/>
+      <x:c r="L84" s="446"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="446"/>
+      <x:c r="B85" s="446"/>
+      <x:c r="C85" s="446"/>
+      <x:c r="D85" s="446"/>
+      <x:c r="E85" s="446"/>
+      <x:c r="F85" s="446"/>
+      <x:c r="G85" s="446"/>
+      <x:c r="H85" s="446"/>
+      <x:c r="I85" s="446"/>
+      <x:c r="J85" s="446"/>
+      <x:c r="K85" s="446"/>
+      <x:c r="L85" s="446"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="446"/>
+      <x:c r="B86" s="446"/>
+      <x:c r="C86" s="446"/>
+      <x:c r="D86" s="446"/>
+      <x:c r="E86" s="446"/>
+      <x:c r="F86" s="446"/>
+      <x:c r="G86" s="446"/>
+      <x:c r="H86" s="446"/>
+      <x:c r="I86" s="446"/>
+      <x:c r="J86" s="446"/>
+      <x:c r="K86" s="446"/>
+      <x:c r="L86" s="446"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="446"/>
+      <x:c r="B87" s="446"/>
+      <x:c r="C87" s="446"/>
+      <x:c r="D87" s="446"/>
+      <x:c r="E87" s="446"/>
+      <x:c r="F87" s="446"/>
+      <x:c r="G87" s="446"/>
+      <x:c r="H87" s="446"/>
+      <x:c r="I87" s="446"/>
+      <x:c r="J87" s="446"/>
+      <x:c r="K87" s="446"/>
+      <x:c r="L87" s="446"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="446"/>
+      <x:c r="B88" s="446"/>
+      <x:c r="C88" s="446"/>
+      <x:c r="D88" s="446"/>
+      <x:c r="E88" s="446"/>
+      <x:c r="F88" s="446"/>
+      <x:c r="G88" s="446"/>
+      <x:c r="H88" s="446"/>
+      <x:c r="I88" s="446"/>
+      <x:c r="J88" s="446"/>
+      <x:c r="K88" s="446"/>
+      <x:c r="L88" s="446"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="446"/>
+      <x:c r="B89" s="446"/>
+      <x:c r="C89" s="446"/>
+      <x:c r="D89" s="446"/>
+      <x:c r="E89" s="446"/>
+      <x:c r="F89" s="446"/>
+      <x:c r="G89" s="446"/>
+      <x:c r="H89" s="446"/>
+      <x:c r="I89" s="446"/>
+      <x:c r="J89" s="446"/>
+      <x:c r="K89" s="446"/>
+      <x:c r="L89" s="446"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="446"/>
+      <x:c r="B90" s="446"/>
+      <x:c r="C90" s="446"/>
+      <x:c r="D90" s="446"/>
+      <x:c r="E90" s="446"/>
+      <x:c r="F90" s="446"/>
+      <x:c r="G90" s="446"/>
+      <x:c r="H90" s="446"/>
+      <x:c r="I90" s="446"/>
+      <x:c r="J90" s="446"/>
+      <x:c r="K90" s="446"/>
+      <x:c r="L90" s="446"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="446"/>
+      <x:c r="B91" s="446"/>
+      <x:c r="C91" s="446"/>
+      <x:c r="D91" s="446"/>
+      <x:c r="E91" s="446"/>
+      <x:c r="F91" s="446"/>
+      <x:c r="G91" s="446"/>
+      <x:c r="H91" s="446"/>
+      <x:c r="I91" s="446"/>
+      <x:c r="J91" s="446"/>
+      <x:c r="K91" s="446"/>
+      <x:c r="L91" s="446"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="446"/>
+      <x:c r="B92" s="446"/>
+      <x:c r="C92" s="446"/>
+      <x:c r="D92" s="446"/>
+      <x:c r="E92" s="446"/>
+      <x:c r="F92" s="446"/>
+      <x:c r="G92" s="446"/>
+      <x:c r="H92" s="446"/>
+      <x:c r="I92" s="446"/>
+      <x:c r="J92" s="446"/>
+      <x:c r="K92" s="446"/>
+      <x:c r="L92" s="446"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="446"/>
+      <x:c r="B93" s="446"/>
+      <x:c r="C93" s="446"/>
+      <x:c r="D93" s="446"/>
+      <x:c r="E93" s="446"/>
+      <x:c r="F93" s="446"/>
+      <x:c r="G93" s="446"/>
+      <x:c r="H93" s="446"/>
+      <x:c r="I93" s="446"/>
+      <x:c r="J93" s="446"/>
+      <x:c r="K93" s="446"/>
+      <x:c r="L93" s="446"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="446"/>
+      <x:c r="B94" s="446"/>
+      <x:c r="C94" s="446"/>
+      <x:c r="D94" s="446"/>
+      <x:c r="E94" s="446"/>
+      <x:c r="F94" s="446"/>
+      <x:c r="G94" s="446"/>
+      <x:c r="H94" s="446"/>
+      <x:c r="I94" s="446"/>
+      <x:c r="J94" s="446"/>
+      <x:c r="K94" s="446"/>
+      <x:c r="L94" s="446"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="446"/>
+      <x:c r="B95" s="446"/>
+      <x:c r="C95" s="446"/>
+      <x:c r="D95" s="446"/>
+      <x:c r="E95" s="446"/>
+      <x:c r="F95" s="446"/>
+      <x:c r="G95" s="446"/>
+      <x:c r="H95" s="446"/>
+      <x:c r="I95" s="446"/>
+      <x:c r="J95" s="446"/>
+      <x:c r="K95" s="446"/>
+      <x:c r="L95" s="446"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="446"/>
+      <x:c r="B96" s="446"/>
+      <x:c r="C96" s="446"/>
+      <x:c r="D96" s="446"/>
+      <x:c r="E96" s="446"/>
+      <x:c r="F96" s="446"/>
+      <x:c r="G96" s="446"/>
+      <x:c r="H96" s="446"/>
+      <x:c r="I96" s="446"/>
+      <x:c r="J96" s="446"/>
+      <x:c r="K96" s="446"/>
+      <x:c r="L96" s="446"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="446"/>
+      <x:c r="B97" s="446"/>
+      <x:c r="C97" s="446"/>
+      <x:c r="D97" s="446"/>
+      <x:c r="E97" s="446"/>
+      <x:c r="F97" s="446"/>
+      <x:c r="G97" s="446"/>
+      <x:c r="H97" s="446"/>
+      <x:c r="I97" s="446"/>
+      <x:c r="J97" s="446"/>
+      <x:c r="K97" s="446"/>
+      <x:c r="L97" s="446"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="446"/>
+      <x:c r="B98" s="446"/>
+      <x:c r="C98" s="446"/>
+      <x:c r="D98" s="446"/>
+      <x:c r="E98" s="446"/>
+      <x:c r="F98" s="446"/>
+      <x:c r="G98" s="446"/>
+      <x:c r="H98" s="446"/>
+      <x:c r="I98" s="446"/>
+      <x:c r="J98" s="446"/>
+      <x:c r="K98" s="446"/>
+      <x:c r="L98" s="446"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="446"/>
+      <x:c r="B99" s="446"/>
+      <x:c r="C99" s="446"/>
+      <x:c r="D99" s="446"/>
+      <x:c r="E99" s="446"/>
+      <x:c r="F99" s="446"/>
+      <x:c r="G99" s="446"/>
+      <x:c r="H99" s="446"/>
+      <x:c r="I99" s="446"/>
+      <x:c r="J99" s="446"/>
+      <x:c r="K99" s="446"/>
+      <x:c r="L99" s="446"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="446"/>
+      <x:c r="B100" s="446"/>
+      <x:c r="C100" s="446"/>
+      <x:c r="D100" s="446"/>
+      <x:c r="E100" s="446"/>
+      <x:c r="F100" s="446"/>
+      <x:c r="G100" s="446"/>
+      <x:c r="H100" s="446"/>
+      <x:c r="I100" s="446"/>
+      <x:c r="J100" s="446"/>
+      <x:c r="K100" s="446"/>
+      <x:c r="L100" s="446"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="446"/>
+      <x:c r="B101" s="446"/>
+      <x:c r="C101" s="446"/>
+      <x:c r="D101" s="446"/>
+      <x:c r="E101" s="446"/>
+      <x:c r="F101" s="446"/>
+      <x:c r="G101" s="446"/>
+      <x:c r="H101" s="446"/>
+      <x:c r="I101" s="446"/>
+      <x:c r="J101" s="446"/>
+      <x:c r="K101" s="446"/>
+      <x:c r="L101" s="446"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="446"/>
+      <x:c r="B102" s="446"/>
+      <x:c r="C102" s="446"/>
+      <x:c r="D102" s="446"/>
+      <x:c r="E102" s="446"/>
+      <x:c r="F102" s="446"/>
+      <x:c r="G102" s="446"/>
+      <x:c r="H102" s="446"/>
+      <x:c r="I102" s="446"/>
+      <x:c r="J102" s="446"/>
+      <x:c r="K102" s="446"/>
+      <x:c r="L102" s="446"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="446"/>
+      <x:c r="B103" s="446"/>
+      <x:c r="C103" s="446"/>
+      <x:c r="D103" s="446"/>
+      <x:c r="E103" s="446"/>
+      <x:c r="F103" s="446"/>
+      <x:c r="G103" s="446"/>
+      <x:c r="H103" s="446"/>
+      <x:c r="I103" s="446"/>
+      <x:c r="J103" s="446"/>
+      <x:c r="K103" s="446"/>
+      <x:c r="L103" s="446"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="446"/>
+      <x:c r="B104" s="446"/>
+      <x:c r="C104" s="446"/>
+      <x:c r="D104" s="446"/>
+      <x:c r="E104" s="446"/>
+      <x:c r="F104" s="446"/>
+      <x:c r="G104" s="446"/>
+      <x:c r="H104" s="446"/>
+      <x:c r="I104" s="446"/>
+      <x:c r="J104" s="446"/>
+      <x:c r="K104" s="446"/>
+      <x:c r="L104" s="446"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="446"/>
+      <x:c r="B105" s="446"/>
+      <x:c r="C105" s="446"/>
+      <x:c r="D105" s="446"/>
+      <x:c r="E105" s="446"/>
+      <x:c r="F105" s="446"/>
+      <x:c r="G105" s="446"/>
+      <x:c r="H105" s="446"/>
+      <x:c r="I105" s="446"/>
+      <x:c r="J105" s="446"/>
+      <x:c r="K105" s="446"/>
+      <x:c r="L105" s="446"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="446"/>
+      <x:c r="B106" s="446"/>
+      <x:c r="C106" s="446"/>
+      <x:c r="D106" s="446"/>
+      <x:c r="E106" s="446"/>
+      <x:c r="F106" s="446"/>
+      <x:c r="G106" s="446"/>
+      <x:c r="H106" s="446"/>
+      <x:c r="I106" s="446"/>
+      <x:c r="J106" s="446"/>
+      <x:c r="K106" s="446"/>
+      <x:c r="L106" s="446"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="446"/>
+      <x:c r="B107" s="446"/>
+      <x:c r="C107" s="446"/>
+      <x:c r="D107" s="446"/>
+      <x:c r="E107" s="446"/>
+      <x:c r="F107" s="446"/>
+      <x:c r="G107" s="446"/>
+      <x:c r="H107" s="446"/>
+      <x:c r="I107" s="446"/>
+      <x:c r="J107" s="446"/>
+      <x:c r="K107" s="446"/>
+      <x:c r="L107" s="446"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="446"/>
+      <x:c r="B108" s="446"/>
+      <x:c r="C108" s="446"/>
+      <x:c r="D108" s="446"/>
+      <x:c r="E108" s="446"/>
+      <x:c r="F108" s="446"/>
+      <x:c r="G108" s="446"/>
+      <x:c r="H108" s="446"/>
+      <x:c r="I108" s="446"/>
+      <x:c r="J108" s="446"/>
+      <x:c r="K108" s="446"/>
+      <x:c r="L108" s="446"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="446"/>
+      <x:c r="B109" s="446"/>
+      <x:c r="C109" s="446"/>
+      <x:c r="D109" s="446"/>
+      <x:c r="E109" s="446"/>
+      <x:c r="F109" s="446"/>
+      <x:c r="G109" s="446"/>
+      <x:c r="H109" s="446"/>
+      <x:c r="I109" s="446"/>
+      <x:c r="J109" s="446"/>
+      <x:c r="K109" s="446"/>
+      <x:c r="L109" s="446"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="446"/>
+      <x:c r="B110" s="446"/>
+      <x:c r="C110" s="446"/>
+      <x:c r="D110" s="446"/>
+      <x:c r="E110" s="446"/>
+      <x:c r="F110" s="446"/>
+      <x:c r="G110" s="446"/>
+      <x:c r="H110" s="446"/>
+      <x:c r="I110" s="446"/>
+      <x:c r="J110" s="446"/>
+      <x:c r="K110" s="446"/>
+      <x:c r="L110" s="446"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="446"/>
+      <x:c r="B111" s="446"/>
+      <x:c r="C111" s="446"/>
+      <x:c r="D111" s="446"/>
+      <x:c r="E111" s="446"/>
+      <x:c r="F111" s="446"/>
+      <x:c r="G111" s="446"/>
+      <x:c r="H111" s="446"/>
+      <x:c r="I111" s="446"/>
+      <x:c r="J111" s="446"/>
+      <x:c r="K111" s="446"/>
+      <x:c r="L111" s="446"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="446"/>
+      <x:c r="B112" s="446"/>
+      <x:c r="C112" s="446"/>
+      <x:c r="D112" s="446"/>
+      <x:c r="E112" s="446"/>
+      <x:c r="F112" s="446"/>
+      <x:c r="G112" s="446"/>
+      <x:c r="H112" s="446"/>
+      <x:c r="I112" s="446"/>
+      <x:c r="J112" s="446"/>
+      <x:c r="K112" s="446"/>
+      <x:c r="L112" s="446"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="446"/>
+      <x:c r="B113" s="446"/>
+      <x:c r="C113" s="446"/>
+      <x:c r="D113" s="446"/>
+      <x:c r="E113" s="446"/>
+      <x:c r="F113" s="446"/>
+      <x:c r="G113" s="446"/>
+      <x:c r="H113" s="446"/>
+      <x:c r="I113" s="446"/>
+      <x:c r="J113" s="446"/>
+      <x:c r="K113" s="446"/>
+      <x:c r="L113" s="446"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="446"/>
+      <x:c r="B114" s="446"/>
+      <x:c r="C114" s="446"/>
+      <x:c r="D114" s="446"/>
+      <x:c r="E114" s="446"/>
+      <x:c r="F114" s="446"/>
+      <x:c r="G114" s="446"/>
+      <x:c r="H114" s="446"/>
+      <x:c r="I114" s="446"/>
+      <x:c r="J114" s="446"/>
+      <x:c r="K114" s="446"/>
+      <x:c r="L114" s="446"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="446"/>
+      <x:c r="B115" s="446"/>
+      <x:c r="C115" s="446"/>
+      <x:c r="D115" s="446"/>
+      <x:c r="E115" s="446"/>
+      <x:c r="F115" s="446"/>
+      <x:c r="G115" s="446"/>
+      <x:c r="H115" s="446"/>
+      <x:c r="I115" s="446"/>
+      <x:c r="J115" s="446"/>
+      <x:c r="K115" s="446"/>
+      <x:c r="L115" s="446"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="446"/>
+      <x:c r="B116" s="446"/>
+      <x:c r="C116" s="446"/>
+      <x:c r="D116" s="446"/>
+      <x:c r="E116" s="446"/>
+      <x:c r="F116" s="446"/>
+      <x:c r="G116" s="446"/>
+      <x:c r="H116" s="446"/>
+      <x:c r="I116" s="446"/>
+      <x:c r="J116" s="446"/>
+      <x:c r="K116" s="446"/>
+      <x:c r="L116" s="446"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="446"/>
+      <x:c r="B117" s="446"/>
+      <x:c r="C117" s="446"/>
+      <x:c r="D117" s="446"/>
+      <x:c r="E117" s="446"/>
+      <x:c r="F117" s="446"/>
+      <x:c r="G117" s="446"/>
+      <x:c r="H117" s="446"/>
+      <x:c r="I117" s="446"/>
+      <x:c r="J117" s="446"/>
+      <x:c r="K117" s="446"/>
+      <x:c r="L117" s="446"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="446"/>
+      <x:c r="B118" s="446"/>
+      <x:c r="C118" s="446"/>
+      <x:c r="D118" s="446"/>
+      <x:c r="E118" s="446"/>
+      <x:c r="F118" s="446"/>
+      <x:c r="G118" s="446"/>
+      <x:c r="H118" s="446"/>
+      <x:c r="I118" s="446"/>
+      <x:c r="J118" s="446"/>
+      <x:c r="K118" s="446"/>
+      <x:c r="L118" s="446"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="446"/>
+      <x:c r="B119" s="446"/>
+      <x:c r="C119" s="446"/>
+      <x:c r="D119" s="446"/>
+      <x:c r="E119" s="446"/>
+      <x:c r="F119" s="446"/>
+      <x:c r="G119" s="446"/>
+      <x:c r="H119" s="446"/>
+      <x:c r="I119" s="446"/>
+      <x:c r="J119" s="446"/>
+      <x:c r="K119" s="446"/>
+      <x:c r="L119" s="446"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="446"/>
+      <x:c r="B120" s="446"/>
+      <x:c r="C120" s="446"/>
+      <x:c r="D120" s="446"/>
+      <x:c r="E120" s="446"/>
+      <x:c r="F120" s="446"/>
+      <x:c r="G120" s="446"/>
+      <x:c r="H120" s="446"/>
+      <x:c r="I120" s="446"/>
+      <x:c r="J120" s="446"/>
+      <x:c r="K120" s="446"/>
+      <x:c r="L120" s="446"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="446"/>
+      <x:c r="B121" s="446"/>
+      <x:c r="C121" s="446"/>
+      <x:c r="D121" s="446"/>
+      <x:c r="E121" s="446"/>
+      <x:c r="F121" s="446"/>
+      <x:c r="G121" s="446"/>
+      <x:c r="H121" s="446"/>
+      <x:c r="I121" s="446"/>
+      <x:c r="J121" s="446"/>
+      <x:c r="K121" s="446"/>
+      <x:c r="L121" s="446"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="446"/>
+      <x:c r="B122" s="446"/>
+      <x:c r="C122" s="446"/>
+      <x:c r="D122" s="446"/>
+      <x:c r="E122" s="446"/>
+      <x:c r="F122" s="446"/>
+      <x:c r="G122" s="446"/>
+      <x:c r="H122" s="446"/>
+      <x:c r="I122" s="446"/>
+      <x:c r="J122" s="446"/>
+      <x:c r="K122" s="446"/>
+      <x:c r="L122" s="446"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="446"/>
+      <x:c r="B123" s="446"/>
+      <x:c r="C123" s="446"/>
+      <x:c r="D123" s="446"/>
+      <x:c r="E123" s="446"/>
+      <x:c r="F123" s="446"/>
+      <x:c r="G123" s="446"/>
+      <x:c r="H123" s="446"/>
+      <x:c r="I123" s="446"/>
+      <x:c r="J123" s="446"/>
+      <x:c r="K123" s="446"/>
+      <x:c r="L123" s="446"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="446"/>
+      <x:c r="B124" s="446"/>
+      <x:c r="C124" s="446"/>
+      <x:c r="D124" s="446"/>
+      <x:c r="E124" s="446"/>
+      <x:c r="F124" s="446"/>
+      <x:c r="G124" s="446"/>
+      <x:c r="H124" s="446"/>
+      <x:c r="I124" s="446"/>
+      <x:c r="J124" s="446"/>
+      <x:c r="K124" s="446"/>
+      <x:c r="L124" s="446"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="446"/>
+      <x:c r="B125" s="446"/>
+      <x:c r="C125" s="446"/>
+      <x:c r="D125" s="446"/>
+      <x:c r="E125" s="446"/>
+      <x:c r="F125" s="446"/>
+      <x:c r="G125" s="446"/>
+      <x:c r="H125" s="446"/>
+      <x:c r="I125" s="446"/>
+      <x:c r="J125" s="446"/>
+      <x:c r="K125" s="446"/>
+      <x:c r="L125" s="446"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="446"/>
+      <x:c r="B126" s="446"/>
+      <x:c r="C126" s="446"/>
+      <x:c r="D126" s="446"/>
+      <x:c r="E126" s="446"/>
+      <x:c r="F126" s="446"/>
+      <x:c r="G126" s="446"/>
+      <x:c r="H126" s="446"/>
+      <x:c r="I126" s="446"/>
+      <x:c r="J126" s="446"/>
+      <x:c r="K126" s="446"/>
+      <x:c r="L126" s="446"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="446"/>
+      <x:c r="B127" s="446"/>
+      <x:c r="C127" s="446"/>
+      <x:c r="D127" s="446"/>
+      <x:c r="E127" s="446"/>
+      <x:c r="F127" s="446"/>
+      <x:c r="G127" s="446"/>
+      <x:c r="H127" s="446"/>
+      <x:c r="I127" s="446"/>
+      <x:c r="J127" s="446"/>
+      <x:c r="K127" s="446"/>
+      <x:c r="L127" s="446"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="446"/>
+      <x:c r="B128" s="446"/>
+      <x:c r="C128" s="446"/>
+      <x:c r="D128" s="446"/>
+      <x:c r="E128" s="446"/>
+      <x:c r="F128" s="446"/>
+      <x:c r="G128" s="446"/>
+      <x:c r="H128" s="446"/>
+      <x:c r="I128" s="446"/>
+      <x:c r="J128" s="446"/>
+      <x:c r="K128" s="446"/>
+      <x:c r="L128" s="446"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="446"/>
+      <x:c r="B129" s="446"/>
+      <x:c r="C129" s="446"/>
+      <x:c r="D129" s="446"/>
+      <x:c r="E129" s="446"/>
+      <x:c r="F129" s="446"/>
+      <x:c r="G129" s="446"/>
+      <x:c r="H129" s="446"/>
+      <x:c r="I129" s="446"/>
+      <x:c r="J129" s="446"/>
+      <x:c r="K129" s="446"/>
+      <x:c r="L129" s="446"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="446"/>
+      <x:c r="B130" s="446"/>
+      <x:c r="C130" s="446"/>
+      <x:c r="D130" s="446"/>
+      <x:c r="E130" s="446"/>
+      <x:c r="F130" s="446"/>
+      <x:c r="G130" s="446"/>
+      <x:c r="H130" s="446"/>
+      <x:c r="I130" s="446"/>
+      <x:c r="J130" s="446"/>
+      <x:c r="K130" s="446"/>
+      <x:c r="L130" s="446"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="446"/>
+      <x:c r="B131" s="446"/>
+      <x:c r="C131" s="446"/>
+      <x:c r="D131" s="446"/>
+      <x:c r="E131" s="446"/>
+      <x:c r="F131" s="446"/>
+      <x:c r="G131" s="446"/>
+      <x:c r="H131" s="446"/>
+      <x:c r="I131" s="446"/>
+      <x:c r="J131" s="446"/>
+      <x:c r="K131" s="446"/>
+      <x:c r="L131" s="446"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="446"/>
+      <x:c r="B132" s="446"/>
+      <x:c r="C132" s="446"/>
+      <x:c r="D132" s="446"/>
+      <x:c r="E132" s="446"/>
+      <x:c r="F132" s="446"/>
+      <x:c r="G132" s="446"/>
+      <x:c r="H132" s="446"/>
+      <x:c r="I132" s="446"/>
+      <x:c r="J132" s="446"/>
+      <x:c r="K132" s="446"/>
+      <x:c r="L132" s="446"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="446"/>
+      <x:c r="B133" s="446"/>
+      <x:c r="C133" s="446"/>
+      <x:c r="D133" s="446"/>
+      <x:c r="E133" s="446"/>
+      <x:c r="F133" s="446"/>
+      <x:c r="G133" s="446"/>
+      <x:c r="H133" s="446"/>
+      <x:c r="I133" s="446"/>
+      <x:c r="J133" s="446"/>
+      <x:c r="K133" s="446"/>
+      <x:c r="L133" s="446"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="446"/>
+      <x:c r="B134" s="446"/>
+      <x:c r="C134" s="446"/>
+      <x:c r="D134" s="446"/>
+      <x:c r="E134" s="446"/>
+      <x:c r="F134" s="446"/>
+      <x:c r="G134" s="446"/>
+      <x:c r="H134" s="446"/>
+      <x:c r="I134" s="446"/>
+      <x:c r="J134" s="446"/>
+      <x:c r="K134" s="446"/>
+      <x:c r="L134" s="446"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="446"/>
+      <x:c r="B135" s="446"/>
+      <x:c r="C135" s="446"/>
+      <x:c r="D135" s="446"/>
+      <x:c r="E135" s="446"/>
+      <x:c r="F135" s="446"/>
+      <x:c r="G135" s="446"/>
+      <x:c r="H135" s="446"/>
+      <x:c r="I135" s="446"/>
+      <x:c r="J135" s="446"/>
+      <x:c r="K135" s="446"/>
+      <x:c r="L135" s="446"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="446"/>
+      <x:c r="B136" s="446"/>
+      <x:c r="C136" s="446"/>
+      <x:c r="D136" s="446"/>
+      <x:c r="E136" s="446"/>
+      <x:c r="F136" s="446"/>
+      <x:c r="G136" s="446"/>
+      <x:c r="H136" s="446"/>
+      <x:c r="I136" s="446"/>
+      <x:c r="J136" s="446"/>
+      <x:c r="K136" s="446"/>
+      <x:c r="L136" s="446"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="446"/>
+      <x:c r="B137" s="446"/>
+      <x:c r="C137" s="446"/>
+      <x:c r="D137" s="446"/>
+      <x:c r="E137" s="446"/>
+      <x:c r="F137" s="446"/>
+      <x:c r="G137" s="446"/>
+      <x:c r="H137" s="446"/>
+      <x:c r="I137" s="446"/>
+      <x:c r="J137" s="446"/>
+      <x:c r="K137" s="446"/>
+      <x:c r="L137" s="446"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="446"/>
+      <x:c r="B138" s="446"/>
+      <x:c r="C138" s="446"/>
+      <x:c r="D138" s="446"/>
+      <x:c r="E138" s="446"/>
+      <x:c r="F138" s="446"/>
+      <x:c r="G138" s="446"/>
+      <x:c r="H138" s="446"/>
+      <x:c r="I138" s="446"/>
+      <x:c r="J138" s="446"/>
+      <x:c r="K138" s="446"/>
+      <x:c r="L138" s="446"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="446"/>
+      <x:c r="B139" s="446"/>
+      <x:c r="C139" s="446"/>
+      <x:c r="D139" s="446"/>
+      <x:c r="E139" s="446"/>
+      <x:c r="F139" s="446"/>
+      <x:c r="G139" s="446"/>
+      <x:c r="H139" s="446"/>
+      <x:c r="I139" s="446"/>
+      <x:c r="J139" s="446"/>
+      <x:c r="K139" s="446"/>
+      <x:c r="L139" s="446"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="446"/>
+      <x:c r="B140" s="446"/>
+      <x:c r="C140" s="446"/>
+      <x:c r="D140" s="446"/>
+      <x:c r="E140" s="446"/>
+      <x:c r="F140" s="446"/>
+      <x:c r="G140" s="446"/>
+      <x:c r="H140" s="446"/>
+      <x:c r="I140" s="446"/>
+      <x:c r="J140" s="446"/>
+      <x:c r="K140" s="446"/>
+      <x:c r="L140" s="446"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="446"/>
+      <x:c r="B141" s="446"/>
+      <x:c r="C141" s="446"/>
+      <x:c r="D141" s="446"/>
+      <x:c r="E141" s="446"/>
+      <x:c r="F141" s="446"/>
+      <x:c r="G141" s="446"/>
+      <x:c r="H141" s="446"/>
+      <x:c r="I141" s="446"/>
+      <x:c r="J141" s="446"/>
+      <x:c r="K141" s="446"/>
+      <x:c r="L141" s="446"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="446"/>
+      <x:c r="B142" s="446"/>
+      <x:c r="C142" s="446"/>
+      <x:c r="D142" s="446"/>
+      <x:c r="E142" s="446"/>
+      <x:c r="F142" s="446"/>
+      <x:c r="G142" s="446"/>
+      <x:c r="H142" s="446"/>
+      <x:c r="I142" s="446"/>
+      <x:c r="J142" s="446"/>
+      <x:c r="K142" s="446"/>
+      <x:c r="L142" s="446"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="446"/>
+      <x:c r="B143" s="446"/>
+      <x:c r="C143" s="446"/>
+      <x:c r="D143" s="446"/>
+      <x:c r="E143" s="446"/>
+      <x:c r="F143" s="446"/>
+      <x:c r="G143" s="446"/>
+      <x:c r="H143" s="446"/>
+      <x:c r="I143" s="446"/>
+      <x:c r="J143" s="446"/>
+      <x:c r="K143" s="446"/>
+      <x:c r="L143" s="446"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="446"/>
+      <x:c r="B144" s="446"/>
+      <x:c r="C144" s="446"/>
+      <x:c r="D144" s="446"/>
+      <x:c r="E144" s="446"/>
+      <x:c r="F144" s="446"/>
+      <x:c r="G144" s="446"/>
+      <x:c r="H144" s="446"/>
+      <x:c r="I144" s="446"/>
+      <x:c r="J144" s="446"/>
+      <x:c r="K144" s="446"/>
+      <x:c r="L144" s="446"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="446"/>
+      <x:c r="B145" s="446"/>
+      <x:c r="C145" s="446"/>
+      <x:c r="D145" s="446"/>
+      <x:c r="E145" s="446"/>
+      <x:c r="F145" s="446"/>
+      <x:c r="G145" s="446"/>
+      <x:c r="H145" s="446"/>
+      <x:c r="I145" s="446"/>
+      <x:c r="J145" s="446"/>
+      <x:c r="K145" s="446"/>
+      <x:c r="L145" s="446"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="446"/>
+      <x:c r="B146" s="446"/>
+      <x:c r="C146" s="446"/>
+      <x:c r="D146" s="446"/>
+      <x:c r="E146" s="446"/>
+      <x:c r="F146" s="446"/>
+      <x:c r="G146" s="446"/>
+      <x:c r="H146" s="446"/>
+      <x:c r="I146" s="446"/>
+      <x:c r="J146" s="446"/>
+      <x:c r="K146" s="446"/>
+      <x:c r="L146" s="446"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="446"/>
+      <x:c r="B147" s="446"/>
+      <x:c r="C147" s="446"/>
+      <x:c r="D147" s="446"/>
+      <x:c r="E147" s="446"/>
+      <x:c r="F147" s="446"/>
+      <x:c r="G147" s="446"/>
+      <x:c r="H147" s="446"/>
+      <x:c r="I147" s="446"/>
+      <x:c r="J147" s="446"/>
+      <x:c r="K147" s="446"/>
+      <x:c r="L147" s="446"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="446"/>
+      <x:c r="B148" s="446"/>
+      <x:c r="C148" s="446"/>
+      <x:c r="D148" s="446"/>
+      <x:c r="E148" s="446"/>
+      <x:c r="F148" s="446"/>
+      <x:c r="G148" s="446"/>
+      <x:c r="H148" s="446"/>
+      <x:c r="I148" s="446"/>
+      <x:c r="J148" s="446"/>
+      <x:c r="K148" s="446"/>
+      <x:c r="L148" s="446"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="446"/>
+      <x:c r="B149" s="446"/>
+      <x:c r="C149" s="446"/>
+      <x:c r="D149" s="446"/>
+      <x:c r="E149" s="446"/>
+      <x:c r="F149" s="446"/>
+      <x:c r="G149" s="446"/>
+      <x:c r="H149" s="446"/>
+      <x:c r="I149" s="446"/>
+      <x:c r="J149" s="446"/>
+      <x:c r="K149" s="446"/>
+      <x:c r="L149" s="446"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="446"/>
+      <x:c r="B150" s="446"/>
+      <x:c r="C150" s="446"/>
+      <x:c r="D150" s="446"/>
+      <x:c r="E150" s="446"/>
+      <x:c r="F150" s="446"/>
+      <x:c r="G150" s="446"/>
+      <x:c r="H150" s="446"/>
+      <x:c r="I150" s="446"/>
+      <x:c r="J150" s="446"/>
+      <x:c r="K150" s="446"/>
+      <x:c r="L150" s="446"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="446"/>
+      <x:c r="B151" s="446"/>
+      <x:c r="C151" s="446"/>
+      <x:c r="D151" s="446"/>
+      <x:c r="E151" s="446"/>
+      <x:c r="F151" s="446"/>
+      <x:c r="G151" s="446"/>
+      <x:c r="H151" s="446"/>
+      <x:c r="I151" s="446"/>
+      <x:c r="J151" s="446"/>
+      <x:c r="K151" s="446"/>
+      <x:c r="L151" s="446"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="446"/>
+      <x:c r="B152" s="446"/>
+      <x:c r="C152" s="446"/>
+      <x:c r="D152" s="446"/>
+      <x:c r="E152" s="446"/>
+      <x:c r="F152" s="446"/>
+      <x:c r="G152" s="446"/>
+      <x:c r="H152" s="446"/>
+      <x:c r="I152" s="446"/>
+      <x:c r="J152" s="446"/>
+      <x:c r="K152" s="446"/>
+      <x:c r="L152" s="446"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="446"/>
+      <x:c r="B153" s="446"/>
+      <x:c r="C153" s="446"/>
+      <x:c r="D153" s="446"/>
+      <x:c r="E153" s="446"/>
+      <x:c r="F153" s="446"/>
+      <x:c r="G153" s="446"/>
+      <x:c r="H153" s="446"/>
+      <x:c r="I153" s="446"/>
+      <x:c r="J153" s="446"/>
+      <x:c r="K153" s="446"/>
+      <x:c r="L153" s="446"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="446"/>
+      <x:c r="B154" s="446"/>
+      <x:c r="C154" s="446"/>
+      <x:c r="D154" s="446"/>
+      <x:c r="E154" s="446"/>
+      <x:c r="F154" s="446"/>
+      <x:c r="G154" s="446"/>
+      <x:c r="H154" s="446"/>
+      <x:c r="I154" s="446"/>
+      <x:c r="J154" s="446"/>
+      <x:c r="K154" s="446"/>
+      <x:c r="L154" s="446"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="446"/>
+      <x:c r="B155" s="446"/>
+      <x:c r="C155" s="446"/>
+      <x:c r="D155" s="446"/>
+      <x:c r="E155" s="446"/>
+      <x:c r="F155" s="446"/>
+      <x:c r="G155" s="446"/>
+      <x:c r="H155" s="446"/>
+      <x:c r="I155" s="446"/>
+      <x:c r="J155" s="446"/>
+      <x:c r="K155" s="446"/>
+      <x:c r="L155" s="446"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="446"/>
+      <x:c r="B156" s="446"/>
+      <x:c r="C156" s="446"/>
+      <x:c r="D156" s="446"/>
+      <x:c r="E156" s="446"/>
+      <x:c r="F156" s="446"/>
+      <x:c r="G156" s="446"/>
+      <x:c r="H156" s="446"/>
+      <x:c r="I156" s="446"/>
+      <x:c r="J156" s="446"/>
+      <x:c r="K156" s="446"/>
+      <x:c r="L156" s="446"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="446"/>
+      <x:c r="B157" s="446"/>
+      <x:c r="C157" s="446"/>
+      <x:c r="D157" s="446"/>
+      <x:c r="E157" s="446"/>
+      <x:c r="F157" s="446"/>
+      <x:c r="G157" s="446"/>
+      <x:c r="H157" s="446"/>
+      <x:c r="I157" s="446"/>
+      <x:c r="J157" s="446"/>
+      <x:c r="K157" s="446"/>
+      <x:c r="L157" s="446"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="446"/>
+      <x:c r="B158" s="446"/>
+      <x:c r="C158" s="446"/>
+      <x:c r="D158" s="446"/>
+      <x:c r="E158" s="446"/>
+      <x:c r="F158" s="446"/>
+      <x:c r="G158" s="446"/>
+      <x:c r="H158" s="446"/>
+      <x:c r="I158" s="446"/>
+      <x:c r="J158" s="446"/>
+      <x:c r="K158" s="446"/>
+      <x:c r="L158" s="446"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="446"/>
+      <x:c r="B159" s="446"/>
+      <x:c r="C159" s="446"/>
+      <x:c r="D159" s="446"/>
+      <x:c r="E159" s="446"/>
+      <x:c r="F159" s="446"/>
+      <x:c r="G159" s="446"/>
+      <x:c r="H159" s="446"/>
+      <x:c r="I159" s="446"/>
+      <x:c r="J159" s="446"/>
+      <x:c r="K159" s="446"/>
+      <x:c r="L159" s="446"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="446"/>
+      <x:c r="B160" s="446"/>
+      <x:c r="C160" s="446"/>
+      <x:c r="D160" s="446"/>
+      <x:c r="E160" s="446"/>
+      <x:c r="F160" s="446"/>
+      <x:c r="G160" s="446"/>
+      <x:c r="H160" s="446"/>
+      <x:c r="I160" s="446"/>
+      <x:c r="J160" s="446"/>
+      <x:c r="K160" s="446"/>
+      <x:c r="L160" s="446"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="446"/>
+      <x:c r="B161" s="446"/>
+      <x:c r="C161" s="446"/>
+      <x:c r="D161" s="446"/>
+      <x:c r="E161" s="446"/>
+      <x:c r="F161" s="446"/>
+      <x:c r="G161" s="446"/>
+      <x:c r="H161" s="446"/>
+      <x:c r="I161" s="446"/>
+      <x:c r="J161" s="446"/>
+      <x:c r="K161" s="446"/>
+      <x:c r="L161" s="446"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="446"/>
+      <x:c r="B162" s="446"/>
+      <x:c r="C162" s="446"/>
+      <x:c r="D162" s="446"/>
+      <x:c r="E162" s="446"/>
+      <x:c r="F162" s="446"/>
+      <x:c r="G162" s="446"/>
+      <x:c r="H162" s="446"/>
+      <x:c r="I162" s="446"/>
+      <x:c r="J162" s="446"/>
+      <x:c r="K162" s="446"/>
+      <x:c r="L162" s="446"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="446"/>
+      <x:c r="B163" s="446"/>
+      <x:c r="C163" s="446"/>
+      <x:c r="D163" s="446"/>
+      <x:c r="E163" s="446"/>
+      <x:c r="F163" s="446"/>
+      <x:c r="G163" s="446"/>
+      <x:c r="H163" s="446"/>
+      <x:c r="I163" s="446"/>
+      <x:c r="J163" s="446"/>
+      <x:c r="K163" s="446"/>
+      <x:c r="L163" s="446"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="446"/>
+      <x:c r="B164" s="446"/>
+      <x:c r="C164" s="446"/>
+      <x:c r="D164" s="446"/>
+      <x:c r="E164" s="446"/>
+      <x:c r="F164" s="446"/>
+      <x:c r="G164" s="446"/>
+      <x:c r="H164" s="446"/>
+      <x:c r="I164" s="446"/>
+      <x:c r="J164" s="446"/>
+      <x:c r="K164" s="446"/>
+      <x:c r="L164" s="446"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="446"/>
+      <x:c r="B165" s="446"/>
+      <x:c r="C165" s="446"/>
+      <x:c r="D165" s="446"/>
+      <x:c r="E165" s="446"/>
+      <x:c r="F165" s="446"/>
+      <x:c r="G165" s="446"/>
+      <x:c r="H165" s="446"/>
+      <x:c r="I165" s="446"/>
+      <x:c r="J165" s="446"/>
+      <x:c r="K165" s="446"/>
+      <x:c r="L165" s="446"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="446"/>
+      <x:c r="B166" s="446"/>
+      <x:c r="C166" s="446"/>
+      <x:c r="D166" s="446"/>
+      <x:c r="E166" s="446"/>
+      <x:c r="F166" s="446"/>
+      <x:c r="G166" s="446"/>
+      <x:c r="H166" s="446"/>
+      <x:c r="I166" s="446"/>
+      <x:c r="J166" s="446"/>
+      <x:c r="K166" s="446"/>
+      <x:c r="L166" s="446"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="446"/>
+      <x:c r="B167" s="446"/>
+      <x:c r="C167" s="446"/>
+      <x:c r="D167" s="446"/>
+      <x:c r="E167" s="446"/>
+      <x:c r="F167" s="446"/>
+      <x:c r="G167" s="446"/>
+      <x:c r="H167" s="446"/>
+      <x:c r="I167" s="446"/>
+      <x:c r="J167" s="446"/>
+      <x:c r="K167" s="446"/>
+      <x:c r="L167" s="446"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="446"/>
+      <x:c r="B168" s="446"/>
+      <x:c r="C168" s="446"/>
+      <x:c r="D168" s="446"/>
+      <x:c r="E168" s="446"/>
+      <x:c r="F168" s="446"/>
+      <x:c r="G168" s="446"/>
+      <x:c r="H168" s="446"/>
+      <x:c r="I168" s="446"/>
+      <x:c r="J168" s="446"/>
+      <x:c r="K168" s="446"/>
+      <x:c r="L168" s="446"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="446"/>
+      <x:c r="B169" s="446"/>
+      <x:c r="C169" s="446"/>
+      <x:c r="D169" s="446"/>
+      <x:c r="E169" s="446"/>
+      <x:c r="F169" s="446"/>
+      <x:c r="G169" s="446"/>
+      <x:c r="H169" s="446"/>
+      <x:c r="I169" s="446"/>
+      <x:c r="J169" s="446"/>
+      <x:c r="K169" s="446"/>
+      <x:c r="L169" s="446"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="446"/>
+      <x:c r="B170" s="446"/>
+      <x:c r="C170" s="446"/>
+      <x:c r="D170" s="446"/>
+      <x:c r="E170" s="446"/>
+      <x:c r="F170" s="446"/>
+      <x:c r="G170" s="446"/>
+      <x:c r="H170" s="446"/>
+      <x:c r="I170" s="446"/>
+      <x:c r="J170" s="446"/>
+      <x:c r="K170" s="446"/>
+      <x:c r="L170" s="446"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="446"/>
+      <x:c r="B171" s="446"/>
+      <x:c r="C171" s="446"/>
+      <x:c r="D171" s="446"/>
+      <x:c r="E171" s="446"/>
+      <x:c r="F171" s="446"/>
+      <x:c r="G171" s="446"/>
+      <x:c r="H171" s="446"/>
+      <x:c r="I171" s="446"/>
+      <x:c r="J171" s="446"/>
+      <x:c r="K171" s="446"/>
+      <x:c r="L171" s="446"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="446"/>
+      <x:c r="B172" s="446"/>
+      <x:c r="C172" s="446"/>
+      <x:c r="D172" s="446"/>
+      <x:c r="E172" s="446"/>
+      <x:c r="F172" s="446"/>
+      <x:c r="G172" s="446"/>
+      <x:c r="H172" s="446"/>
+      <x:c r="I172" s="446"/>
+      <x:c r="J172" s="446"/>
+      <x:c r="K172" s="446"/>
+      <x:c r="L172" s="446"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="446"/>
+      <x:c r="B173" s="446"/>
+      <x:c r="C173" s="446"/>
+      <x:c r="D173" s="446"/>
+      <x:c r="E173" s="446"/>
+      <x:c r="F173" s="446"/>
+      <x:c r="G173" s="446"/>
+      <x:c r="H173" s="446"/>
+      <x:c r="I173" s="446"/>
+      <x:c r="J173" s="446"/>
+      <x:c r="K173" s="446"/>
+      <x:c r="L173" s="446"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="446"/>
+      <x:c r="B174" s="446"/>
+      <x:c r="C174" s="446"/>
+      <x:c r="D174" s="446"/>
+      <x:c r="E174" s="446"/>
+      <x:c r="F174" s="446"/>
+      <x:c r="G174" s="446"/>
+      <x:c r="H174" s="446"/>
+      <x:c r="I174" s="446"/>
+      <x:c r="J174" s="446"/>
+      <x:c r="K174" s="446"/>
+      <x:c r="L174" s="446"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="446"/>
+      <x:c r="B175" s="446"/>
+      <x:c r="C175" s="446"/>
+      <x:c r="D175" s="446"/>
+      <x:c r="E175" s="446"/>
+      <x:c r="F175" s="446"/>
+      <x:c r="G175" s="446"/>
+      <x:c r="H175" s="446"/>
+      <x:c r="I175" s="446"/>
+      <x:c r="J175" s="446"/>
+      <x:c r="K175" s="446"/>
+      <x:c r="L175" s="446"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="446"/>
+      <x:c r="B176" s="446"/>
+      <x:c r="C176" s="446"/>
+      <x:c r="D176" s="446"/>
+      <x:c r="E176" s="446"/>
+      <x:c r="F176" s="446"/>
+      <x:c r="G176" s="446"/>
+      <x:c r="H176" s="446"/>
+      <x:c r="I176" s="446"/>
+      <x:c r="J176" s="446"/>
+      <x:c r="K176" s="446"/>
+      <x:c r="L176" s="446"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="446"/>
+      <x:c r="B177" s="446"/>
+      <x:c r="C177" s="446"/>
+      <x:c r="D177" s="446"/>
+      <x:c r="E177" s="446"/>
+      <x:c r="F177" s="446"/>
+      <x:c r="G177" s="446"/>
+      <x:c r="H177" s="446"/>
+      <x:c r="I177" s="446"/>
+      <x:c r="J177" s="446"/>
+      <x:c r="K177" s="446"/>
+      <x:c r="L177" s="446"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="446"/>
+      <x:c r="B178" s="446"/>
+      <x:c r="C178" s="446"/>
+      <x:c r="D178" s="446"/>
+      <x:c r="E178" s="446"/>
+      <x:c r="F178" s="446"/>
+      <x:c r="G178" s="446"/>
+      <x:c r="H178" s="446"/>
+      <x:c r="I178" s="446"/>
+      <x:c r="J178" s="446"/>
+      <x:c r="K178" s="446"/>
+      <x:c r="L178" s="446"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="446"/>
+      <x:c r="B179" s="446"/>
+      <x:c r="C179" s="446"/>
+      <x:c r="D179" s="446"/>
+      <x:c r="E179" s="446"/>
+      <x:c r="F179" s="446"/>
+      <x:c r="G179" s="446"/>
+      <x:c r="H179" s="446"/>
+      <x:c r="I179" s="446"/>
+      <x:c r="J179" s="446"/>
+      <x:c r="K179" s="446"/>
+      <x:c r="L179" s="446"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="446"/>
+      <x:c r="B180" s="446"/>
+      <x:c r="C180" s="446"/>
+      <x:c r="D180" s="446"/>
+      <x:c r="E180" s="446"/>
+      <x:c r="F180" s="446"/>
+      <x:c r="G180" s="446"/>
+      <x:c r="H180" s="446"/>
+      <x:c r="I180" s="446"/>
+      <x:c r="J180" s="446"/>
+      <x:c r="K180" s="446"/>
+      <x:c r="L180" s="446"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="446"/>
+      <x:c r="B181" s="446"/>
+      <x:c r="C181" s="446"/>
+      <x:c r="D181" s="446"/>
+      <x:c r="E181" s="446"/>
+      <x:c r="F181" s="446"/>
+      <x:c r="G181" s="446"/>
+      <x:c r="H181" s="446"/>
+      <x:c r="I181" s="446"/>
+      <x:c r="J181" s="446"/>
+      <x:c r="K181" s="446"/>
+      <x:c r="L181" s="446"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="446"/>
+      <x:c r="B182" s="446"/>
+      <x:c r="C182" s="446"/>
+      <x:c r="D182" s="446"/>
+      <x:c r="E182" s="446"/>
+      <x:c r="F182" s="446"/>
+      <x:c r="G182" s="446"/>
+      <x:c r="H182" s="446"/>
+      <x:c r="I182" s="446"/>
+      <x:c r="J182" s="446"/>
+      <x:c r="K182" s="446"/>
+      <x:c r="L182" s="446"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="446"/>
+      <x:c r="B183" s="446"/>
+      <x:c r="C183" s="446"/>
+      <x:c r="D183" s="446"/>
+      <x:c r="E183" s="446"/>
+      <x:c r="F183" s="446"/>
+      <x:c r="G183" s="446"/>
+      <x:c r="H183" s="446"/>
+      <x:c r="I183" s="446"/>
+      <x:c r="J183" s="446"/>
+      <x:c r="K183" s="446"/>
+      <x:c r="L183" s="446"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="446"/>
+      <x:c r="B184" s="446"/>
+      <x:c r="C184" s="446"/>
+      <x:c r="D184" s="446"/>
+      <x:c r="E184" s="446"/>
+      <x:c r="F184" s="446"/>
+      <x:c r="G184" s="446"/>
+      <x:c r="H184" s="446"/>
+      <x:c r="I184" s="446"/>
+      <x:c r="J184" s="446"/>
+      <x:c r="K184" s="446"/>
+      <x:c r="L184" s="446"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="446"/>
+      <x:c r="B185" s="446"/>
+      <x:c r="C185" s="446"/>
+      <x:c r="D185" s="446"/>
+      <x:c r="E185" s="446"/>
+      <x:c r="F185" s="446"/>
+      <x:c r="G185" s="446"/>
+      <x:c r="H185" s="446"/>
+      <x:c r="I185" s="446"/>
+      <x:c r="J185" s="446"/>
+      <x:c r="K185" s="446"/>
+      <x:c r="L185" s="446"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="446"/>
+      <x:c r="B186" s="446"/>
+      <x:c r="C186" s="446"/>
+      <x:c r="D186" s="446"/>
+      <x:c r="E186" s="446"/>
+      <x:c r="F186" s="446"/>
+      <x:c r="G186" s="446"/>
+      <x:c r="H186" s="446"/>
+      <x:c r="I186" s="446"/>
+      <x:c r="J186" s="446"/>
+      <x:c r="K186" s="446"/>
+      <x:c r="L186" s="446"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="446"/>
+      <x:c r="B187" s="446"/>
+      <x:c r="C187" s="446"/>
+      <x:c r="D187" s="446"/>
+      <x:c r="E187" s="446"/>
+      <x:c r="F187" s="446"/>
+      <x:c r="G187" s="446"/>
+      <x:c r="H187" s="446"/>
+      <x:c r="I187" s="446"/>
+      <x:c r="J187" s="446"/>
+      <x:c r="K187" s="446"/>
+      <x:c r="L187" s="446"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="446"/>
+      <x:c r="B188" s="446"/>
+      <x:c r="C188" s="446"/>
+      <x:c r="D188" s="446"/>
+      <x:c r="E188" s="446"/>
+      <x:c r="F188" s="446"/>
+      <x:c r="G188" s="446"/>
+      <x:c r="H188" s="446"/>
+      <x:c r="I188" s="446"/>
+      <x:c r="J188" s="446"/>
+      <x:c r="K188" s="446"/>
+      <x:c r="L188" s="446"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="446"/>
+      <x:c r="B189" s="446"/>
+      <x:c r="C189" s="446"/>
+      <x:c r="D189" s="446"/>
+      <x:c r="E189" s="446"/>
+      <x:c r="F189" s="446"/>
+      <x:c r="G189" s="446"/>
+      <x:c r="H189" s="446"/>
+      <x:c r="I189" s="446"/>
+      <x:c r="J189" s="446"/>
+      <x:c r="K189" s="446"/>
+      <x:c r="L189" s="446"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="446"/>
+      <x:c r="B190" s="446"/>
+      <x:c r="C190" s="446"/>
+      <x:c r="D190" s="446"/>
+      <x:c r="E190" s="446"/>
+      <x:c r="F190" s="446"/>
+      <x:c r="G190" s="446"/>
+      <x:c r="H190" s="446"/>
+      <x:c r="I190" s="446"/>
+      <x:c r="J190" s="446"/>
+      <x:c r="K190" s="446"/>
+      <x:c r="L190" s="446"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="446"/>
+      <x:c r="B191" s="446"/>
+      <x:c r="C191" s="446"/>
+      <x:c r="D191" s="446"/>
+      <x:c r="E191" s="446"/>
+      <x:c r="F191" s="446"/>
+      <x:c r="G191" s="446"/>
+      <x:c r="H191" s="446"/>
+      <x:c r="I191" s="446"/>
+      <x:c r="J191" s="446"/>
+      <x:c r="K191" s="446"/>
+      <x:c r="L191" s="446"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="446"/>
+      <x:c r="B192" s="446"/>
+      <x:c r="C192" s="446"/>
+      <x:c r="D192" s="446"/>
+      <x:c r="E192" s="446"/>
+      <x:c r="F192" s="446"/>
+      <x:c r="G192" s="446"/>
+      <x:c r="H192" s="446"/>
+      <x:c r="I192" s="446"/>
+      <x:c r="J192" s="446"/>
+      <x:c r="K192" s="446"/>
+      <x:c r="L192" s="446"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="446"/>
+      <x:c r="B193" s="446"/>
+      <x:c r="C193" s="446"/>
+      <x:c r="D193" s="446"/>
+      <x:c r="E193" s="446"/>
+      <x:c r="F193" s="446"/>
+      <x:c r="G193" s="446"/>
+      <x:c r="H193" s="446"/>
+      <x:c r="I193" s="446"/>
+      <x:c r="J193" s="446"/>
+      <x:c r="K193" s="446"/>
+      <x:c r="L193" s="446"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="446"/>
+      <x:c r="B194" s="446"/>
+      <x:c r="C194" s="446"/>
+      <x:c r="D194" s="446"/>
+      <x:c r="E194" s="446"/>
+      <x:c r="F194" s="446"/>
+      <x:c r="G194" s="446"/>
+      <x:c r="H194" s="446"/>
+      <x:c r="I194" s="446"/>
+      <x:c r="J194" s="446"/>
+      <x:c r="K194" s="446"/>
+      <x:c r="L194" s="446"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="446"/>
+      <x:c r="B195" s="446"/>
+      <x:c r="C195" s="446"/>
+      <x:c r="D195" s="446"/>
+      <x:c r="E195" s="446"/>
+      <x:c r="F195" s="446"/>
+      <x:c r="G195" s="446"/>
+      <x:c r="H195" s="446"/>
+      <x:c r="I195" s="446"/>
+      <x:c r="J195" s="446"/>
+      <x:c r="K195" s="446"/>
+      <x:c r="L195" s="446"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="446"/>
+      <x:c r="B196" s="446"/>
+      <x:c r="C196" s="446"/>
+      <x:c r="D196" s="446"/>
+      <x:c r="E196" s="446"/>
+      <x:c r="F196" s="446"/>
+      <x:c r="G196" s="446"/>
+      <x:c r="H196" s="446"/>
+      <x:c r="I196" s="446"/>
+      <x:c r="J196" s="446"/>
+      <x:c r="K196" s="446"/>
+      <x:c r="L196" s="446"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="446"/>
+      <x:c r="B197" s="446"/>
+      <x:c r="C197" s="446"/>
+      <x:c r="D197" s="446"/>
+      <x:c r="E197" s="446"/>
+      <x:c r="F197" s="446"/>
+      <x:c r="G197" s="446"/>
+      <x:c r="H197" s="446"/>
+      <x:c r="I197" s="446"/>
+      <x:c r="J197" s="446"/>
+      <x:c r="K197" s="446"/>
+      <x:c r="L197" s="446"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="446"/>
+      <x:c r="B198" s="446"/>
+      <x:c r="C198" s="446"/>
+      <x:c r="D198" s="446"/>
+      <x:c r="E198" s="446"/>
+      <x:c r="F198" s="446"/>
+      <x:c r="G198" s="446"/>
+      <x:c r="H198" s="446"/>
+      <x:c r="I198" s="446"/>
+      <x:c r="J198" s="446"/>
+      <x:c r="K198" s="446"/>
+      <x:c r="L198" s="446"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="446"/>
+      <x:c r="B199" s="446"/>
+      <x:c r="C199" s="446"/>
+      <x:c r="D199" s="446"/>
+      <x:c r="E199" s="446"/>
+      <x:c r="F199" s="446"/>
+      <x:c r="G199" s="446"/>
+      <x:c r="H199" s="446"/>
+      <x:c r="I199" s="446"/>
+      <x:c r="J199" s="446"/>
+      <x:c r="K199" s="446"/>
+      <x:c r="L199" s="446"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="446"/>
+      <x:c r="B200" s="446"/>
+      <x:c r="C200" s="446"/>
+      <x:c r="D200" s="446"/>
+      <x:c r="E200" s="446"/>
+      <x:c r="F200" s="446"/>
+      <x:c r="G200" s="446"/>
+      <x:c r="H200" s="446"/>
+      <x:c r="I200" s="446"/>
+      <x:c r="J200" s="446"/>
+      <x:c r="K200" s="446"/>
+      <x:c r="L200" s="446"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4982,44 +9419,62 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="519" t="str">
         <x:v>唐长安城知识图谱 · 更新日志</x:v>
       </x:c>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
-      <x:c r="F1" s="3"/>
+      <x:c r="B1" s="519"/>
+      <x:c r="C1" s="519"/>
+      <x:c r="D1" s="519"/>
+      <x:c r="E1" s="519"/>
+      <x:c r="F1" s="519"/>
+      <x:c r="G1" s="446"/>
+      <x:c r="H1" s="446"/>
+      <x:c r="I1" s="446"/>
+      <x:c r="J1" s="446"/>
+      <x:c r="K1" s="446"/>
+      <x:c r="L1" s="446"/>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="5" t="str">
+      <x:c r="A2" s="520" t="str">
         <x:v>每次工作结束只增加一行。即使隔很久再回来，也可以从最上方的新记录快速恢复记忆。</x:v>
       </x:c>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="B2" s="520"/>
+      <x:c r="C2" s="520"/>
+      <x:c r="D2" s="520"/>
+      <x:c r="E2" s="520"/>
+      <x:c r="F2" s="520"/>
+      <x:c r="G2" s="446"/>
+      <x:c r="H2" s="446"/>
+      <x:c r="I2" s="446"/>
+      <x:c r="J2" s="446"/>
+      <x:c r="K2" s="446"/>
+      <x:c r="L2" s="446"/>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="521" t="str">
         <x:v>日期</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="521" t="str">
         <x:v>更新人</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="521" t="str">
         <x:v>完成内容</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="521" t="str">
         <x:v>Git提交/文件</x:v>
       </x:c>
-      <x:c r="E3" s="12" t="str">
+      <x:c r="E3" s="521" t="str">
         <x:v>下一步</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="str">
+      <x:c r="F3" s="521" t="str">
         <x:v>备注</x:v>
       </x:c>
+      <x:c r="G3" s="446"/>
+      <x:c r="H3" s="446"/>
+      <x:c r="I3" s="446"/>
+      <x:c r="J3" s="446"/>
+      <x:c r="K3" s="446"/>
+      <x:c r="L3" s="446"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="207" t="str">
@@ -5038,6 +9493,12 @@
         <x:v>复制并建立新平台仓库</x:v>
       </x:c>
       <x:c r="F4" s="207"/>
+      <x:c r="G4" s="446"/>
+      <x:c r="H4" s="446"/>
+      <x:c r="I4" s="446"/>
+      <x:c r="J4" s="446"/>
+      <x:c r="K4" s="446"/>
+      <x:c r="L4" s="446"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="207" t="str">
@@ -5058,6 +9519,12 @@
       <x:c r="F5" s="207" t="str">
         <x:v>未复制.env</x:v>
       </x:c>
+      <x:c r="G5" s="446"/>
+      <x:c r="H5" s="446"/>
+      <x:c r="I5" s="446"/>
+      <x:c r="J5" s="446"/>
+      <x:c r="K5" s="446"/>
+      <x:c r="L5" s="446"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="207" t="str">
@@ -5076,6 +9543,12 @@
         <x:v>组织六张表字段联合评审</x:v>
       </x:c>
       <x:c r="F6" s="207"/>
+      <x:c r="G6" s="446"/>
+      <x:c r="H6" s="446"/>
+      <x:c r="I6" s="446"/>
+      <x:c r="J6" s="446"/>
+      <x:c r="K6" s="446"/>
+      <x:c r="L6" s="446"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="207" t="str">
@@ -5096,766 +9569,1000 @@
       <x:c r="F7" s="207" t="str">
         <x:v>以后每次工作后更新本表</x:v>
       </x:c>
+      <x:c r="G7" s="446"/>
+      <x:c r="H7" s="446"/>
+      <x:c r="I7" s="446"/>
+      <x:c r="J7" s="446"/>
+      <x:c r="K7" s="446"/>
+      <x:c r="L7" s="446"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="212" t="str">
+      <x:c r="A8" s="522" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
-      <x:c r="B8" s="213" t="str">
+      <x:c r="B8" s="523" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C8" s="213" t="str">
+      <x:c r="C8" s="523" t="str">
         <x:v>新增坊间空间关系表与专题表转换规则v1；确认后三张字段</x:v>
       </x:c>
-      <x:c r="D8" s="213" t="str">
+      <x:c r="D8" s="523" t="str">
         <x:v>阶段二v1模板</x:v>
       </x:c>
-      <x:c r="E8" s="213" t="str">
+      <x:c r="E8" s="523" t="str">
         <x:v>同事确认前三张表并召开联合评审</x:v>
       </x:c>
-      <x:c r="F8" s="214" t="str">
+      <x:c r="F8" s="524" t="str">
         <x:v>六张核心表不变，新增两张辅助表</x:v>
       </x:c>
+      <x:c r="G8" s="446"/>
+      <x:c r="H8" s="446"/>
+      <x:c r="I8" s="446"/>
+      <x:c r="J8" s="446"/>
+      <x:c r="K8" s="446"/>
+      <x:c r="L8" s="446"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="212" t="str">
+      <x:c r="A9" s="522" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
-      <x:c r="B9" s="213" t="str">
+      <x:c r="B9" s="523" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C9" s="213" t="str">
+      <x:c r="C9" s="523" t="str">
         <x:v>完成小型样例文献初选，确定3份现有主文献、5份建议补充资料及样例对象群</x:v>
       </x:c>
-      <x:c r="D9" s="213" t="str">
+      <x:c r="D9" s="523" t="str">
         <x:v>小型样例文献选择方案_v1.md</x:v>
       </x:c>
-      <x:c r="E9" s="213" t="str">
+      <x:c r="E9" s="523" t="str">
         <x:v>团队确认名单并取得优先考古资料</x:v>
       </x:c>
-      <x:c r="F9" s="214" t="str">
+      <x:c r="F9" s="524" t="str">
         <x:v>尺度与坐标缺口暂不推测</x:v>
       </x:c>
+      <x:c r="G9" s="446"/>
+      <x:c r="H9" s="446"/>
+      <x:c r="I9" s="446"/>
+      <x:c r="J9" s="446"/>
+      <x:c r="K9" s="446"/>
+      <x:c r="L9" s="446"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="212" t="str">
+      <x:c r="A10" s="522" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
-      <x:c r="B10" s="213" t="str">
+      <x:c r="B10" s="523" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C10" s="213" t="str">
+      <x:c r="C10" s="523" t="str">
         <x:v>完成小型样例第1批：9条片段、13实体、6关系及道路/水渠/城门/尺度/规则专题记录</x:v>
       </x:c>
-      <x:c r="D10" s="213" t="str">
+      <x:c r="D10" s="523" t="str">
         <x:v>小型样例_第1批_文献片段与基础对象_v1.xlsx</x:v>
       </x:c>
-      <x:c r="E10" s="213" t="str">
+      <x:c r="E10" s="523" t="str">
         <x:v>扫描版核对并继续提取5坊</x:v>
       </x:c>
-      <x:c r="F10" s="214" t="str">
+      <x:c r="F10" s="524" t="str">
         <x:v>未填写坐标和米制换算，全部待审核</x:v>
       </x:c>
+      <x:c r="G10" s="446"/>
+      <x:c r="H10" s="446"/>
+      <x:c r="I10" s="446"/>
+      <x:c r="J10" s="446"/>
+      <x:c r="K10" s="446"/>
+      <x:c r="L10" s="446"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="212" t="str">
+      <x:c r="A11" s="522" t="str">
         <x:v>2026-08-08</x:v>
       </x:c>
-      <x:c r="B11" s="213" t="str">
+      <x:c r="B11" s="523" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C11" s="213" t="str">
+      <x:c r="C11" s="523" t="str">
         <x:v>新增坊平面网格坐标与道路网格序位字段，并同步转换规则和样例</x:v>
       </x:c>
-      <x:c r="D11" s="213" t="str">
+      <x:c r="D11" s="523" t="str">
         <x:v>阶段二模板 / 第1批小样例</x:v>
       </x:c>
-      <x:c r="E11" s="213" t="str">
+      <x:c r="E11" s="523" t="str">
         <x:v>确认复原网格基准后填写具体序号</x:v>
       </x:c>
-      <x:c r="F11" s="214" t="str">
+      <x:c r="F11" s="524" t="str">
         <x:v>网格位置不等同经纬度</x:v>
       </x:c>
+      <x:c r="G11" s="446"/>
+      <x:c r="H11" s="446"/>
+      <x:c r="I11" s="446"/>
+      <x:c r="J11" s="446"/>
+      <x:c r="K11" s="446"/>
+      <x:c r="L11" s="446"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
+      <x:c r="A12" s="446" t="str">
         <x:v>2026-08-08</x:v>
       </x:c>
-      <x:c r="B12" t="str">
+      <x:c r="B12" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C12" t="str">
+      <x:c r="C12" s="446" t="str">
         <x:v>新增坊平面网格坐标与道路网格序位字段，并同步转换规则和样例</x:v>
       </x:c>
-      <x:c r="D12" t="str">
+      <x:c r="D12" s="446" t="str">
         <x:v>阶段二模板 / 第1批小样例</x:v>
       </x:c>
-      <x:c r="E12" t="str">
+      <x:c r="E12" s="446" t="str">
         <x:v>确认复原网格基准后填写具体序号</x:v>
       </x:c>
-      <x:c r="F12" t="str">
+      <x:c r="F12" s="446" t="str">
         <x:v>网格位置不等同经纬度</x:v>
       </x:c>
+      <x:c r="G12" s="446"/>
+      <x:c r="H12" s="446"/>
+      <x:c r="I12" s="446"/>
+      <x:c r="J12" s="446"/>
+      <x:c r="K12" s="446"/>
+      <x:c r="L12" s="446"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="str">
+      <x:c r="A13" s="446" t="str">
         <x:v>2026-08-08</x:v>
       </x:c>
-      <x:c r="B13" t="str">
+      <x:c r="B13" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C13" t="str">
+      <x:c r="C13" s="446" t="str">
         <x:v>建立道路轴线序位规则并试编横街、承天门街</x:v>
       </x:c>
-      <x:c r="D13" t="str">
+      <x:c r="D13" s="446" t="str">
         <x:v>阶段二模板 / 第1批小样例</x:v>
       </x:c>
-      <x:c r="E13" t="str">
+      <x:c r="E13" s="446" t="str">
         <x:v>人工核对两条道路后扩展主要道路</x:v>
       </x:c>
-      <x:c r="F13" t="str">
+      <x:c r="F13" s="446" t="str">
         <x:v>轴线编号不等于道路实体</x:v>
       </x:c>
+      <x:c r="G13" s="446"/>
+      <x:c r="H13" s="446"/>
+      <x:c r="I13" s="446"/>
+      <x:c r="J13" s="446"/>
+      <x:c r="K13" s="446"/>
+      <x:c r="L13" s="446"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="str">
+      <x:c r="A14" s="446" t="str">
         <x:v>2026-08-08</x:v>
       </x:c>
-      <x:c r="B14" t="str">
+      <x:c r="B14" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C14" t="str">
+      <x:c r="C14" s="446" t="str">
         <x:v>修正东西向坊间道路为12条，横街移出EW序位</x:v>
       </x:c>
-      <x:c r="D14" t="str">
+      <x:c r="D14" s="446" t="str">
         <x:v>阶段二模板 / 第1批小样例</x:v>
       </x:c>
-      <x:c r="E14" t="str">
+      <x:c r="E14" s="446" t="str">
         <x:v>继续核对主要命名道路</x:v>
       </x:c>
-      <x:c r="F14" t="str">
+      <x:c r="F14" s="446" t="str">
         <x:v>横街位于第1排坊北侧</x:v>
       </x:c>
+      <x:c r="G14" s="446"/>
+      <x:c r="H14" s="446"/>
+      <x:c r="I14" s="446"/>
+      <x:c r="J14" s="446"/>
+      <x:c r="K14" s="446"/>
+      <x:c r="L14" s="446"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="str">
+      <x:c r="A15" s="446" t="str">
         <x:v>2026-08-08</x:v>
       </x:c>
-      <x:c r="B15" t="str">
+      <x:c r="B15" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C15" t="str">
+      <x:c r="C15" s="446" t="str">
         <x:v>试编朱雀大街及安化门、启夏门向北道路</x:v>
       </x:c>
-      <x:c r="D15" t="str">
+      <x:c r="D15" s="446" t="str">
         <x:v>阶段二模板 / 第1批小样例</x:v>
       </x:c>
-      <x:c r="E15" t="str">
+      <x:c r="E15" s="446" t="str">
         <x:v>确认两条暂名道路的史料名称</x:v>
       </x:c>
-      <x:c r="F15" t="str">
+      <x:c r="F15" s="446" t="str">
         <x:v>三条轴线分别为NS-05、NS-03、NS-07</x:v>
       </x:c>
+      <x:c r="G15" s="446"/>
+      <x:c r="H15" s="446"/>
+      <x:c r="I15" s="446"/>
+      <x:c r="J15" s="446"/>
+      <x:c r="K15" s="446"/>
+      <x:c r="L15" s="446"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="str">
+      <x:c r="A16" s="446" t="str">
         <x:v>2026-08-08</x:v>
       </x:c>
-      <x:c r="B16" t="str">
+      <x:c r="B16" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C16" t="str">
+      <x:c r="C16" s="446" t="str">
         <x:v>补录安化门、启夏门及4条城门—道路连接关系</x:v>
       </x:c>
-      <x:c r="D16" t="str">
+      <x:c r="D16" s="446" t="str">
         <x:v>第1批小型样例</x:v>
       </x:c>
-      <x:c r="E16" t="str">
+      <x:c r="E16" s="446" t="str">
         <x:v>人工审核新增关系并扩充其余外郭城门</x:v>
       </x:c>
-      <x:c r="F16" t="str">
+      <x:c r="F16" s="446" t="str">
         <x:v>连接关系来自图15；两条道路仍使用项目暂名</x:v>
       </x:c>
+      <x:c r="G16" s="446"/>
+      <x:c r="H16" s="446"/>
+      <x:c r="I16" s="446"/>
+      <x:c r="J16" s="446"/>
+      <x:c r="K16" s="446"/>
+      <x:c r="L16" s="446"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
+      <x:c r="A17" s="446" t="str">
         <x:v>2026-08-09</x:v>
       </x:c>
-      <x:c r="B17" t="str">
+      <x:c r="B17" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C17" t="str">
+      <x:c r="C17" s="446" t="str">
         <x:v>新增坊内平面规则表与研究结论表，补充转换和代码规则并重排页签</x:v>
       </x:c>
-      <x:c r="D17" t="str">
+      <x:c r="D17" s="446" t="str">
         <x:v>阶段二模板 / 第1批小型样例</x:v>
       </x:c>
-      <x:c r="E17" t="str">
+      <x:c r="E17" s="446" t="str">
         <x:v>用3—5篇道路宽度论文试录字段</x:v>
       </x:c>
-      <x:c r="F17" t="str">
+      <x:c r="F17" s="446" t="str">
         <x:v>基础事实与研究解释分层存储</x:v>
       </x:c>
+      <x:c r="G17" s="446"/>
+      <x:c r="H17" s="446"/>
+      <x:c r="I17" s="446"/>
+      <x:c r="J17" s="446"/>
+      <x:c r="K17" s="446"/>
+      <x:c r="L17" s="446"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="str">
+      <x:c r="A18" s="446" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="B18" t="str">
+      <x:c r="B18" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C18" t="str">
+      <x:c r="C18" s="446" t="str">
         <x:v>完成相关论文12篇初筛，确定道路宽度专题首批5篇</x:v>
       </x:c>
-      <x:c r="D18" t="str">
+      <x:c r="D18" s="446" t="str">
         <x:v>道路宽度专题_论文筛选清单_v1.md</x:v>
       </x:c>
-      <x:c r="E18" t="str">
+      <x:c r="E18" s="446" t="str">
         <x:v>精读贺从容、张小娟并试录研究结论</x:v>
       </x:c>
-      <x:c r="F18" t="str">
+      <x:c r="F18" s="446" t="str">
         <x:v>防火、绿化、基础设施材料仅作辅助证据</x:v>
       </x:c>
+      <x:c r="G18" s="446"/>
+      <x:c r="H18" s="446"/>
+      <x:c r="I18" s="446"/>
+      <x:c r="J18" s="446"/>
+      <x:c r="K18" s="446"/>
+      <x:c r="L18" s="446"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" t="str">
+      <x:c r="A19" s="446" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="B19" t="str">
+      <x:c r="B19" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C19" t="str">
+      <x:c r="C19" s="446" t="str">
         <x:v>完成李瑞论文首轮精读并试录6条研究结论</x:v>
       </x:c>
-      <x:c r="D19" t="str">
+      <x:c r="D19" s="446" t="str">
         <x:v>阶段二录入模板 / 李瑞2005精读说明</x:v>
       </x:c>
-      <x:c r="E19" t="str">
+      <x:c r="E19" s="446" t="str">
         <x:v>人工审核6条结论，再精读贺从容和张小娟</x:v>
       </x:c>
-      <x:c r="F19" t="str">
+      <x:c r="F19" s="446" t="str">
         <x:v>评价性观点与基础事实分开保存</x:v>
       </x:c>
+      <x:c r="G19" s="446"/>
+      <x:c r="H19" s="446"/>
+      <x:c r="I19" s="446"/>
+      <x:c r="J19" s="446"/>
+      <x:c r="K19" s="446"/>
+      <x:c r="L19" s="446"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" t="str">
+      <x:c r="A20" s="446" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="B20" t="str">
+      <x:c r="B20" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C20" t="str">
+      <x:c r="C20" s="446" t="str">
         <x:v>完成贺从容论文精读并试录坊内规则和研究结论</x:v>
       </x:c>
-      <x:c r="D20" t="str">
+      <x:c r="D20" s="446" t="str">
         <x:v>阶段二录入模板 / 贺从容精读说明</x:v>
       </x:c>
-      <x:c r="E20" t="str">
+      <x:c r="E20" s="446" t="str">
         <x:v>人工审核后精读张小娟</x:v>
       </x:c>
-      <x:c r="F20" t="str">
+      <x:c r="F20" s="446" t="str">
         <x:v>十六分区与宽度推测均保留限制</x:v>
       </x:c>
+      <x:c r="G20" s="446"/>
+      <x:c r="H20" s="446"/>
+      <x:c r="I20" s="446"/>
+      <x:c r="J20" s="446"/>
+      <x:c r="K20" s="446"/>
+      <x:c r="L20" s="446"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" t="str">
+      <x:c r="A21" s="446" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="B21" t="str">
+      <x:c r="B21" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C21" t="str">
+      <x:c r="C21" s="446" t="str">
         <x:v>完成张小娟论文精读、交叉验证与试录</x:v>
       </x:c>
-      <x:c r="D21" t="str">
+      <x:c r="D21" s="446" t="str">
         <x:v>阶段二录入模板 / 张小娟精读说明</x:v>
       </x:c>
-      <x:c r="E21" t="str">
+      <x:c r="E21" s="446" t="str">
         <x:v>人工审核后进行三篇核心论文字段评估</x:v>
       </x:c>
-      <x:c r="F21" t="str">
+      <x:c r="F21" s="446" t="str">
         <x:v>道路数量冲突暂不修改；两类坊内模型保留适用限制</x:v>
       </x:c>
+      <x:c r="G21" s="446"/>
+      <x:c r="H21" s="446"/>
+      <x:c r="I21" s="446"/>
+      <x:c r="J21" s="446"/>
+      <x:c r="K21" s="446"/>
+      <x:c r="L21" s="446"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" t="str">
+      <x:c r="A22" s="446" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
-      <x:c r="B22" t="str">
+      <x:c r="B22" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C22" t="str">
+      <x:c r="C22" s="446" t="str">
         <x:v>完成三篇论文试录数据迁移与编号整理</x:v>
       </x:c>
-      <x:c r="D22" t="str">
+      <x:c r="D22" s="446" t="str">
         <x:v>小型样例表 / 正式录入模板 / 项目看板</x:v>
       </x:c>
-      <x:c r="E22" t="str">
+      <x:c r="E22" s="446" t="str">
         <x:v>审核张小娟并开展三篇论文字段小结</x:v>
       </x:c>
-      <x:c r="F22" t="str">
+      <x:c r="F22" s="446" t="str">
         <x:v>片段编号改为1000、1100、1200段，正式模板不再存放论文试录</x:v>
       </x:c>
+      <x:c r="G22" s="446"/>
+      <x:c r="H22" s="446"/>
+      <x:c r="I22" s="446"/>
+      <x:c r="J22" s="446"/>
+      <x:c r="K22" s="446"/>
+      <x:c r="L22" s="446"/>
     </x:row>
     <x:row r="23" ht="40" customHeight="1">
-      <x:c r="A23" s="217" t="n">
+      <x:c r="A23" s="467" t="n">
         <x:v>46245</x:v>
       </x:c>
-      <x:c r="B23" s="216" t="str">
+      <x:c r="B23" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C23" s="216" t="str">
+      <x:c r="C23" s="446" t="str">
         <x:v>建立首条科普问答及7条证据关联，完成三层闭环试录</x:v>
       </x:c>
-      <x:c r="D23" s="216" t="str">
+      <x:c r="D23" s="446" t="str">
         <x:v>小型样例表 / 项目看板</x:v>
       </x:c>
-      <x:c r="E23" s="216" t="str">
+      <x:c r="E23" s="446" t="str">
         <x:v>人工审核科普文字、依据角色和公开范围</x:v>
       </x:c>
-      <x:c r="F23" s="216" t="str">
+      <x:c r="F23" s="446" t="str">
         <x:v>未修改空白正式模板；全部标记待审核</x:v>
       </x:c>
+      <x:c r="G23" s="446"/>
+      <x:c r="H23" s="446"/>
+      <x:c r="I23" s="446"/>
+      <x:c r="J23" s="446"/>
+      <x:c r="K23" s="446"/>
+      <x:c r="L23" s="446"/>
     </x:row>
     <x:row r="24" ht="40" customHeight="1">
-      <x:c r="A24" s="217" t="n">
+      <x:c r="A24" s="467" t="n">
         <x:v>46245</x:v>
       </x:c>
-      <x:c r="B24" s="216" t="str">
+      <x:c r="B24" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C24" s="216" t="str">
+      <x:c r="C24" s="446" t="str">
         <x:v>完成平台只读盘点，形成保留、替换、新增及六步实施清单</x:v>
       </x:c>
-      <x:c r="D24" s="216" t="str">
+      <x:c r="D24" s="446" t="str">
         <x:v>平台迁移盘点与实施清单v1 / 项目看板</x:v>
       </x:c>
-      <x:c r="E24" s="216" t="str">
+      <x:c r="E24" s="446" t="str">
         <x:v>确定唐长安平台数据契约v1</x:v>
       </x:c>
-      <x:c r="F24" s="216" t="str">
+      <x:c r="F24" s="446" t="str">
         <x:v>平台代码未修改；发现一个百度云同步临时文件并保持不动</x:v>
       </x:c>
+      <x:c r="G24" s="446"/>
+      <x:c r="H24" s="446"/>
+      <x:c r="I24" s="446"/>
+      <x:c r="J24" s="446"/>
+      <x:c r="K24" s="446"/>
+      <x:c r="L24" s="446"/>
     </x:row>
     <x:row r="25" ht="40" customHeight="1">
-      <x:c r="A25" s="217" t="n">
+      <x:c r="A25" s="467" t="n">
         <x:v>46245</x:v>
       </x:c>
-      <x:c r="B25" s="216" t="str">
+      <x:c r="B25" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C25" s="216" t="str">
+      <x:c r="C25" s="446" t="str">
         <x:v>完成平台数据契约v1，确定四类数据、三层标识、状态映射和导入顺序</x:v>
       </x:c>
-      <x:c r="D25" s="216" t="str">
+      <x:c r="D25" s="446" t="str">
         <x:v>平台数据契约v1 / 导入包结构示例v1 / 项目看板</x:v>
       </x:c>
-      <x:c r="E25" s="216" t="str">
+      <x:c r="E25" s="446" t="str">
         <x:v>编写小型样例Excel转换程序</x:v>
       </x:c>
-      <x:c r="F25" s="216" t="str">
+      <x:c r="F25" s="446" t="str">
         <x:v>v1优先兼容现有数据库；不自动发布数据</x:v>
       </x:c>
+      <x:c r="G25" s="446"/>
+      <x:c r="H25" s="446"/>
+      <x:c r="I25" s="446"/>
+      <x:c r="J25" s="446"/>
+      <x:c r="K25" s="446"/>
+      <x:c r="L25" s="446"/>
     </x:row>
     <x:row r="26" ht="40" customHeight="1">
-      <x:c r="A26" s="217" t="n">
+      <x:c r="A26" s="467" t="n">
         <x:v>46245</x:v>
       </x:c>
-      <x:c r="B26" s="216" t="str">
+      <x:c r="B26" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C26" s="216" t="str">
+      <x:c r="C26" s="446" t="str">
         <x:v>完成Excel转换程序、首个真实导入包和校验报告</x:v>
       </x:c>
-      <x:c r="D26" s="216" t="str">
+      <x:c r="D26" s="446" t="str">
         <x:v>转换程序 / 平台导入包 / 项目看板</x:v>
       </x:c>
-      <x:c r="E26" s="216" t="str">
+      <x:c r="E26" s="446" t="str">
         <x:v>人工复核后在测试数据库首次导入</x:v>
       </x:c>
-      <x:c r="F26" s="216" t="str">
+      <x:c r="F26" s="446" t="str">
         <x:v>UUID稳定；0悬空关系；科普样例保持待审核</x:v>
       </x:c>
+      <x:c r="G26" s="446"/>
+      <x:c r="H26" s="446"/>
+      <x:c r="I26" s="446"/>
+      <x:c r="J26" s="446"/>
+      <x:c r="K26" s="446"/>
+      <x:c r="L26" s="446"/>
     </x:row>
     <x:row r="27" ht="40" customHeight="1">
-      <x:c r="A27" s="217" t="n">
+      <x:c r="A27" s="467" t="n">
         <x:v>46245</x:v>
       </x:c>
-      <x:c r="B27" s="216" t="str">
+      <x:c r="B27" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C27" s="216" t="str">
+      <x:c r="C27" s="446" t="str">
         <x:v>完成人工复核并形成问题清单</x:v>
       </x:c>
-      <x:c r="D27" s="216" t="str">
+      <x:c r="D27" s="446" t="str">
         <x:v>人工复核报告 / 复核问题JSON / 项目看板</x:v>
       </x:c>
-      <x:c r="E27" s="216" t="str">
+      <x:c r="E27" s="446" t="str">
         <x:v>修正7项问题后重新生成并复核</x:v>
       </x:c>
-      <x:c r="F27" s="216" t="str">
+      <x:c r="F27" s="446" t="str">
         <x:v>结构通过；人工复核退回；2项P0、5项P1</x:v>
       </x:c>
+      <x:c r="G27" s="446"/>
+      <x:c r="H27" s="446"/>
+      <x:c r="I27" s="446"/>
+      <x:c r="J27" s="446"/>
+      <x:c r="K27" s="446"/>
+      <x:c r="L27" s="446"/>
     </x:row>
     <x:row r="28" ht="40" customHeight="1">
-      <x:c r="A28" s="217" t="n">
+      <x:c r="A28" s="467" t="n">
         <x:v>46245</x:v>
       </x:c>
-      <x:c r="B28" s="216" t="str">
+      <x:c r="B28" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C28" s="216" t="str">
+      <x:c r="C28" s="446" t="str">
         <x:v>关闭7项人工复核问题并通过第二轮复核</x:v>
       </x:c>
-      <x:c r="D28" s="216" t="str">
+      <x:c r="D28" s="446" t="str">
         <x:v>小型样例v2 / 转换程序 / 数据契约 / 导入包 / 项目看板</x:v>
       </x:c>
-      <x:c r="E28" s="216" t="str">
+      <x:c r="E28" s="446" t="str">
         <x:v>在测试数据库执行首次导入</x:v>
       </x:c>
-      <x:c r="F28" s="216" t="str">
+      <x:c r="F28" s="446" t="str">
         <x:v>新增RoadNetwork；6条原文片段标记审核通过；0错误、0警告</x:v>
       </x:c>
+      <x:c r="G28" s="446"/>
+      <x:c r="H28" s="446"/>
+      <x:c r="I28" s="446"/>
+      <x:c r="J28" s="446"/>
+      <x:c r="K28" s="446"/>
+      <x:c r="L28" s="446"/>
     </x:row>
     <x:row r="29" ht="40" customHeight="1">
-      <x:c r="A29" s="217" t="n">
+      <x:c r="A29" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="B29" s="216" t="str">
+      <x:c r="B29" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C29" s="216" t="str">
+      <x:c r="C29" s="446" t="str">
         <x:v>修正TC-CHUNK-1102证据对象并完成补充复核</x:v>
       </x:c>
-      <x:c r="D29" s="216" t="str">
+      <x:c r="D29" s="446" t="str">
         <x:v>小型样例v3 / 导入包 / 人工复核报告v3 / 项目看板</x:v>
       </x:c>
-      <x:c r="E29" s="216" t="str">
+      <x:c r="E29" s="446" t="str">
         <x:v>在测试数据库执行首次导入</x:v>
       </x:c>
-      <x:c r="F29" s="216" t="str">
+      <x:c r="F29" s="446" t="str">
         <x:v>改连TC-LAYOUT-0005；0错误、0警告</x:v>
       </x:c>
+      <x:c r="G29" s="446"/>
+      <x:c r="H29" s="446"/>
+      <x:c r="I29" s="446"/>
+      <x:c r="J29" s="446"/>
+      <x:c r="K29" s="446"/>
+      <x:c r="L29" s="446"/>
     </x:row>
     <x:row r="30" ht="40" customHeight="1">
-      <x:c r="A30" s="217" t="n">
+      <x:c r="A30" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="B30" s="216" t="str">
+      <x:c r="B30" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C30" s="216" t="str">
+      <x:c r="C30" s="446" t="str">
         <x:v>完成隔离测试环境、首次导入和数据库/图谱/检索验收</x:v>
       </x:c>
-      <x:c r="D30" s="216" t="str">
+      <x:c r="D30" s="446" t="str">
         <x:v>测试数据库 / 兼容转换脚本 / 导入报告 / 项目看板</x:v>
       </x:c>
-      <x:c r="E30" s="216" t="str">
+      <x:c r="E30" s="446" t="str">
         <x:v>启动测试API与页面进行界面验收</x:v>
       </x:c>
-      <x:c r="F30" s="216" t="str">
+      <x:c r="F30" s="446" t="str">
         <x:v>重复导入幂等；未发布数据不进入公众搜索；青瓷库未变化</x:v>
       </x:c>
+      <x:c r="G30" s="446"/>
+      <x:c r="H30" s="446"/>
+      <x:c r="I30" s="446"/>
+      <x:c r="J30" s="446"/>
+      <x:c r="K30" s="446"/>
+      <x:c r="L30" s="446"/>
     </x:row>
     <x:row r="31" ht="40" customHeight="1">
-      <x:c r="A31" s="217" t="n">
+      <x:c r="A31" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="B31" s="216" t="str">
+      <x:c r="B31" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C31" s="216" t="str">
+      <x:c r="C31" s="446" t="str">
         <x:v>启动唐长安隔离测试平台并完成管理端页面验收</x:v>
       </x:c>
-      <x:c r="D31" s="216" t="str">
+      <x:c r="D31" s="446" t="str">
         <x:v>测试API / 测试网页 / 页面验收报告 / 项目看板</x:v>
       </x:c>
-      <x:c r="E31" s="216" t="str">
+      <x:c r="E31" s="446" t="str">
         <x:v>迁移前端品牌和首页数据逻辑</x:v>
       </x:c>
-      <x:c r="F31" s="216" t="str">
+      <x:c r="F31" s="446" t="str">
         <x:v>管理端数据正确；前台仍是青瓷主题；来源题名待去重判断</x:v>
       </x:c>
+      <x:c r="G31" s="446"/>
+      <x:c r="H31" s="446"/>
+      <x:c r="I31" s="446"/>
+      <x:c r="J31" s="446"/>
+      <x:c r="K31" s="446"/>
+      <x:c r="L31" s="446"/>
     </x:row>
     <x:row r="32" ht="40" customHeight="1">
-      <x:c r="A32" s="217" t="n">
+      <x:c r="A32" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="B32" s="216" t="str">
+      <x:c r="B32" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C32" s="216" t="str">
+      <x:c r="C32" s="446" t="str">
         <x:v>完成唐长安前端换壳、实时统计和公开数据安全验收</x:v>
       </x:c>
-      <x:c r="D32" s="216" t="str">
+      <x:c r="D32" s="446" t="str">
         <x:v>平台前端 / API / 验收报告 / 项目看板</x:v>
       </x:c>
-      <x:c r="E32" s="216" t="str">
+      <x:c r="E32" s="446" t="str">
         <x:v>选定并执行首次小型测试发布</x:v>
       </x:c>
-      <x:c r="F32" s="216" t="str">
+      <x:c r="F32" s="446" t="str">
         <x:v>48/32/6/29实时一致；7项测试通过；未发布数据未公开</x:v>
       </x:c>
+      <x:c r="G32" s="446"/>
+      <x:c r="H32" s="446"/>
+      <x:c r="I32" s="446"/>
+      <x:c r="J32" s="446"/>
+      <x:c r="K32" s="446"/>
+      <x:c r="L32" s="446"/>
     </x:row>
     <x:row r="33" ht="44" customHeight="1">
-      <x:c r="A33" s="217" t="n">
+      <x:c r="A33" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="B33" s="216" t="str">
+      <x:c r="B33" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C33" s="216" t="str">
+      <x:c r="C33" s="446" t="str">
         <x:v>完成选择性发布、依赖保护、公开图谱与检索同步及证据回溯验收</x:v>
       </x:c>
-      <x:c r="D33" s="216" t="str">
+      <x:c r="D33" s="446" t="str">
         <x:v>隔离测试平台 / 首次小型测试发布报告 / 项目看板</x:v>
       </x:c>
-      <x:c r="E33" s="216" t="str">
+      <x:c r="E33" s="446" t="str">
         <x:v>人工复核公众呈现并确定第二批发布范围</x:v>
       </x:c>
-      <x:c r="F33" s="216" t="str">
+      <x:c r="F33" s="446" t="str">
         <x:v>发布v1：2实体、1关系、1来源、2片段；4个检索文档；其余记录未变</x:v>
       </x:c>
+      <x:c r="G33" s="446"/>
+      <x:c r="H33" s="446"/>
+      <x:c r="I33" s="446"/>
+      <x:c r="J33" s="446"/>
+      <x:c r="K33" s="446"/>
+      <x:c r="L33" s="446"/>
     </x:row>
     <x:row r="34" ht="44" customHeight="1">
-      <x:c r="A34" s="217" t="n">
+      <x:c r="A34" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="B34" s="216" t="str">
+      <x:c r="B34" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="C34" s="216" t="str">
+      <x:c r="C34" s="446" t="str">
         <x:v>首次小型发布人工审核通过，图谱连接与公众呈现确认无误</x:v>
       </x:c>
-      <x:c r="D34" s="216" t="str">
+      <x:c r="D34" s="446" t="str">
         <x:v>公众检索 / 知识图谱 / 发布报告 / 项目看板</x:v>
       </x:c>
-      <x:c r="E34" s="216" t="str">
+      <x:c r="E34" s="446" t="str">
         <x:v>筛选第二批可发布的证据闭环</x:v>
       </x:c>
-      <x:c r="F34" s="216" t="str">
+      <x:c r="F34" s="446" t="str">
         <x:v>继续保持先审核、后发布；本次未新增公开记录</x:v>
       </x:c>
+      <x:c r="G34" s="446"/>
+      <x:c r="H34" s="446"/>
+      <x:c r="I34" s="446"/>
+      <x:c r="J34" s="446"/>
+      <x:c r="K34" s="446"/>
+      <x:c r="L34" s="446"/>
     </x:row>
     <x:row r="35" ht="44" customHeight="1">
-      <x:c r="A35" s="217" t="n">
+      <x:c r="A35" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="B35" s="216" t="str">
+      <x:c r="B35" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C35" s="216" t="str">
+      <x:c r="C35" s="446" t="str">
         <x:v>完成第二批4个候选闭环筛选与依赖核对</x:v>
       </x:c>
-      <x:c r="D35" s="216" t="str">
+      <x:c r="D35" s="446" t="str">
         <x:v>隔离测试数据库 / 第二批平台发布候选清单v1 / 项目看板</x:v>
       </x:c>
-      <x:c r="E35" s="216" t="str">
+      <x:c r="E35" s="446" t="str">
         <x:v>人工确认4个闭环后执行第二批发布</x:v>
       </x:c>
-      <x:c r="F35" s="216" t="str">
+      <x:c r="F35" s="446" t="str">
         <x:v>8实体、4关系、4片段；同一已公开来源；尚未新增公开记录</x:v>
       </x:c>
+      <x:c r="G35" s="446"/>
+      <x:c r="H35" s="446"/>
+      <x:c r="I35" s="446"/>
+      <x:c r="J35" s="446"/>
+      <x:c r="K35" s="446"/>
+      <x:c r="L35" s="446"/>
     </x:row>
     <x:row r="36" ht="44" customHeight="1">
-      <x:c r="A36" s="217" t="n">
+      <x:c r="A36" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="B36" s="216" t="str">
+      <x:c r="B36" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C36" s="216" t="str">
+      <x:c r="C36" s="446" t="str">
         <x:v>完成第二批4个坊内道路规则闭环发布与公众端验收</x:v>
       </x:c>
-      <x:c r="D36" s="216" t="str">
+      <x:c r="D36" s="446" t="str">
         <x:v>发布版本v2 / 公开图谱 / 检索索引 / 第二批平台发布报告v1</x:v>
       </x:c>
-      <x:c r="E36" s="216" t="str">
+      <x:c r="E36" s="446" t="str">
         <x:v>人工抽查后确定正式迁移优先级</x:v>
       </x:c>
-      <x:c r="F36" s="216" t="str">
+      <x:c r="F36" s="446" t="str">
         <x:v>8实体、4关系、4片段发布；索引摘要改为自然语言；其余数据未变</x:v>
       </x:c>
+      <x:c r="G36" s="446"/>
+      <x:c r="H36" s="446"/>
+      <x:c r="I36" s="446"/>
+      <x:c r="J36" s="446"/>
+      <x:c r="K36" s="446"/>
+      <x:c r="L36" s="446"/>
     </x:row>
     <x:row r="37" ht="44" customHeight="1">
-      <x:c r="A37" s="217" t="n">
+      <x:c r="A37" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="B37" s="216" t="str">
+      <x:c r="B37" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C37" s="216" t="str">
+      <x:c r="C37" s="446" t="str">
         <x:v>同步小型样例的实体表与关系表</x:v>
       </x:c>
-      <x:c r="D37" s="216" t="str">
+      <x:c r="D37" s="446" t="str">
         <x:v>小型样例v4 / 转换程序</x:v>
       </x:c>
-      <x:c r="E37" s="216" t="str">
+      <x:c r="E37" s="446" t="str">
         <x:v>人工抽查v4新增记录</x:v>
       </x:c>
-      <x:c r="F37" s="216" t="str">
+      <x:c r="F37" s="446" t="str">
         <x:v>补写25实体、22关系；转换验证为48实体、32关系、0错误、0警告</x:v>
       </x:c>
+      <x:c r="G37" s="446"/>
+      <x:c r="H37" s="446"/>
+      <x:c r="I37" s="446"/>
+      <x:c r="J37" s="446"/>
+      <x:c r="K37" s="446"/>
+      <x:c r="L37" s="446"/>
     </x:row>
     <x:row r="38" ht="44" customHeight="1">
-      <x:c r="A38" s="217" t="n">
+      <x:c r="A38" s="467" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="B38" s="216" t="str">
+      <x:c r="B38" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C38" s="216" t="str">
+      <x:c r="C38" s="446" t="str">
         <x:v>完成专题关系反向审计、补写与转换程序修正</x:v>
       </x:c>
-      <x:c r="D38" s="216" t="str">
+      <x:c r="D38" s="446" t="str">
         <x:v>小型样例v5 / 转换程序 / 校验报告</x:v>
       </x:c>
-      <x:c r="E38" s="216" t="str">
+      <x:c r="E38" s="446" t="str">
         <x:v>人工抽查11条新增关系</x:v>
       </x:c>
-      <x:c r="F38" s="216" t="str">
+      <x:c r="F38" s="446" t="str">
         <x:v>补写11关系；48实体、43关系；0错误；11条不完整记录阻断警告</x:v>
       </x:c>
+      <x:c r="G38" s="446"/>
+      <x:c r="H38" s="446"/>
+      <x:c r="I38" s="446"/>
+      <x:c r="J38" s="446"/>
+      <x:c r="K38" s="446"/>
+      <x:c r="L38" s="446"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" t="str">
+      <x:c r="A39" s="446" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="B39" t="str">
+      <x:c r="B39" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="C39" t="str">
+      <x:c r="C39" s="446" t="str">
         <x:v>审核通过11条专题关系，完成第三批空间基础事实发布、索引同步与网页验收</x:v>
       </x:c>
-      <x:c r="D39" t="str">
+      <x:c r="D39" s="446" t="str">
         <x:v>小型样例v6 / 平台导入包v2 / 发布版本v3 / 网页验收报告v1 / 项目看板</x:v>
       </x:c>
-      <x:c r="E39" t="str">
+      <x:c r="E39" s="446" t="str">
         <x:v>补齐3项P0结构数据后升级提取Skill并进入正式全量迁移</x:v>
       </x:c>
-      <x:c r="F39" t="str">
+      <x:c r="F39" s="446" t="str">
         <x:v>公开21实体、16关系、2来源、12片段；搜索索引33文档；工作清单已按任务编号重排</x:v>
       </x:c>
+      <x:c r="G39" s="446"/>
+      <x:c r="H39" s="446"/>
+      <x:c r="I39" s="446"/>
+      <x:c r="J39" s="446"/>
+      <x:c r="K39" s="446"/>
+      <x:c r="L39" s="446"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" t="str">
+      <x:c r="A40" s="446" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="B40" t="str">
+      <x:c r="B40" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C40" t="str">
+      <x:c r="C40" s="446" t="str">
         <x:v>补齐正式迁移前3项P0结构缺口，并发现、修正平康坊空间方向错误</x:v>
       </x:c>
-      <x:c r="D40" t="str">
+      <x:c r="D40" s="446" t="str">
         <x:v>小型样例v7 / 平台导入包v3 / P0结构补全说明v1 / 项目看板</x:v>
       </x:c>
-      <x:c r="E40" t="str">
+      <x:c r="E40" s="446" t="str">
         <x:v>人工审核外郭城归属、永安渠六坊和两坊空间关系；通过后升级提取Skill</x:v>
       </x:c>
-      <x:c r="F40" t="str">
+      <x:c r="F40" s="446" t="str">
         <x:v>新增9实体、14关系、1来源、2片段；57实体/62关系；0错误、0警告；未导入平台</x:v>
       </x:c>
+      <x:c r="G40" s="446"/>
+      <x:c r="H40" s="446"/>
+      <x:c r="I40" s="446"/>
+      <x:c r="J40" s="446"/>
+      <x:c r="K40" s="446"/>
+      <x:c r="L40" s="446"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" t="str">
+      <x:c r="A41" s="446" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="B41" t="str">
+      <x:c r="B41" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="C41" t="str">
+      <x:c r="C41" s="446" t="str">
         <x:v>核对ROAD-0004/0009与坊功能area，修正x=±3坊列为第二街与第三街之间，并补齐双边界关系</x:v>
       </x:c>
-      <x:c r="D41" t="str">
+      <x:c r="D41" s="446" t="str">
         <x:v>小型样例v8 / 平台导入包v4 / P0结构补全说明v1 / 项目看板</x:v>
       </x:c>
-      <x:c r="E41" t="str">
+      <x:c r="E41" s="446" t="str">
         <x:v>只需人工复核本轮area和边界关系；通过后执行平台导入并升级提取Skill</x:v>
       </x:c>
-      <x:c r="F41" t="str">
+      <x:c r="F41" s="446" t="str">
         <x:v>新增2道路实体、14坊—道路关系、1解释片段；59实体/77关系；0错误、0警告；未导入平台</x:v>
       </x:c>
+      <x:c r="G41" s="446"/>
+      <x:c r="H41" s="446"/>
+      <x:c r="I41" s="446"/>
+      <x:c r="J41" s="446"/>
+      <x:c r="K41" s="446"/>
+      <x:c r="L41" s="446"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" t="str">
+      <x:c r="A42" s="446" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="B42" t="str">
+      <x:c r="B42" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="C42" t="str">
+      <x:c r="C42" s="446" t="str">
         <x:v>审核通过P0修正，完成第四批白名单导入、选择性发布、检索索引和网页图谱验收</x:v>
       </x:c>
-      <x:c r="D42" t="str">
+      <x:c r="D42" s="446" t="str">
         <x:v>小型样例v9 / 平台导入包v5 / 发布版本v4 / 第四批平台发布与网页验收报告v1 / 项目看板</x:v>
       </x:c>
-      <x:c r="E42" t="str">
+      <x:c r="E42" s="446" t="str">
         <x:v>升级knowledge-graph-extraction Skill，并用v9执行回归测试</x:v>
       </x:c>
-      <x:c r="F42" t="str">
+      <x:c r="F42" s="446" t="str">
         <x:v>总库59实体/77关系/7来源/32片段；公开39实体/50关系/4来源/19片段；结构0错误、0警告</x:v>
       </x:c>
+      <x:c r="G42" s="446"/>
+      <x:c r="H42" s="446"/>
+      <x:c r="I42" s="446"/>
+      <x:c r="J42" s="446"/>
+      <x:c r="K42" s="446"/>
+      <x:c r="L42" s="446"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" t="str">
+      <x:c r="A43" s="446" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="B43" t="str">
+      <x:c r="B43" s="446" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="C43" t="str">
+      <x:c r="C43" s="446" t="str">
         <x:v>升级并打包knowledge-graph-extraction v2，完成v9规则回归检查</x:v>
       </x:c>
-      <x:c r="D43" t="str">
+      <x:c r="D43" s="446" t="str">
         <x:v>06-Skill/knowledge-graph-extraction / knowledge-graph-extraction-v2.skill / 项目看板</x:v>
       </x:c>
-      <x:c r="E43" t="str">
+      <x:c r="E43" s="446" t="str">
         <x:v>进入阶段七全量提取，按团队分工选择下一批资料</x:v>
       </x:c>
-      <x:c r="F43" t="str">
+      <x:c r="F43" s="446" t="str">
         <x:v>固化专题表转换、三层知识、双边界道路、证据依赖、审核白名单和网页验收规则</x:v>
       </x:c>
+      <x:c r="G43" s="446"/>
+      <x:c r="H43" s="446"/>
+      <x:c r="I43" s="446"/>
+      <x:c r="J43" s="446"/>
+      <x:c r="K43" s="446"/>
+      <x:c r="L43" s="446"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" t="str">
+      <x:c r="A44" s="446" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="B44" t="str">
+      <x:c r="B44" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="C44" t="str">
+      <x:c r="C44" s="446" t="str">
         <x:v>补发RoadNetwork实体及8条研究结论关系，完成公众图谱验收</x:v>
       </x:c>
-      <x:c r="D44" t="str">
+      <x:c r="D44" s="446" t="str">
         <x:v>小型样例v10 / 平台导入包v6 / 发布版本v5 / 第五批发布报告v1</x:v>
       </x:c>
-      <x:c r="E44" t="str">
+      <x:c r="E44" s="446" t="str">
         <x:v>人工查看RoadNetwork图谱后进入全量提取</x:v>
       </x:c>
-      <x:c r="F44" t="str">
+      <x:c r="F44" s="446" t="str">
         <x:v>公开48实体/58关系/6来源/27片段；RoadNetwork为9节点/8关系；科普候选仍未审核</x:v>
       </x:c>
+      <x:c r="G44" s="446"/>
+      <x:c r="H44" s="446"/>
+      <x:c r="I44" s="446"/>
+      <x:c r="J44" s="446"/>
+      <x:c r="K44" s="446"/>
+      <x:c r="L44" s="446"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" t="str">
+      <x:c r="A45" s="446" t="str">
         <x:v>2026-08-12</x:v>
       </x:c>
-      <x:c r="B45" t="str">
+      <x:c r="B45" s="446" t="str">
         <x:v>用户 / Codex</x:v>
       </x:c>
-      <x:c r="C45" t="str">
+      <x:c r="C45" s="446" t="str">
         <x:v>修复第四个“空间知识检索”按钮不可用及搜索页状态不同步问题，并完成生产构建与网页验收</x:v>
       </x:c>
-      <x:c r="D45" t="str">
+      <x:c r="D45" s="446" t="str">
         <x:v>唐长安测试平台前端 / 项目看板</x:v>
       </x:c>
-      <x:c r="E45" t="str">
+      <x:c r="E45" s="446" t="str">
         <x:v>确认平台呈现后进入阶段七全量提取</x:v>
       </x:c>
-      <x:c r="F45" t="str">
+      <x:c r="F45" s="446" t="str">
         <x:v>第四按钮现进入?q=长安；第五按钮仍为SourceChunk证据检索；数据库未改动</x:v>
       </x:c>
+      <x:c r="G45" s="446"/>
+      <x:c r="H45" s="446"/>
+      <x:c r="I45" s="446"/>
+      <x:c r="J45" s="446"/>
+      <x:c r="K45" s="446"/>
+      <x:c r="L45" s="446"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="446" t="str">
@@ -5876,6 +10583,12 @@
       <x:c r="F46" s="446" t="str">
         <x:v>包内含正式模板、v10稳定样例、协作登记模板；个人批次不得直接发布</x:v>
       </x:c>
+      <x:c r="G46" s="446"/>
+      <x:c r="H46" s="446"/>
+      <x:c r="I46" s="446"/>
+      <x:c r="J46" s="446"/>
+      <x:c r="K46" s="446"/>
+      <x:c r="L46" s="446"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="446" t="str">
@@ -5896,6 +10609,12 @@
       <x:c r="F47" s="446" t="str">
         <x:v>133项均为待补字段；仅锁定公共编号，不进入正式实体表或自动审核</x:v>
       </x:c>
+      <x:c r="G47" s="446"/>
+      <x:c r="H47" s="446"/>
+      <x:c r="I47" s="446"/>
+      <x:c r="J47" s="446"/>
+      <x:c r="K47" s="446"/>
+      <x:c r="L47" s="446"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="446" t="str">
@@ -5916,6 +10635,12 @@
       <x:c r="F48" s="446" t="str">
         <x:v>成员A使用2000段、成员B使用3000段；公共坊/道路复用原编号；自动关系不人工分配</x:v>
       </x:c>
+      <x:c r="G48" s="446"/>
+      <x:c r="H48" s="446"/>
+      <x:c r="I48" s="446"/>
+      <x:c r="J48" s="446"/>
+      <x:c r="K48" s="446"/>
+      <x:c r="L48" s="446"/>
     </x:row>
     <x:row r="49" ht="44" customHeight="1">
       <x:c r="A49" s="467" t="str">
@@ -5936,6 +10661,12 @@
       <x:c r="F49" s="446" t="str">
         <x:v>协作登记表现有176个公共对象；新增43项均为待补字段，功能规则仅锁定编号和名称</x:v>
       </x:c>
+      <x:c r="G49" s="446"/>
+      <x:c r="H49" s="446"/>
+      <x:c r="I49" s="446"/>
+      <x:c r="J49" s="446"/>
+      <x:c r="K49" s="446"/>
+      <x:c r="L49" s="446"/>
     </x:row>
     <x:row r="50" ht="44" customHeight="1">
       <x:c r="A50" s="467" t="str">
@@ -5956,6 +10687,12 @@
       <x:c r="F50" s="446" t="str">
         <x:v>公共对象仍为176个；新增C来源0400段、片段/关系4000段、新实体4000—4499</x:v>
       </x:c>
+      <x:c r="G50" s="446"/>
+      <x:c r="H50" s="446"/>
+      <x:c r="I50" s="446"/>
+      <x:c r="J50" s="446"/>
+      <x:c r="K50" s="446"/>
+      <x:c r="L50" s="446"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="446" t="str">
@@ -5976,6 +10713,12 @@
       <x:c r="F51" s="446" t="str">
         <x:v>覆盖宫城至三苑；574实体、886关系、50片段；保留异文候选及位置不详对象，统一关系类型代码</x:v>
       </x:c>
+      <x:c r="G51" s="446"/>
+      <x:c r="H51" s="446"/>
+      <x:c r="I51" s="446"/>
+      <x:c r="J51" s="446"/>
+      <x:c r="K51" s="446"/>
+      <x:c r="L51" s="446"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="446" t="str">
@@ -5996,6 +10739,12 @@
       <x:c r="F52" s="446" t="str">
         <x:v>沿用当前协作登记表编号；不采用早期小型样例中的冲突城门编号</x:v>
       </x:c>
+      <x:c r="G52" s="446"/>
+      <x:c r="H52" s="446"/>
+      <x:c r="I52" s="446"/>
+      <x:c r="J52" s="446"/>
+      <x:c r="K52" s="446"/>
+      <x:c r="L52" s="446"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="446" t="str">
@@ -6016,6 +10765,12 @@
       <x:c r="F53" s="446" t="str">
         <x:v>复用TC-FANG-0045—0053；新增49处设施；保留两项待扫描版核名记录</x:v>
       </x:c>
+      <x:c r="G53" s="446"/>
+      <x:c r="H53" s="446"/>
+      <x:c r="I53" s="446"/>
+      <x:c r="J53" s="446"/>
+      <x:c r="K53" s="446"/>
+      <x:c r="L53" s="446"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="446" t="str">
@@ -6036,46 +10791,2092 @@
       <x:c r="F54" s="446" t="str">
         <x:v>已移除包内v3.1 Skill和旧v1手册；5个Excel公式错误扫描均为0，Word三页版式检查通过</x:v>
       </x:c>
+      <x:c r="G54" s="446"/>
+      <x:c r="H54" s="446"/>
+      <x:c r="I54" s="446"/>
+      <x:c r="J54" s="446"/>
+      <x:c r="K54" s="446"/>
+      <x:c r="L54" s="446"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" t="str">
+      <x:c r="A55" s="446" t="str">
         <x:v>2026-08-16</x:v>
       </x:c>
-      <x:c r="B55" t="str">
+      <x:c r="B55" s="446" t="str">
         <x:v>成员A / Codex</x:v>
       </x:c>
-      <x:c r="C55" t="str">
+      <x:c r="C55" s="446" t="str">
         <x:v>启动卷三并完成翊善—光宅、永昌—来庭首批提取</x:v>
       </x:c>
-      <x:c r="D55" t="str">
+      <x:c r="D55" s="446" t="str">
         <x:v>卷三工作簿 / 协作登记表 / 项目看板</x:v>
       </x:c>
-      <x:c r="E55" t="str">
+      <x:c r="E55" s="446" t="str">
         <x:v>继续东第三街后续各坊</x:v>
       </x:c>
-      <x:c r="F55" t="str">
+      <x:c r="F55" s="446" t="str">
         <x:v>四段原文独立保留；实体层复用两个稳定坊编号；新增20处设施</x:v>
       </x:c>
+      <x:c r="G55" s="446"/>
+      <x:c r="H55" s="446"/>
+      <x:c r="I55" s="446"/>
+      <x:c r="J55" s="446"/>
+      <x:c r="K55" s="446"/>
+      <x:c r="L55" s="446"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" t="str">
+      <x:c r="A56" s="446" t="str">
         <x:v>2026-08-16</x:v>
       </x:c>
-      <x:c r="B56" t="str">
+      <x:c r="B56" s="446" t="str">
         <x:v>成员A / Codex</x:v>
       </x:c>
-      <x:c r="C56" t="str">
+      <x:c r="C56" s="446" t="str">
         <x:v>完成《唐两京城坊考》卷三全卷提取、自主审核与图谱转换</x:v>
       </x:c>
-      <x:c r="D56" t="str">
+      <x:c r="D56" s="446" t="str">
         <x:v>卷三工作簿 / 协作登记表 / 项目看板</x:v>
       </x:c>
-      <x:c r="E56" t="str">
+      <x:c r="E56" s="446" t="str">
         <x:v>卷一至卷三联合导入与网页验收</x:v>
       </x:c>
-      <x:c r="F56" t="str">
+      <x:c r="F56" s="446" t="str">
         <x:v>完成道路编号纠错；东市、曲江、芙蓉园新增Area实体；建筑编号用至TC-BUILDING-2943</x:v>
       </x:c>
+      <x:c r="G56" s="446"/>
+      <x:c r="H56" s="446"/>
+      <x:c r="I56" s="446"/>
+      <x:c r="J56" s="446"/>
+      <x:c r="K56" s="446"/>
+      <x:c r="L56" s="446"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="446" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="B57" s="446" t="str">
+        <x:v>成员A / Codex</x:v>
+      </x:c>
+      <x:c r="C57" s="446" t="str">
+        <x:v>完成卷一至卷三联合导入、平台备份与网页验收</x:v>
+      </x:c>
+      <x:c r="D57" s="446" t="str">
+        <x:v>联合导入包 / 协作登记表 / 项目看板</x:v>
+      </x:c>
+      <x:c r="E57" s="446" t="str">
+        <x:v>开始卷四；卷五洛阳暂不录</x:v>
+      </x:c>
+      <x:c r="F57" s="446" t="str">
+        <x:v>联合包去重后1212实体、1576关系、112片段；平台抽查永兴坊、曲江和来源关系正常；A建筑编号扩展至5000段</x:v>
+      </x:c>
+      <x:c r="G57" s="446"/>
+      <x:c r="H57" s="446"/>
+      <x:c r="I57" s="446"/>
+      <x:c r="J57" s="446"/>
+      <x:c r="K57" s="446"/>
+      <x:c r="L57" s="446"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="446"/>
+      <x:c r="B58" s="446"/>
+      <x:c r="C58" s="446"/>
+      <x:c r="D58" s="446"/>
+      <x:c r="E58" s="446"/>
+      <x:c r="F58" s="446"/>
+      <x:c r="G58" s="446"/>
+      <x:c r="H58" s="446"/>
+      <x:c r="I58" s="446"/>
+      <x:c r="J58" s="446"/>
+      <x:c r="K58" s="446"/>
+      <x:c r="L58" s="446"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="446"/>
+      <x:c r="B59" s="446"/>
+      <x:c r="C59" s="446"/>
+      <x:c r="D59" s="446"/>
+      <x:c r="E59" s="446"/>
+      <x:c r="F59" s="446"/>
+      <x:c r="G59" s="446"/>
+      <x:c r="H59" s="446"/>
+      <x:c r="I59" s="446"/>
+      <x:c r="J59" s="446"/>
+      <x:c r="K59" s="446"/>
+      <x:c r="L59" s="446"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="446"/>
+      <x:c r="B60" s="446"/>
+      <x:c r="C60" s="446"/>
+      <x:c r="D60" s="446"/>
+      <x:c r="E60" s="446"/>
+      <x:c r="F60" s="446"/>
+      <x:c r="G60" s="446"/>
+      <x:c r="H60" s="446"/>
+      <x:c r="I60" s="446"/>
+      <x:c r="J60" s="446"/>
+      <x:c r="K60" s="446"/>
+      <x:c r="L60" s="446"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="446"/>
+      <x:c r="B61" s="446"/>
+      <x:c r="C61" s="446"/>
+      <x:c r="D61" s="446"/>
+      <x:c r="E61" s="446"/>
+      <x:c r="F61" s="446"/>
+      <x:c r="G61" s="446"/>
+      <x:c r="H61" s="446"/>
+      <x:c r="I61" s="446"/>
+      <x:c r="J61" s="446"/>
+      <x:c r="K61" s="446"/>
+      <x:c r="L61" s="446"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="446"/>
+      <x:c r="B62" s="446"/>
+      <x:c r="C62" s="446"/>
+      <x:c r="D62" s="446"/>
+      <x:c r="E62" s="446"/>
+      <x:c r="F62" s="446"/>
+      <x:c r="G62" s="446"/>
+      <x:c r="H62" s="446"/>
+      <x:c r="I62" s="446"/>
+      <x:c r="J62" s="446"/>
+      <x:c r="K62" s="446"/>
+      <x:c r="L62" s="446"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="446"/>
+      <x:c r="B63" s="446"/>
+      <x:c r="C63" s="446"/>
+      <x:c r="D63" s="446"/>
+      <x:c r="E63" s="446"/>
+      <x:c r="F63" s="446"/>
+      <x:c r="G63" s="446"/>
+      <x:c r="H63" s="446"/>
+      <x:c r="I63" s="446"/>
+      <x:c r="J63" s="446"/>
+      <x:c r="K63" s="446"/>
+      <x:c r="L63" s="446"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="446"/>
+      <x:c r="B64" s="446"/>
+      <x:c r="C64" s="446"/>
+      <x:c r="D64" s="446"/>
+      <x:c r="E64" s="446"/>
+      <x:c r="F64" s="446"/>
+      <x:c r="G64" s="446"/>
+      <x:c r="H64" s="446"/>
+      <x:c r="I64" s="446"/>
+      <x:c r="J64" s="446"/>
+      <x:c r="K64" s="446"/>
+      <x:c r="L64" s="446"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="446"/>
+      <x:c r="B65" s="446"/>
+      <x:c r="C65" s="446"/>
+      <x:c r="D65" s="446"/>
+      <x:c r="E65" s="446"/>
+      <x:c r="F65" s="446"/>
+      <x:c r="G65" s="446"/>
+      <x:c r="H65" s="446"/>
+      <x:c r="I65" s="446"/>
+      <x:c r="J65" s="446"/>
+      <x:c r="K65" s="446"/>
+      <x:c r="L65" s="446"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="446"/>
+      <x:c r="B66" s="446"/>
+      <x:c r="C66" s="446"/>
+      <x:c r="D66" s="446"/>
+      <x:c r="E66" s="446"/>
+      <x:c r="F66" s="446"/>
+      <x:c r="G66" s="446"/>
+      <x:c r="H66" s="446"/>
+      <x:c r="I66" s="446"/>
+      <x:c r="J66" s="446"/>
+      <x:c r="K66" s="446"/>
+      <x:c r="L66" s="446"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="446"/>
+      <x:c r="B67" s="446"/>
+      <x:c r="C67" s="446"/>
+      <x:c r="D67" s="446"/>
+      <x:c r="E67" s="446"/>
+      <x:c r="F67" s="446"/>
+      <x:c r="G67" s="446"/>
+      <x:c r="H67" s="446"/>
+      <x:c r="I67" s="446"/>
+      <x:c r="J67" s="446"/>
+      <x:c r="K67" s="446"/>
+      <x:c r="L67" s="446"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="446"/>
+      <x:c r="B68" s="446"/>
+      <x:c r="C68" s="446"/>
+      <x:c r="D68" s="446"/>
+      <x:c r="E68" s="446"/>
+      <x:c r="F68" s="446"/>
+      <x:c r="G68" s="446"/>
+      <x:c r="H68" s="446"/>
+      <x:c r="I68" s="446"/>
+      <x:c r="J68" s="446"/>
+      <x:c r="K68" s="446"/>
+      <x:c r="L68" s="446"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="446"/>
+      <x:c r="B69" s="446"/>
+      <x:c r="C69" s="446"/>
+      <x:c r="D69" s="446"/>
+      <x:c r="E69" s="446"/>
+      <x:c r="F69" s="446"/>
+      <x:c r="G69" s="446"/>
+      <x:c r="H69" s="446"/>
+      <x:c r="I69" s="446"/>
+      <x:c r="J69" s="446"/>
+      <x:c r="K69" s="446"/>
+      <x:c r="L69" s="446"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="446"/>
+      <x:c r="B70" s="446"/>
+      <x:c r="C70" s="446"/>
+      <x:c r="D70" s="446"/>
+      <x:c r="E70" s="446"/>
+      <x:c r="F70" s="446"/>
+      <x:c r="G70" s="446"/>
+      <x:c r="H70" s="446"/>
+      <x:c r="I70" s="446"/>
+      <x:c r="J70" s="446"/>
+      <x:c r="K70" s="446"/>
+      <x:c r="L70" s="446"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="446"/>
+      <x:c r="B71" s="446"/>
+      <x:c r="C71" s="446"/>
+      <x:c r="D71" s="446"/>
+      <x:c r="E71" s="446"/>
+      <x:c r="F71" s="446"/>
+      <x:c r="G71" s="446"/>
+      <x:c r="H71" s="446"/>
+      <x:c r="I71" s="446"/>
+      <x:c r="J71" s="446"/>
+      <x:c r="K71" s="446"/>
+      <x:c r="L71" s="446"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="446"/>
+      <x:c r="B72" s="446"/>
+      <x:c r="C72" s="446"/>
+      <x:c r="D72" s="446"/>
+      <x:c r="E72" s="446"/>
+      <x:c r="F72" s="446"/>
+      <x:c r="G72" s="446"/>
+      <x:c r="H72" s="446"/>
+      <x:c r="I72" s="446"/>
+      <x:c r="J72" s="446"/>
+      <x:c r="K72" s="446"/>
+      <x:c r="L72" s="446"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="446"/>
+      <x:c r="B73" s="446"/>
+      <x:c r="C73" s="446"/>
+      <x:c r="D73" s="446"/>
+      <x:c r="E73" s="446"/>
+      <x:c r="F73" s="446"/>
+      <x:c r="G73" s="446"/>
+      <x:c r="H73" s="446"/>
+      <x:c r="I73" s="446"/>
+      <x:c r="J73" s="446"/>
+      <x:c r="K73" s="446"/>
+      <x:c r="L73" s="446"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="446"/>
+      <x:c r="B74" s="446"/>
+      <x:c r="C74" s="446"/>
+      <x:c r="D74" s="446"/>
+      <x:c r="E74" s="446"/>
+      <x:c r="F74" s="446"/>
+      <x:c r="G74" s="446"/>
+      <x:c r="H74" s="446"/>
+      <x:c r="I74" s="446"/>
+      <x:c r="J74" s="446"/>
+      <x:c r="K74" s="446"/>
+      <x:c r="L74" s="446"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="446"/>
+      <x:c r="B75" s="446"/>
+      <x:c r="C75" s="446"/>
+      <x:c r="D75" s="446"/>
+      <x:c r="E75" s="446"/>
+      <x:c r="F75" s="446"/>
+      <x:c r="G75" s="446"/>
+      <x:c r="H75" s="446"/>
+      <x:c r="I75" s="446"/>
+      <x:c r="J75" s="446"/>
+      <x:c r="K75" s="446"/>
+      <x:c r="L75" s="446"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="446"/>
+      <x:c r="B76" s="446"/>
+      <x:c r="C76" s="446"/>
+      <x:c r="D76" s="446"/>
+      <x:c r="E76" s="446"/>
+      <x:c r="F76" s="446"/>
+      <x:c r="G76" s="446"/>
+      <x:c r="H76" s="446"/>
+      <x:c r="I76" s="446"/>
+      <x:c r="J76" s="446"/>
+      <x:c r="K76" s="446"/>
+      <x:c r="L76" s="446"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="446"/>
+      <x:c r="B77" s="446"/>
+      <x:c r="C77" s="446"/>
+      <x:c r="D77" s="446"/>
+      <x:c r="E77" s="446"/>
+      <x:c r="F77" s="446"/>
+      <x:c r="G77" s="446"/>
+      <x:c r="H77" s="446"/>
+      <x:c r="I77" s="446"/>
+      <x:c r="J77" s="446"/>
+      <x:c r="K77" s="446"/>
+      <x:c r="L77" s="446"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="446"/>
+      <x:c r="B78" s="446"/>
+      <x:c r="C78" s="446"/>
+      <x:c r="D78" s="446"/>
+      <x:c r="E78" s="446"/>
+      <x:c r="F78" s="446"/>
+      <x:c r="G78" s="446"/>
+      <x:c r="H78" s="446"/>
+      <x:c r="I78" s="446"/>
+      <x:c r="J78" s="446"/>
+      <x:c r="K78" s="446"/>
+      <x:c r="L78" s="446"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="446"/>
+      <x:c r="B79" s="446"/>
+      <x:c r="C79" s="446"/>
+      <x:c r="D79" s="446"/>
+      <x:c r="E79" s="446"/>
+      <x:c r="F79" s="446"/>
+      <x:c r="G79" s="446"/>
+      <x:c r="H79" s="446"/>
+      <x:c r="I79" s="446"/>
+      <x:c r="J79" s="446"/>
+      <x:c r="K79" s="446"/>
+      <x:c r="L79" s="446"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="446"/>
+      <x:c r="B80" s="446"/>
+      <x:c r="C80" s="446"/>
+      <x:c r="D80" s="446"/>
+      <x:c r="E80" s="446"/>
+      <x:c r="F80" s="446"/>
+      <x:c r="G80" s="446"/>
+      <x:c r="H80" s="446"/>
+      <x:c r="I80" s="446"/>
+      <x:c r="J80" s="446"/>
+      <x:c r="K80" s="446"/>
+      <x:c r="L80" s="446"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="446"/>
+      <x:c r="B81" s="446"/>
+      <x:c r="C81" s="446"/>
+      <x:c r="D81" s="446"/>
+      <x:c r="E81" s="446"/>
+      <x:c r="F81" s="446"/>
+      <x:c r="G81" s="446"/>
+      <x:c r="H81" s="446"/>
+      <x:c r="I81" s="446"/>
+      <x:c r="J81" s="446"/>
+      <x:c r="K81" s="446"/>
+      <x:c r="L81" s="446"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="446"/>
+      <x:c r="B82" s="446"/>
+      <x:c r="C82" s="446"/>
+      <x:c r="D82" s="446"/>
+      <x:c r="E82" s="446"/>
+      <x:c r="F82" s="446"/>
+      <x:c r="G82" s="446"/>
+      <x:c r="H82" s="446"/>
+      <x:c r="I82" s="446"/>
+      <x:c r="J82" s="446"/>
+      <x:c r="K82" s="446"/>
+      <x:c r="L82" s="446"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="446"/>
+      <x:c r="B83" s="446"/>
+      <x:c r="C83" s="446"/>
+      <x:c r="D83" s="446"/>
+      <x:c r="E83" s="446"/>
+      <x:c r="F83" s="446"/>
+      <x:c r="G83" s="446"/>
+      <x:c r="H83" s="446"/>
+      <x:c r="I83" s="446"/>
+      <x:c r="J83" s="446"/>
+      <x:c r="K83" s="446"/>
+      <x:c r="L83" s="446"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="446"/>
+      <x:c r="B84" s="446"/>
+      <x:c r="C84" s="446"/>
+      <x:c r="D84" s="446"/>
+      <x:c r="E84" s="446"/>
+      <x:c r="F84" s="446"/>
+      <x:c r="G84" s="446"/>
+      <x:c r="H84" s="446"/>
+      <x:c r="I84" s="446"/>
+      <x:c r="J84" s="446"/>
+      <x:c r="K84" s="446"/>
+      <x:c r="L84" s="446"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="446"/>
+      <x:c r="B85" s="446"/>
+      <x:c r="C85" s="446"/>
+      <x:c r="D85" s="446"/>
+      <x:c r="E85" s="446"/>
+      <x:c r="F85" s="446"/>
+      <x:c r="G85" s="446"/>
+      <x:c r="H85" s="446"/>
+      <x:c r="I85" s="446"/>
+      <x:c r="J85" s="446"/>
+      <x:c r="K85" s="446"/>
+      <x:c r="L85" s="446"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="446"/>
+      <x:c r="B86" s="446"/>
+      <x:c r="C86" s="446"/>
+      <x:c r="D86" s="446"/>
+      <x:c r="E86" s="446"/>
+      <x:c r="F86" s="446"/>
+      <x:c r="G86" s="446"/>
+      <x:c r="H86" s="446"/>
+      <x:c r="I86" s="446"/>
+      <x:c r="J86" s="446"/>
+      <x:c r="K86" s="446"/>
+      <x:c r="L86" s="446"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="446"/>
+      <x:c r="B87" s="446"/>
+      <x:c r="C87" s="446"/>
+      <x:c r="D87" s="446"/>
+      <x:c r="E87" s="446"/>
+      <x:c r="F87" s="446"/>
+      <x:c r="G87" s="446"/>
+      <x:c r="H87" s="446"/>
+      <x:c r="I87" s="446"/>
+      <x:c r="J87" s="446"/>
+      <x:c r="K87" s="446"/>
+      <x:c r="L87" s="446"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="446"/>
+      <x:c r="B88" s="446"/>
+      <x:c r="C88" s="446"/>
+      <x:c r="D88" s="446"/>
+      <x:c r="E88" s="446"/>
+      <x:c r="F88" s="446"/>
+      <x:c r="G88" s="446"/>
+      <x:c r="H88" s="446"/>
+      <x:c r="I88" s="446"/>
+      <x:c r="J88" s="446"/>
+      <x:c r="K88" s="446"/>
+      <x:c r="L88" s="446"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="446"/>
+      <x:c r="B89" s="446"/>
+      <x:c r="C89" s="446"/>
+      <x:c r="D89" s="446"/>
+      <x:c r="E89" s="446"/>
+      <x:c r="F89" s="446"/>
+      <x:c r="G89" s="446"/>
+      <x:c r="H89" s="446"/>
+      <x:c r="I89" s="446"/>
+      <x:c r="J89" s="446"/>
+      <x:c r="K89" s="446"/>
+      <x:c r="L89" s="446"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="446"/>
+      <x:c r="B90" s="446"/>
+      <x:c r="C90" s="446"/>
+      <x:c r="D90" s="446"/>
+      <x:c r="E90" s="446"/>
+      <x:c r="F90" s="446"/>
+      <x:c r="G90" s="446"/>
+      <x:c r="H90" s="446"/>
+      <x:c r="I90" s="446"/>
+      <x:c r="J90" s="446"/>
+      <x:c r="K90" s="446"/>
+      <x:c r="L90" s="446"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="446"/>
+      <x:c r="B91" s="446"/>
+      <x:c r="C91" s="446"/>
+      <x:c r="D91" s="446"/>
+      <x:c r="E91" s="446"/>
+      <x:c r="F91" s="446"/>
+      <x:c r="G91" s="446"/>
+      <x:c r="H91" s="446"/>
+      <x:c r="I91" s="446"/>
+      <x:c r="J91" s="446"/>
+      <x:c r="K91" s="446"/>
+      <x:c r="L91" s="446"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="446"/>
+      <x:c r="B92" s="446"/>
+      <x:c r="C92" s="446"/>
+      <x:c r="D92" s="446"/>
+      <x:c r="E92" s="446"/>
+      <x:c r="F92" s="446"/>
+      <x:c r="G92" s="446"/>
+      <x:c r="H92" s="446"/>
+      <x:c r="I92" s="446"/>
+      <x:c r="J92" s="446"/>
+      <x:c r="K92" s="446"/>
+      <x:c r="L92" s="446"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="446"/>
+      <x:c r="B93" s="446"/>
+      <x:c r="C93" s="446"/>
+      <x:c r="D93" s="446"/>
+      <x:c r="E93" s="446"/>
+      <x:c r="F93" s="446"/>
+      <x:c r="G93" s="446"/>
+      <x:c r="H93" s="446"/>
+      <x:c r="I93" s="446"/>
+      <x:c r="J93" s="446"/>
+      <x:c r="K93" s="446"/>
+      <x:c r="L93" s="446"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="446"/>
+      <x:c r="B94" s="446"/>
+      <x:c r="C94" s="446"/>
+      <x:c r="D94" s="446"/>
+      <x:c r="E94" s="446"/>
+      <x:c r="F94" s="446"/>
+      <x:c r="G94" s="446"/>
+      <x:c r="H94" s="446"/>
+      <x:c r="I94" s="446"/>
+      <x:c r="J94" s="446"/>
+      <x:c r="K94" s="446"/>
+      <x:c r="L94" s="446"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="446"/>
+      <x:c r="B95" s="446"/>
+      <x:c r="C95" s="446"/>
+      <x:c r="D95" s="446"/>
+      <x:c r="E95" s="446"/>
+      <x:c r="F95" s="446"/>
+      <x:c r="G95" s="446"/>
+      <x:c r="H95" s="446"/>
+      <x:c r="I95" s="446"/>
+      <x:c r="J95" s="446"/>
+      <x:c r="K95" s="446"/>
+      <x:c r="L95" s="446"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="446"/>
+      <x:c r="B96" s="446"/>
+      <x:c r="C96" s="446"/>
+      <x:c r="D96" s="446"/>
+      <x:c r="E96" s="446"/>
+      <x:c r="F96" s="446"/>
+      <x:c r="G96" s="446"/>
+      <x:c r="H96" s="446"/>
+      <x:c r="I96" s="446"/>
+      <x:c r="J96" s="446"/>
+      <x:c r="K96" s="446"/>
+      <x:c r="L96" s="446"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="446"/>
+      <x:c r="B97" s="446"/>
+      <x:c r="C97" s="446"/>
+      <x:c r="D97" s="446"/>
+      <x:c r="E97" s="446"/>
+      <x:c r="F97" s="446"/>
+      <x:c r="G97" s="446"/>
+      <x:c r="H97" s="446"/>
+      <x:c r="I97" s="446"/>
+      <x:c r="J97" s="446"/>
+      <x:c r="K97" s="446"/>
+      <x:c r="L97" s="446"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="446"/>
+      <x:c r="B98" s="446"/>
+      <x:c r="C98" s="446"/>
+      <x:c r="D98" s="446"/>
+      <x:c r="E98" s="446"/>
+      <x:c r="F98" s="446"/>
+      <x:c r="G98" s="446"/>
+      <x:c r="H98" s="446"/>
+      <x:c r="I98" s="446"/>
+      <x:c r="J98" s="446"/>
+      <x:c r="K98" s="446"/>
+      <x:c r="L98" s="446"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="446"/>
+      <x:c r="B99" s="446"/>
+      <x:c r="C99" s="446"/>
+      <x:c r="D99" s="446"/>
+      <x:c r="E99" s="446"/>
+      <x:c r="F99" s="446"/>
+      <x:c r="G99" s="446"/>
+      <x:c r="H99" s="446"/>
+      <x:c r="I99" s="446"/>
+      <x:c r="J99" s="446"/>
+      <x:c r="K99" s="446"/>
+      <x:c r="L99" s="446"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="446"/>
+      <x:c r="B100" s="446"/>
+      <x:c r="C100" s="446"/>
+      <x:c r="D100" s="446"/>
+      <x:c r="E100" s="446"/>
+      <x:c r="F100" s="446"/>
+      <x:c r="G100" s="446"/>
+      <x:c r="H100" s="446"/>
+      <x:c r="I100" s="446"/>
+      <x:c r="J100" s="446"/>
+      <x:c r="K100" s="446"/>
+      <x:c r="L100" s="446"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="446"/>
+      <x:c r="B101" s="446"/>
+      <x:c r="C101" s="446"/>
+      <x:c r="D101" s="446"/>
+      <x:c r="E101" s="446"/>
+      <x:c r="F101" s="446"/>
+      <x:c r="G101" s="446"/>
+      <x:c r="H101" s="446"/>
+      <x:c r="I101" s="446"/>
+      <x:c r="J101" s="446"/>
+      <x:c r="K101" s="446"/>
+      <x:c r="L101" s="446"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="446"/>
+      <x:c r="B102" s="446"/>
+      <x:c r="C102" s="446"/>
+      <x:c r="D102" s="446"/>
+      <x:c r="E102" s="446"/>
+      <x:c r="F102" s="446"/>
+      <x:c r="G102" s="446"/>
+      <x:c r="H102" s="446"/>
+      <x:c r="I102" s="446"/>
+      <x:c r="J102" s="446"/>
+      <x:c r="K102" s="446"/>
+      <x:c r="L102" s="446"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="446"/>
+      <x:c r="B103" s="446"/>
+      <x:c r="C103" s="446"/>
+      <x:c r="D103" s="446"/>
+      <x:c r="E103" s="446"/>
+      <x:c r="F103" s="446"/>
+      <x:c r="G103" s="446"/>
+      <x:c r="H103" s="446"/>
+      <x:c r="I103" s="446"/>
+      <x:c r="J103" s="446"/>
+      <x:c r="K103" s="446"/>
+      <x:c r="L103" s="446"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="446"/>
+      <x:c r="B104" s="446"/>
+      <x:c r="C104" s="446"/>
+      <x:c r="D104" s="446"/>
+      <x:c r="E104" s="446"/>
+      <x:c r="F104" s="446"/>
+      <x:c r="G104" s="446"/>
+      <x:c r="H104" s="446"/>
+      <x:c r="I104" s="446"/>
+      <x:c r="J104" s="446"/>
+      <x:c r="K104" s="446"/>
+      <x:c r="L104" s="446"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="446"/>
+      <x:c r="B105" s="446"/>
+      <x:c r="C105" s="446"/>
+      <x:c r="D105" s="446"/>
+      <x:c r="E105" s="446"/>
+      <x:c r="F105" s="446"/>
+      <x:c r="G105" s="446"/>
+      <x:c r="H105" s="446"/>
+      <x:c r="I105" s="446"/>
+      <x:c r="J105" s="446"/>
+      <x:c r="K105" s="446"/>
+      <x:c r="L105" s="446"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="446"/>
+      <x:c r="B106" s="446"/>
+      <x:c r="C106" s="446"/>
+      <x:c r="D106" s="446"/>
+      <x:c r="E106" s="446"/>
+      <x:c r="F106" s="446"/>
+      <x:c r="G106" s="446"/>
+      <x:c r="H106" s="446"/>
+      <x:c r="I106" s="446"/>
+      <x:c r="J106" s="446"/>
+      <x:c r="K106" s="446"/>
+      <x:c r="L106" s="446"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="446"/>
+      <x:c r="B107" s="446"/>
+      <x:c r="C107" s="446"/>
+      <x:c r="D107" s="446"/>
+      <x:c r="E107" s="446"/>
+      <x:c r="F107" s="446"/>
+      <x:c r="G107" s="446"/>
+      <x:c r="H107" s="446"/>
+      <x:c r="I107" s="446"/>
+      <x:c r="J107" s="446"/>
+      <x:c r="K107" s="446"/>
+      <x:c r="L107" s="446"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="446"/>
+      <x:c r="B108" s="446"/>
+      <x:c r="C108" s="446"/>
+      <x:c r="D108" s="446"/>
+      <x:c r="E108" s="446"/>
+      <x:c r="F108" s="446"/>
+      <x:c r="G108" s="446"/>
+      <x:c r="H108" s="446"/>
+      <x:c r="I108" s="446"/>
+      <x:c r="J108" s="446"/>
+      <x:c r="K108" s="446"/>
+      <x:c r="L108" s="446"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="446"/>
+      <x:c r="B109" s="446"/>
+      <x:c r="C109" s="446"/>
+      <x:c r="D109" s="446"/>
+      <x:c r="E109" s="446"/>
+      <x:c r="F109" s="446"/>
+      <x:c r="G109" s="446"/>
+      <x:c r="H109" s="446"/>
+      <x:c r="I109" s="446"/>
+      <x:c r="J109" s="446"/>
+      <x:c r="K109" s="446"/>
+      <x:c r="L109" s="446"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="446"/>
+      <x:c r="B110" s="446"/>
+      <x:c r="C110" s="446"/>
+      <x:c r="D110" s="446"/>
+      <x:c r="E110" s="446"/>
+      <x:c r="F110" s="446"/>
+      <x:c r="G110" s="446"/>
+      <x:c r="H110" s="446"/>
+      <x:c r="I110" s="446"/>
+      <x:c r="J110" s="446"/>
+      <x:c r="K110" s="446"/>
+      <x:c r="L110" s="446"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="446"/>
+      <x:c r="B111" s="446"/>
+      <x:c r="C111" s="446"/>
+      <x:c r="D111" s="446"/>
+      <x:c r="E111" s="446"/>
+      <x:c r="F111" s="446"/>
+      <x:c r="G111" s="446"/>
+      <x:c r="H111" s="446"/>
+      <x:c r="I111" s="446"/>
+      <x:c r="J111" s="446"/>
+      <x:c r="K111" s="446"/>
+      <x:c r="L111" s="446"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="446"/>
+      <x:c r="B112" s="446"/>
+      <x:c r="C112" s="446"/>
+      <x:c r="D112" s="446"/>
+      <x:c r="E112" s="446"/>
+      <x:c r="F112" s="446"/>
+      <x:c r="G112" s="446"/>
+      <x:c r="H112" s="446"/>
+      <x:c r="I112" s="446"/>
+      <x:c r="J112" s="446"/>
+      <x:c r="K112" s="446"/>
+      <x:c r="L112" s="446"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="446"/>
+      <x:c r="B113" s="446"/>
+      <x:c r="C113" s="446"/>
+      <x:c r="D113" s="446"/>
+      <x:c r="E113" s="446"/>
+      <x:c r="F113" s="446"/>
+      <x:c r="G113" s="446"/>
+      <x:c r="H113" s="446"/>
+      <x:c r="I113" s="446"/>
+      <x:c r="J113" s="446"/>
+      <x:c r="K113" s="446"/>
+      <x:c r="L113" s="446"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="446"/>
+      <x:c r="B114" s="446"/>
+      <x:c r="C114" s="446"/>
+      <x:c r="D114" s="446"/>
+      <x:c r="E114" s="446"/>
+      <x:c r="F114" s="446"/>
+      <x:c r="G114" s="446"/>
+      <x:c r="H114" s="446"/>
+      <x:c r="I114" s="446"/>
+      <x:c r="J114" s="446"/>
+      <x:c r="K114" s="446"/>
+      <x:c r="L114" s="446"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="446"/>
+      <x:c r="B115" s="446"/>
+      <x:c r="C115" s="446"/>
+      <x:c r="D115" s="446"/>
+      <x:c r="E115" s="446"/>
+      <x:c r="F115" s="446"/>
+      <x:c r="G115" s="446"/>
+      <x:c r="H115" s="446"/>
+      <x:c r="I115" s="446"/>
+      <x:c r="J115" s="446"/>
+      <x:c r="K115" s="446"/>
+      <x:c r="L115" s="446"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="446"/>
+      <x:c r="B116" s="446"/>
+      <x:c r="C116" s="446"/>
+      <x:c r="D116" s="446"/>
+      <x:c r="E116" s="446"/>
+      <x:c r="F116" s="446"/>
+      <x:c r="G116" s="446"/>
+      <x:c r="H116" s="446"/>
+      <x:c r="I116" s="446"/>
+      <x:c r="J116" s="446"/>
+      <x:c r="K116" s="446"/>
+      <x:c r="L116" s="446"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="446"/>
+      <x:c r="B117" s="446"/>
+      <x:c r="C117" s="446"/>
+      <x:c r="D117" s="446"/>
+      <x:c r="E117" s="446"/>
+      <x:c r="F117" s="446"/>
+      <x:c r="G117" s="446"/>
+      <x:c r="H117" s="446"/>
+      <x:c r="I117" s="446"/>
+      <x:c r="J117" s="446"/>
+      <x:c r="K117" s="446"/>
+      <x:c r="L117" s="446"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="446"/>
+      <x:c r="B118" s="446"/>
+      <x:c r="C118" s="446"/>
+      <x:c r="D118" s="446"/>
+      <x:c r="E118" s="446"/>
+      <x:c r="F118" s="446"/>
+      <x:c r="G118" s="446"/>
+      <x:c r="H118" s="446"/>
+      <x:c r="I118" s="446"/>
+      <x:c r="J118" s="446"/>
+      <x:c r="K118" s="446"/>
+      <x:c r="L118" s="446"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="446"/>
+      <x:c r="B119" s="446"/>
+      <x:c r="C119" s="446"/>
+      <x:c r="D119" s="446"/>
+      <x:c r="E119" s="446"/>
+      <x:c r="F119" s="446"/>
+      <x:c r="G119" s="446"/>
+      <x:c r="H119" s="446"/>
+      <x:c r="I119" s="446"/>
+      <x:c r="J119" s="446"/>
+      <x:c r="K119" s="446"/>
+      <x:c r="L119" s="446"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="446"/>
+      <x:c r="B120" s="446"/>
+      <x:c r="C120" s="446"/>
+      <x:c r="D120" s="446"/>
+      <x:c r="E120" s="446"/>
+      <x:c r="F120" s="446"/>
+      <x:c r="G120" s="446"/>
+      <x:c r="H120" s="446"/>
+      <x:c r="I120" s="446"/>
+      <x:c r="J120" s="446"/>
+      <x:c r="K120" s="446"/>
+      <x:c r="L120" s="446"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="446"/>
+      <x:c r="B121" s="446"/>
+      <x:c r="C121" s="446"/>
+      <x:c r="D121" s="446"/>
+      <x:c r="E121" s="446"/>
+      <x:c r="F121" s="446"/>
+      <x:c r="G121" s="446"/>
+      <x:c r="H121" s="446"/>
+      <x:c r="I121" s="446"/>
+      <x:c r="J121" s="446"/>
+      <x:c r="K121" s="446"/>
+      <x:c r="L121" s="446"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="446"/>
+      <x:c r="B122" s="446"/>
+      <x:c r="C122" s="446"/>
+      <x:c r="D122" s="446"/>
+      <x:c r="E122" s="446"/>
+      <x:c r="F122" s="446"/>
+      <x:c r="G122" s="446"/>
+      <x:c r="H122" s="446"/>
+      <x:c r="I122" s="446"/>
+      <x:c r="J122" s="446"/>
+      <x:c r="K122" s="446"/>
+      <x:c r="L122" s="446"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="446"/>
+      <x:c r="B123" s="446"/>
+      <x:c r="C123" s="446"/>
+      <x:c r="D123" s="446"/>
+      <x:c r="E123" s="446"/>
+      <x:c r="F123" s="446"/>
+      <x:c r="G123" s="446"/>
+      <x:c r="H123" s="446"/>
+      <x:c r="I123" s="446"/>
+      <x:c r="J123" s="446"/>
+      <x:c r="K123" s="446"/>
+      <x:c r="L123" s="446"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="446"/>
+      <x:c r="B124" s="446"/>
+      <x:c r="C124" s="446"/>
+      <x:c r="D124" s="446"/>
+      <x:c r="E124" s="446"/>
+      <x:c r="F124" s="446"/>
+      <x:c r="G124" s="446"/>
+      <x:c r="H124" s="446"/>
+      <x:c r="I124" s="446"/>
+      <x:c r="J124" s="446"/>
+      <x:c r="K124" s="446"/>
+      <x:c r="L124" s="446"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="446"/>
+      <x:c r="B125" s="446"/>
+      <x:c r="C125" s="446"/>
+      <x:c r="D125" s="446"/>
+      <x:c r="E125" s="446"/>
+      <x:c r="F125" s="446"/>
+      <x:c r="G125" s="446"/>
+      <x:c r="H125" s="446"/>
+      <x:c r="I125" s="446"/>
+      <x:c r="J125" s="446"/>
+      <x:c r="K125" s="446"/>
+      <x:c r="L125" s="446"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="446"/>
+      <x:c r="B126" s="446"/>
+      <x:c r="C126" s="446"/>
+      <x:c r="D126" s="446"/>
+      <x:c r="E126" s="446"/>
+      <x:c r="F126" s="446"/>
+      <x:c r="G126" s="446"/>
+      <x:c r="H126" s="446"/>
+      <x:c r="I126" s="446"/>
+      <x:c r="J126" s="446"/>
+      <x:c r="K126" s="446"/>
+      <x:c r="L126" s="446"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="446"/>
+      <x:c r="B127" s="446"/>
+      <x:c r="C127" s="446"/>
+      <x:c r="D127" s="446"/>
+      <x:c r="E127" s="446"/>
+      <x:c r="F127" s="446"/>
+      <x:c r="G127" s="446"/>
+      <x:c r="H127" s="446"/>
+      <x:c r="I127" s="446"/>
+      <x:c r="J127" s="446"/>
+      <x:c r="K127" s="446"/>
+      <x:c r="L127" s="446"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="446"/>
+      <x:c r="B128" s="446"/>
+      <x:c r="C128" s="446"/>
+      <x:c r="D128" s="446"/>
+      <x:c r="E128" s="446"/>
+      <x:c r="F128" s="446"/>
+      <x:c r="G128" s="446"/>
+      <x:c r="H128" s="446"/>
+      <x:c r="I128" s="446"/>
+      <x:c r="J128" s="446"/>
+      <x:c r="K128" s="446"/>
+      <x:c r="L128" s="446"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="446"/>
+      <x:c r="B129" s="446"/>
+      <x:c r="C129" s="446"/>
+      <x:c r="D129" s="446"/>
+      <x:c r="E129" s="446"/>
+      <x:c r="F129" s="446"/>
+      <x:c r="G129" s="446"/>
+      <x:c r="H129" s="446"/>
+      <x:c r="I129" s="446"/>
+      <x:c r="J129" s="446"/>
+      <x:c r="K129" s="446"/>
+      <x:c r="L129" s="446"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="446"/>
+      <x:c r="B130" s="446"/>
+      <x:c r="C130" s="446"/>
+      <x:c r="D130" s="446"/>
+      <x:c r="E130" s="446"/>
+      <x:c r="F130" s="446"/>
+      <x:c r="G130" s="446"/>
+      <x:c r="H130" s="446"/>
+      <x:c r="I130" s="446"/>
+      <x:c r="J130" s="446"/>
+      <x:c r="K130" s="446"/>
+      <x:c r="L130" s="446"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="446"/>
+      <x:c r="B131" s="446"/>
+      <x:c r="C131" s="446"/>
+      <x:c r="D131" s="446"/>
+      <x:c r="E131" s="446"/>
+      <x:c r="F131" s="446"/>
+      <x:c r="G131" s="446"/>
+      <x:c r="H131" s="446"/>
+      <x:c r="I131" s="446"/>
+      <x:c r="J131" s="446"/>
+      <x:c r="K131" s="446"/>
+      <x:c r="L131" s="446"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="446"/>
+      <x:c r="B132" s="446"/>
+      <x:c r="C132" s="446"/>
+      <x:c r="D132" s="446"/>
+      <x:c r="E132" s="446"/>
+      <x:c r="F132" s="446"/>
+      <x:c r="G132" s="446"/>
+      <x:c r="H132" s="446"/>
+      <x:c r="I132" s="446"/>
+      <x:c r="J132" s="446"/>
+      <x:c r="K132" s="446"/>
+      <x:c r="L132" s="446"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="446"/>
+      <x:c r="B133" s="446"/>
+      <x:c r="C133" s="446"/>
+      <x:c r="D133" s="446"/>
+      <x:c r="E133" s="446"/>
+      <x:c r="F133" s="446"/>
+      <x:c r="G133" s="446"/>
+      <x:c r="H133" s="446"/>
+      <x:c r="I133" s="446"/>
+      <x:c r="J133" s="446"/>
+      <x:c r="K133" s="446"/>
+      <x:c r="L133" s="446"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="446"/>
+      <x:c r="B134" s="446"/>
+      <x:c r="C134" s="446"/>
+      <x:c r="D134" s="446"/>
+      <x:c r="E134" s="446"/>
+      <x:c r="F134" s="446"/>
+      <x:c r="G134" s="446"/>
+      <x:c r="H134" s="446"/>
+      <x:c r="I134" s="446"/>
+      <x:c r="J134" s="446"/>
+      <x:c r="K134" s="446"/>
+      <x:c r="L134" s="446"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="446"/>
+      <x:c r="B135" s="446"/>
+      <x:c r="C135" s="446"/>
+      <x:c r="D135" s="446"/>
+      <x:c r="E135" s="446"/>
+      <x:c r="F135" s="446"/>
+      <x:c r="G135" s="446"/>
+      <x:c r="H135" s="446"/>
+      <x:c r="I135" s="446"/>
+      <x:c r="J135" s="446"/>
+      <x:c r="K135" s="446"/>
+      <x:c r="L135" s="446"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="446"/>
+      <x:c r="B136" s="446"/>
+      <x:c r="C136" s="446"/>
+      <x:c r="D136" s="446"/>
+      <x:c r="E136" s="446"/>
+      <x:c r="F136" s="446"/>
+      <x:c r="G136" s="446"/>
+      <x:c r="H136" s="446"/>
+      <x:c r="I136" s="446"/>
+      <x:c r="J136" s="446"/>
+      <x:c r="K136" s="446"/>
+      <x:c r="L136" s="446"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="446"/>
+      <x:c r="B137" s="446"/>
+      <x:c r="C137" s="446"/>
+      <x:c r="D137" s="446"/>
+      <x:c r="E137" s="446"/>
+      <x:c r="F137" s="446"/>
+      <x:c r="G137" s="446"/>
+      <x:c r="H137" s="446"/>
+      <x:c r="I137" s="446"/>
+      <x:c r="J137" s="446"/>
+      <x:c r="K137" s="446"/>
+      <x:c r="L137" s="446"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="446"/>
+      <x:c r="B138" s="446"/>
+      <x:c r="C138" s="446"/>
+      <x:c r="D138" s="446"/>
+      <x:c r="E138" s="446"/>
+      <x:c r="F138" s="446"/>
+      <x:c r="G138" s="446"/>
+      <x:c r="H138" s="446"/>
+      <x:c r="I138" s="446"/>
+      <x:c r="J138" s="446"/>
+      <x:c r="K138" s="446"/>
+      <x:c r="L138" s="446"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="446"/>
+      <x:c r="B139" s="446"/>
+      <x:c r="C139" s="446"/>
+      <x:c r="D139" s="446"/>
+      <x:c r="E139" s="446"/>
+      <x:c r="F139" s="446"/>
+      <x:c r="G139" s="446"/>
+      <x:c r="H139" s="446"/>
+      <x:c r="I139" s="446"/>
+      <x:c r="J139" s="446"/>
+      <x:c r="K139" s="446"/>
+      <x:c r="L139" s="446"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="446"/>
+      <x:c r="B140" s="446"/>
+      <x:c r="C140" s="446"/>
+      <x:c r="D140" s="446"/>
+      <x:c r="E140" s="446"/>
+      <x:c r="F140" s="446"/>
+      <x:c r="G140" s="446"/>
+      <x:c r="H140" s="446"/>
+      <x:c r="I140" s="446"/>
+      <x:c r="J140" s="446"/>
+      <x:c r="K140" s="446"/>
+      <x:c r="L140" s="446"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="446"/>
+      <x:c r="B141" s="446"/>
+      <x:c r="C141" s="446"/>
+      <x:c r="D141" s="446"/>
+      <x:c r="E141" s="446"/>
+      <x:c r="F141" s="446"/>
+      <x:c r="G141" s="446"/>
+      <x:c r="H141" s="446"/>
+      <x:c r="I141" s="446"/>
+      <x:c r="J141" s="446"/>
+      <x:c r="K141" s="446"/>
+      <x:c r="L141" s="446"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="446"/>
+      <x:c r="B142" s="446"/>
+      <x:c r="C142" s="446"/>
+      <x:c r="D142" s="446"/>
+      <x:c r="E142" s="446"/>
+      <x:c r="F142" s="446"/>
+      <x:c r="G142" s="446"/>
+      <x:c r="H142" s="446"/>
+      <x:c r="I142" s="446"/>
+      <x:c r="J142" s="446"/>
+      <x:c r="K142" s="446"/>
+      <x:c r="L142" s="446"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="446"/>
+      <x:c r="B143" s="446"/>
+      <x:c r="C143" s="446"/>
+      <x:c r="D143" s="446"/>
+      <x:c r="E143" s="446"/>
+      <x:c r="F143" s="446"/>
+      <x:c r="G143" s="446"/>
+      <x:c r="H143" s="446"/>
+      <x:c r="I143" s="446"/>
+      <x:c r="J143" s="446"/>
+      <x:c r="K143" s="446"/>
+      <x:c r="L143" s="446"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="446"/>
+      <x:c r="B144" s="446"/>
+      <x:c r="C144" s="446"/>
+      <x:c r="D144" s="446"/>
+      <x:c r="E144" s="446"/>
+      <x:c r="F144" s="446"/>
+      <x:c r="G144" s="446"/>
+      <x:c r="H144" s="446"/>
+      <x:c r="I144" s="446"/>
+      <x:c r="J144" s="446"/>
+      <x:c r="K144" s="446"/>
+      <x:c r="L144" s="446"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="446"/>
+      <x:c r="B145" s="446"/>
+      <x:c r="C145" s="446"/>
+      <x:c r="D145" s="446"/>
+      <x:c r="E145" s="446"/>
+      <x:c r="F145" s="446"/>
+      <x:c r="G145" s="446"/>
+      <x:c r="H145" s="446"/>
+      <x:c r="I145" s="446"/>
+      <x:c r="J145" s="446"/>
+      <x:c r="K145" s="446"/>
+      <x:c r="L145" s="446"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="446"/>
+      <x:c r="B146" s="446"/>
+      <x:c r="C146" s="446"/>
+      <x:c r="D146" s="446"/>
+      <x:c r="E146" s="446"/>
+      <x:c r="F146" s="446"/>
+      <x:c r="G146" s="446"/>
+      <x:c r="H146" s="446"/>
+      <x:c r="I146" s="446"/>
+      <x:c r="J146" s="446"/>
+      <x:c r="K146" s="446"/>
+      <x:c r="L146" s="446"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="446"/>
+      <x:c r="B147" s="446"/>
+      <x:c r="C147" s="446"/>
+      <x:c r="D147" s="446"/>
+      <x:c r="E147" s="446"/>
+      <x:c r="F147" s="446"/>
+      <x:c r="G147" s="446"/>
+      <x:c r="H147" s="446"/>
+      <x:c r="I147" s="446"/>
+      <x:c r="J147" s="446"/>
+      <x:c r="K147" s="446"/>
+      <x:c r="L147" s="446"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="446"/>
+      <x:c r="B148" s="446"/>
+      <x:c r="C148" s="446"/>
+      <x:c r="D148" s="446"/>
+      <x:c r="E148" s="446"/>
+      <x:c r="F148" s="446"/>
+      <x:c r="G148" s="446"/>
+      <x:c r="H148" s="446"/>
+      <x:c r="I148" s="446"/>
+      <x:c r="J148" s="446"/>
+      <x:c r="K148" s="446"/>
+      <x:c r="L148" s="446"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="446"/>
+      <x:c r="B149" s="446"/>
+      <x:c r="C149" s="446"/>
+      <x:c r="D149" s="446"/>
+      <x:c r="E149" s="446"/>
+      <x:c r="F149" s="446"/>
+      <x:c r="G149" s="446"/>
+      <x:c r="H149" s="446"/>
+      <x:c r="I149" s="446"/>
+      <x:c r="J149" s="446"/>
+      <x:c r="K149" s="446"/>
+      <x:c r="L149" s="446"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="446"/>
+      <x:c r="B150" s="446"/>
+      <x:c r="C150" s="446"/>
+      <x:c r="D150" s="446"/>
+      <x:c r="E150" s="446"/>
+      <x:c r="F150" s="446"/>
+      <x:c r="G150" s="446"/>
+      <x:c r="H150" s="446"/>
+      <x:c r="I150" s="446"/>
+      <x:c r="J150" s="446"/>
+      <x:c r="K150" s="446"/>
+      <x:c r="L150" s="446"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="446"/>
+      <x:c r="B151" s="446"/>
+      <x:c r="C151" s="446"/>
+      <x:c r="D151" s="446"/>
+      <x:c r="E151" s="446"/>
+      <x:c r="F151" s="446"/>
+      <x:c r="G151" s="446"/>
+      <x:c r="H151" s="446"/>
+      <x:c r="I151" s="446"/>
+      <x:c r="J151" s="446"/>
+      <x:c r="K151" s="446"/>
+      <x:c r="L151" s="446"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="446"/>
+      <x:c r="B152" s="446"/>
+      <x:c r="C152" s="446"/>
+      <x:c r="D152" s="446"/>
+      <x:c r="E152" s="446"/>
+      <x:c r="F152" s="446"/>
+      <x:c r="G152" s="446"/>
+      <x:c r="H152" s="446"/>
+      <x:c r="I152" s="446"/>
+      <x:c r="J152" s="446"/>
+      <x:c r="K152" s="446"/>
+      <x:c r="L152" s="446"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="446"/>
+      <x:c r="B153" s="446"/>
+      <x:c r="C153" s="446"/>
+      <x:c r="D153" s="446"/>
+      <x:c r="E153" s="446"/>
+      <x:c r="F153" s="446"/>
+      <x:c r="G153" s="446"/>
+      <x:c r="H153" s="446"/>
+      <x:c r="I153" s="446"/>
+      <x:c r="J153" s="446"/>
+      <x:c r="K153" s="446"/>
+      <x:c r="L153" s="446"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="446"/>
+      <x:c r="B154" s="446"/>
+      <x:c r="C154" s="446"/>
+      <x:c r="D154" s="446"/>
+      <x:c r="E154" s="446"/>
+      <x:c r="F154" s="446"/>
+      <x:c r="G154" s="446"/>
+      <x:c r="H154" s="446"/>
+      <x:c r="I154" s="446"/>
+      <x:c r="J154" s="446"/>
+      <x:c r="K154" s="446"/>
+      <x:c r="L154" s="446"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="446"/>
+      <x:c r="B155" s="446"/>
+      <x:c r="C155" s="446"/>
+      <x:c r="D155" s="446"/>
+      <x:c r="E155" s="446"/>
+      <x:c r="F155" s="446"/>
+      <x:c r="G155" s="446"/>
+      <x:c r="H155" s="446"/>
+      <x:c r="I155" s="446"/>
+      <x:c r="J155" s="446"/>
+      <x:c r="K155" s="446"/>
+      <x:c r="L155" s="446"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="446"/>
+      <x:c r="B156" s="446"/>
+      <x:c r="C156" s="446"/>
+      <x:c r="D156" s="446"/>
+      <x:c r="E156" s="446"/>
+      <x:c r="F156" s="446"/>
+      <x:c r="G156" s="446"/>
+      <x:c r="H156" s="446"/>
+      <x:c r="I156" s="446"/>
+      <x:c r="J156" s="446"/>
+      <x:c r="K156" s="446"/>
+      <x:c r="L156" s="446"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="446"/>
+      <x:c r="B157" s="446"/>
+      <x:c r="C157" s="446"/>
+      <x:c r="D157" s="446"/>
+      <x:c r="E157" s="446"/>
+      <x:c r="F157" s="446"/>
+      <x:c r="G157" s="446"/>
+      <x:c r="H157" s="446"/>
+      <x:c r="I157" s="446"/>
+      <x:c r="J157" s="446"/>
+      <x:c r="K157" s="446"/>
+      <x:c r="L157" s="446"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="446"/>
+      <x:c r="B158" s="446"/>
+      <x:c r="C158" s="446"/>
+      <x:c r="D158" s="446"/>
+      <x:c r="E158" s="446"/>
+      <x:c r="F158" s="446"/>
+      <x:c r="G158" s="446"/>
+      <x:c r="H158" s="446"/>
+      <x:c r="I158" s="446"/>
+      <x:c r="J158" s="446"/>
+      <x:c r="K158" s="446"/>
+      <x:c r="L158" s="446"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="446"/>
+      <x:c r="B159" s="446"/>
+      <x:c r="C159" s="446"/>
+      <x:c r="D159" s="446"/>
+      <x:c r="E159" s="446"/>
+      <x:c r="F159" s="446"/>
+      <x:c r="G159" s="446"/>
+      <x:c r="H159" s="446"/>
+      <x:c r="I159" s="446"/>
+      <x:c r="J159" s="446"/>
+      <x:c r="K159" s="446"/>
+      <x:c r="L159" s="446"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="446"/>
+      <x:c r="B160" s="446"/>
+      <x:c r="C160" s="446"/>
+      <x:c r="D160" s="446"/>
+      <x:c r="E160" s="446"/>
+      <x:c r="F160" s="446"/>
+      <x:c r="G160" s="446"/>
+      <x:c r="H160" s="446"/>
+      <x:c r="I160" s="446"/>
+      <x:c r="J160" s="446"/>
+      <x:c r="K160" s="446"/>
+      <x:c r="L160" s="446"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="446"/>
+      <x:c r="B161" s="446"/>
+      <x:c r="C161" s="446"/>
+      <x:c r="D161" s="446"/>
+      <x:c r="E161" s="446"/>
+      <x:c r="F161" s="446"/>
+      <x:c r="G161" s="446"/>
+      <x:c r="H161" s="446"/>
+      <x:c r="I161" s="446"/>
+      <x:c r="J161" s="446"/>
+      <x:c r="K161" s="446"/>
+      <x:c r="L161" s="446"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="446"/>
+      <x:c r="B162" s="446"/>
+      <x:c r="C162" s="446"/>
+      <x:c r="D162" s="446"/>
+      <x:c r="E162" s="446"/>
+      <x:c r="F162" s="446"/>
+      <x:c r="G162" s="446"/>
+      <x:c r="H162" s="446"/>
+      <x:c r="I162" s="446"/>
+      <x:c r="J162" s="446"/>
+      <x:c r="K162" s="446"/>
+      <x:c r="L162" s="446"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="446"/>
+      <x:c r="B163" s="446"/>
+      <x:c r="C163" s="446"/>
+      <x:c r="D163" s="446"/>
+      <x:c r="E163" s="446"/>
+      <x:c r="F163" s="446"/>
+      <x:c r="G163" s="446"/>
+      <x:c r="H163" s="446"/>
+      <x:c r="I163" s="446"/>
+      <x:c r="J163" s="446"/>
+      <x:c r="K163" s="446"/>
+      <x:c r="L163" s="446"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="446"/>
+      <x:c r="B164" s="446"/>
+      <x:c r="C164" s="446"/>
+      <x:c r="D164" s="446"/>
+      <x:c r="E164" s="446"/>
+      <x:c r="F164" s="446"/>
+      <x:c r="G164" s="446"/>
+      <x:c r="H164" s="446"/>
+      <x:c r="I164" s="446"/>
+      <x:c r="J164" s="446"/>
+      <x:c r="K164" s="446"/>
+      <x:c r="L164" s="446"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="446"/>
+      <x:c r="B165" s="446"/>
+      <x:c r="C165" s="446"/>
+      <x:c r="D165" s="446"/>
+      <x:c r="E165" s="446"/>
+      <x:c r="F165" s="446"/>
+      <x:c r="G165" s="446"/>
+      <x:c r="H165" s="446"/>
+      <x:c r="I165" s="446"/>
+      <x:c r="J165" s="446"/>
+      <x:c r="K165" s="446"/>
+      <x:c r="L165" s="446"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="446"/>
+      <x:c r="B166" s="446"/>
+      <x:c r="C166" s="446"/>
+      <x:c r="D166" s="446"/>
+      <x:c r="E166" s="446"/>
+      <x:c r="F166" s="446"/>
+      <x:c r="G166" s="446"/>
+      <x:c r="H166" s="446"/>
+      <x:c r="I166" s="446"/>
+      <x:c r="J166" s="446"/>
+      <x:c r="K166" s="446"/>
+      <x:c r="L166" s="446"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="446"/>
+      <x:c r="B167" s="446"/>
+      <x:c r="C167" s="446"/>
+      <x:c r="D167" s="446"/>
+      <x:c r="E167" s="446"/>
+      <x:c r="F167" s="446"/>
+      <x:c r="G167" s="446"/>
+      <x:c r="H167" s="446"/>
+      <x:c r="I167" s="446"/>
+      <x:c r="J167" s="446"/>
+      <x:c r="K167" s="446"/>
+      <x:c r="L167" s="446"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="446"/>
+      <x:c r="B168" s="446"/>
+      <x:c r="C168" s="446"/>
+      <x:c r="D168" s="446"/>
+      <x:c r="E168" s="446"/>
+      <x:c r="F168" s="446"/>
+      <x:c r="G168" s="446"/>
+      <x:c r="H168" s="446"/>
+      <x:c r="I168" s="446"/>
+      <x:c r="J168" s="446"/>
+      <x:c r="K168" s="446"/>
+      <x:c r="L168" s="446"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="446"/>
+      <x:c r="B169" s="446"/>
+      <x:c r="C169" s="446"/>
+      <x:c r="D169" s="446"/>
+      <x:c r="E169" s="446"/>
+      <x:c r="F169" s="446"/>
+      <x:c r="G169" s="446"/>
+      <x:c r="H169" s="446"/>
+      <x:c r="I169" s="446"/>
+      <x:c r="J169" s="446"/>
+      <x:c r="K169" s="446"/>
+      <x:c r="L169" s="446"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="446"/>
+      <x:c r="B170" s="446"/>
+      <x:c r="C170" s="446"/>
+      <x:c r="D170" s="446"/>
+      <x:c r="E170" s="446"/>
+      <x:c r="F170" s="446"/>
+      <x:c r="G170" s="446"/>
+      <x:c r="H170" s="446"/>
+      <x:c r="I170" s="446"/>
+      <x:c r="J170" s="446"/>
+      <x:c r="K170" s="446"/>
+      <x:c r="L170" s="446"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="446"/>
+      <x:c r="B171" s="446"/>
+      <x:c r="C171" s="446"/>
+      <x:c r="D171" s="446"/>
+      <x:c r="E171" s="446"/>
+      <x:c r="F171" s="446"/>
+      <x:c r="G171" s="446"/>
+      <x:c r="H171" s="446"/>
+      <x:c r="I171" s="446"/>
+      <x:c r="J171" s="446"/>
+      <x:c r="K171" s="446"/>
+      <x:c r="L171" s="446"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="446"/>
+      <x:c r="B172" s="446"/>
+      <x:c r="C172" s="446"/>
+      <x:c r="D172" s="446"/>
+      <x:c r="E172" s="446"/>
+      <x:c r="F172" s="446"/>
+      <x:c r="G172" s="446"/>
+      <x:c r="H172" s="446"/>
+      <x:c r="I172" s="446"/>
+      <x:c r="J172" s="446"/>
+      <x:c r="K172" s="446"/>
+      <x:c r="L172" s="446"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="446"/>
+      <x:c r="B173" s="446"/>
+      <x:c r="C173" s="446"/>
+      <x:c r="D173" s="446"/>
+      <x:c r="E173" s="446"/>
+      <x:c r="F173" s="446"/>
+      <x:c r="G173" s="446"/>
+      <x:c r="H173" s="446"/>
+      <x:c r="I173" s="446"/>
+      <x:c r="J173" s="446"/>
+      <x:c r="K173" s="446"/>
+      <x:c r="L173" s="446"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="446"/>
+      <x:c r="B174" s="446"/>
+      <x:c r="C174" s="446"/>
+      <x:c r="D174" s="446"/>
+      <x:c r="E174" s="446"/>
+      <x:c r="F174" s="446"/>
+      <x:c r="G174" s="446"/>
+      <x:c r="H174" s="446"/>
+      <x:c r="I174" s="446"/>
+      <x:c r="J174" s="446"/>
+      <x:c r="K174" s="446"/>
+      <x:c r="L174" s="446"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="446"/>
+      <x:c r="B175" s="446"/>
+      <x:c r="C175" s="446"/>
+      <x:c r="D175" s="446"/>
+      <x:c r="E175" s="446"/>
+      <x:c r="F175" s="446"/>
+      <x:c r="G175" s="446"/>
+      <x:c r="H175" s="446"/>
+      <x:c r="I175" s="446"/>
+      <x:c r="J175" s="446"/>
+      <x:c r="K175" s="446"/>
+      <x:c r="L175" s="446"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="446"/>
+      <x:c r="B176" s="446"/>
+      <x:c r="C176" s="446"/>
+      <x:c r="D176" s="446"/>
+      <x:c r="E176" s="446"/>
+      <x:c r="F176" s="446"/>
+      <x:c r="G176" s="446"/>
+      <x:c r="H176" s="446"/>
+      <x:c r="I176" s="446"/>
+      <x:c r="J176" s="446"/>
+      <x:c r="K176" s="446"/>
+      <x:c r="L176" s="446"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="446"/>
+      <x:c r="B177" s="446"/>
+      <x:c r="C177" s="446"/>
+      <x:c r="D177" s="446"/>
+      <x:c r="E177" s="446"/>
+      <x:c r="F177" s="446"/>
+      <x:c r="G177" s="446"/>
+      <x:c r="H177" s="446"/>
+      <x:c r="I177" s="446"/>
+      <x:c r="J177" s="446"/>
+      <x:c r="K177" s="446"/>
+      <x:c r="L177" s="446"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="446"/>
+      <x:c r="B178" s="446"/>
+      <x:c r="C178" s="446"/>
+      <x:c r="D178" s="446"/>
+      <x:c r="E178" s="446"/>
+      <x:c r="F178" s="446"/>
+      <x:c r="G178" s="446"/>
+      <x:c r="H178" s="446"/>
+      <x:c r="I178" s="446"/>
+      <x:c r="J178" s="446"/>
+      <x:c r="K178" s="446"/>
+      <x:c r="L178" s="446"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="446"/>
+      <x:c r="B179" s="446"/>
+      <x:c r="C179" s="446"/>
+      <x:c r="D179" s="446"/>
+      <x:c r="E179" s="446"/>
+      <x:c r="F179" s="446"/>
+      <x:c r="G179" s="446"/>
+      <x:c r="H179" s="446"/>
+      <x:c r="I179" s="446"/>
+      <x:c r="J179" s="446"/>
+      <x:c r="K179" s="446"/>
+      <x:c r="L179" s="446"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="446"/>
+      <x:c r="B180" s="446"/>
+      <x:c r="C180" s="446"/>
+      <x:c r="D180" s="446"/>
+      <x:c r="E180" s="446"/>
+      <x:c r="F180" s="446"/>
+      <x:c r="G180" s="446"/>
+      <x:c r="H180" s="446"/>
+      <x:c r="I180" s="446"/>
+      <x:c r="J180" s="446"/>
+      <x:c r="K180" s="446"/>
+      <x:c r="L180" s="446"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="446"/>
+      <x:c r="B181" s="446"/>
+      <x:c r="C181" s="446"/>
+      <x:c r="D181" s="446"/>
+      <x:c r="E181" s="446"/>
+      <x:c r="F181" s="446"/>
+      <x:c r="G181" s="446"/>
+      <x:c r="H181" s="446"/>
+      <x:c r="I181" s="446"/>
+      <x:c r="J181" s="446"/>
+      <x:c r="K181" s="446"/>
+      <x:c r="L181" s="446"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="446"/>
+      <x:c r="B182" s="446"/>
+      <x:c r="C182" s="446"/>
+      <x:c r="D182" s="446"/>
+      <x:c r="E182" s="446"/>
+      <x:c r="F182" s="446"/>
+      <x:c r="G182" s="446"/>
+      <x:c r="H182" s="446"/>
+      <x:c r="I182" s="446"/>
+      <x:c r="J182" s="446"/>
+      <x:c r="K182" s="446"/>
+      <x:c r="L182" s="446"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="446"/>
+      <x:c r="B183" s="446"/>
+      <x:c r="C183" s="446"/>
+      <x:c r="D183" s="446"/>
+      <x:c r="E183" s="446"/>
+      <x:c r="F183" s="446"/>
+      <x:c r="G183" s="446"/>
+      <x:c r="H183" s="446"/>
+      <x:c r="I183" s="446"/>
+      <x:c r="J183" s="446"/>
+      <x:c r="K183" s="446"/>
+      <x:c r="L183" s="446"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="446"/>
+      <x:c r="B184" s="446"/>
+      <x:c r="C184" s="446"/>
+      <x:c r="D184" s="446"/>
+      <x:c r="E184" s="446"/>
+      <x:c r="F184" s="446"/>
+      <x:c r="G184" s="446"/>
+      <x:c r="H184" s="446"/>
+      <x:c r="I184" s="446"/>
+      <x:c r="J184" s="446"/>
+      <x:c r="K184" s="446"/>
+      <x:c r="L184" s="446"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="446"/>
+      <x:c r="B185" s="446"/>
+      <x:c r="C185" s="446"/>
+      <x:c r="D185" s="446"/>
+      <x:c r="E185" s="446"/>
+      <x:c r="F185" s="446"/>
+      <x:c r="G185" s="446"/>
+      <x:c r="H185" s="446"/>
+      <x:c r="I185" s="446"/>
+      <x:c r="J185" s="446"/>
+      <x:c r="K185" s="446"/>
+      <x:c r="L185" s="446"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="446"/>
+      <x:c r="B186" s="446"/>
+      <x:c r="C186" s="446"/>
+      <x:c r="D186" s="446"/>
+      <x:c r="E186" s="446"/>
+      <x:c r="F186" s="446"/>
+      <x:c r="G186" s="446"/>
+      <x:c r="H186" s="446"/>
+      <x:c r="I186" s="446"/>
+      <x:c r="J186" s="446"/>
+      <x:c r="K186" s="446"/>
+      <x:c r="L186" s="446"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="446"/>
+      <x:c r="B187" s="446"/>
+      <x:c r="C187" s="446"/>
+      <x:c r="D187" s="446"/>
+      <x:c r="E187" s="446"/>
+      <x:c r="F187" s="446"/>
+      <x:c r="G187" s="446"/>
+      <x:c r="H187" s="446"/>
+      <x:c r="I187" s="446"/>
+      <x:c r="J187" s="446"/>
+      <x:c r="K187" s="446"/>
+      <x:c r="L187" s="446"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="446"/>
+      <x:c r="B188" s="446"/>
+      <x:c r="C188" s="446"/>
+      <x:c r="D188" s="446"/>
+      <x:c r="E188" s="446"/>
+      <x:c r="F188" s="446"/>
+      <x:c r="G188" s="446"/>
+      <x:c r="H188" s="446"/>
+      <x:c r="I188" s="446"/>
+      <x:c r="J188" s="446"/>
+      <x:c r="K188" s="446"/>
+      <x:c r="L188" s="446"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="446"/>
+      <x:c r="B189" s="446"/>
+      <x:c r="C189" s="446"/>
+      <x:c r="D189" s="446"/>
+      <x:c r="E189" s="446"/>
+      <x:c r="F189" s="446"/>
+      <x:c r="G189" s="446"/>
+      <x:c r="H189" s="446"/>
+      <x:c r="I189" s="446"/>
+      <x:c r="J189" s="446"/>
+      <x:c r="K189" s="446"/>
+      <x:c r="L189" s="446"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="446"/>
+      <x:c r="B190" s="446"/>
+      <x:c r="C190" s="446"/>
+      <x:c r="D190" s="446"/>
+      <x:c r="E190" s="446"/>
+      <x:c r="F190" s="446"/>
+      <x:c r="G190" s="446"/>
+      <x:c r="H190" s="446"/>
+      <x:c r="I190" s="446"/>
+      <x:c r="J190" s="446"/>
+      <x:c r="K190" s="446"/>
+      <x:c r="L190" s="446"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="446"/>
+      <x:c r="B191" s="446"/>
+      <x:c r="C191" s="446"/>
+      <x:c r="D191" s="446"/>
+      <x:c r="E191" s="446"/>
+      <x:c r="F191" s="446"/>
+      <x:c r="G191" s="446"/>
+      <x:c r="H191" s="446"/>
+      <x:c r="I191" s="446"/>
+      <x:c r="J191" s="446"/>
+      <x:c r="K191" s="446"/>
+      <x:c r="L191" s="446"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="446"/>
+      <x:c r="B192" s="446"/>
+      <x:c r="C192" s="446"/>
+      <x:c r="D192" s="446"/>
+      <x:c r="E192" s="446"/>
+      <x:c r="F192" s="446"/>
+      <x:c r="G192" s="446"/>
+      <x:c r="H192" s="446"/>
+      <x:c r="I192" s="446"/>
+      <x:c r="J192" s="446"/>
+      <x:c r="K192" s="446"/>
+      <x:c r="L192" s="446"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="446"/>
+      <x:c r="B193" s="446"/>
+      <x:c r="C193" s="446"/>
+      <x:c r="D193" s="446"/>
+      <x:c r="E193" s="446"/>
+      <x:c r="F193" s="446"/>
+      <x:c r="G193" s="446"/>
+      <x:c r="H193" s="446"/>
+      <x:c r="I193" s="446"/>
+      <x:c r="J193" s="446"/>
+      <x:c r="K193" s="446"/>
+      <x:c r="L193" s="446"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="446"/>
+      <x:c r="B194" s="446"/>
+      <x:c r="C194" s="446"/>
+      <x:c r="D194" s="446"/>
+      <x:c r="E194" s="446"/>
+      <x:c r="F194" s="446"/>
+      <x:c r="G194" s="446"/>
+      <x:c r="H194" s="446"/>
+      <x:c r="I194" s="446"/>
+      <x:c r="J194" s="446"/>
+      <x:c r="K194" s="446"/>
+      <x:c r="L194" s="446"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="446"/>
+      <x:c r="B195" s="446"/>
+      <x:c r="C195" s="446"/>
+      <x:c r="D195" s="446"/>
+      <x:c r="E195" s="446"/>
+      <x:c r="F195" s="446"/>
+      <x:c r="G195" s="446"/>
+      <x:c r="H195" s="446"/>
+      <x:c r="I195" s="446"/>
+      <x:c r="J195" s="446"/>
+      <x:c r="K195" s="446"/>
+      <x:c r="L195" s="446"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="446"/>
+      <x:c r="B196" s="446"/>
+      <x:c r="C196" s="446"/>
+      <x:c r="D196" s="446"/>
+      <x:c r="E196" s="446"/>
+      <x:c r="F196" s="446"/>
+      <x:c r="G196" s="446"/>
+      <x:c r="H196" s="446"/>
+      <x:c r="I196" s="446"/>
+      <x:c r="J196" s="446"/>
+      <x:c r="K196" s="446"/>
+      <x:c r="L196" s="446"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="446"/>
+      <x:c r="B197" s="446"/>
+      <x:c r="C197" s="446"/>
+      <x:c r="D197" s="446"/>
+      <x:c r="E197" s="446"/>
+      <x:c r="F197" s="446"/>
+      <x:c r="G197" s="446"/>
+      <x:c r="H197" s="446"/>
+      <x:c r="I197" s="446"/>
+      <x:c r="J197" s="446"/>
+      <x:c r="K197" s="446"/>
+      <x:c r="L197" s="446"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="446"/>
+      <x:c r="B198" s="446"/>
+      <x:c r="C198" s="446"/>
+      <x:c r="D198" s="446"/>
+      <x:c r="E198" s="446"/>
+      <x:c r="F198" s="446"/>
+      <x:c r="G198" s="446"/>
+      <x:c r="H198" s="446"/>
+      <x:c r="I198" s="446"/>
+      <x:c r="J198" s="446"/>
+      <x:c r="K198" s="446"/>
+      <x:c r="L198" s="446"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="446"/>
+      <x:c r="B199" s="446"/>
+      <x:c r="C199" s="446"/>
+      <x:c r="D199" s="446"/>
+      <x:c r="E199" s="446"/>
+      <x:c r="F199" s="446"/>
+      <x:c r="G199" s="446"/>
+      <x:c r="H199" s="446"/>
+      <x:c r="I199" s="446"/>
+      <x:c r="J199" s="446"/>
+      <x:c r="K199" s="446"/>
+      <x:c r="L199" s="446"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="446"/>
+      <x:c r="B200" s="446"/>
+      <x:c r="C200" s="446"/>
+      <x:c r="D200" s="446"/>
+      <x:c r="E200" s="446"/>
+      <x:c r="F200" s="446"/>
+      <x:c r="G200" s="446"/>
+      <x:c r="H200" s="446"/>
+      <x:c r="I200" s="446"/>
+      <x:c r="J200" s="446"/>
+      <x:c r="K200" s="446"/>
+      <x:c r="L200" s="446"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
